--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -572,22 +572,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.045755275</v>
+        <v>0.04537362500000001</v>
       </c>
       <c r="C2">
-        <v>0.036902325</v>
+        <v>0.037133475</v>
       </c>
       <c r="D2">
-        <v>0.03086115</v>
+        <v>0.03167575</v>
       </c>
       <c r="E2">
-        <v>0.06159002500000001</v>
+        <v>0.061977075</v>
       </c>
       <c r="F2">
-        <v>0.09425559999999999</v>
+        <v>0.095404725</v>
       </c>
       <c r="G2">
-        <v>0.053872875</v>
+        <v>0.05431293</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006369825000000001</v>
+        <v>0.006423900000000001</v>
       </c>
       <c r="C3">
-        <v>0.006745625000000001</v>
+        <v>0.006966475</v>
       </c>
       <c r="D3">
-        <v>0.005467149999999999</v>
+        <v>0.005986050000000001</v>
       </c>
       <c r="E3">
-        <v>0.006639975000000001</v>
+        <v>0.006828949999999999</v>
       </c>
       <c r="F3">
-        <v>0.004999399999999999</v>
+        <v>0.0052471</v>
       </c>
       <c r="G3">
-        <v>0.006044394999999999</v>
+        <v>0.006290495</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -618,22 +618,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.01002655</v>
+        <v>0.010066</v>
       </c>
       <c r="C4">
-        <v>0.04966737499999999</v>
+        <v>0.0503714</v>
       </c>
       <c r="D4">
-        <v>0.018291775</v>
+        <v>0.01890995</v>
       </c>
       <c r="E4">
-        <v>0.010583675</v>
+        <v>0.010793</v>
       </c>
       <c r="F4">
-        <v>0.007077</v>
+        <v>0.0072778</v>
       </c>
       <c r="G4">
-        <v>0.019129275</v>
+        <v>0.01948363</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,22 +641,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.024258775</v>
+        <v>0.024656</v>
       </c>
       <c r="C5">
-        <v>0.032697325</v>
+        <v>0.03220025</v>
       </c>
       <c r="D5">
-        <v>0.024824075</v>
+        <v>0.0253811</v>
       </c>
       <c r="E5">
-        <v>0.035159325</v>
+        <v>0.034898075</v>
       </c>
       <c r="F5">
-        <v>0.044880175</v>
+        <v>0.0454917</v>
       </c>
       <c r="G5">
-        <v>0.032363935</v>
+        <v>0.032525425</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -664,22 +664,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.0048966</v>
+        <v>0.004847725</v>
       </c>
       <c r="C6">
-        <v>0.004250925</v>
+        <v>0.004273275</v>
       </c>
       <c r="D6">
-        <v>0.006666</v>
+        <v>0.006875825</v>
       </c>
       <c r="E6">
-        <v>0.006490925</v>
+        <v>0.006618525</v>
       </c>
       <c r="F6">
-        <v>0.010279925</v>
+        <v>0.01032265</v>
       </c>
       <c r="G6">
-        <v>0.006516875000000001</v>
+        <v>0.006587599999999999</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -687,22 +687,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.04597025</v>
+        <v>0.04566025</v>
       </c>
       <c r="C7">
-        <v>0.037095925</v>
+        <v>0.0375998</v>
       </c>
       <c r="D7">
-        <v>0.031282075</v>
+        <v>0.032013325</v>
       </c>
       <c r="E7">
-        <v>0.06120434999999999</v>
+        <v>0.06195417500000001</v>
       </c>
       <c r="F7">
-        <v>0.0938287</v>
+        <v>0.09722252499999999</v>
       </c>
       <c r="G7">
-        <v>0.05387626</v>
+        <v>0.054890015</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -710,22 +710,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.043431675</v>
+        <v>0.04300682500000001</v>
       </c>
       <c r="C8">
-        <v>0.03496104999999999</v>
+        <v>0.0354778</v>
       </c>
       <c r="D8">
-        <v>0.027668</v>
+        <v>0.0285224</v>
       </c>
       <c r="E8">
-        <v>0.05780734999999999</v>
+        <v>0.05846377500000001</v>
       </c>
       <c r="F8">
-        <v>0.09385832500000002</v>
+        <v>0.09661275</v>
       </c>
       <c r="G8">
-        <v>0.05154528000000001</v>
+        <v>0.05241671000000001</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -733,22 +733,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.00471495</v>
+        <v>0.004887424999999999</v>
       </c>
       <c r="C9">
-        <v>0.0154885</v>
+        <v>0.015940075</v>
       </c>
       <c r="D9">
-        <v>0.00666365</v>
+        <v>0.0069278</v>
       </c>
       <c r="E9">
-        <v>0.004076375</v>
+        <v>0.004259374999999999</v>
       </c>
       <c r="F9">
-        <v>0.0027412</v>
+        <v>0.00279665</v>
       </c>
       <c r="G9">
-        <v>0.006736935000000001</v>
+        <v>0.006962264999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -756,22 +756,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.0075802</v>
+        <v>0.007675325</v>
       </c>
       <c r="C10">
-        <v>0.008041925</v>
+        <v>0.008307825000000001</v>
       </c>
       <c r="D10">
-        <v>0.005304275000000001</v>
+        <v>0.0055774</v>
       </c>
       <c r="E10">
-        <v>0.008175075</v>
+        <v>0.0086091</v>
       </c>
       <c r="F10">
-        <v>0.006884975000000001</v>
+        <v>0.0069488</v>
       </c>
       <c r="G10">
-        <v>0.00719729</v>
+        <v>0.007423689999999999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -779,22 +779,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.00667885</v>
+        <v>0.006823099999999999</v>
       </c>
       <c r="C11">
-        <v>0.006993249999999999</v>
+        <v>0.00720205</v>
       </c>
       <c r="D11">
-        <v>0.005692125</v>
+        <v>0.005979199999999999</v>
       </c>
       <c r="E11">
-        <v>0.006921575</v>
+        <v>0.007173000000000001</v>
       </c>
       <c r="F11">
-        <v>0.005266750000000001</v>
+        <v>0.0053904</v>
       </c>
       <c r="G11">
-        <v>0.00631051</v>
+        <v>0.00651355</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -802,22 +802,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.006861875000000001</v>
+        <v>0.006982975000000001</v>
       </c>
       <c r="C12">
-        <v>0.007204475000000001</v>
+        <v>0.007395325</v>
       </c>
       <c r="D12">
-        <v>0.00586945</v>
+        <v>0.0060631</v>
       </c>
       <c r="E12">
-        <v>0.007207649999999999</v>
+        <v>0.007297175</v>
       </c>
       <c r="F12">
-        <v>0.005317725000000001</v>
+        <v>0.0053441</v>
       </c>
       <c r="G12">
-        <v>0.006492235000000001</v>
+        <v>0.006616535</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -825,22 +825,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.0103431</v>
+        <v>0.010447475</v>
       </c>
       <c r="C13">
-        <v>0.04969609999999999</v>
+        <v>0.05058235</v>
       </c>
       <c r="D13">
-        <v>0.018325775</v>
+        <v>0.019190325</v>
       </c>
       <c r="E13">
-        <v>0.010672075</v>
+        <v>0.010871025</v>
       </c>
       <c r="F13">
-        <v>0.007572224999999999</v>
+        <v>0.007564824999999999</v>
       </c>
       <c r="G13">
-        <v>0.019321855</v>
+        <v>0.0197312</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -848,22 +848,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.0101845</v>
+        <v>0.01020105</v>
       </c>
       <c r="C14">
-        <v>0.04749725</v>
+        <v>0.04782270000000001</v>
       </c>
       <c r="D14">
-        <v>0.025842975</v>
+        <v>0.0266651</v>
       </c>
       <c r="E14">
-        <v>0.009357375000000001</v>
+        <v>0.009545350000000001</v>
       </c>
       <c r="F14">
-        <v>0.0069764</v>
+        <v>0.007026425</v>
       </c>
       <c r="G14">
-        <v>0.0199717</v>
+        <v>0.020252125</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -871,22 +871,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.015825375</v>
+        <v>0.0160334</v>
       </c>
       <c r="C15">
-        <v>0.05900265</v>
+        <v>0.05988284999999999</v>
       </c>
       <c r="D15">
-        <v>0.018970275</v>
+        <v>0.02010065</v>
       </c>
       <c r="E15">
-        <v>0.009318100000000001</v>
+        <v>0.009468850000000001</v>
       </c>
       <c r="F15">
-        <v>0.019282525</v>
+        <v>0.01987045</v>
       </c>
       <c r="G15">
-        <v>0.024479785</v>
+        <v>0.02507124</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -894,22 +894,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.024644575</v>
+        <v>0.024876</v>
       </c>
       <c r="C16">
-        <v>0.032749725</v>
+        <v>0.0325584</v>
       </c>
       <c r="D16">
-        <v>0.025090825</v>
+        <v>0.0258621</v>
       </c>
       <c r="E16">
-        <v>0.035063025</v>
+        <v>0.035321925</v>
       </c>
       <c r="F16">
-        <v>0.04563014999999999</v>
+        <v>0.04607307499999999</v>
       </c>
       <c r="G16">
-        <v>0.03263566</v>
+        <v>0.0329383</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -917,22 +917,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.02542385</v>
+        <v>0.02551265</v>
       </c>
       <c r="C17">
-        <v>0.03156845</v>
+        <v>0.03133395</v>
       </c>
       <c r="D17">
-        <v>0.023605325</v>
+        <v>0.02461715</v>
       </c>
       <c r="E17">
-        <v>0.032287775</v>
+        <v>0.032812075</v>
       </c>
       <c r="F17">
-        <v>0.04190945</v>
+        <v>0.0426814</v>
       </c>
       <c r="G17">
-        <v>0.03095897</v>
+        <v>0.031391445</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -940,22 +940,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.005548274999999999</v>
+        <v>0.005507225</v>
       </c>
       <c r="C18">
-        <v>0.003712225</v>
+        <v>0.00384005</v>
       </c>
       <c r="D18">
-        <v>0.005028825000000001</v>
+        <v>0.005167475</v>
       </c>
       <c r="E18">
-        <v>0.003579975</v>
+        <v>0.003604375</v>
       </c>
       <c r="F18">
-        <v>0.007498949999999999</v>
+        <v>0.007600225</v>
       </c>
       <c r="G18">
-        <v>0.005073650000000001</v>
+        <v>0.00514387</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -963,22 +963,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.002827000000000001</v>
+        <v>0.002790375</v>
       </c>
       <c r="C19">
-        <v>0.003978475</v>
+        <v>0.004072375</v>
       </c>
       <c r="D19">
-        <v>0.002562475</v>
+        <v>0.002614175</v>
       </c>
       <c r="E19">
-        <v>0.002974249999999999</v>
+        <v>0.003013025</v>
       </c>
       <c r="F19">
-        <v>0.005067475</v>
+        <v>0.0051277</v>
       </c>
       <c r="G19">
-        <v>0.003481935</v>
+        <v>0.00352353</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -986,22 +986,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004788975</v>
+        <v>0.004749975</v>
       </c>
       <c r="C20">
-        <v>0.004636625</v>
+        <v>0.004593524999999999</v>
       </c>
       <c r="D20">
-        <v>0.004744325</v>
+        <v>0.00484465</v>
       </c>
       <c r="E20">
-        <v>0.00481165</v>
+        <v>0.004857</v>
       </c>
       <c r="F20">
-        <v>0.008057375</v>
+        <v>0.008157774999999999</v>
       </c>
       <c r="G20">
-        <v>0.00540779</v>
+        <v>0.005440585</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1009,22 +1009,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.005095975000000001</v>
+        <v>0.004941549999999999</v>
       </c>
       <c r="C21">
-        <v>0.00420145</v>
+        <v>0.004243475</v>
       </c>
       <c r="D21">
-        <v>0.006648225000000001</v>
+        <v>0.00681695</v>
       </c>
       <c r="E21">
-        <v>0.006579075</v>
+        <v>0.0067182</v>
       </c>
       <c r="F21">
-        <v>0.010405175</v>
+        <v>0.010316725</v>
       </c>
       <c r="G21">
-        <v>0.00658598</v>
+        <v>0.00660738</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1032,22 +1032,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.04379112499999999</v>
+        <v>0.04338085</v>
       </c>
       <c r="C22">
-        <v>0.03581332500000001</v>
+        <v>0.03585585</v>
       </c>
       <c r="D22">
-        <v>0.027752075</v>
+        <v>0.028797025</v>
       </c>
       <c r="E22">
-        <v>0.05786835</v>
+        <v>0.05846927499999999</v>
       </c>
       <c r="F22">
-        <v>0.0933886</v>
+        <v>0.09736060000000001</v>
       </c>
       <c r="G22">
-        <v>0.051722695</v>
+        <v>0.05277272</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1055,22 +1055,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.005231174999999999</v>
+        <v>0.005288849999999999</v>
       </c>
       <c r="C23">
-        <v>0.015919975</v>
+        <v>0.016373075</v>
       </c>
       <c r="D23">
-        <v>0.00673015</v>
+        <v>0.007172825000000001</v>
       </c>
       <c r="E23">
-        <v>0.004510825</v>
+        <v>0.0045382</v>
       </c>
       <c r="F23">
-        <v>0.003007525</v>
+        <v>0.003079075</v>
       </c>
       <c r="G23">
-        <v>0.00707993</v>
+        <v>0.007290405</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1078,22 +1078,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.00502455</v>
+        <v>0.005167275</v>
       </c>
       <c r="C24">
-        <v>0.01624835</v>
+        <v>0.01667345</v>
       </c>
       <c r="D24">
-        <v>0.00841925</v>
+        <v>0.00897835</v>
       </c>
       <c r="E24">
-        <v>0.0044718</v>
+        <v>0.004514900000000001</v>
       </c>
       <c r="F24">
-        <v>0.002739125</v>
+        <v>0.002791575</v>
       </c>
       <c r="G24">
-        <v>0.007380615</v>
+        <v>0.007625109999999999</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1101,22 +1101,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.009633175000000001</v>
+        <v>0.009683875</v>
       </c>
       <c r="C25">
-        <v>0.0259808</v>
+        <v>0.027062275</v>
       </c>
       <c r="D25">
-        <v>0.010912425</v>
+        <v>0.01160835</v>
       </c>
       <c r="E25">
-        <v>0.005028175</v>
+        <v>0.00519125</v>
       </c>
       <c r="F25">
-        <v>0.01075485</v>
+        <v>0.01104095</v>
       </c>
       <c r="G25">
-        <v>0.012461885</v>
+        <v>0.01291734</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1124,22 +1124,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.007714</v>
+        <v>0.00783815</v>
       </c>
       <c r="C26">
-        <v>0.0083125</v>
+        <v>0.008652449999999999</v>
       </c>
       <c r="D26">
-        <v>0.005598675000000001</v>
+        <v>0.0058301</v>
       </c>
       <c r="E26">
-        <v>0.008462899999999999</v>
+        <v>0.008776975000000001</v>
       </c>
       <c r="F26">
-        <v>0.00718715</v>
+        <v>0.00734695</v>
       </c>
       <c r="G26">
-        <v>0.007455044999999999</v>
+        <v>0.007688925000000001</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1147,22 +1147,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.007728725</v>
+        <v>0.007989</v>
       </c>
       <c r="C27">
-        <v>0.008842775000000001</v>
+        <v>0.008886125</v>
       </c>
       <c r="D27">
-        <v>0.005536025</v>
+        <v>0.005680899999999999</v>
       </c>
       <c r="E27">
-        <v>0.008408025</v>
+        <v>0.008571499999999999</v>
       </c>
       <c r="F27">
-        <v>0.007147775</v>
+        <v>0.007288149999999999</v>
       </c>
       <c r="G27">
-        <v>0.007532664999999999</v>
+        <v>0.007683134999999999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1170,22 +1170,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.0072802</v>
+        <v>0.007420650000000001</v>
       </c>
       <c r="C28">
-        <v>0.007622825</v>
+        <v>0.0077784</v>
       </c>
       <c r="D28">
-        <v>0.005894974999999999</v>
+        <v>0.006293575</v>
       </c>
       <c r="E28">
-        <v>0.007387049999999999</v>
+        <v>0.007590275</v>
       </c>
       <c r="F28">
-        <v>0.005607600000000001</v>
+        <v>0.00594775</v>
       </c>
       <c r="G28">
-        <v>0.00675853</v>
+        <v>0.007006130000000001</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1193,22 +1193,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.0105557</v>
+        <v>0.010652425</v>
       </c>
       <c r="C29">
-        <v>0.047628875</v>
+        <v>0.04816585</v>
       </c>
       <c r="D29">
-        <v>0.026329225</v>
+        <v>0.026876925</v>
       </c>
       <c r="E29">
-        <v>0.009927100000000001</v>
+        <v>0.009714350000000002</v>
       </c>
       <c r="F29">
-        <v>0.0073587</v>
+        <v>0.007708024999999999</v>
       </c>
       <c r="G29">
-        <v>0.02035992</v>
+        <v>0.020623515</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1216,22 +1216,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.0161349</v>
+        <v>0.01632385</v>
       </c>
       <c r="C30">
-        <v>0.059148775</v>
+        <v>0.06030754999999999</v>
       </c>
       <c r="D30">
-        <v>0.01910195</v>
+        <v>0.020156825</v>
       </c>
       <c r="E30">
-        <v>0.009491425</v>
+        <v>0.009730925</v>
       </c>
       <c r="F30">
-        <v>0.0197836</v>
+        <v>0.020242575</v>
       </c>
       <c r="G30">
-        <v>0.02473213</v>
+        <v>0.025352345</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1239,22 +1239,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.013661325</v>
+        <v>0.01382505</v>
       </c>
       <c r="C31">
-        <v>0.05822627499999999</v>
+        <v>0.05980769999999999</v>
       </c>
       <c r="D31">
-        <v>0.019385625</v>
+        <v>0.020428675</v>
       </c>
       <c r="E31">
-        <v>0.008911275</v>
+        <v>0.0091699</v>
       </c>
       <c r="F31">
-        <v>0.0163996</v>
+        <v>0.01698675</v>
       </c>
       <c r="G31">
-        <v>0.02331682</v>
+        <v>0.024043615</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1262,22 +1262,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.025424275</v>
+        <v>0.02566585</v>
       </c>
       <c r="C32">
-        <v>0.0317383</v>
+        <v>0.0320633</v>
       </c>
       <c r="D32">
-        <v>0.02379185</v>
+        <v>0.024742075</v>
       </c>
       <c r="E32">
-        <v>0.032681225</v>
+        <v>0.03337205</v>
       </c>
       <c r="F32">
-        <v>0.04181585</v>
+        <v>0.043375725</v>
       </c>
       <c r="G32">
-        <v>0.0310903</v>
+        <v>0.0318438</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1285,22 +1285,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.005526299999999999</v>
+        <v>0.005563075</v>
       </c>
       <c r="C33">
-        <v>0.004029775</v>
+        <v>0.004078525</v>
       </c>
       <c r="D33">
-        <v>0.003073325</v>
+        <v>0.003174600000000001</v>
       </c>
       <c r="E33">
-        <v>0.00404905</v>
+        <v>0.004179924999999999</v>
       </c>
       <c r="F33">
-        <v>0.008036125</v>
+        <v>0.008145100000000001</v>
       </c>
       <c r="G33">
-        <v>0.004942914999999999</v>
+        <v>0.005028245000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1308,22 +1308,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.008464375</v>
+        <v>0.008478099999999999</v>
       </c>
       <c r="C34">
-        <v>0.003818375</v>
+        <v>0.00401885</v>
       </c>
       <c r="D34">
-        <v>0.003477475000000001</v>
+        <v>0.0034743</v>
       </c>
       <c r="E34">
-        <v>0.0036898</v>
+        <v>0.003788425</v>
       </c>
       <c r="F34">
-        <v>0.008898675</v>
+        <v>0.008956200000000001</v>
       </c>
       <c r="G34">
-        <v>0.005669740000000001</v>
+        <v>0.005743175000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1331,22 +1331,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.005627974999999999</v>
+        <v>0.005595149999999998</v>
       </c>
       <c r="C35">
-        <v>0.003851574999999999</v>
+        <v>0.0038784</v>
       </c>
       <c r="D35">
-        <v>0.005114675</v>
+        <v>0.00518475</v>
       </c>
       <c r="E35">
-        <v>0.003577475</v>
+        <v>0.003701149999999999</v>
       </c>
       <c r="F35">
-        <v>0.007511174999999999</v>
+        <v>0.007603724999999999</v>
       </c>
       <c r="G35">
-        <v>0.005136574999999999</v>
+        <v>0.005192634999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1354,22 +1354,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.002844425</v>
+        <v>0.002858175</v>
       </c>
       <c r="C36">
-        <v>0.004127425</v>
+        <v>0.004120425</v>
       </c>
       <c r="D36">
-        <v>0.002596875</v>
+        <v>0.002676125</v>
       </c>
       <c r="E36">
-        <v>0.003000375</v>
+        <v>0.003049325</v>
       </c>
       <c r="F36">
-        <v>0.005199925</v>
+        <v>0.005155775</v>
       </c>
       <c r="G36">
-        <v>0.003553805</v>
+        <v>0.003571965</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1377,22 +1377,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.00357325</v>
+        <v>0.003613575</v>
       </c>
       <c r="C37">
-        <v>0.0042377</v>
+        <v>0.004256175000000001</v>
       </c>
       <c r="D37">
-        <v>0.003388675</v>
+        <v>0.0034929</v>
       </c>
       <c r="E37">
-        <v>0.0027671</v>
+        <v>0.002814225</v>
       </c>
       <c r="F37">
-        <v>0.0045646</v>
+        <v>0.004682575</v>
       </c>
       <c r="G37">
-        <v>0.003706265</v>
+        <v>0.00377189</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1400,22 +1400,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004793575</v>
+        <v>0.004869825</v>
       </c>
       <c r="C38">
-        <v>0.00464335</v>
+        <v>0.004739125</v>
       </c>
       <c r="D38">
-        <v>0.004903299999999999</v>
+        <v>0.004987275</v>
       </c>
       <c r="E38">
-        <v>0.004881475</v>
+        <v>0.004925525</v>
       </c>
       <c r="F38">
-        <v>0.008365050000000001</v>
+        <v>0.008264825</v>
       </c>
       <c r="G38">
-        <v>0.00551735</v>
+        <v>0.005557315</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1423,22 +1423,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.005437674999999999</v>
+        <v>0.00566075</v>
       </c>
       <c r="C39">
-        <v>0.016501</v>
+        <v>0.017067475</v>
       </c>
       <c r="D39">
-        <v>0.008738375</v>
+        <v>0.009290349999999999</v>
       </c>
       <c r="E39">
-        <v>0.004648025</v>
+        <v>0.0047869</v>
       </c>
       <c r="F39">
-        <v>0.00304425</v>
+        <v>0.0032086</v>
       </c>
       <c r="G39">
-        <v>0.007673864999999999</v>
+        <v>0.008002814999999998</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1446,22 +1446,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.010011075</v>
+        <v>0.010092175</v>
       </c>
       <c r="C40">
-        <v>0.02648415</v>
+        <v>0.0272685</v>
       </c>
       <c r="D40">
-        <v>0.0115957</v>
+        <v>0.011962775</v>
       </c>
       <c r="E40">
-        <v>0.005284624999999999</v>
+        <v>0.005414675</v>
       </c>
       <c r="F40">
-        <v>0.011025775</v>
+        <v>0.011559675</v>
       </c>
       <c r="G40">
-        <v>0.012880265</v>
+        <v>0.01325956</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1469,22 +1469,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.008283800000000001</v>
+        <v>0.008499949999999999</v>
       </c>
       <c r="C41">
-        <v>0.026309525</v>
+        <v>0.027297</v>
       </c>
       <c r="D41">
-        <v>0.01069675</v>
+        <v>0.01124555</v>
       </c>
       <c r="E41">
-        <v>0.005072825</v>
+        <v>0.005200475</v>
       </c>
       <c r="F41">
-        <v>0.008973150000000001</v>
+        <v>0.009091575000000001</v>
       </c>
       <c r="G41">
-        <v>0.01186721</v>
+        <v>0.01226691</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1492,22 +1492,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.00823435</v>
+        <v>0.008465425</v>
       </c>
       <c r="C42">
-        <v>0.008841475000000001</v>
+        <v>0.009256250000000001</v>
       </c>
       <c r="D42">
-        <v>0.00576255</v>
+        <v>0.00608025</v>
       </c>
       <c r="E42">
-        <v>0.008607</v>
+        <v>0.008823900000000001</v>
       </c>
       <c r="F42">
-        <v>0.0074603</v>
+        <v>0.007745674999999999</v>
       </c>
       <c r="G42">
-        <v>0.007781135</v>
+        <v>0.0080743</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1515,22 +1515,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.01409015</v>
+        <v>0.0141081</v>
       </c>
       <c r="C43">
-        <v>0.05831610000000001</v>
+        <v>0.0599003</v>
       </c>
       <c r="D43">
-        <v>0.020001875</v>
+        <v>0.02065529999999999</v>
       </c>
       <c r="E43">
-        <v>0.009070749999999999</v>
+        <v>0.009409899999999999</v>
       </c>
       <c r="F43">
-        <v>0.01684185</v>
+        <v>0.017254525</v>
       </c>
       <c r="G43">
-        <v>0.023664145</v>
+        <v>0.024265625</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1538,22 +1538,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.005592524999999999</v>
+        <v>0.005646674999999999</v>
       </c>
       <c r="C44">
-        <v>0.004108275</v>
+        <v>0.00419345</v>
       </c>
       <c r="D44">
-        <v>0.003139400000000001</v>
+        <v>0.003250975</v>
       </c>
       <c r="E44">
-        <v>0.004142799999999999</v>
+        <v>0.00427745</v>
       </c>
       <c r="F44">
-        <v>0.0081776</v>
+        <v>0.008234150000000001</v>
       </c>
       <c r="G44">
-        <v>0.005032119999999999</v>
+        <v>0.00512054</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1561,22 +1561,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.006026574999999999</v>
+        <v>0.0060334</v>
       </c>
       <c r="C45">
-        <v>0.00443255</v>
+        <v>0.004473575</v>
       </c>
       <c r="D45">
-        <v>0.00375835</v>
+        <v>0.0038815</v>
       </c>
       <c r="E45">
-        <v>0.00382735</v>
+        <v>0.00411905</v>
       </c>
       <c r="F45">
-        <v>0.008433224999999999</v>
+        <v>0.008536599999999998</v>
       </c>
       <c r="G45">
-        <v>0.00529561</v>
+        <v>0.005408825</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1584,22 +1584,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.008493625000000001</v>
+        <v>0.008640600000000002</v>
       </c>
       <c r="C46">
-        <v>0.00397375</v>
+        <v>0.004088325</v>
       </c>
       <c r="D46">
-        <v>0.003531225</v>
+        <v>0.0036034</v>
       </c>
       <c r="E46">
-        <v>0.0037774</v>
+        <v>0.0038975</v>
       </c>
       <c r="F46">
-        <v>0.008991075000000001</v>
+        <v>0.009158099999999999</v>
       </c>
       <c r="G46">
-        <v>0.005753415</v>
+        <v>0.005877584999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1607,22 +1607,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.003643275</v>
+        <v>0.00363435</v>
       </c>
       <c r="C47">
-        <v>0.0044247</v>
+        <v>0.0043871</v>
       </c>
       <c r="D47">
-        <v>0.003486625</v>
+        <v>0.0035842</v>
       </c>
       <c r="E47">
-        <v>0.0027726</v>
+        <v>0.0029311</v>
       </c>
       <c r="F47">
-        <v>0.004768975</v>
+        <v>0.00468885</v>
       </c>
       <c r="G47">
-        <v>0.003819235</v>
+        <v>0.003845119999999999</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1630,22 +1630,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.008621725</v>
+        <v>0.0087245</v>
       </c>
       <c r="C48">
-        <v>0.02645285</v>
+        <v>0.027567875</v>
       </c>
       <c r="D48">
-        <v>0.01101365</v>
+        <v>0.0116931</v>
       </c>
       <c r="E48">
-        <v>0.005305900000000001</v>
+        <v>0.005508375</v>
       </c>
       <c r="F48">
-        <v>0.009301975000000001</v>
+        <v>0.009623100000000001</v>
       </c>
       <c r="G48">
-        <v>0.01213922</v>
+        <v>0.01262339</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1653,22 +1653,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.006066975</v>
+        <v>0.00616065</v>
       </c>
       <c r="C49">
-        <v>0.004536175</v>
+        <v>0.004594325</v>
       </c>
       <c r="D49">
-        <v>0.0038182</v>
+        <v>0.004005175</v>
       </c>
       <c r="E49">
-        <v>0.00384035</v>
+        <v>0.0039245</v>
       </c>
       <c r="F49">
-        <v>0.008475775</v>
+        <v>0.008776600000000001</v>
       </c>
       <c r="G49">
-        <v>0.005347494999999999</v>
+        <v>0.00549225</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -572,22 +572,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.04537362500000001</v>
+        <v>0.04495092499999999</v>
       </c>
       <c r="C2">
-        <v>0.037133475</v>
+        <v>0.03602815</v>
       </c>
       <c r="D2">
-        <v>0.03167575</v>
+        <v>0.030476075</v>
       </c>
       <c r="E2">
-        <v>0.061977075</v>
+        <v>0.06081697500000001</v>
       </c>
       <c r="F2">
-        <v>0.095404725</v>
+        <v>0.09353719999999999</v>
       </c>
       <c r="G2">
-        <v>0.05431293</v>
+        <v>0.053161865</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006423900000000001</v>
+        <v>0.0064005</v>
       </c>
       <c r="C3">
-        <v>0.006966475</v>
+        <v>0.006771325000000001</v>
       </c>
       <c r="D3">
-        <v>0.005986050000000001</v>
+        <v>0.005526025</v>
       </c>
       <c r="E3">
-        <v>0.006828949999999999</v>
+        <v>0.006659575</v>
       </c>
       <c r="F3">
-        <v>0.0052471</v>
+        <v>0.005015</v>
       </c>
       <c r="G3">
-        <v>0.006290495</v>
+        <v>0.006074485</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -618,22 +618,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.010066</v>
+        <v>0.010092325</v>
       </c>
       <c r="C4">
-        <v>0.0503714</v>
+        <v>0.04809945</v>
       </c>
       <c r="D4">
-        <v>0.01890995</v>
+        <v>0.01806635</v>
       </c>
       <c r="E4">
-        <v>0.010793</v>
+        <v>0.01053475</v>
       </c>
       <c r="F4">
-        <v>0.0072778</v>
+        <v>0.007082100000000001</v>
       </c>
       <c r="G4">
-        <v>0.01948363</v>
+        <v>0.018774995</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,22 +641,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.024656</v>
+        <v>0.02438905</v>
       </c>
       <c r="C5">
-        <v>0.03220025</v>
+        <v>0.0309793</v>
       </c>
       <c r="D5">
-        <v>0.0253811</v>
+        <v>0.024755975</v>
       </c>
       <c r="E5">
-        <v>0.034898075</v>
+        <v>0.03457350000000001</v>
       </c>
       <c r="F5">
-        <v>0.0454917</v>
+        <v>0.0451429</v>
       </c>
       <c r="G5">
-        <v>0.032525425</v>
+        <v>0.031968145</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -664,22 +664,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.004847725</v>
+        <v>0.004798149999999999</v>
       </c>
       <c r="C6">
-        <v>0.004273275</v>
+        <v>0.00416185</v>
       </c>
       <c r="D6">
-        <v>0.006875825</v>
+        <v>0.00666415</v>
       </c>
       <c r="E6">
-        <v>0.006618525</v>
+        <v>0.00643215</v>
       </c>
       <c r="F6">
-        <v>0.01032265</v>
+        <v>0.010466575</v>
       </c>
       <c r="G6">
-        <v>0.006587599999999999</v>
+        <v>0.006504575</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -687,22 +687,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.04566025</v>
+        <v>0.04513039999999999</v>
       </c>
       <c r="C7">
-        <v>0.0375998</v>
+        <v>0.03603435</v>
       </c>
       <c r="D7">
-        <v>0.032013325</v>
+        <v>0.0311252</v>
       </c>
       <c r="E7">
-        <v>0.06195417500000001</v>
+        <v>0.06070265000000001</v>
       </c>
       <c r="F7">
-        <v>0.09722252499999999</v>
+        <v>0.09391085000000002</v>
       </c>
       <c r="G7">
-        <v>0.054890015</v>
+        <v>0.05338069000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -710,22 +710,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.04300682500000001</v>
+        <v>0.04238987499999999</v>
       </c>
       <c r="C8">
-        <v>0.0354778</v>
+        <v>0.034142625</v>
       </c>
       <c r="D8">
-        <v>0.0285224</v>
+        <v>0.02728855</v>
       </c>
       <c r="E8">
-        <v>0.05846377500000001</v>
+        <v>0.05698795</v>
       </c>
       <c r="F8">
-        <v>0.09661275</v>
+        <v>0.09399302499999999</v>
       </c>
       <c r="G8">
-        <v>0.05241671000000001</v>
+        <v>0.050960405</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -733,22 +733,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.004887424999999999</v>
+        <v>0.004872</v>
       </c>
       <c r="C9">
-        <v>0.015940075</v>
+        <v>0.0155931</v>
       </c>
       <c r="D9">
-        <v>0.0069278</v>
+        <v>0.006664775</v>
       </c>
       <c r="E9">
-        <v>0.004259374999999999</v>
+        <v>0.004209424999999999</v>
       </c>
       <c r="F9">
-        <v>0.00279665</v>
+        <v>0.002743275</v>
       </c>
       <c r="G9">
-        <v>0.006962264999999998</v>
+        <v>0.006816515</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -756,22 +756,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.007675325</v>
+        <v>0.007476375</v>
       </c>
       <c r="C10">
-        <v>0.008307825000000001</v>
+        <v>0.00807475</v>
       </c>
       <c r="D10">
-        <v>0.0055774</v>
+        <v>0.005321375</v>
       </c>
       <c r="E10">
-        <v>0.0086091</v>
+        <v>0.0082272</v>
       </c>
       <c r="F10">
-        <v>0.0069488</v>
+        <v>0.00680565</v>
       </c>
       <c r="G10">
-        <v>0.007423689999999999</v>
+        <v>0.00718107</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -779,22 +779,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.006823099999999999</v>
+        <v>0.006691325000000001</v>
       </c>
       <c r="C11">
-        <v>0.00720205</v>
+        <v>0.007218599999999999</v>
       </c>
       <c r="D11">
-        <v>0.005979199999999999</v>
+        <v>0.005733975000000001</v>
       </c>
       <c r="E11">
-        <v>0.007173000000000001</v>
+        <v>0.0069365</v>
       </c>
       <c r="F11">
-        <v>0.0053904</v>
+        <v>0.005447550000000001</v>
       </c>
       <c r="G11">
-        <v>0.00651355</v>
+        <v>0.006405590000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -802,22 +802,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.006982975000000001</v>
+        <v>0.0068519</v>
       </c>
       <c r="C12">
-        <v>0.007395325</v>
+        <v>0.00731425</v>
       </c>
       <c r="D12">
-        <v>0.0060631</v>
+        <v>0.005854974999999999</v>
       </c>
       <c r="E12">
-        <v>0.007297175</v>
+        <v>0.007199375</v>
       </c>
       <c r="F12">
-        <v>0.0053441</v>
+        <v>0.005277825</v>
       </c>
       <c r="G12">
-        <v>0.006616535</v>
+        <v>0.006499664999999999</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -825,22 +825,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.010447475</v>
+        <v>0.01045155</v>
       </c>
       <c r="C13">
-        <v>0.05058235</v>
+        <v>0.0488622</v>
       </c>
       <c r="D13">
-        <v>0.019190325</v>
+        <v>0.018292175</v>
       </c>
       <c r="E13">
-        <v>0.010871025</v>
+        <v>0.010616075</v>
       </c>
       <c r="F13">
-        <v>0.007564824999999999</v>
+        <v>0.0075686</v>
       </c>
       <c r="G13">
-        <v>0.0197312</v>
+        <v>0.01915812</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -848,22 +848,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.01020105</v>
+        <v>0.010367975</v>
       </c>
       <c r="C14">
-        <v>0.04782270000000001</v>
+        <v>0.04596152499999999</v>
       </c>
       <c r="D14">
-        <v>0.0266651</v>
+        <v>0.02551215</v>
       </c>
       <c r="E14">
-        <v>0.009545350000000001</v>
+        <v>0.009463525</v>
       </c>
       <c r="F14">
-        <v>0.007026425</v>
+        <v>0.0069345</v>
       </c>
       <c r="G14">
-        <v>0.020252125</v>
+        <v>0.019647935</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -871,22 +871,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.0160334</v>
+        <v>0.01607695</v>
       </c>
       <c r="C15">
-        <v>0.05988284999999999</v>
+        <v>0.057900125</v>
       </c>
       <c r="D15">
-        <v>0.02010065</v>
+        <v>0.018933275</v>
       </c>
       <c r="E15">
-        <v>0.009468850000000001</v>
+        <v>0.00919625</v>
       </c>
       <c r="F15">
-        <v>0.01987045</v>
+        <v>0.019279475</v>
       </c>
       <c r="G15">
-        <v>0.02507124</v>
+        <v>0.024277215</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -894,22 +894,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.024876</v>
+        <v>0.02475495</v>
       </c>
       <c r="C16">
-        <v>0.0325584</v>
+        <v>0.03132025</v>
       </c>
       <c r="D16">
-        <v>0.0258621</v>
+        <v>0.02525645</v>
       </c>
       <c r="E16">
-        <v>0.035321925</v>
+        <v>0.0349613</v>
       </c>
       <c r="F16">
-        <v>0.04607307499999999</v>
+        <v>0.04502727499999999</v>
       </c>
       <c r="G16">
-        <v>0.0329383</v>
+        <v>0.032264045</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -917,22 +917,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.02551265</v>
+        <v>0.025203975</v>
       </c>
       <c r="C17">
-        <v>0.03133395</v>
+        <v>0.0308002</v>
       </c>
       <c r="D17">
-        <v>0.02461715</v>
+        <v>0.0234269</v>
       </c>
       <c r="E17">
-        <v>0.032812075</v>
+        <v>0.031586725</v>
       </c>
       <c r="F17">
-        <v>0.0426814</v>
+        <v>0.041456925</v>
       </c>
       <c r="G17">
-        <v>0.031391445</v>
+        <v>0.030494945</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -940,22 +940,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.005507225</v>
+        <v>0.005503725000000001</v>
       </c>
       <c r="C18">
-        <v>0.00384005</v>
+        <v>0.003759475</v>
       </c>
       <c r="D18">
-        <v>0.005167475</v>
+        <v>0.0050537</v>
       </c>
       <c r="E18">
-        <v>0.003604375</v>
+        <v>0.003605025</v>
       </c>
       <c r="F18">
-        <v>0.007600225</v>
+        <v>0.007552425</v>
       </c>
       <c r="G18">
-        <v>0.00514387</v>
+        <v>0.00509487</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -963,22 +963,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.002790375</v>
+        <v>0.002771075</v>
       </c>
       <c r="C19">
-        <v>0.004072375</v>
+        <v>0.004054625</v>
       </c>
       <c r="D19">
-        <v>0.002614175</v>
+        <v>0.00252845</v>
       </c>
       <c r="E19">
-        <v>0.003013025</v>
+        <v>0.002949625</v>
       </c>
       <c r="F19">
-        <v>0.0051277</v>
+        <v>0.0052891</v>
       </c>
       <c r="G19">
-        <v>0.00352353</v>
+        <v>0.003518575</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -986,22 +986,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004749975</v>
+        <v>0.004767850000000001</v>
       </c>
       <c r="C20">
-        <v>0.004593524999999999</v>
+        <v>0.004616574999999999</v>
       </c>
       <c r="D20">
-        <v>0.00484465</v>
+        <v>0.0047845</v>
       </c>
       <c r="E20">
-        <v>0.004857</v>
+        <v>0.0048496</v>
       </c>
       <c r="F20">
-        <v>0.008157774999999999</v>
+        <v>0.008061075000000001</v>
       </c>
       <c r="G20">
-        <v>0.005440585</v>
+        <v>0.005415919999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1009,22 +1009,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.004941549999999999</v>
+        <v>0.00491875</v>
       </c>
       <c r="C21">
-        <v>0.004243475</v>
+        <v>0.00424915</v>
       </c>
       <c r="D21">
-        <v>0.00681695</v>
+        <v>0.006713525000000001</v>
       </c>
       <c r="E21">
-        <v>0.0067182</v>
+        <v>0.00655855</v>
       </c>
       <c r="F21">
-        <v>0.010316725</v>
+        <v>0.01061885</v>
       </c>
       <c r="G21">
-        <v>0.00660738</v>
+        <v>0.006611765</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1032,22 +1032,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.04338085</v>
+        <v>0.04303274999999999</v>
       </c>
       <c r="C22">
-        <v>0.03585585</v>
+        <v>0.034634825</v>
       </c>
       <c r="D22">
-        <v>0.028797025</v>
+        <v>0.027536425</v>
       </c>
       <c r="E22">
-        <v>0.05846927499999999</v>
+        <v>0.05727599999999999</v>
       </c>
       <c r="F22">
-        <v>0.09736060000000001</v>
+        <v>0.09369627500000001</v>
       </c>
       <c r="G22">
-        <v>0.05277272</v>
+        <v>0.051235255</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1055,22 +1055,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.005288849999999999</v>
+        <v>0.0051491</v>
       </c>
       <c r="C23">
-        <v>0.016373075</v>
+        <v>0.01636485</v>
       </c>
       <c r="D23">
-        <v>0.007172825000000001</v>
+        <v>0.006863224999999999</v>
       </c>
       <c r="E23">
-        <v>0.0045382</v>
+        <v>0.004431450000000001</v>
       </c>
       <c r="F23">
-        <v>0.003079075</v>
+        <v>0.003000125</v>
       </c>
       <c r="G23">
-        <v>0.007290405</v>
+        <v>0.00716175</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1078,22 +1078,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.005167275</v>
+        <v>0.0052407</v>
       </c>
       <c r="C24">
-        <v>0.01667345</v>
+        <v>0.016468875</v>
       </c>
       <c r="D24">
-        <v>0.00897835</v>
+        <v>0.00867045</v>
       </c>
       <c r="E24">
-        <v>0.004514900000000001</v>
+        <v>0.0044424</v>
       </c>
       <c r="F24">
-        <v>0.002791575</v>
+        <v>0.0027877</v>
       </c>
       <c r="G24">
-        <v>0.007625109999999999</v>
+        <v>0.007522025</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1101,22 +1101,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.009683875</v>
+        <v>0.009783899999999998</v>
       </c>
       <c r="C25">
-        <v>0.027062275</v>
+        <v>0.02582195</v>
       </c>
       <c r="D25">
-        <v>0.01160835</v>
+        <v>0.011564225</v>
       </c>
       <c r="E25">
-        <v>0.00519125</v>
+        <v>0.005113125</v>
       </c>
       <c r="F25">
-        <v>0.01104095</v>
+        <v>0.01087075</v>
       </c>
       <c r="G25">
-        <v>0.01291734</v>
+        <v>0.01263079</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1124,22 +1124,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.00783815</v>
+        <v>0.007724999999999999</v>
       </c>
       <c r="C26">
-        <v>0.008652449999999999</v>
+        <v>0.0083131</v>
       </c>
       <c r="D26">
-        <v>0.0058301</v>
+        <v>0.005540575</v>
       </c>
       <c r="E26">
-        <v>0.008776975000000001</v>
+        <v>0.0084936</v>
       </c>
       <c r="F26">
-        <v>0.00734695</v>
+        <v>0.007331525</v>
       </c>
       <c r="G26">
-        <v>0.007688925000000001</v>
+        <v>0.00748076</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1147,22 +1147,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.007989</v>
+        <v>0.008093325</v>
       </c>
       <c r="C27">
-        <v>0.008886125</v>
+        <v>0.008559325000000001</v>
       </c>
       <c r="D27">
-        <v>0.005680899999999999</v>
+        <v>0.005566300000000001</v>
       </c>
       <c r="E27">
-        <v>0.008571499999999999</v>
+        <v>0.008343275000000001</v>
       </c>
       <c r="F27">
-        <v>0.007288149999999999</v>
+        <v>0.007203775</v>
       </c>
       <c r="G27">
-        <v>0.007683134999999999</v>
+        <v>0.0075532</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1170,22 +1170,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.007420650000000001</v>
+        <v>0.007160175</v>
       </c>
       <c r="C28">
-        <v>0.0077784</v>
+        <v>0.007516324999999999</v>
       </c>
       <c r="D28">
-        <v>0.006293575</v>
+        <v>0.006166125</v>
       </c>
       <c r="E28">
-        <v>0.007590275</v>
+        <v>0.007366775</v>
       </c>
       <c r="F28">
-        <v>0.00594775</v>
+        <v>0.005700350000000001</v>
       </c>
       <c r="G28">
-        <v>0.007006130000000001</v>
+        <v>0.006781949999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1193,22 +1193,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.010652425</v>
+        <v>0.010516325</v>
       </c>
       <c r="C29">
-        <v>0.04816585</v>
+        <v>0.04703395</v>
       </c>
       <c r="D29">
-        <v>0.026876925</v>
+        <v>0.02621945</v>
       </c>
       <c r="E29">
-        <v>0.009714350000000002</v>
+        <v>0.00954205</v>
       </c>
       <c r="F29">
-        <v>0.007708024999999999</v>
+        <v>0.007421975</v>
       </c>
       <c r="G29">
-        <v>0.020623515</v>
+        <v>0.02014675</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1216,22 +1216,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.01632385</v>
+        <v>0.016441825</v>
       </c>
       <c r="C30">
-        <v>0.06030754999999999</v>
+        <v>0.05788620000000001</v>
       </c>
       <c r="D30">
-        <v>0.020156825</v>
+        <v>0.019103</v>
       </c>
       <c r="E30">
-        <v>0.009730925</v>
+        <v>0.009438599999999998</v>
       </c>
       <c r="F30">
-        <v>0.020242575</v>
+        <v>0.019814875</v>
       </c>
       <c r="G30">
-        <v>0.025352345</v>
+        <v>0.0245369</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1239,22 +1239,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.01382505</v>
+        <v>0.013820225</v>
       </c>
       <c r="C31">
-        <v>0.05980769999999999</v>
+        <v>0.05753235</v>
       </c>
       <c r="D31">
-        <v>0.020428675</v>
+        <v>0.0196674</v>
       </c>
       <c r="E31">
-        <v>0.0091699</v>
+        <v>0.008816850000000001</v>
       </c>
       <c r="F31">
-        <v>0.01698675</v>
+        <v>0.01669665</v>
       </c>
       <c r="G31">
-        <v>0.024043615</v>
+        <v>0.023306695</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1262,22 +1262,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.02566585</v>
+        <v>0.02554045</v>
       </c>
       <c r="C32">
-        <v>0.0320633</v>
+        <v>0.03139975</v>
       </c>
       <c r="D32">
-        <v>0.024742075</v>
+        <v>0.0236449</v>
       </c>
       <c r="E32">
-        <v>0.03337205</v>
+        <v>0.031760775</v>
       </c>
       <c r="F32">
-        <v>0.043375725</v>
+        <v>0.04162724999999999</v>
       </c>
       <c r="G32">
-        <v>0.0318438</v>
+        <v>0.030794625</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1285,22 +1285,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.005563075</v>
+        <v>0.0056144</v>
       </c>
       <c r="C33">
-        <v>0.004078525</v>
+        <v>0.004153799999999999</v>
       </c>
       <c r="D33">
-        <v>0.003174600000000001</v>
+        <v>0.003070225</v>
       </c>
       <c r="E33">
-        <v>0.004179924999999999</v>
+        <v>0.004064725</v>
       </c>
       <c r="F33">
-        <v>0.008145100000000001</v>
+        <v>0.008104875000000001</v>
       </c>
       <c r="G33">
-        <v>0.005028245000000001</v>
+        <v>0.005001605</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1308,22 +1308,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.008478099999999999</v>
+        <v>0.008455724999999999</v>
       </c>
       <c r="C34">
-        <v>0.00401885</v>
+        <v>0.003913625</v>
       </c>
       <c r="D34">
-        <v>0.0034743</v>
+        <v>0.003461575</v>
       </c>
       <c r="E34">
-        <v>0.003788425</v>
+        <v>0.003782225</v>
       </c>
       <c r="F34">
-        <v>0.008956200000000001</v>
+        <v>0.0089763</v>
       </c>
       <c r="G34">
-        <v>0.005743175000000001</v>
+        <v>0.00571789</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1331,22 +1331,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.005595149999999998</v>
+        <v>0.005878299999999999</v>
       </c>
       <c r="C35">
-        <v>0.0038784</v>
+        <v>0.00381805</v>
       </c>
       <c r="D35">
-        <v>0.00518475</v>
+        <v>0.00518875</v>
       </c>
       <c r="E35">
-        <v>0.003701149999999999</v>
+        <v>0.00360265</v>
       </c>
       <c r="F35">
-        <v>0.007603724999999999</v>
+        <v>0.007565350000000001</v>
       </c>
       <c r="G35">
-        <v>0.005192634999999999</v>
+        <v>0.00521062</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1354,22 +1354,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.002858175</v>
+        <v>0.002829949999999999</v>
       </c>
       <c r="C36">
-        <v>0.004120425</v>
+        <v>0.0040699</v>
       </c>
       <c r="D36">
-        <v>0.002676125</v>
+        <v>0.002607025</v>
       </c>
       <c r="E36">
-        <v>0.003049325</v>
+        <v>0.002956325</v>
       </c>
       <c r="F36">
-        <v>0.005155775</v>
+        <v>0.005150975</v>
       </c>
       <c r="G36">
-        <v>0.003571965</v>
+        <v>0.003522834999999999</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1377,22 +1377,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.003613575</v>
+        <v>0.00358465</v>
       </c>
       <c r="C37">
-        <v>0.004256175000000001</v>
+        <v>0.0042121</v>
       </c>
       <c r="D37">
-        <v>0.0034929</v>
+        <v>0.0033971</v>
       </c>
       <c r="E37">
-        <v>0.002814225</v>
+        <v>0.002787175</v>
       </c>
       <c r="F37">
-        <v>0.004682575</v>
+        <v>0.00463045</v>
       </c>
       <c r="G37">
-        <v>0.00377189</v>
+        <v>0.003722295</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1400,22 +1400,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004869825</v>
+        <v>0.004833325</v>
       </c>
       <c r="C38">
-        <v>0.004739125</v>
+        <v>0.00463145</v>
       </c>
       <c r="D38">
-        <v>0.004987275</v>
+        <v>0.004861625</v>
       </c>
       <c r="E38">
-        <v>0.004925525</v>
+        <v>0.004861375</v>
       </c>
       <c r="F38">
-        <v>0.008264825</v>
+        <v>0.00811835</v>
       </c>
       <c r="G38">
-        <v>0.005557315</v>
+        <v>0.005461225</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1423,22 +1423,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.00566075</v>
+        <v>0.00553905</v>
       </c>
       <c r="C39">
-        <v>0.017067475</v>
+        <v>0.016621725</v>
       </c>
       <c r="D39">
-        <v>0.009290349999999999</v>
+        <v>0.008725499999999999</v>
       </c>
       <c r="E39">
-        <v>0.0047869</v>
+        <v>0.004607675</v>
       </c>
       <c r="F39">
-        <v>0.0032086</v>
+        <v>0.003043875</v>
       </c>
       <c r="G39">
-        <v>0.008002814999999998</v>
+        <v>0.007707565</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1446,22 +1446,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.010092175</v>
+        <v>0.010108025</v>
       </c>
       <c r="C40">
-        <v>0.0272685</v>
+        <v>0.02624135</v>
       </c>
       <c r="D40">
-        <v>0.011962775</v>
+        <v>0.01107915</v>
       </c>
       <c r="E40">
-        <v>0.005414675</v>
+        <v>0.0053021</v>
       </c>
       <c r="F40">
-        <v>0.011559675</v>
+        <v>0.0112927</v>
       </c>
       <c r="G40">
-        <v>0.01325956</v>
+        <v>0.012804665</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1469,22 +1469,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.008499949999999999</v>
+        <v>0.008642149999999999</v>
       </c>
       <c r="C41">
-        <v>0.027297</v>
+        <v>0.0261051</v>
       </c>
       <c r="D41">
-        <v>0.01124555</v>
+        <v>0.0106154</v>
       </c>
       <c r="E41">
-        <v>0.005200475</v>
+        <v>0.005131500000000001</v>
       </c>
       <c r="F41">
-        <v>0.009091575000000001</v>
+        <v>0.009022299999999999</v>
       </c>
       <c r="G41">
-        <v>0.01226691</v>
+        <v>0.01190329</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1492,22 +1492,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.008465425</v>
+        <v>0.008134124999999999</v>
       </c>
       <c r="C42">
-        <v>0.009256250000000001</v>
+        <v>0.00882465</v>
       </c>
       <c r="D42">
-        <v>0.00608025</v>
+        <v>0.005791474999999999</v>
       </c>
       <c r="E42">
-        <v>0.008823900000000001</v>
+        <v>0.008921100000000001</v>
       </c>
       <c r="F42">
-        <v>0.007745674999999999</v>
+        <v>0.007520674999999999</v>
       </c>
       <c r="G42">
-        <v>0.0080743</v>
+        <v>0.007838405</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1515,22 +1515,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.0141081</v>
+        <v>0.0141256</v>
       </c>
       <c r="C43">
-        <v>0.0599003</v>
+        <v>0.05748179999999999</v>
       </c>
       <c r="D43">
-        <v>0.02065529999999999</v>
+        <v>0.01950055</v>
       </c>
       <c r="E43">
-        <v>0.009409899999999999</v>
+        <v>0.009166849999999999</v>
       </c>
       <c r="F43">
-        <v>0.017254525</v>
+        <v>0.016954</v>
       </c>
       <c r="G43">
-        <v>0.024265625</v>
+        <v>0.02344576</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1538,22 +1538,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.005646674999999999</v>
+        <v>0.0055933</v>
       </c>
       <c r="C44">
-        <v>0.00419345</v>
+        <v>0.004103525</v>
       </c>
       <c r="D44">
-        <v>0.003250975</v>
+        <v>0.003165425</v>
       </c>
       <c r="E44">
-        <v>0.00427745</v>
+        <v>0.004178825000000001</v>
       </c>
       <c r="F44">
-        <v>0.008234150000000001</v>
+        <v>0.00810755</v>
       </c>
       <c r="G44">
-        <v>0.00512054</v>
+        <v>0.005029725000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1561,22 +1561,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0060334</v>
+        <v>0.006123324999999999</v>
       </c>
       <c r="C45">
-        <v>0.004473575</v>
+        <v>0.00459715</v>
       </c>
       <c r="D45">
-        <v>0.0038815</v>
+        <v>0.0037878</v>
       </c>
       <c r="E45">
-        <v>0.00411905</v>
+        <v>0.003869549999999999</v>
       </c>
       <c r="F45">
-        <v>0.008536599999999998</v>
+        <v>0.0084998</v>
       </c>
       <c r="G45">
-        <v>0.005408825</v>
+        <v>0.005375525000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1584,22 +1584,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.008640600000000002</v>
+        <v>0.00855885</v>
       </c>
       <c r="C46">
-        <v>0.004088325</v>
+        <v>0.004022825</v>
       </c>
       <c r="D46">
-        <v>0.0036034</v>
+        <v>0.003522525</v>
       </c>
       <c r="E46">
-        <v>0.0038975</v>
+        <v>0.003783225</v>
       </c>
       <c r="F46">
-        <v>0.009158099999999999</v>
+        <v>0.008915724999999999</v>
       </c>
       <c r="G46">
-        <v>0.005877584999999999</v>
+        <v>0.00576063</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1607,22 +1607,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.00363435</v>
+        <v>0.003643975</v>
       </c>
       <c r="C47">
-        <v>0.0043871</v>
+        <v>0.0042112</v>
       </c>
       <c r="D47">
-        <v>0.0035842</v>
+        <v>0.00348915</v>
       </c>
       <c r="E47">
-        <v>0.0029311</v>
+        <v>0.002819625</v>
       </c>
       <c r="F47">
-        <v>0.00468885</v>
+        <v>0.00465595</v>
       </c>
       <c r="G47">
-        <v>0.003845119999999999</v>
+        <v>0.003763979999999999</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1630,22 +1630,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.0087245</v>
+        <v>0.008533275</v>
       </c>
       <c r="C48">
-        <v>0.027567875</v>
+        <v>0.02636425</v>
       </c>
       <c r="D48">
-        <v>0.0116931</v>
+        <v>0.011042775</v>
       </c>
       <c r="E48">
-        <v>0.005508375</v>
+        <v>0.00536295</v>
       </c>
       <c r="F48">
-        <v>0.009623100000000001</v>
+        <v>0.009244024999999999</v>
       </c>
       <c r="G48">
-        <v>0.01262339</v>
+        <v>0.012109455</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1653,22 +1653,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.00616065</v>
+        <v>0.006097749999999999</v>
       </c>
       <c r="C49">
-        <v>0.004594325</v>
+        <v>0.0046258</v>
       </c>
       <c r="D49">
-        <v>0.004005175</v>
+        <v>0.003862475</v>
       </c>
       <c r="E49">
-        <v>0.0039245</v>
+        <v>0.003937475</v>
       </c>
       <c r="F49">
-        <v>0.008776600000000001</v>
+        <v>0.008391375</v>
       </c>
       <c r="G49">
-        <v>0.00549225</v>
+        <v>0.005382975</v>
       </c>
     </row>
   </sheetData>
@@ -1824,22 +1824,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="C7">
-        <v>10.25</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E7">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7">
-        <v>9.199999999999999</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1916,22 +1916,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>8.75</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>15.25</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>10.25</v>
+        <v>8.25</v>
       </c>
       <c r="F11">
         <v>4</v>
       </c>
       <c r="G11">
-        <v>9.65</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1962,22 +1962,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="D13">
-        <v>16.75</v>
+        <v>14.25</v>
       </c>
       <c r="E13">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>10.7</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2031,22 +2031,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>10.25</v>
+        <v>8.25</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="E16">
-        <v>11.25</v>
+        <v>8.5</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2146,22 +2146,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
-        <v>9.6</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2169,22 +2169,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>9.25</v>
+        <v>6.75</v>
       </c>
       <c r="C22">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22">
-        <v>9.25</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2192,22 +2192,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="C23">
-        <v>11.25</v>
+        <v>8.5</v>
       </c>
       <c r="D23">
-        <v>16.5</v>
+        <v>14.25</v>
       </c>
       <c r="E23">
-        <v>9.25</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2261,22 +2261,22 @@
         <v>31</v>
       </c>
       <c r="B26">
+        <v>8.5</v>
+      </c>
+      <c r="C26">
         <v>10.75</v>
       </c>
-      <c r="C26">
-        <v>12.25</v>
-      </c>
       <c r="D26">
-        <v>16.75</v>
+        <v>15.5</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>11.35</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2307,22 +2307,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>8.75</v>
+        <v>6.25</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28">
-        <v>9.75</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2330,22 +2330,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="D29">
-        <v>15.75</v>
+        <v>14.25</v>
       </c>
       <c r="E29">
-        <v>9.5</v>
+        <v>8.25</v>
       </c>
       <c r="F29">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>10.25</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2353,22 +2353,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="C30">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>16.5</v>
+        <v>14.75</v>
       </c>
       <c r="E30">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="F30">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="G30">
-        <v>10.7</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2399,22 +2399,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>10.25</v>
+        <v>8.25</v>
       </c>
       <c r="C32">
-        <v>10.75</v>
+        <v>9.25</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="E32">
-        <v>11.25</v>
+        <v>8.5</v>
       </c>
       <c r="F32">
         <v>4</v>
       </c>
       <c r="G32">
-        <v>10.25</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2468,22 +2468,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>7.75</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G35">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2491,22 +2491,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="C36">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D36">
-        <v>15.5</v>
+        <v>14.25</v>
       </c>
       <c r="E36">
-        <v>10.25</v>
+        <v>6.75</v>
       </c>
       <c r="F36">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>10.6</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2537,22 +2537,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>10.5</v>
+        <v>8.25</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="E38">
-        <v>11.25</v>
+        <v>8.75</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G38">
-        <v>9.75</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2560,22 +2560,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>9.25</v>
+        <v>7.25</v>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="D39">
-        <v>15.75</v>
+        <v>14.25</v>
       </c>
       <c r="E39">
-        <v>9.25</v>
+        <v>8.25</v>
       </c>
       <c r="F39">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>10.3</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2583,22 +2583,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>10.75</v>
+        <v>7.25</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="D40">
-        <v>16.5</v>
+        <v>14.75</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="F40">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="G40">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2629,22 +2629,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>11.75</v>
+        <v>10.5</v>
       </c>
       <c r="D42">
-        <v>16.75</v>
+        <v>15.5</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>11.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2652,22 +2652,22 @@
         <v>48</v>
       </c>
       <c r="B43">
+        <v>7.5</v>
+      </c>
+      <c r="C43">
         <v>9</v>
       </c>
-      <c r="C43">
-        <v>10.5</v>
-      </c>
       <c r="D43">
-        <v>16.75</v>
+        <v>14.75</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="G43">
-        <v>10.45</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2675,22 +2675,22 @@
         <v>49</v>
       </c>
       <c r="B44">
+        <v>6.75</v>
+      </c>
+      <c r="C44">
         <v>8.75</v>
       </c>
-      <c r="C44">
-        <v>12</v>
-      </c>
       <c r="D44">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="E44">
-        <v>11.25</v>
+        <v>8.5</v>
       </c>
       <c r="F44">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>10.65</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2721,22 +2721,22 @@
         <v>51</v>
       </c>
       <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
         <v>9</v>
       </c>
-      <c r="C46">
-        <v>12.25</v>
-      </c>
       <c r="D46">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="E46">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="F46">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="G46">
-        <v>10.65</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2744,22 +2744,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="D47">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="E47">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="F47">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>10.6</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2767,22 +2767,22 @@
         <v>53</v>
       </c>
       <c r="B48">
+        <v>7.25</v>
+      </c>
+      <c r="C48">
         <v>9.5</v>
       </c>
-      <c r="C48">
-        <v>11</v>
-      </c>
       <c r="D48">
-        <v>16.75</v>
+        <v>14.75</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="G48">
-        <v>10.65</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2790,22 +2790,22 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
         <v>9</v>
       </c>
-      <c r="C49">
-        <v>12.25</v>
-      </c>
       <c r="D49">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="E49">
-        <v>9.75</v>
+        <v>8.25</v>
       </c>
       <c r="F49">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>10.75</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2961,22 +2961,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>91.72485257725916</v>
+        <v>89.13939731950015</v>
       </c>
       <c r="C7">
-        <v>94.28719018831526</v>
+        <v>92.92004125279729</v>
       </c>
       <c r="D7">
-        <v>96.09135241389544</v>
+        <v>94.65664671106151</v>
       </c>
       <c r="E7">
-        <v>89.60451849562072</v>
+        <v>88.12126645620715</v>
       </c>
       <c r="F7">
         <v>87.33691238960859</v>
       </c>
       <c r="G7">
-        <v>91.80896521293984</v>
+        <v>90.43485282583494</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3053,22 +3053,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>90.54621526063178</v>
+        <v>88.81605475511716</v>
       </c>
       <c r="C11">
-        <v>92.52641660713583</v>
+        <v>92.35155128758481</v>
       </c>
       <c r="D11">
-        <v>95.79404337902628</v>
+        <v>94.77232629366651</v>
       </c>
       <c r="E11">
-        <v>88.20410850128535</v>
+        <v>87.44194575170043</v>
       </c>
       <c r="F11">
         <v>87.83084116930945</v>
       </c>
       <c r="G11">
-        <v>90.98032498347774</v>
+        <v>90.24254385147567</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3099,22 +3099,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>89.5194338638298</v>
+        <v>89.22701017523383</v>
       </c>
       <c r="C13">
-        <v>95.55804687106941</v>
+        <v>94.92412607931394</v>
       </c>
       <c r="D13">
-        <v>101.8589186747198</v>
+        <v>99.63732995997091</v>
       </c>
       <c r="E13">
-        <v>89.35311325426825</v>
+        <v>88.58420760391871</v>
       </c>
       <c r="F13">
-        <v>90.29777793799398</v>
+        <v>90.05714420705036</v>
       </c>
       <c r="G13">
-        <v>93.31745812037624</v>
+        <v>92.48596360509755</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3168,22 +3168,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>88.99921179650484</v>
+        <v>88.57888496415744</v>
       </c>
       <c r="C16">
-        <v>93.01525638432572</v>
+        <v>92.3043155870872</v>
       </c>
       <c r="D16">
-        <v>95.24546858635269</v>
+        <v>94.42117856929082</v>
       </c>
       <c r="E16">
-        <v>87.02915991771309</v>
+        <v>86.50435909119437</v>
       </c>
       <c r="F16">
         <v>87.25337971078574</v>
       </c>
       <c r="G16">
-        <v>90.30849527913641</v>
+        <v>89.81242358450312</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3283,22 +3283,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>94.42209588551708</v>
+        <v>91.1611041251298</v>
       </c>
       <c r="C21">
-        <v>96.0303354056141</v>
+        <v>93.72825760107301</v>
       </c>
       <c r="D21">
-        <v>98.25915590201265</v>
+        <v>98.15890054347378</v>
       </c>
       <c r="E21">
-        <v>89.70359386802247</v>
+        <v>88.73381198849388</v>
       </c>
       <c r="F21">
-        <v>89.17676618598557</v>
+        <v>88.98646867694093</v>
       </c>
       <c r="G21">
-        <v>93.51838944943037</v>
+        <v>92.15370858702228</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3306,22 +3306,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>90.93685523906024</v>
+        <v>89.2776595859244</v>
       </c>
       <c r="C22">
-        <v>93.91391810676384</v>
+        <v>92.90307720918985</v>
       </c>
       <c r="D22">
-        <v>95.40427079958275</v>
+        <v>94.41051680500189</v>
       </c>
       <c r="E22">
-        <v>89.52248109096848</v>
+        <v>88.1854601545144</v>
       </c>
       <c r="F22">
         <v>87.38393931334436</v>
       </c>
       <c r="G22">
-        <v>91.43229290994392</v>
+        <v>90.43213061359498</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3329,22 +3329,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>89.6159900426394</v>
+        <v>89.22701017523383</v>
       </c>
       <c r="C23">
-        <v>94.74917278692931</v>
+        <v>94.66869395521077</v>
       </c>
       <c r="D23">
-        <v>100.9296464662099</v>
+        <v>98.53898956548846</v>
       </c>
       <c r="E23">
-        <v>89.60108077810561</v>
+        <v>88.86499004755807</v>
       </c>
       <c r="F23">
-        <v>87.91636272147292</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G23">
-        <v>92.56245055907142</v>
+        <v>91.83043403847076</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3398,22 +3398,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>89.14083905815238</v>
+        <v>88.75888657103675</v>
       </c>
       <c r="C26">
-        <v>97.03251914740976</v>
+        <v>97.00780758575567</v>
       </c>
       <c r="D26">
-        <v>97.77239606356295</v>
+        <v>97.64968979182635</v>
       </c>
       <c r="E26">
-        <v>89.04474251239938</v>
+        <v>88.86499004755807</v>
       </c>
       <c r="F26">
-        <v>89.2164034626815</v>
+        <v>88.62102407633546</v>
       </c>
       <c r="G26">
-        <v>92.4413800488412</v>
+        <v>92.18047961450246</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3444,22 +3444,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>90.54114361467967</v>
+        <v>89.12431128621597</v>
       </c>
       <c r="C28">
-        <v>92.8466097608916</v>
+        <v>92.35632712783598</v>
       </c>
       <c r="D28">
-        <v>95.82890158590824</v>
+        <v>94.39401605200109</v>
       </c>
       <c r="E28">
-        <v>89.72300720183679</v>
+        <v>88.88690818712263</v>
       </c>
       <c r="F28">
         <v>87.25337971078574</v>
       </c>
       <c r="G28">
-        <v>91.2386083748204</v>
+        <v>90.40298847279227</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3467,22 +3467,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>89.54733577687858</v>
+        <v>88.89834825349419</v>
       </c>
       <c r="C29">
-        <v>96.12967005510683</v>
+        <v>94.58157556205583</v>
       </c>
       <c r="D29">
-        <v>103.4295116012851</v>
+        <v>102.1853912455699</v>
       </c>
       <c r="E29">
-        <v>89.35350062346056</v>
+        <v>88.58420760391871</v>
       </c>
       <c r="F29">
-        <v>90.58368323137562</v>
+        <v>90.14531001978574</v>
       </c>
       <c r="G29">
-        <v>93.80874025762134</v>
+        <v>92.87896653696487</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3490,22 +3490,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>90.03093966588489</v>
+        <v>88.98799547445716</v>
       </c>
       <c r="C30">
-        <v>97.12757998731722</v>
+        <v>96.23340722565031</v>
       </c>
       <c r="D30">
-        <v>98.95532963718236</v>
+        <v>98.3909295861728</v>
       </c>
       <c r="E30">
-        <v>89.38253734231658</v>
+        <v>88.59805700955056</v>
       </c>
       <c r="F30">
-        <v>92.69865149093101</v>
+        <v>92.13466900158528</v>
       </c>
       <c r="G30">
-        <v>93.63900762472642</v>
+        <v>92.86901165948322</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3536,22 +3536,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>88.99921179650484</v>
+        <v>88.57888496415744</v>
       </c>
       <c r="C32">
-        <v>93.84773767906115</v>
+        <v>93.24939669889704</v>
       </c>
       <c r="D32">
-        <v>95.24546858635269</v>
+        <v>94.42117856929082</v>
       </c>
       <c r="E32">
-        <v>87.02915991771309</v>
+        <v>86.50435909119437</v>
       </c>
       <c r="F32">
         <v>87.25337971078574</v>
       </c>
       <c r="G32">
-        <v>90.4749915380835</v>
+        <v>90.00143980686508</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3605,22 +3605,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>92.86734279435822</v>
+        <v>91.10993454476508</v>
       </c>
       <c r="C35">
-        <v>94.72051092461355</v>
+        <v>92.29928073650612</v>
       </c>
       <c r="D35">
-        <v>96.2945479532705</v>
+        <v>96.01541363581259</v>
       </c>
       <c r="E35">
-        <v>89.63197465251324</v>
+        <v>88.86857894582849</v>
       </c>
       <c r="F35">
-        <v>87.25337971078574</v>
+        <v>87.0681506715672</v>
       </c>
       <c r="G35">
-        <v>92.15355120710825</v>
+        <v>91.07227170689589</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3628,22 +3628,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>97.42466324028555</v>
+        <v>95.43566511011795</v>
       </c>
       <c r="C36">
-        <v>101.0884357896212</v>
+        <v>99.02144924571451</v>
       </c>
       <c r="D36">
-        <v>98.75915590201265</v>
+        <v>98.52857770962854</v>
       </c>
       <c r="E36">
-        <v>91.5118722934187</v>
+        <v>88.88470486692829</v>
       </c>
       <c r="F36">
-        <v>91.29592613104968</v>
+        <v>89.4557226091525</v>
       </c>
       <c r="G36">
-        <v>96.01601067127756</v>
+        <v>94.26522390830834</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3674,22 +3674,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>93.08600399896729</v>
+        <v>90.74289877000135</v>
       </c>
       <c r="C38">
-        <v>96.17678201502082</v>
+        <v>93.91924060669805</v>
       </c>
       <c r="D38">
-        <v>98.25915590201265</v>
+        <v>98.12554671335766</v>
       </c>
       <c r="E38">
-        <v>88.47938871750956</v>
+        <v>87.00466654293592</v>
       </c>
       <c r="F38">
-        <v>89.17676618598557</v>
+        <v>88.98646867694093</v>
       </c>
       <c r="G38">
-        <v>93.03561936389917</v>
+        <v>91.75576426198678</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3697,22 +3697,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>89.60406067016351</v>
+        <v>88.89834825349419</v>
       </c>
       <c r="C39">
-        <v>95.76906682557187</v>
+        <v>94.59092271771277</v>
       </c>
       <c r="D39">
-        <v>102.1639796876998</v>
+        <v>100.8161412879935</v>
       </c>
       <c r="E39">
-        <v>89.63438094807063</v>
+        <v>88.91691119506876</v>
       </c>
       <c r="F39">
-        <v>87.91636272147292</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G39">
-        <v>93.01757017059575</v>
+        <v>92.21496198062638</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3720,22 +3720,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>90.65444921294146</v>
+        <v>89.0003034744495</v>
       </c>
       <c r="C40">
-        <v>97.51119481579398</v>
+        <v>96.75656827501791</v>
       </c>
       <c r="D40">
-        <v>98.76494818645951</v>
+        <v>98.20054813544995</v>
       </c>
       <c r="E40">
-        <v>89.60108077810561</v>
+        <v>88.86499004755807</v>
       </c>
       <c r="F40">
-        <v>92.55515667937578</v>
+        <v>92.13301812599349</v>
       </c>
       <c r="G40">
-        <v>93.81736593453527</v>
+        <v>92.99108561169378</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3766,22 +3766,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>89.17692153974153</v>
+        <v>88.97492867645308</v>
       </c>
       <c r="C42">
-        <v>97.06542392572945</v>
+        <v>97.05189493017757</v>
       </c>
       <c r="D42">
-        <v>97.89291056653599</v>
+        <v>97.77020429479941</v>
       </c>
       <c r="E42">
-        <v>89.04474251239938</v>
+        <v>88.86499004755807</v>
       </c>
       <c r="F42">
-        <v>89.2164034626815</v>
+        <v>88.62102407633546</v>
       </c>
       <c r="G42">
-        <v>92.47928040141757</v>
+        <v>92.25660840506472</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3789,22 +3789,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>89.45770732525547</v>
+        <v>88.89834825349419</v>
       </c>
       <c r="C43">
-        <v>97.12757998731722</v>
+        <v>96.23340722565031</v>
       </c>
       <c r="D43">
-        <v>99.50277513396722</v>
+        <v>98.65358861299265</v>
       </c>
       <c r="E43">
-        <v>89.34618134646816</v>
+        <v>88.58420760391871</v>
       </c>
       <c r="F43">
-        <v>91.43396250283749</v>
+        <v>90.57933017944244</v>
       </c>
       <c r="G43">
-        <v>93.3736412591691</v>
+        <v>92.58977637509966</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3812,22 +3812,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>97.61169407182825</v>
+        <v>95.63997164837502</v>
       </c>
       <c r="C44">
-        <v>98.37401427221501</v>
+        <v>96.60137900637835</v>
       </c>
       <c r="D44">
-        <v>97.14647937060019</v>
+        <v>96.86734505314232</v>
       </c>
       <c r="E44">
-        <v>88.00534867131728</v>
+        <v>87.06506325136354</v>
       </c>
       <c r="F44">
-        <v>90.50304247160911</v>
+        <v>90.40120411245863</v>
       </c>
       <c r="G44">
-        <v>94.32811577151396</v>
+        <v>93.31499261434357</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3858,22 +3858,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>92.86734279435822</v>
+        <v>91.10993454476508</v>
       </c>
       <c r="C46">
-        <v>98.62237109481013</v>
+        <v>96.87551720889043</v>
       </c>
       <c r="D46">
-        <v>100.3085436257117</v>
+        <v>100.1769997821878</v>
       </c>
       <c r="E46">
-        <v>89.44302272585969</v>
+        <v>88.65353820228947</v>
       </c>
       <c r="F46">
-        <v>89.63303155760246</v>
+        <v>89.61956084446015</v>
       </c>
       <c r="G46">
-        <v>94.17486235966844</v>
+        <v>93.28711011651858</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3881,22 +3881,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>93.08600399896729</v>
+        <v>90.74289877000135</v>
       </c>
       <c r="C47">
-        <v>99.84825346925018</v>
+        <v>97.71788715626477</v>
       </c>
       <c r="D47">
-        <v>100.9307287772664</v>
+        <v>100.7001505848823</v>
       </c>
       <c r="E47">
-        <v>92.21947187576669</v>
+        <v>91.51690837354806</v>
       </c>
       <c r="F47">
-        <v>91.29592613104968</v>
+        <v>89.4557226091525</v>
       </c>
       <c r="G47">
-        <v>95.47607685046005</v>
+        <v>94.02671349876979</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3904,22 +3904,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>89.73341899102348</v>
+        <v>88.89834825349419</v>
       </c>
       <c r="C48">
-        <v>97.51119481579398</v>
+        <v>96.75656827501791</v>
       </c>
       <c r="D48">
-        <v>99.31239368324435</v>
+        <v>98.46320716226978</v>
       </c>
       <c r="E48">
-        <v>89.60108077810561</v>
+        <v>88.86499004755807</v>
       </c>
       <c r="F48">
-        <v>91.1329880230457</v>
+        <v>90.3710000566772</v>
       </c>
       <c r="G48">
-        <v>93.45821525824263</v>
+        <v>92.67082275900343</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3927,22 +3927,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>92.86734279435822</v>
+        <v>91.10993454476508</v>
       </c>
       <c r="C49">
-        <v>98.62237109481013</v>
+        <v>96.87551720889043</v>
       </c>
       <c r="D49">
-        <v>100.3085436257117</v>
+        <v>100.1658172160856</v>
       </c>
       <c r="E49">
-        <v>91.26310109453651</v>
+        <v>90.49970538785178</v>
       </c>
       <c r="F49">
-        <v>89.86604866666633</v>
+        <v>89.8428632552461</v>
       </c>
       <c r="G49">
-        <v>94.58548145521658</v>
+        <v>93.69876752256781</v>
       </c>
     </row>
   </sheetData>
@@ -6372,22 +6372,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>7.25</v>
+        <v>4.5</v>
       </c>
       <c r="C7">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="E7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>7.2</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -6464,22 +6464,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>4.25</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E11">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6510,22 +6510,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="D13">
-        <v>14.75</v>
+        <v>12.25</v>
       </c>
       <c r="E13">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13">
-        <v>8.550000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6579,22 +6579,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E16">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>8.1</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6694,22 +6694,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G21">
-        <v>7.6</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6717,22 +6717,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>7.25</v>
+        <v>4.75</v>
       </c>
       <c r="C22">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F22">
         <v>2</v>
       </c>
       <c r="G22">
-        <v>7.2</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6740,22 +6740,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="C23">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="D23">
-        <v>14.5</v>
+        <v>12.25</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F23">
         <v>4</v>
       </c>
       <c r="G23">
-        <v>8.550000000000001</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -6809,22 +6809,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>8.75</v>
+        <v>5.75</v>
       </c>
       <c r="C26">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="D26">
-        <v>14.75</v>
+        <v>13.5</v>
       </c>
       <c r="E26">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>9.050000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6855,22 +6855,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E28">
-        <v>8.75</v>
+        <v>6.75</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28">
-        <v>7.65</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6878,22 +6878,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D29">
-        <v>13.75</v>
+        <v>12.25</v>
       </c>
       <c r="E29">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>8.15</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6901,22 +6901,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>14.5</v>
+        <v>12.75</v>
       </c>
       <c r="E30">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="F30">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="G30">
-        <v>8.699999999999999</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6947,22 +6947,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="C32">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E32">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7016,22 +7016,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G35">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7039,22 +7039,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="C36">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="D36">
-        <v>13.5</v>
+        <v>12.25</v>
       </c>
       <c r="E36">
-        <v>8.25</v>
+        <v>4.75</v>
       </c>
       <c r="F36">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>8.6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7085,22 +7085,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>12.25</v>
       </c>
       <c r="E38">
-        <v>9.25</v>
+        <v>6.75</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G38">
-        <v>7.75</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -7108,22 +7108,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="D39">
-        <v>13.75</v>
+        <v>12.25</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39">
-        <v>8.15</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7131,22 +7131,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>8.75</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D40">
-        <v>14.5</v>
+        <v>12.75</v>
       </c>
       <c r="E40">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F40">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="G40">
-        <v>8.9</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -7177,22 +7177,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="C42">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="D42">
-        <v>14.75</v>
+        <v>13.5</v>
       </c>
       <c r="E42">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>9.050000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7200,22 +7200,22 @@
         <v>48</v>
       </c>
       <c r="B43">
+        <v>4.5</v>
+      </c>
+      <c r="C43">
         <v>7</v>
       </c>
-      <c r="C43">
-        <v>8.5</v>
-      </c>
       <c r="D43">
-        <v>14.75</v>
+        <v>12.75</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F43">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="G43">
-        <v>8.4</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7223,22 +7223,22 @@
         <v>49</v>
       </c>
       <c r="B44">
+        <v>4.75</v>
+      </c>
+      <c r="C44">
         <v>6.75</v>
       </c>
-      <c r="C44">
-        <v>9.75</v>
-      </c>
       <c r="D44">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="E44">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="F44">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>8.6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7269,22 +7269,22 @@
         <v>51</v>
       </c>
       <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46">
         <v>7</v>
       </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
       <c r="D46">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="E46">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F46">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>8.550000000000001</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7292,22 +7292,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D47">
-        <v>14.5</v>
+        <v>13.25</v>
       </c>
       <c r="E47">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="F47">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>8.6</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7315,22 +7315,22 @@
         <v>53</v>
       </c>
       <c r="B48">
+        <v>4.5</v>
+      </c>
+      <c r="C48">
         <v>7.5</v>
       </c>
-      <c r="C48">
-        <v>9</v>
-      </c>
       <c r="D48">
-        <v>14.75</v>
+        <v>12.75</v>
       </c>
       <c r="E48">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F48">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="G48">
-        <v>8.6</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7338,22 +7338,22 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
         <v>7</v>
       </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
       <c r="D49">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="E49">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="F49">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>8.699999999999999</v>
+        <v>6.95</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -572,22 +572,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.04495092499999999</v>
+        <v>0.0460137</v>
       </c>
       <c r="C2">
-        <v>0.03602815</v>
+        <v>0.037243725</v>
       </c>
       <c r="D2">
-        <v>0.030476075</v>
+        <v>0.03130615</v>
       </c>
       <c r="E2">
-        <v>0.06081697500000001</v>
+        <v>0.06314729999999999</v>
       </c>
       <c r="F2">
-        <v>0.09353719999999999</v>
+        <v>0.095351275</v>
       </c>
       <c r="G2">
-        <v>0.053161865</v>
+        <v>0.05461243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.0064005</v>
+        <v>0.006362725</v>
       </c>
       <c r="C3">
-        <v>0.006771325000000001</v>
+        <v>0.006829100000000001</v>
       </c>
       <c r="D3">
-        <v>0.005526025</v>
+        <v>0.00565735</v>
       </c>
       <c r="E3">
-        <v>0.006659575</v>
+        <v>0.006724399999999999</v>
       </c>
       <c r="F3">
-        <v>0.005015</v>
+        <v>0.005039425</v>
       </c>
       <c r="G3">
-        <v>0.006074485</v>
+        <v>0.006122600000000001</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -618,22 +618,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.010092325</v>
+        <v>0.008479225</v>
       </c>
       <c r="C4">
-        <v>0.04809945</v>
+        <v>0.04526405</v>
       </c>
       <c r="D4">
-        <v>0.01806635</v>
+        <v>0.0189611</v>
       </c>
       <c r="E4">
-        <v>0.01053475</v>
+        <v>0.0069072</v>
       </c>
       <c r="F4">
-        <v>0.007082100000000001</v>
+        <v>0.00603365</v>
       </c>
       <c r="G4">
-        <v>0.018774995</v>
+        <v>0.017129045</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,22 +641,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02438905</v>
+        <v>0.02422885</v>
       </c>
       <c r="C5">
-        <v>0.0309793</v>
+        <v>0.032410825</v>
       </c>
       <c r="D5">
-        <v>0.024755975</v>
+        <v>0.02511424999999999</v>
       </c>
       <c r="E5">
-        <v>0.03457350000000001</v>
+        <v>0.036170525</v>
       </c>
       <c r="F5">
-        <v>0.0451429</v>
+        <v>0.04625655</v>
       </c>
       <c r="G5">
-        <v>0.031968145</v>
+        <v>0.0328362</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -664,22 +664,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.004798149999999999</v>
+        <v>0.004827349999999999</v>
       </c>
       <c r="C6">
-        <v>0.00416185</v>
+        <v>0.00425435</v>
       </c>
       <c r="D6">
-        <v>0.00666415</v>
+        <v>0.006761925</v>
       </c>
       <c r="E6">
-        <v>0.00643215</v>
+        <v>0.006501525</v>
       </c>
       <c r="F6">
-        <v>0.010466575</v>
+        <v>0.010427625</v>
       </c>
       <c r="G6">
-        <v>0.006504575</v>
+        <v>0.006554555000000001</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -687,22 +687,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.04513039999999999</v>
+        <v>0.047109075</v>
       </c>
       <c r="C7">
-        <v>0.03603435</v>
+        <v>0.0377646</v>
       </c>
       <c r="D7">
-        <v>0.0311252</v>
+        <v>0.0318911</v>
       </c>
       <c r="E7">
-        <v>0.06070265000000001</v>
+        <v>0.06217297500000001</v>
       </c>
       <c r="F7">
-        <v>0.09391085000000002</v>
+        <v>0.09654549999999999</v>
       </c>
       <c r="G7">
-        <v>0.05338069000000001</v>
+        <v>0.05509665</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -710,22 +710,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.04238987499999999</v>
+        <v>0.043956075</v>
       </c>
       <c r="C8">
-        <v>0.034142625</v>
+        <v>0.03524475</v>
       </c>
       <c r="D8">
-        <v>0.02728855</v>
+        <v>0.028158175</v>
       </c>
       <c r="E8">
-        <v>0.05698795</v>
+        <v>0.0586749</v>
       </c>
       <c r="F8">
-        <v>0.09399302499999999</v>
+        <v>0.09563797499999999</v>
       </c>
       <c r="G8">
-        <v>0.050960405</v>
+        <v>0.052334375</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -733,22 +733,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.004872</v>
+        <v>0.00403035</v>
       </c>
       <c r="C9">
-        <v>0.0155931</v>
+        <v>0.0159408</v>
       </c>
       <c r="D9">
-        <v>0.006664775</v>
+        <v>0.007063625</v>
       </c>
       <c r="E9">
-        <v>0.004209424999999999</v>
+        <v>0.003768975</v>
       </c>
       <c r="F9">
-        <v>0.002743275</v>
+        <v>0.00290595</v>
       </c>
       <c r="G9">
-        <v>0.006816515</v>
+        <v>0.00674194</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -756,22 +756,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.007476375</v>
+        <v>0.007290474999999999</v>
       </c>
       <c r="C10">
-        <v>0.00807475</v>
+        <v>0.0081592</v>
       </c>
       <c r="D10">
-        <v>0.005321375</v>
+        <v>0.005459525000000001</v>
       </c>
       <c r="E10">
-        <v>0.0082272</v>
+        <v>0.008305525000000001</v>
       </c>
       <c r="F10">
-        <v>0.00680565</v>
+        <v>0.006956125000000001</v>
       </c>
       <c r="G10">
-        <v>0.00718107</v>
+        <v>0.007234170000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -779,22 +779,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.006691325000000001</v>
+        <v>0.006693625</v>
       </c>
       <c r="C11">
-        <v>0.007218599999999999</v>
+        <v>0.007111825</v>
       </c>
       <c r="D11">
-        <v>0.005733975000000001</v>
+        <v>0.005992074999999999</v>
       </c>
       <c r="E11">
-        <v>0.0069365</v>
+        <v>0.006905175</v>
       </c>
       <c r="F11">
-        <v>0.005447550000000001</v>
+        <v>0.005415375</v>
       </c>
       <c r="G11">
-        <v>0.006405590000000001</v>
+        <v>0.006423614999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -802,22 +802,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.0068519</v>
+        <v>0.006958824999999999</v>
       </c>
       <c r="C12">
-        <v>0.00731425</v>
+        <v>0.007291674999999999</v>
       </c>
       <c r="D12">
-        <v>0.005854974999999999</v>
+        <v>0.00604505</v>
       </c>
       <c r="E12">
-        <v>0.007199375</v>
+        <v>0.007211725</v>
       </c>
       <c r="F12">
-        <v>0.005277825</v>
+        <v>0.005276550000000001</v>
       </c>
       <c r="G12">
-        <v>0.006499664999999999</v>
+        <v>0.006556765000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -825,22 +825,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.01045155</v>
+        <v>0.008603425000000001</v>
       </c>
       <c r="C13">
-        <v>0.0488622</v>
+        <v>0.045884525</v>
       </c>
       <c r="D13">
-        <v>0.018292175</v>
+        <v>0.01910955</v>
       </c>
       <c r="E13">
-        <v>0.010616075</v>
+        <v>0.006978</v>
       </c>
       <c r="F13">
-        <v>0.0075686</v>
+        <v>0.006425775000000001</v>
       </c>
       <c r="G13">
-        <v>0.01915812</v>
+        <v>0.017400255</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -848,22 +848,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.010367975</v>
+        <v>0.0086344</v>
       </c>
       <c r="C14">
-        <v>0.04596152499999999</v>
+        <v>0.04447937499999999</v>
       </c>
       <c r="D14">
-        <v>0.02551215</v>
+        <v>0.018521325</v>
       </c>
       <c r="E14">
-        <v>0.009463525</v>
+        <v>0.007215874999999999</v>
       </c>
       <c r="F14">
-        <v>0.0069345</v>
+        <v>0.006591975</v>
       </c>
       <c r="G14">
-        <v>0.019647935</v>
+        <v>0.01708859</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -871,22 +871,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.01607695</v>
+        <v>0.010101175</v>
       </c>
       <c r="C15">
-        <v>0.057900125</v>
+        <v>0.04948885</v>
       </c>
       <c r="D15">
-        <v>0.018933275</v>
+        <v>0.0183353</v>
       </c>
       <c r="E15">
-        <v>0.00919625</v>
+        <v>0.008107675</v>
       </c>
       <c r="F15">
-        <v>0.019279475</v>
+        <v>0.009775600000000001</v>
       </c>
       <c r="G15">
-        <v>0.024277215</v>
+        <v>0.01916172</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -894,22 +894,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.02475495</v>
+        <v>0.024532875</v>
       </c>
       <c r="C16">
-        <v>0.03132025</v>
+        <v>0.0329486</v>
       </c>
       <c r="D16">
-        <v>0.02525645</v>
+        <v>0.0255309</v>
       </c>
       <c r="E16">
-        <v>0.0349613</v>
+        <v>0.035995875</v>
       </c>
       <c r="F16">
-        <v>0.04502727499999999</v>
+        <v>0.046478675</v>
       </c>
       <c r="G16">
-        <v>0.032264045</v>
+        <v>0.033097385</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -917,22 +917,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.025203975</v>
+        <v>0.025267675</v>
       </c>
       <c r="C17">
-        <v>0.0308002</v>
+        <v>0.0314272</v>
       </c>
       <c r="D17">
-        <v>0.0234269</v>
+        <v>0.024368875</v>
       </c>
       <c r="E17">
-        <v>0.031586725</v>
+        <v>0.0331724</v>
       </c>
       <c r="F17">
-        <v>0.041456925</v>
+        <v>0.043006475</v>
       </c>
       <c r="G17">
-        <v>0.030494945</v>
+        <v>0.031448525</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -940,22 +940,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.005503725000000001</v>
+        <v>0.005567775000000001</v>
       </c>
       <c r="C18">
-        <v>0.003759475</v>
+        <v>0.003768625</v>
       </c>
       <c r="D18">
-        <v>0.0050537</v>
+        <v>0.005111275</v>
       </c>
       <c r="E18">
-        <v>0.003605025</v>
+        <v>0.003643475</v>
       </c>
       <c r="F18">
-        <v>0.007552425</v>
+        <v>0.007524825000000001</v>
       </c>
       <c r="G18">
-        <v>0.00509487</v>
+        <v>0.005123195</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -963,22 +963,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.002771075</v>
+        <v>0.0031739</v>
       </c>
       <c r="C19">
-        <v>0.004054625</v>
+        <v>0.003989125</v>
       </c>
       <c r="D19">
-        <v>0.00252845</v>
+        <v>0.0022872</v>
       </c>
       <c r="E19">
-        <v>0.002949625</v>
+        <v>0.0021283</v>
       </c>
       <c r="F19">
-        <v>0.0052891</v>
+        <v>0.004496150000000001</v>
       </c>
       <c r="G19">
-        <v>0.003518575</v>
+        <v>0.003214935</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -986,22 +986,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004767850000000001</v>
+        <v>0.004706325</v>
       </c>
       <c r="C20">
-        <v>0.004616574999999999</v>
+        <v>0.00461575</v>
       </c>
       <c r="D20">
-        <v>0.0047845</v>
+        <v>0.004871725</v>
       </c>
       <c r="E20">
-        <v>0.0048496</v>
+        <v>0.004851225000000001</v>
       </c>
       <c r="F20">
-        <v>0.008061075000000001</v>
+        <v>0.008211949999999999</v>
       </c>
       <c r="G20">
-        <v>0.005415919999999999</v>
+        <v>0.005451395</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1009,22 +1009,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.00491875</v>
+        <v>0.0049666</v>
       </c>
       <c r="C21">
-        <v>0.00424915</v>
+        <v>0.004285975</v>
       </c>
       <c r="D21">
-        <v>0.006713525000000001</v>
+        <v>0.006827175</v>
       </c>
       <c r="E21">
-        <v>0.00655855</v>
+        <v>0.0066965</v>
       </c>
       <c r="F21">
-        <v>0.01061885</v>
+        <v>0.010546125</v>
       </c>
       <c r="G21">
-        <v>0.006611765</v>
+        <v>0.006664475</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1032,22 +1032,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.04303274999999999</v>
+        <v>0.0442347</v>
       </c>
       <c r="C22">
-        <v>0.034634825</v>
+        <v>0.035764325</v>
       </c>
       <c r="D22">
-        <v>0.027536425</v>
+        <v>0.028338375</v>
       </c>
       <c r="E22">
-        <v>0.05727599999999999</v>
+        <v>0.05903795</v>
       </c>
       <c r="F22">
-        <v>0.09369627500000001</v>
+        <v>0.097218875</v>
       </c>
       <c r="G22">
-        <v>0.051235255</v>
+        <v>0.05291884500000001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1055,22 +1055,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.0051491</v>
+        <v>0.004304400000000001</v>
       </c>
       <c r="C23">
-        <v>0.01636485</v>
+        <v>0.0158988</v>
       </c>
       <c r="D23">
-        <v>0.006863224999999999</v>
+        <v>0.007082275</v>
       </c>
       <c r="E23">
-        <v>0.004431450000000001</v>
+        <v>0.00404895</v>
       </c>
       <c r="F23">
-        <v>0.003000125</v>
+        <v>0.003194750000000001</v>
       </c>
       <c r="G23">
-        <v>0.00716175</v>
+        <v>0.006905835000000001</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1078,22 +1078,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0052407</v>
+        <v>0.0042136</v>
       </c>
       <c r="C24">
-        <v>0.016468875</v>
+        <v>0.01605125</v>
       </c>
       <c r="D24">
-        <v>0.00867045</v>
+        <v>0.007044700000000001</v>
       </c>
       <c r="E24">
-        <v>0.0044424</v>
+        <v>0.0041164</v>
       </c>
       <c r="F24">
-        <v>0.0027877</v>
+        <v>0.00314205</v>
       </c>
       <c r="G24">
-        <v>0.007522025</v>
+        <v>0.006913600000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1101,22 +1101,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.009783899999999998</v>
+        <v>0.006749049999999999</v>
       </c>
       <c r="C25">
-        <v>0.02582195</v>
+        <v>0.025034375</v>
       </c>
       <c r="D25">
-        <v>0.011564225</v>
+        <v>0.011096375</v>
       </c>
       <c r="E25">
-        <v>0.005113125</v>
+        <v>0.005204375000000001</v>
       </c>
       <c r="F25">
-        <v>0.01087075</v>
+        <v>0.004723425</v>
       </c>
       <c r="G25">
-        <v>0.01263079</v>
+        <v>0.01056152</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1124,22 +1124,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.007724999999999999</v>
+        <v>0.007572675000000001</v>
       </c>
       <c r="C26">
-        <v>0.0083131</v>
+        <v>0.008546149999999999</v>
       </c>
       <c r="D26">
-        <v>0.005540575</v>
+        <v>0.005658225</v>
       </c>
       <c r="E26">
-        <v>0.0084936</v>
+        <v>0.008509375000000001</v>
       </c>
       <c r="F26">
-        <v>0.007331525</v>
+        <v>0.00734525</v>
       </c>
       <c r="G26">
-        <v>0.00748076</v>
+        <v>0.007526334999999999</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1147,22 +1147,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.008093325</v>
+        <v>0.007833325</v>
       </c>
       <c r="C27">
-        <v>0.008559325000000001</v>
+        <v>0.008700899999999999</v>
       </c>
       <c r="D27">
-        <v>0.005566300000000001</v>
+        <v>0.005892125000000001</v>
       </c>
       <c r="E27">
-        <v>0.008343275000000001</v>
+        <v>0.008405899999999999</v>
       </c>
       <c r="F27">
-        <v>0.007203775</v>
+        <v>0.007254825</v>
       </c>
       <c r="G27">
-        <v>0.0075532</v>
+        <v>0.007617415</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1170,22 +1170,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.007160175</v>
+        <v>0.007200325</v>
       </c>
       <c r="C28">
-        <v>0.007516324999999999</v>
+        <v>0.007617899999999999</v>
       </c>
       <c r="D28">
-        <v>0.006166125</v>
+        <v>0.006241175</v>
       </c>
       <c r="E28">
-        <v>0.007366775</v>
+        <v>0.007490025000000001</v>
       </c>
       <c r="F28">
-        <v>0.005700350000000001</v>
+        <v>0.005766774999999999</v>
       </c>
       <c r="G28">
-        <v>0.006781949999999999</v>
+        <v>0.00686324</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1193,22 +1193,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.010516325</v>
+        <v>0.008827100000000001</v>
       </c>
       <c r="C29">
-        <v>0.04703395</v>
+        <v>0.045320525</v>
       </c>
       <c r="D29">
-        <v>0.02621945</v>
+        <v>0.01910895</v>
       </c>
       <c r="E29">
-        <v>0.00954205</v>
+        <v>0.007552950000000001</v>
       </c>
       <c r="F29">
-        <v>0.007421975</v>
+        <v>0.006935650000000001</v>
       </c>
       <c r="G29">
-        <v>0.02014675</v>
+        <v>0.017549035</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1216,22 +1216,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.016441825</v>
+        <v>0.01038225</v>
       </c>
       <c r="C30">
-        <v>0.05788620000000001</v>
+        <v>0.050268275</v>
       </c>
       <c r="D30">
-        <v>0.019103</v>
+        <v>0.01862715</v>
       </c>
       <c r="E30">
-        <v>0.009438599999999998</v>
+        <v>0.008213575000000001</v>
       </c>
       <c r="F30">
-        <v>0.019814875</v>
+        <v>0.010182475</v>
       </c>
       <c r="G30">
-        <v>0.0245369</v>
+        <v>0.019534745</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1239,22 +1239,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.013820225</v>
+        <v>0.0123384</v>
       </c>
       <c r="C31">
-        <v>0.05753235</v>
+        <v>0.043281225</v>
       </c>
       <c r="D31">
-        <v>0.0196674</v>
+        <v>0.018552475</v>
       </c>
       <c r="E31">
-        <v>0.008816850000000001</v>
+        <v>0.008341724999999999</v>
       </c>
       <c r="F31">
-        <v>0.01669665</v>
+        <v>0.01054165</v>
       </c>
       <c r="G31">
-        <v>0.023306695</v>
+        <v>0.018611095</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1262,22 +1262,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.02554045</v>
+        <v>0.025774</v>
       </c>
       <c r="C32">
-        <v>0.03139975</v>
+        <v>0.0320023</v>
       </c>
       <c r="D32">
-        <v>0.0236449</v>
+        <v>0.024446175</v>
       </c>
       <c r="E32">
-        <v>0.031760775</v>
+        <v>0.033374125</v>
       </c>
       <c r="F32">
-        <v>0.04162724999999999</v>
+        <v>0.043136275</v>
       </c>
       <c r="G32">
-        <v>0.030794625</v>
+        <v>0.031746575</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1285,22 +1285,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.0056144</v>
+        <v>0.005845725000000001</v>
       </c>
       <c r="C33">
-        <v>0.004153799999999999</v>
+        <v>0.003891975</v>
       </c>
       <c r="D33">
-        <v>0.003070225</v>
+        <v>0.0030917</v>
       </c>
       <c r="E33">
-        <v>0.004064725</v>
+        <v>0.003483925</v>
       </c>
       <c r="F33">
-        <v>0.008104875000000001</v>
+        <v>0.008622724999999999</v>
       </c>
       <c r="G33">
-        <v>0.005001605</v>
+        <v>0.004987210000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1308,22 +1308,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.008455724999999999</v>
+        <v>0.008765475</v>
       </c>
       <c r="C34">
-        <v>0.003913625</v>
+        <v>0.003922225000000001</v>
       </c>
       <c r="D34">
-        <v>0.003461575</v>
+        <v>0.0035071</v>
       </c>
       <c r="E34">
-        <v>0.003782225</v>
+        <v>0.003737375</v>
       </c>
       <c r="F34">
-        <v>0.0089763</v>
+        <v>0.009070375</v>
       </c>
       <c r="G34">
-        <v>0.00571789</v>
+        <v>0.00580051</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1331,22 +1331,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.005878299999999999</v>
+        <v>0.005755400000000001</v>
       </c>
       <c r="C35">
-        <v>0.00381805</v>
+        <v>0.003867675</v>
       </c>
       <c r="D35">
-        <v>0.00518875</v>
+        <v>0.0052889</v>
       </c>
       <c r="E35">
-        <v>0.00360265</v>
+        <v>0.003665575</v>
       </c>
       <c r="F35">
-        <v>0.007565350000000001</v>
+        <v>0.007701725</v>
       </c>
       <c r="G35">
-        <v>0.00521062</v>
+        <v>0.005255855</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1354,22 +1354,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.002829949999999999</v>
+        <v>0.0031857</v>
       </c>
       <c r="C36">
-        <v>0.0040699</v>
+        <v>0.00400445</v>
       </c>
       <c r="D36">
-        <v>0.002607025</v>
+        <v>0.002279425000000001</v>
       </c>
       <c r="E36">
-        <v>0.002956325</v>
+        <v>0.002247025</v>
       </c>
       <c r="F36">
-        <v>0.005150975</v>
+        <v>0.0045243</v>
       </c>
       <c r="G36">
-        <v>0.003522834999999999</v>
+        <v>0.003248180000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1377,22 +1377,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.00358465</v>
+        <v>0.003650975</v>
       </c>
       <c r="C37">
-        <v>0.0042121</v>
+        <v>0.00385745</v>
       </c>
       <c r="D37">
-        <v>0.0033971</v>
+        <v>0.003507725</v>
       </c>
       <c r="E37">
-        <v>0.002787175</v>
+        <v>0.002606525</v>
       </c>
       <c r="F37">
-        <v>0.00463045</v>
+        <v>0.00468305</v>
       </c>
       <c r="G37">
-        <v>0.003722295</v>
+        <v>0.003661145</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1400,22 +1400,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004833325</v>
+        <v>0.00485035</v>
       </c>
       <c r="C38">
-        <v>0.00463145</v>
+        <v>0.004667900000000001</v>
       </c>
       <c r="D38">
-        <v>0.004861625</v>
+        <v>0.004895725</v>
       </c>
       <c r="E38">
-        <v>0.004861375</v>
+        <v>0.00489805</v>
       </c>
       <c r="F38">
-        <v>0.00811835</v>
+        <v>0.008246425</v>
       </c>
       <c r="G38">
-        <v>0.005461225</v>
+        <v>0.00551169</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1423,22 +1423,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.00553905</v>
+        <v>0.004486325</v>
       </c>
       <c r="C39">
-        <v>0.016621725</v>
+        <v>0.0165773</v>
       </c>
       <c r="D39">
-        <v>0.008725499999999999</v>
+        <v>0.007403925</v>
       </c>
       <c r="E39">
-        <v>0.004607675</v>
+        <v>0.004338325</v>
       </c>
       <c r="F39">
-        <v>0.003043875</v>
+        <v>0.0034511</v>
       </c>
       <c r="G39">
-        <v>0.007707565</v>
+        <v>0.007251394999999999</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1446,22 +1446,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.010108025</v>
+        <v>0.007296175</v>
       </c>
       <c r="C40">
-        <v>0.02624135</v>
+        <v>0.02550535</v>
       </c>
       <c r="D40">
-        <v>0.01107915</v>
+        <v>0.0112842</v>
       </c>
       <c r="E40">
-        <v>0.0053021</v>
+        <v>0.00509355</v>
       </c>
       <c r="F40">
-        <v>0.0112927</v>
+        <v>0.0050067</v>
       </c>
       <c r="G40">
-        <v>0.012804665</v>
+        <v>0.010837195</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1469,22 +1469,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.008642149999999999</v>
+        <v>0.00823025</v>
       </c>
       <c r="C41">
-        <v>0.0261051</v>
+        <v>0.025785725</v>
       </c>
       <c r="D41">
-        <v>0.0106154</v>
+        <v>0.010390025</v>
       </c>
       <c r="E41">
-        <v>0.005131500000000001</v>
+        <v>0.005171025000000001</v>
       </c>
       <c r="F41">
-        <v>0.009022299999999999</v>
+        <v>0.0043771</v>
       </c>
       <c r="G41">
-        <v>0.01190329</v>
+        <v>0.010790825</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1492,22 +1492,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.008134124999999999</v>
+        <v>0.0080751</v>
       </c>
       <c r="C42">
-        <v>0.00882465</v>
+        <v>0.008979375</v>
       </c>
       <c r="D42">
-        <v>0.005791474999999999</v>
+        <v>0.00585915</v>
       </c>
       <c r="E42">
-        <v>0.008921100000000001</v>
+        <v>0.008786325000000001</v>
       </c>
       <c r="F42">
-        <v>0.007520674999999999</v>
+        <v>0.007717975</v>
       </c>
       <c r="G42">
-        <v>0.007838405</v>
+        <v>0.007883585000000002</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1515,22 +1515,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.0141256</v>
+        <v>0.012615575</v>
       </c>
       <c r="C43">
-        <v>0.05748179999999999</v>
+        <v>0.04353822500000001</v>
       </c>
       <c r="D43">
-        <v>0.01950055</v>
+        <v>0.01892695</v>
       </c>
       <c r="E43">
-        <v>0.009166849999999999</v>
+        <v>0.008585074999999999</v>
       </c>
       <c r="F43">
-        <v>0.016954</v>
+        <v>0.0108471</v>
       </c>
       <c r="G43">
-        <v>0.02344576</v>
+        <v>0.018902585</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1538,22 +1538,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.0055933</v>
+        <v>0.005956025</v>
       </c>
       <c r="C44">
-        <v>0.004103525</v>
+        <v>0.003871775</v>
       </c>
       <c r="D44">
-        <v>0.003165425</v>
+        <v>0.003124024999999999</v>
       </c>
       <c r="E44">
-        <v>0.004178825000000001</v>
+        <v>0.0034552</v>
       </c>
       <c r="F44">
-        <v>0.00810755</v>
+        <v>0.008599975000000001</v>
       </c>
       <c r="G44">
-        <v>0.005029725000000001</v>
+        <v>0.0050014</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1561,22 +1561,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.006123324999999999</v>
+        <v>0.0060807</v>
       </c>
       <c r="C45">
-        <v>0.00459715</v>
+        <v>0.004239224999999999</v>
       </c>
       <c r="D45">
-        <v>0.0037878</v>
+        <v>0.00390195</v>
       </c>
       <c r="E45">
-        <v>0.003869549999999999</v>
+        <v>0.003792124999999999</v>
       </c>
       <c r="F45">
-        <v>0.0084998</v>
+        <v>0.00853225</v>
       </c>
       <c r="G45">
-        <v>0.005375525000000001</v>
+        <v>0.00530925</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1584,22 +1584,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.00855885</v>
+        <v>0.008637675000000001</v>
       </c>
       <c r="C46">
-        <v>0.004022825</v>
+        <v>0.003948574999999999</v>
       </c>
       <c r="D46">
-        <v>0.003522525</v>
+        <v>0.003574725</v>
       </c>
       <c r="E46">
-        <v>0.003783225</v>
+        <v>0.003812724999999999</v>
       </c>
       <c r="F46">
-        <v>0.008915724999999999</v>
+        <v>0.009032249999999999</v>
       </c>
       <c r="G46">
-        <v>0.00576063</v>
+        <v>0.005801189999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1607,22 +1607,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.003643975</v>
+        <v>0.0037506</v>
       </c>
       <c r="C47">
-        <v>0.0042112</v>
+        <v>0.0038887</v>
       </c>
       <c r="D47">
-        <v>0.00348915</v>
+        <v>0.003555625</v>
       </c>
       <c r="E47">
-        <v>0.002819625</v>
+        <v>0.00273665</v>
       </c>
       <c r="F47">
-        <v>0.00465595</v>
+        <v>0.00476905</v>
       </c>
       <c r="G47">
-        <v>0.003763979999999999</v>
+        <v>0.003740125</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1630,22 +1630,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.008533275</v>
+        <v>0.008376499999999999</v>
       </c>
       <c r="C48">
-        <v>0.02636425</v>
+        <v>0.02608495</v>
       </c>
       <c r="D48">
-        <v>0.011042775</v>
+        <v>0.01059355</v>
       </c>
       <c r="E48">
-        <v>0.00536295</v>
+        <v>0.005475900000000001</v>
       </c>
       <c r="F48">
-        <v>0.009244024999999999</v>
+        <v>0.004670624999999999</v>
       </c>
       <c r="G48">
-        <v>0.012109455</v>
+        <v>0.011040305</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1653,22 +1653,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.006097749999999999</v>
+        <v>0.0062583</v>
       </c>
       <c r="C49">
-        <v>0.0046258</v>
+        <v>0.004242775</v>
       </c>
       <c r="D49">
-        <v>0.003862475</v>
+        <v>0.0039376</v>
       </c>
       <c r="E49">
-        <v>0.003937475</v>
+        <v>0.003961475</v>
       </c>
       <c r="F49">
-        <v>0.008391375</v>
+        <v>0.008642225</v>
       </c>
       <c r="G49">
-        <v>0.005382975</v>
+        <v>0.005408474999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1755,22 +1755,22 @@
         <v>9</v>
       </c>
       <c r="B4">
+        <v>78.75</v>
+      </c>
+      <c r="C4">
+        <v>82.5</v>
+      </c>
+      <c r="D4">
+        <v>92.25</v>
+      </c>
+      <c r="E4">
+        <v>75</v>
+      </c>
+      <c r="F4">
         <v>81.75</v>
       </c>
-      <c r="C4">
-        <v>82.75</v>
-      </c>
-      <c r="D4">
-        <v>93.75</v>
-      </c>
-      <c r="E4">
-        <v>76</v>
-      </c>
-      <c r="F4">
-        <v>86.75</v>
-      </c>
       <c r="G4">
-        <v>84.2</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1824,13 +1824,13 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1839,7 +1839,7 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>7.45</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1870,7 +1870,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>81.75</v>
+        <v>78.75</v>
       </c>
       <c r="C9">
         <v>82.5</v>
@@ -1882,10 +1882,10 @@
         <v>75</v>
       </c>
       <c r="F9">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G9">
-        <v>81.25</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1916,13 +1916,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="E11">
         <v>8.25</v>
@@ -1931,7 +1931,7 @@
         <v>4</v>
       </c>
       <c r="G11">
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1962,13 +1962,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="D13">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1977,7 +1977,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1985,22 +1985,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>81.75</v>
+        <v>78.75</v>
       </c>
       <c r="C14">
         <v>82.5</v>
       </c>
       <c r="D14">
-        <v>100.75</v>
+        <v>92.5</v>
       </c>
       <c r="E14">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="F14">
-        <v>86.25</v>
+        <v>81.5</v>
       </c>
       <c r="G14">
-        <v>85.34999999999999</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2008,22 +2008,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>83</v>
+        <v>78.75</v>
       </c>
       <c r="C15">
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="D15">
-        <v>91.5</v>
+        <v>90.25</v>
       </c>
       <c r="E15">
         <v>75.25</v>
       </c>
       <c r="F15">
-        <v>85.75</v>
+        <v>82.75</v>
       </c>
       <c r="G15">
-        <v>84.8</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2031,13 +2031,13 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="C16">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>8.5</v>
@@ -2046,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="G16">
-        <v>8.5</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2100,13 +2100,13 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="C19">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="E19">
         <v>21</v>
@@ -2115,7 +2115,7 @@
         <v>14.25</v>
       </c>
       <c r="G19">
-        <v>18.8</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2146,10 +2146,10 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="D21">
         <v>13.5</v>
@@ -2158,10 +2158,10 @@
         <v>8.5</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>8.050000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2169,13 +2169,13 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C22">
         <v>8</v>
       </c>
       <c r="D22">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2184,7 +2184,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2192,13 +2192,13 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C23">
         <v>8.5</v>
       </c>
       <c r="D23">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -2207,7 +2207,7 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2215,22 +2215,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>81.75</v>
+        <v>78.75</v>
       </c>
       <c r="C24">
         <v>82.5</v>
       </c>
       <c r="D24">
-        <v>95.75</v>
+        <v>90.25</v>
       </c>
       <c r="E24">
-        <v>75.25</v>
+        <v>75</v>
       </c>
       <c r="F24">
-        <v>75.25</v>
+        <v>75</v>
       </c>
       <c r="G24">
-        <v>82.09999999999999</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2238,22 +2238,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>83</v>
+        <v>78.75</v>
       </c>
       <c r="C25">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25">
-        <v>90.5</v>
+        <v>90.25</v>
       </c>
       <c r="E25">
         <v>75.25</v>
       </c>
       <c r="F25">
-        <v>85.75</v>
+        <v>78.25</v>
       </c>
       <c r="G25">
-        <v>84.7</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2261,22 +2261,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C26">
         <v>10.75</v>
       </c>
       <c r="D26">
-        <v>15.5</v>
+        <v>14.75</v>
       </c>
       <c r="E26">
         <v>8.5</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>9.85</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2307,13 +2307,13 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -2322,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="G28">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2330,13 +2330,13 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>8.5</v>
       </c>
       <c r="D29">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
       <c r="E29">
         <v>8.25</v>
@@ -2353,22 +2353,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="D30">
-        <v>14.75</v>
+        <v>13.75</v>
       </c>
       <c r="E30">
         <v>7.75</v>
       </c>
       <c r="F30">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="G30">
-        <v>9.050000000000001</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2376,22 +2376,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>81.75</v>
+        <v>81.5</v>
       </c>
       <c r="C31">
-        <v>88.5</v>
+        <v>82.5</v>
       </c>
       <c r="D31">
-        <v>92</v>
+        <v>90.75</v>
       </c>
       <c r="E31">
         <v>75</v>
       </c>
       <c r="F31">
-        <v>82.75</v>
+        <v>77.25</v>
       </c>
       <c r="G31">
-        <v>84</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2399,13 +2399,13 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="C32">
         <v>9.25</v>
       </c>
       <c r="D32">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E32">
         <v>8.5</v>
@@ -2414,7 +2414,7 @@
         <v>4</v>
       </c>
       <c r="G32">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2434,10 +2434,10 @@
         <v>21.75</v>
       </c>
       <c r="F33">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="G33">
-        <v>18.8</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2468,22 +2468,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="D35">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="E35">
         <v>7.75</v>
       </c>
       <c r="F35">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2491,22 +2491,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="D36">
-        <v>14.25</v>
+        <v>15</v>
       </c>
       <c r="E36">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="G36">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2523,13 +2523,13 @@
         <v>23.5</v>
       </c>
       <c r="E37">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="F37">
         <v>14.25</v>
       </c>
       <c r="G37">
-        <v>19.05</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2537,22 +2537,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="D38">
-        <v>14.25</v>
+        <v>13.5</v>
       </c>
       <c r="E38">
         <v>8.75</v>
       </c>
       <c r="F38">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2560,13 +2560,13 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C39">
         <v>8.5</v>
       </c>
       <c r="D39">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
       <c r="E39">
         <v>8.25</v>
@@ -2583,22 +2583,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C40">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>14.75</v>
+        <v>13.75</v>
       </c>
       <c r="E40">
         <v>7.75</v>
       </c>
       <c r="F40">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="G40">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2606,22 +2606,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>81.75</v>
+        <v>81.5</v>
       </c>
       <c r="C41">
-        <v>89</v>
+        <v>82.5</v>
       </c>
       <c r="D41">
-        <v>91</v>
+        <v>90.75</v>
       </c>
       <c r="E41">
         <v>75</v>
       </c>
       <c r="F41">
-        <v>81.75</v>
+        <v>75.25</v>
       </c>
       <c r="G41">
-        <v>83.7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2629,22 +2629,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="C42">
         <v>10.5</v>
       </c>
       <c r="D42">
-        <v>15.5</v>
+        <v>14.75</v>
       </c>
       <c r="E42">
         <v>8.5</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>9.9</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2655,19 +2655,19 @@
         <v>7.5</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
       <c r="E43">
         <v>7.75</v>
       </c>
       <c r="F43">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="G43">
-        <v>9.050000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2675,22 +2675,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C44">
-        <v>8.75</v>
+        <v>10.25</v>
       </c>
       <c r="D44">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="E44">
         <v>8.5</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="G44">
-        <v>8.550000000000001</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2707,10 +2707,10 @@
         <v>22.75</v>
       </c>
       <c r="E45">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="F45">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="G45">
         <v>19.35</v>
@@ -2721,22 +2721,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>14.5</v>
+        <v>13.75</v>
       </c>
       <c r="E46">
         <v>7.75</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2744,22 +2744,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="D47">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="E47">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="G47">
-        <v>9.050000000000001</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2767,22 +2767,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="C48">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="D48">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
       <c r="E48">
         <v>7.75</v>
       </c>
       <c r="F48">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="G48">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2790,22 +2790,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
       <c r="E49">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="G49">
-        <v>8.949999999999999</v>
+        <v>9.15</v>
       </c>
     </row>
   </sheetData>
@@ -2892,22 +2892,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>96.1794551983978</v>
+        <v>94.83630944789019</v>
       </c>
       <c r="C4">
-        <v>100.0789501350095</v>
+        <v>99.72539674441619</v>
       </c>
       <c r="D4">
-        <v>104.865746699413</v>
+        <v>104.6083873865323</v>
       </c>
       <c r="E4">
-        <v>93.22539674441617</v>
+        <v>92.63961030678928</v>
       </c>
       <c r="F4">
-        <v>99.10838738653231</v>
+        <v>96.17945519839779</v>
       </c>
       <c r="G4">
-        <v>98.69158723275378</v>
+        <v>97.59783181680514</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2961,13 +2961,13 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>89.13939731950015</v>
+        <v>89.25075883146134</v>
       </c>
       <c r="C7">
         <v>92.92004125279729</v>
       </c>
       <c r="D7">
-        <v>94.65664671106151</v>
+        <v>94.60065799581339</v>
       </c>
       <c r="E7">
         <v>88.12126645620715</v>
@@ -2976,7 +2976,7 @@
         <v>87.33691238960859</v>
       </c>
       <c r="G7">
-        <v>90.43485282583494</v>
+        <v>90.44592738517755</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3007,22 +3007,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>97.21498910433053</v>
+        <v>95.45762979144983</v>
       </c>
       <c r="C9">
-        <v>100.3467170879758</v>
+        <v>100.1396103067893</v>
       </c>
       <c r="D9">
-        <v>102.8761543394987</v>
+        <v>103.7045814642449</v>
       </c>
       <c r="E9">
-        <v>93.05382386916237</v>
+        <v>93.26093065034893</v>
       </c>
       <c r="F9">
-        <v>93.39696961967</v>
+        <v>92.63961030678928</v>
       </c>
       <c r="G9">
-        <v>97.37773080412748</v>
+        <v>97.04047250392445</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3053,13 +3053,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>88.81605475511716</v>
+        <v>88.92741626707834</v>
       </c>
       <c r="C11">
         <v>92.35155128758481</v>
       </c>
       <c r="D11">
-        <v>94.77232629366651</v>
+        <v>94.60476576617593</v>
       </c>
       <c r="E11">
         <v>87.44194575170043</v>
@@ -3068,7 +3068,7 @@
         <v>87.83084116930945</v>
       </c>
       <c r="G11">
-        <v>90.24254385147567</v>
+        <v>90.23130404836979</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3099,22 +3099,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>89.22701017523383</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C13">
-        <v>94.92412607931394</v>
+        <v>94.58157556205583</v>
       </c>
       <c r="D13">
-        <v>99.63732995997091</v>
+        <v>99.62978514978414</v>
       </c>
       <c r="E13">
         <v>88.58420760391871</v>
       </c>
       <c r="F13">
-        <v>90.05714420705036</v>
+        <v>89.66858848991086</v>
       </c>
       <c r="G13">
-        <v>92.48596360509755</v>
+        <v>92.31175209375547</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3122,22 +3122,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>96.1794551983978</v>
+        <v>95.04341622907673</v>
       </c>
       <c r="C14">
         <v>99.72539674441619</v>
       </c>
       <c r="D14">
-        <v>109.7946788875475</v>
+        <v>104.754833995939</v>
       </c>
       <c r="E14">
-        <v>92.93250352560273</v>
+        <v>93.05382386916239</v>
       </c>
       <c r="F14">
-        <v>98.81549416771885</v>
+        <v>96.03300858899107</v>
       </c>
       <c r="G14">
-        <v>99.48950570473662</v>
+        <v>97.72209588551706</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3145,22 +3145,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>96.91168824543144</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C15">
-        <v>101.3761543394987</v>
+        <v>102.254833995939</v>
       </c>
       <c r="D15">
-        <v>103.3406204335659</v>
+        <v>102.1941738241592</v>
       </c>
       <c r="E15">
         <v>92.3718433538229</v>
       </c>
       <c r="F15">
-        <v>100.1794551983978</v>
+        <v>97.5936687607709</v>
       </c>
       <c r="G15">
-        <v>98.83595231414336</v>
+        <v>97.76732316404181</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3168,13 +3168,13 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>88.57888496415744</v>
+        <v>88.69024647611863</v>
       </c>
       <c r="C16">
         <v>92.3043155870872</v>
       </c>
       <c r="D16">
-        <v>94.42117856929082</v>
+        <v>94.35400728794046</v>
       </c>
       <c r="E16">
         <v>86.50435909119437</v>
@@ -3183,7 +3183,7 @@
         <v>87.25337971078574</v>
       </c>
       <c r="G16">
-        <v>89.81242358450312</v>
+        <v>89.82126163062529</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3237,22 +3237,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>98.14392129246505</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C19">
-        <v>102.6941738241592</v>
+        <v>103.4264068711929</v>
       </c>
       <c r="D19">
-        <v>99.31549416771887</v>
+        <v>101.4870670429727</v>
       </c>
       <c r="E19">
-        <v>94.42209588551708</v>
+        <v>94.27564927611036</v>
       </c>
       <c r="F19">
         <v>94.27564927611036</v>
       </c>
       <c r="G19">
-        <v>97.7702668891941</v>
+        <v>97.57737367038068</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3283,22 +3283,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>91.1611041251298</v>
+        <v>92.82101084022804</v>
       </c>
       <c r="C21">
-        <v>93.72825760107301</v>
+        <v>95.27757408669811</v>
       </c>
       <c r="D21">
-        <v>98.15890054347378</v>
+        <v>97.57316238510808</v>
       </c>
       <c r="E21">
         <v>88.73381198849388</v>
       </c>
       <c r="F21">
-        <v>88.98646867694093</v>
+        <v>89.17676618598557</v>
       </c>
       <c r="G21">
-        <v>92.15370858702228</v>
+        <v>92.71646509730273</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3306,13 +3306,13 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>89.2776595859244</v>
+        <v>89.43632429655094</v>
       </c>
       <c r="C22">
         <v>92.90307720918985</v>
       </c>
       <c r="D22">
-        <v>94.41051680500189</v>
+        <v>94.35452808975376</v>
       </c>
       <c r="E22">
         <v>88.1854601545144</v>
@@ -3321,7 +3321,7 @@
         <v>87.38393931334436</v>
       </c>
       <c r="G22">
-        <v>90.43213061359498</v>
+        <v>90.45266581267066</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3329,22 +3329,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>89.22701017523383</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C23">
-        <v>94.66869395521077</v>
+        <v>94.62447041601945</v>
       </c>
       <c r="D23">
-        <v>98.53898956548846</v>
+        <v>98.89708851747093</v>
       </c>
       <c r="E23">
-        <v>88.86499004755807</v>
+        <v>88.78274546727857</v>
       </c>
       <c r="F23">
-        <v>87.85248644886262</v>
+        <v>87.83032228066719</v>
       </c>
       <c r="G23">
-        <v>91.83043403847076</v>
+        <v>91.84584606890881</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3352,22 +3352,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>96.80077554195742</v>
+        <v>95.66473657263637</v>
       </c>
       <c r="C24">
         <v>99.72539674441619</v>
       </c>
       <c r="D24">
-        <v>106.865746699413</v>
+        <v>103.6439212924651</v>
       </c>
       <c r="E24">
-        <v>93.20027047856911</v>
+        <v>93.26093065034893</v>
       </c>
       <c r="F24">
-        <v>92.3718433538229</v>
+        <v>92.43250352560273</v>
       </c>
       <c r="G24">
-        <v>97.79280656363571</v>
+        <v>96.94549775709388</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3375,22 +3375,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>97.53300858899107</v>
+        <v>95.04341622907674</v>
       </c>
       <c r="C25">
-        <v>102.4974746830583</v>
+        <v>102.4619407771256</v>
       </c>
       <c r="D25">
-        <v>102.754833995939</v>
+        <v>102.1941738241592</v>
       </c>
       <c r="E25">
-        <v>92.786056916196</v>
+        <v>92.99316369738256</v>
       </c>
       <c r="F25">
-        <v>99.35102807365161</v>
+        <v>94.75052301026329</v>
       </c>
       <c r="G25">
-        <v>98.98448045156719</v>
+        <v>97.48864350760148</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3398,22 +3398,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>88.75888657103675</v>
+        <v>88.87024808299795</v>
       </c>
       <c r="C26">
         <v>97.00780758575567</v>
       </c>
       <c r="D26">
-        <v>97.64968979182635</v>
+        <v>97.58251851047601</v>
       </c>
       <c r="E26">
         <v>88.86499004755807</v>
       </c>
       <c r="F26">
-        <v>88.62102407633546</v>
+        <v>88.53498363552973</v>
       </c>
       <c r="G26">
-        <v>92.18047961450246</v>
+        <v>92.17210957246348</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3444,13 +3444,13 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>89.12431128621597</v>
+        <v>89.2829759968425</v>
       </c>
       <c r="C28">
         <v>92.35632712783598</v>
       </c>
       <c r="D28">
-        <v>94.39401605200109</v>
+        <v>94.33802733675296</v>
       </c>
       <c r="E28">
         <v>88.88690818712263</v>
@@ -3459,7 +3459,7 @@
         <v>87.25337971078574</v>
       </c>
       <c r="G28">
-        <v>90.40298847279227</v>
+        <v>90.42352367186795</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3467,22 +3467,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>88.89834825349419</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C29">
-        <v>94.58157556205583</v>
+        <v>94.45358464300712</v>
       </c>
       <c r="D29">
-        <v>102.1853912455699</v>
+        <v>99.27552891329529</v>
       </c>
       <c r="E29">
-        <v>88.58420760391871</v>
+        <v>88.85416467479621</v>
       </c>
       <c r="F29">
-        <v>90.14531001978574</v>
+        <v>89.66858848991086</v>
       </c>
       <c r="G29">
-        <v>92.87896653696487</v>
+        <v>92.26929407682348</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3490,22 +3490,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>88.98799547445716</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C30">
-        <v>96.23340722565031</v>
+        <v>96.6764618508823</v>
       </c>
       <c r="D30">
-        <v>98.3909295861728</v>
+        <v>97.56926017986011</v>
       </c>
       <c r="E30">
-        <v>88.59805700955056</v>
+        <v>88.621334550597</v>
       </c>
       <c r="F30">
-        <v>92.13466900158528</v>
+        <v>88.77645555917422</v>
       </c>
       <c r="G30">
-        <v>92.86901165948322</v>
+        <v>92.14762316072431</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3513,22 +3513,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>96.1794551983978</v>
+        <v>96.24011537017762</v>
       </c>
       <c r="C31">
-        <v>101.3761543394987</v>
+        <v>97.44722215136416</v>
       </c>
       <c r="D31">
-        <v>104.254833995939</v>
+        <v>103.9368145112785</v>
       </c>
       <c r="E31">
         <v>92.22539674441617</v>
       </c>
       <c r="F31">
-        <v>96.97234841721126</v>
+        <v>93.75052301026327</v>
       </c>
       <c r="G31">
-        <v>98.20163773909259</v>
+        <v>96.72001435749993</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3536,13 +3536,13 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>88.57888496415744</v>
+        <v>88.69024647611863</v>
       </c>
       <c r="C32">
         <v>93.24939669889704</v>
       </c>
       <c r="D32">
-        <v>94.42117856929082</v>
+        <v>94.35400728794046</v>
       </c>
       <c r="E32">
         <v>86.50435909119437</v>
@@ -3551,7 +3551,7 @@
         <v>87.25337971078574</v>
       </c>
       <c r="G32">
-        <v>90.00143980686508</v>
+        <v>90.01027785298724</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3559,10 +3559,10 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>98.14392129246505</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C33">
-        <v>101.5477272147525</v>
+        <v>102.0477272147525</v>
       </c>
       <c r="D33">
         <v>98.81549416771887</v>
@@ -3574,7 +3574,7 @@
         <v>94.71498910433053</v>
       </c>
       <c r="G33">
-        <v>97.08950570473662</v>
+        <v>96.44514062334704</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3605,22 +3605,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>91.10993454476508</v>
+        <v>92.76984125986333</v>
       </c>
       <c r="C35">
-        <v>92.29928073650612</v>
+        <v>93.84859722213122</v>
       </c>
       <c r="D35">
-        <v>96.01541363581259</v>
+        <v>95.19327994086169</v>
       </c>
       <c r="E35">
         <v>88.86857894582849</v>
       </c>
       <c r="F35">
-        <v>87.0681506715672</v>
+        <v>87.25337971078574</v>
       </c>
       <c r="G35">
-        <v>91.07227170689589</v>
+        <v>91.58673541589408</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3628,22 +3628,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>95.43566511011795</v>
+        <v>92.40280548509956</v>
       </c>
       <c r="C36">
-        <v>99.02144924571451</v>
+        <v>101.9623159042316</v>
       </c>
       <c r="D36">
-        <v>98.52857770962854</v>
+        <v>99.87801688993142</v>
       </c>
       <c r="E36">
-        <v>88.88470486692829</v>
+        <v>88.8918485922793</v>
       </c>
       <c r="F36">
-        <v>89.4557226091525</v>
+        <v>88.53160015664891</v>
       </c>
       <c r="G36">
-        <v>94.26522390830834</v>
+        <v>94.33331740563816</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3660,13 +3660,13 @@
         <v>101.4870670429727</v>
       </c>
       <c r="E37">
-        <v>94.77564927611036</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="F37">
         <v>94.27564927611036</v>
       </c>
       <c r="G37">
-        <v>97.36021638285527</v>
+        <v>96.85016587651644</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3674,22 +3674,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>90.74289877000135</v>
+        <v>92.40280548509956</v>
       </c>
       <c r="C38">
-        <v>93.91924060669805</v>
+        <v>95.46855709232315</v>
       </c>
       <c r="D38">
-        <v>98.12554671335766</v>
+        <v>97.2064440146776</v>
       </c>
       <c r="E38">
         <v>87.00466654293592</v>
       </c>
       <c r="F38">
-        <v>88.98646867694093</v>
+        <v>89.17676618598557</v>
       </c>
       <c r="G38">
-        <v>91.75576426198678</v>
+        <v>92.25184786420435</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3697,22 +3697,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>88.89834825349419</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C39">
-        <v>94.59092271771277</v>
+        <v>94.46293179866406</v>
       </c>
       <c r="D39">
-        <v>100.8161412879935</v>
+        <v>98.47341173209446</v>
       </c>
       <c r="E39">
-        <v>88.91691119506876</v>
+        <v>88.69158843007904</v>
       </c>
       <c r="F39">
-        <v>87.85248644886262</v>
+        <v>87.90912079286227</v>
       </c>
       <c r="G39">
-        <v>92.21496198062638</v>
+        <v>91.72633128336155</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3720,22 +3720,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>89.0003034744495</v>
+        <v>89.0946036631079</v>
       </c>
       <c r="C40">
-        <v>96.75656827501791</v>
+        <v>96.7088660075274</v>
       </c>
       <c r="D40">
-        <v>98.20054813544995</v>
+        <v>97.56926017986011</v>
       </c>
       <c r="E40">
         <v>88.86499004755807</v>
       </c>
       <c r="F40">
-        <v>92.13301812599349</v>
+        <v>87.91250427174307</v>
       </c>
       <c r="G40">
-        <v>92.99108561169378</v>
+        <v>92.03004483395932</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3743,22 +3743,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>96.80077554195744</v>
+        <v>96.86143571373725</v>
       </c>
       <c r="C41">
-        <v>102.4974746830583</v>
+        <v>98.0685424949238</v>
       </c>
       <c r="D41">
-        <v>103.6690475583121</v>
+        <v>103.9368145112785</v>
       </c>
       <c r="E41">
         <v>92.63961030678928</v>
       </c>
       <c r="F41">
-        <v>96.5936687607709</v>
+        <v>92.57895013500945</v>
       </c>
       <c r="G41">
-        <v>98.44011537017761</v>
+        <v>96.81707063234765</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3766,22 +3766,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>88.97492867645308</v>
+        <v>89.08629018841425</v>
       </c>
       <c r="C42">
         <v>97.05189493017757</v>
       </c>
       <c r="D42">
-        <v>97.77020429479941</v>
+        <v>97.70303301344907</v>
       </c>
       <c r="E42">
         <v>88.86499004755807</v>
       </c>
       <c r="F42">
-        <v>88.62102407633546</v>
+        <v>88.53498363552973</v>
       </c>
       <c r="G42">
-        <v>92.25660840506472</v>
+        <v>92.24823836302575</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3789,22 +3789,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>88.89834825349419</v>
+        <v>89.33099381337391</v>
       </c>
       <c r="C43">
-        <v>96.23340722565031</v>
+        <v>92.66202135457306</v>
       </c>
       <c r="D43">
-        <v>98.65358861299265</v>
+        <v>98.58481778704089</v>
       </c>
       <c r="E43">
         <v>88.58420760391871</v>
       </c>
       <c r="F43">
-        <v>90.57933017944244</v>
+        <v>88.26865180661878</v>
       </c>
       <c r="G43">
-        <v>92.58977637509966</v>
+        <v>91.48613847310507</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3812,22 +3812,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>95.63997164837502</v>
+        <v>92.75128824484617</v>
       </c>
       <c r="C44">
-        <v>96.60137900637835</v>
+        <v>98.6431230418043</v>
       </c>
       <c r="D44">
-        <v>96.86734505314232</v>
+        <v>96.04521135819138</v>
       </c>
       <c r="E44">
-        <v>87.06506325136354</v>
+        <v>87.213712376662</v>
       </c>
       <c r="F44">
-        <v>90.40120411245863</v>
+        <v>89.88120665263305</v>
       </c>
       <c r="G44">
-        <v>93.31499261434357</v>
+        <v>92.90690833482738</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3844,13 +3844,13 @@
         <v>101.8406204335659</v>
       </c>
       <c r="E45">
-        <v>94.77564927611036</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="F45">
         <v>94.71498910433053</v>
       </c>
       <c r="G45">
-        <v>97.51879502661795</v>
+        <v>97.00874452027912</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3858,22 +3858,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>91.10993454476508</v>
+        <v>92.76984125986333</v>
       </c>
       <c r="C46">
-        <v>96.87551720889043</v>
+        <v>98.42483369451554</v>
       </c>
       <c r="D46">
-        <v>100.1769997821878</v>
+        <v>99.2578970835078</v>
       </c>
       <c r="E46">
         <v>88.65353820228947</v>
       </c>
       <c r="F46">
-        <v>89.61956084446015</v>
+        <v>88.76737542395162</v>
       </c>
       <c r="G46">
-        <v>93.28711011651858</v>
+        <v>93.57469713282555</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3881,22 +3881,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>90.74289877000135</v>
+        <v>92.40280548509956</v>
       </c>
       <c r="C47">
-        <v>97.71788715626477</v>
+        <v>99.26720364188988</v>
       </c>
       <c r="D47">
-        <v>100.7001505848823</v>
+        <v>100.6441618696342</v>
       </c>
       <c r="E47">
-        <v>91.51690837354806</v>
+        <v>89.88578193152478</v>
       </c>
       <c r="F47">
-        <v>89.4557226091525</v>
+        <v>88.53160015664891</v>
       </c>
       <c r="G47">
-        <v>94.02671349876979</v>
+        <v>94.14631061695947</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3904,22 +3904,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>88.89834825349419</v>
+        <v>89.44445095091294</v>
       </c>
       <c r="C48">
-        <v>96.75656827501791</v>
+        <v>92.70624489376438</v>
       </c>
       <c r="D48">
-        <v>98.46320716226978</v>
+        <v>98.58481778704089</v>
       </c>
       <c r="E48">
         <v>88.86499004755807</v>
       </c>
       <c r="F48">
-        <v>90.3710000566772</v>
+        <v>87.91250427174307</v>
       </c>
       <c r="G48">
-        <v>92.67082275900343</v>
+        <v>91.50260159020388</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3927,22 +3927,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>91.10993454476508</v>
+        <v>92.76984125986333</v>
       </c>
       <c r="C49">
-        <v>96.87551720889043</v>
+        <v>98.42483369451554</v>
       </c>
       <c r="D49">
-        <v>100.1658172160856</v>
+        <v>100.1098285008375</v>
       </c>
       <c r="E49">
-        <v>90.49970538785178</v>
+        <v>88.86857894582849</v>
       </c>
       <c r="F49">
-        <v>89.8428632552461</v>
+        <v>88.77213545194753</v>
       </c>
       <c r="G49">
-        <v>93.69876752256781</v>
+        <v>93.78904357059848</v>
       </c>
     </row>
   </sheetData>
@@ -4029,22 +4029,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>241.25</v>
+        <v>236.75</v>
       </c>
       <c r="C4">
-        <v>268.5</v>
+        <v>252.75</v>
       </c>
       <c r="D4">
-        <v>197.5</v>
+        <v>212.25</v>
       </c>
       <c r="E4">
-        <v>238.75</v>
+        <v>223.5</v>
       </c>
       <c r="F4">
-        <v>203.5</v>
+        <v>236.25</v>
       </c>
       <c r="G4">
-        <v>229.9</v>
+        <v>232.3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4144,22 +4144,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>289.75</v>
+        <v>272.75</v>
       </c>
       <c r="C9">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D9">
-        <v>203.75</v>
+        <v>216.5</v>
       </c>
       <c r="E9">
-        <v>281.75</v>
+        <v>287</v>
       </c>
       <c r="F9">
-        <v>228.75</v>
+        <v>265</v>
       </c>
       <c r="G9">
-        <v>253.6</v>
+        <v>260.65</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4236,22 +4236,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>241.25</v>
+        <v>236.75</v>
       </c>
       <c r="C13">
-        <v>268.5</v>
+        <v>252.75</v>
       </c>
       <c r="D13">
-        <v>197.5</v>
+        <v>212.25</v>
       </c>
       <c r="E13">
-        <v>238.75</v>
+        <v>223.5</v>
       </c>
       <c r="F13">
-        <v>203.5</v>
+        <v>236.25</v>
       </c>
       <c r="G13">
-        <v>229.9</v>
+        <v>232.3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4259,22 +4259,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>245.25</v>
+        <v>237.5</v>
       </c>
       <c r="C14">
-        <v>272.25</v>
+        <v>253</v>
       </c>
       <c r="D14">
-        <v>175.25</v>
+        <v>217.25</v>
       </c>
       <c r="E14">
-        <v>227.25</v>
+        <v>225</v>
       </c>
       <c r="F14">
-        <v>201.75</v>
+        <v>245</v>
       </c>
       <c r="G14">
-        <v>224.35</v>
+        <v>235.55</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4282,22 +4282,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>235</v>
+        <v>220.75</v>
       </c>
       <c r="C15">
-        <v>210.75</v>
+        <v>196.25</v>
       </c>
       <c r="D15">
-        <v>217.5</v>
+        <v>216.75</v>
       </c>
       <c r="E15">
-        <v>214</v>
+        <v>218.5</v>
       </c>
       <c r="F15">
-        <v>260</v>
+        <v>237.5</v>
       </c>
       <c r="G15">
-        <v>227.45</v>
+        <v>217.95</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4374,22 +4374,22 @@
         <v>24</v>
       </c>
       <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>12.75</v>
+      </c>
+      <c r="D19">
         <v>10.75</v>
       </c>
-      <c r="C19">
-        <v>13.5</v>
-      </c>
-      <c r="D19">
-        <v>11</v>
-      </c>
       <c r="E19">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="G19">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4466,22 +4466,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>289.75</v>
+        <v>272.75</v>
       </c>
       <c r="C23">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D23">
-        <v>203.75</v>
+        <v>216.5</v>
       </c>
       <c r="E23">
-        <v>281.75</v>
+        <v>287</v>
       </c>
       <c r="F23">
-        <v>228.75</v>
+        <v>265</v>
       </c>
       <c r="G23">
-        <v>253.6</v>
+        <v>260.65</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4489,22 +4489,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>281</v>
+        <v>264.25</v>
       </c>
       <c r="C24">
-        <v>237</v>
+        <v>220.75</v>
       </c>
       <c r="D24">
-        <v>202</v>
+        <v>197.25</v>
       </c>
       <c r="E24">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="F24">
-        <v>216</v>
+        <v>255.5</v>
       </c>
       <c r="G24">
-        <v>239.4</v>
+        <v>243.95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4512,22 +4512,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>285</v>
+        <v>297.75</v>
       </c>
       <c r="C25">
-        <v>207.75</v>
+        <v>207.25</v>
       </c>
       <c r="D25">
-        <v>190.75</v>
+        <v>191.25</v>
       </c>
       <c r="E25">
-        <v>245</v>
+        <v>239.5</v>
       </c>
       <c r="F25">
-        <v>261</v>
+        <v>261.75</v>
       </c>
       <c r="G25">
-        <v>237.9</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4604,22 +4604,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>245.25</v>
+        <v>237.5</v>
       </c>
       <c r="C29">
-        <v>272.25</v>
+        <v>253</v>
       </c>
       <c r="D29">
-        <v>175.25</v>
+        <v>217.25</v>
       </c>
       <c r="E29">
-        <v>227.25</v>
+        <v>225</v>
       </c>
       <c r="F29">
-        <v>201.75</v>
+        <v>245</v>
       </c>
       <c r="G29">
-        <v>224.35</v>
+        <v>235.55</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4627,22 +4627,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>235</v>
+        <v>220.75</v>
       </c>
       <c r="C30">
-        <v>210.75</v>
+        <v>196.25</v>
       </c>
       <c r="D30">
-        <v>217.5</v>
+        <v>216.75</v>
       </c>
       <c r="E30">
-        <v>214</v>
+        <v>218.5</v>
       </c>
       <c r="F30">
-        <v>260</v>
+        <v>237.5</v>
       </c>
       <c r="G30">
-        <v>227.45</v>
+        <v>217.95</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4650,22 +4650,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>240</v>
+        <v>237.5</v>
       </c>
       <c r="C31">
-        <v>223.75</v>
+        <v>221.5</v>
       </c>
       <c r="D31">
-        <v>211.5</v>
+        <v>203</v>
       </c>
       <c r="E31">
-        <v>217.5</v>
+        <v>225.75</v>
       </c>
       <c r="F31">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="G31">
-        <v>228.55</v>
+        <v>224.15</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4696,22 +4696,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="C33">
-        <v>16.25</v>
+        <v>15.75</v>
       </c>
       <c r="D33">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>19.75</v>
+        <v>18.75</v>
       </c>
       <c r="F33">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4765,22 +4765,22 @@
         <v>41</v>
       </c>
       <c r="B36">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>12.75</v>
+      </c>
+      <c r="D36">
         <v>10.75</v>
       </c>
-      <c r="C36">
-        <v>13.5</v>
-      </c>
-      <c r="D36">
-        <v>11</v>
-      </c>
       <c r="E36">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="G36">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4788,22 +4788,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="C37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D37">
         <v>14.25</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="F37">
         <v>8.25</v>
       </c>
       <c r="G37">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4834,22 +4834,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>281</v>
+        <v>264.25</v>
       </c>
       <c r="C39">
-        <v>237</v>
+        <v>220.75</v>
       </c>
       <c r="D39">
-        <v>202</v>
+        <v>197.25</v>
       </c>
       <c r="E39">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="F39">
-        <v>216</v>
+        <v>255.5</v>
       </c>
       <c r="G39">
-        <v>239.4</v>
+        <v>243.95</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4857,22 +4857,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>285</v>
+        <v>297.75</v>
       </c>
       <c r="C40">
-        <v>207.75</v>
+        <v>207.25</v>
       </c>
       <c r="D40">
-        <v>190.75</v>
+        <v>191.25</v>
       </c>
       <c r="E40">
-        <v>245</v>
+        <v>239.5</v>
       </c>
       <c r="F40">
-        <v>261</v>
+        <v>261.75</v>
       </c>
       <c r="G40">
-        <v>237.9</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4880,22 +4880,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>294.5</v>
+        <v>300.25</v>
       </c>
       <c r="C41">
-        <v>231</v>
+        <v>259.5</v>
       </c>
       <c r="D41">
-        <v>202.5</v>
+        <v>185.75</v>
       </c>
       <c r="E41">
-        <v>253.25</v>
+        <v>256.75</v>
       </c>
       <c r="F41">
-        <v>275.75</v>
+        <v>267.5</v>
       </c>
       <c r="G41">
-        <v>251.4</v>
+        <v>253.95</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4926,22 +4926,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>240</v>
+        <v>237.5</v>
       </c>
       <c r="C43">
-        <v>223.75</v>
+        <v>221.5</v>
       </c>
       <c r="D43">
-        <v>211.5</v>
+        <v>203</v>
       </c>
       <c r="E43">
-        <v>217.5</v>
+        <v>225.75</v>
       </c>
       <c r="F43">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="G43">
-        <v>228.55</v>
+        <v>224.15</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4949,22 +4949,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="C44">
-        <v>16.25</v>
+        <v>15.75</v>
       </c>
       <c r="D44">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>19.75</v>
+        <v>18.75</v>
       </c>
       <c r="F44">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="G44">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4972,10 +4972,10 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>19.5</v>
+        <v>19.75</v>
       </c>
       <c r="C45">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D45">
         <v>18.5</v>
@@ -4984,7 +4984,7 @@
         <v>23</v>
       </c>
       <c r="F45">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="G45">
         <v>18.95</v>
@@ -5018,22 +5018,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="C47">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D47">
         <v>14.25</v>
       </c>
       <c r="E47">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="F47">
         <v>8.25</v>
       </c>
       <c r="G47">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5041,22 +5041,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>294.5</v>
+        <v>300.25</v>
       </c>
       <c r="C48">
-        <v>231</v>
+        <v>259.5</v>
       </c>
       <c r="D48">
-        <v>202.5</v>
+        <v>185.75</v>
       </c>
       <c r="E48">
-        <v>253.25</v>
+        <v>256.75</v>
       </c>
       <c r="F48">
-        <v>275.75</v>
+        <v>267.5</v>
       </c>
       <c r="G48">
-        <v>251.4</v>
+        <v>253.95</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5064,10 +5064,10 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>19.5</v>
+        <v>19.75</v>
       </c>
       <c r="C49">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D49">
         <v>18.5</v>
@@ -5076,7 +5076,7 @@
         <v>23</v>
       </c>
       <c r="F49">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="G49">
         <v>18.95</v>
@@ -5166,22 +5166,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>179.25</v>
+        <v>149.75</v>
       </c>
       <c r="C4">
-        <v>703.5</v>
+        <v>646.75</v>
       </c>
       <c r="D4">
-        <v>376.25</v>
+        <v>367.75</v>
       </c>
       <c r="E4">
-        <v>200.75</v>
+        <v>136.75</v>
       </c>
       <c r="F4">
-        <v>146.5</v>
+        <v>115.5</v>
       </c>
       <c r="G4">
-        <v>321.25</v>
+        <v>283.3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5281,22 +5281,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>206.75</v>
+        <v>168.5</v>
       </c>
       <c r="C9">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="D9">
-        <v>347.75</v>
+        <v>357.25</v>
       </c>
       <c r="E9">
-        <v>203.75</v>
+        <v>187</v>
       </c>
       <c r="F9">
-        <v>122.75</v>
+        <v>131.5</v>
       </c>
       <c r="G9">
-        <v>305</v>
+        <v>291.45</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5373,22 +5373,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>179.25</v>
+        <v>149.75</v>
       </c>
       <c r="C13">
-        <v>703.5</v>
+        <v>646.75</v>
       </c>
       <c r="D13">
-        <v>376.25</v>
+        <v>367.75</v>
       </c>
       <c r="E13">
-        <v>200.75</v>
+        <v>136.75</v>
       </c>
       <c r="F13">
-        <v>146.5</v>
+        <v>115.5</v>
       </c>
       <c r="G13">
-        <v>321.25</v>
+        <v>283.3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5396,22 +5396,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>178.5</v>
+        <v>148.25</v>
       </c>
       <c r="C14">
-        <v>694</v>
+        <v>639.75</v>
       </c>
       <c r="D14">
-        <v>523.5</v>
+        <v>365.5</v>
       </c>
       <c r="E14">
-        <v>176.5</v>
+        <v>141.75</v>
       </c>
       <c r="F14">
-        <v>142.75</v>
+        <v>120</v>
       </c>
       <c r="G14">
-        <v>343.05</v>
+        <v>283.05</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5419,22 +5419,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>247.75</v>
+        <v>160.5</v>
       </c>
       <c r="C15">
-        <v>881.5</v>
+        <v>767.75</v>
       </c>
       <c r="D15">
-        <v>364</v>
+        <v>353.5</v>
       </c>
       <c r="E15">
-        <v>171.75</v>
+        <v>149.75</v>
       </c>
       <c r="F15">
-        <v>316</v>
+        <v>174</v>
       </c>
       <c r="G15">
-        <v>396.2</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5511,22 +5511,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>19.75</v>
       </c>
       <c r="C19">
-        <v>34</v>
+        <v>31.25</v>
       </c>
       <c r="D19">
-        <v>27.25</v>
+        <v>25.5</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="G19">
-        <v>24.15</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5603,22 +5603,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>206.75</v>
+        <v>168.5</v>
       </c>
       <c r="C23">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="D23">
-        <v>347.75</v>
+        <v>357.25</v>
       </c>
       <c r="E23">
-        <v>203.75</v>
+        <v>187</v>
       </c>
       <c r="F23">
-        <v>122.75</v>
+        <v>131.5</v>
       </c>
       <c r="G23">
-        <v>305</v>
+        <v>291.45</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5626,22 +5626,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>210.75</v>
+        <v>167.25</v>
       </c>
       <c r="C24">
-        <v>703.25</v>
+        <v>650</v>
       </c>
       <c r="D24">
-        <v>452.5</v>
+        <v>358.25</v>
       </c>
       <c r="E24">
-        <v>207.25</v>
+        <v>194.25</v>
       </c>
       <c r="F24">
-        <v>112.25</v>
+        <v>129.75</v>
       </c>
       <c r="G24">
-        <v>337.2</v>
+        <v>299.9</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5649,22 +5649,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>342.75</v>
+        <v>225</v>
       </c>
       <c r="C25">
-        <v>836.75</v>
+        <v>800</v>
       </c>
       <c r="D25">
-        <v>443.5</v>
+        <v>446.5</v>
       </c>
       <c r="E25">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F25">
-        <v>414.5</v>
+        <v>187.5</v>
       </c>
       <c r="G25">
-        <v>450.9</v>
+        <v>372.4</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5741,22 +5741,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>178.5</v>
+        <v>148.25</v>
       </c>
       <c r="C29">
-        <v>694</v>
+        <v>639.75</v>
       </c>
       <c r="D29">
-        <v>523.5</v>
+        <v>365.5</v>
       </c>
       <c r="E29">
-        <v>176.5</v>
+        <v>141.75</v>
       </c>
       <c r="F29">
-        <v>142.75</v>
+        <v>120</v>
       </c>
       <c r="G29">
-        <v>343.05</v>
+        <v>283.05</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5764,22 +5764,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>247.75</v>
+        <v>160.5</v>
       </c>
       <c r="C30">
-        <v>881.5</v>
+        <v>767.75</v>
       </c>
       <c r="D30">
-        <v>364</v>
+        <v>353.5</v>
       </c>
       <c r="E30">
-        <v>171.75</v>
+        <v>149.75</v>
       </c>
       <c r="F30">
-        <v>316</v>
+        <v>174</v>
       </c>
       <c r="G30">
-        <v>396.2</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5787,22 +5787,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>213.75</v>
+        <v>193</v>
       </c>
       <c r="C31">
-        <v>886.25</v>
+        <v>683.25</v>
       </c>
       <c r="D31">
-        <v>379.5</v>
+        <v>371.75</v>
       </c>
       <c r="E31">
-        <v>166</v>
+        <v>151.75</v>
       </c>
       <c r="F31">
-        <v>268</v>
+        <v>181.75</v>
       </c>
       <c r="G31">
-        <v>382.7</v>
+        <v>316.3</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5833,22 +5833,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>27</v>
+        <v>30.25</v>
       </c>
       <c r="C33">
-        <v>36.25</v>
+        <v>34.5</v>
       </c>
       <c r="D33">
         <v>27.25</v>
       </c>
       <c r="E33">
-        <v>35.5</v>
+        <v>32.25</v>
       </c>
       <c r="F33">
-        <v>22.25</v>
+        <v>21.25</v>
       </c>
       <c r="G33">
-        <v>29.65</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5902,22 +5902,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>19.75</v>
       </c>
       <c r="C36">
-        <v>34</v>
+        <v>31.25</v>
       </c>
       <c r="D36">
-        <v>27.25</v>
+        <v>25.5</v>
       </c>
       <c r="E36">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F36">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="G36">
-        <v>24.15</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5925,22 +5925,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>22</v>
+        <v>22.75</v>
       </c>
       <c r="C37">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D37">
-        <v>29.5</v>
+        <v>29.25</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="G37">
-        <v>25.1</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5971,22 +5971,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>210.75</v>
+        <v>167.25</v>
       </c>
       <c r="C39">
-        <v>703.25</v>
+        <v>650</v>
       </c>
       <c r="D39">
-        <v>452.5</v>
+        <v>358.25</v>
       </c>
       <c r="E39">
-        <v>207.25</v>
+        <v>194.25</v>
       </c>
       <c r="F39">
-        <v>112.25</v>
+        <v>129.75</v>
       </c>
       <c r="G39">
-        <v>337.2</v>
+        <v>299.9</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5994,22 +5994,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>342.75</v>
+        <v>225</v>
       </c>
       <c r="C40">
-        <v>836.75</v>
+        <v>800</v>
       </c>
       <c r="D40">
-        <v>443.5</v>
+        <v>446.5</v>
       </c>
       <c r="E40">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="F40">
-        <v>414.5</v>
+        <v>187.5</v>
       </c>
       <c r="G40">
-        <v>450.9</v>
+        <v>372.4</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6017,22 +6017,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>293.25</v>
+        <v>279.25</v>
       </c>
       <c r="C41">
-        <v>881.5</v>
+        <v>851.75</v>
       </c>
       <c r="D41">
-        <v>446.75</v>
+        <v>444.75</v>
       </c>
       <c r="E41">
-        <v>215.5</v>
+        <v>216.25</v>
       </c>
       <c r="F41">
-        <v>338.5</v>
+        <v>171</v>
       </c>
       <c r="G41">
-        <v>435.1</v>
+        <v>392.6</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6063,22 +6063,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>213.75</v>
+        <v>193</v>
       </c>
       <c r="C43">
-        <v>886.25</v>
+        <v>683.25</v>
       </c>
       <c r="D43">
-        <v>379.5</v>
+        <v>371.75</v>
       </c>
       <c r="E43">
-        <v>166</v>
+        <v>151.75</v>
       </c>
       <c r="F43">
-        <v>268</v>
+        <v>181.75</v>
       </c>
       <c r="G43">
-        <v>382.7</v>
+        <v>316.3</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6086,22 +6086,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>27</v>
+        <v>30.25</v>
       </c>
       <c r="C44">
-        <v>36.25</v>
+        <v>34.5</v>
       </c>
       <c r="D44">
         <v>27.25</v>
       </c>
       <c r="E44">
-        <v>35.5</v>
+        <v>32.25</v>
       </c>
       <c r="F44">
-        <v>22.25</v>
+        <v>21.25</v>
       </c>
       <c r="G44">
-        <v>29.65</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6109,10 +6109,10 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>31.5</v>
+        <v>32.25</v>
       </c>
       <c r="C45">
-        <v>38.25</v>
+        <v>35.75</v>
       </c>
       <c r="D45">
         <v>32.25</v>
@@ -6121,10 +6121,10 @@
         <v>33</v>
       </c>
       <c r="F45">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="G45">
-        <v>31.6</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6155,22 +6155,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>22</v>
+        <v>22.75</v>
       </c>
       <c r="C47">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D47">
-        <v>29.5</v>
+        <v>29.25</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="G47">
-        <v>25.1</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6178,22 +6178,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>293.25</v>
+        <v>279.25</v>
       </c>
       <c r="C48">
-        <v>881.5</v>
+        <v>851.75</v>
       </c>
       <c r="D48">
-        <v>446.75</v>
+        <v>444.75</v>
       </c>
       <c r="E48">
-        <v>215.5</v>
+        <v>216.25</v>
       </c>
       <c r="F48">
-        <v>338.5</v>
+        <v>171</v>
       </c>
       <c r="G48">
-        <v>435.1</v>
+        <v>392.6</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6201,10 +6201,10 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>31.5</v>
+        <v>32.25</v>
       </c>
       <c r="C49">
-        <v>38.25</v>
+        <v>35.75</v>
       </c>
       <c r="D49">
         <v>32.25</v>
@@ -6213,10 +6213,10 @@
         <v>33</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="G49">
-        <v>31.6</v>
+        <v>31.15</v>
       </c>
     </row>
   </sheetData>
@@ -6303,22 +6303,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>22.25</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
       <c r="D4">
-        <v>19.75</v>
+        <v>20.5</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="F4">
-        <v>14.25</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -6372,13 +6372,13 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -6387,7 +6387,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -6418,22 +6418,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>20.5</v>
+        <v>12.25</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="F9">
         <v>8.5</v>
       </c>
       <c r="G9">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6464,13 +6464,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C11">
         <v>7</v>
       </c>
       <c r="D11">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -6479,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6510,22 +6510,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="E13">
         <v>5.75</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6533,22 +6533,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>15.25</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>21.25</v>
       </c>
       <c r="E14">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="G14">
-        <v>14.4</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6556,22 +6556,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>15.75</v>
+        <v>11.25</v>
       </c>
       <c r="C15">
-        <v>13.5</v>
+        <v>18.75</v>
       </c>
       <c r="D15">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>12.75</v>
+        <v>14.25</v>
       </c>
       <c r="G15">
-        <v>14.85</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6579,13 +6579,13 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>7</v>
       </c>
       <c r="D16">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>6.5</v>
@@ -6594,7 +6594,7 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6651,19 +6651,19 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="D19">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="F19">
         <v>6.75</v>
       </c>
       <c r="G19">
-        <v>10.45</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6694,10 +6694,10 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D21">
         <v>11.5</v>
@@ -6706,10 +6706,10 @@
         <v>6.5</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6717,13 +6717,13 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="E22">
         <v>5.75</v>
@@ -6732,7 +6732,7 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6740,22 +6740,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C23">
         <v>6.5</v>
       </c>
       <c r="D23">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="E23">
         <v>5.75</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -6763,22 +6763,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>15.25</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>20.75</v>
       </c>
       <c r="E24">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="F24">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="G24">
-        <v>13.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6786,22 +6786,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>17.25</v>
+        <v>14.25</v>
       </c>
       <c r="C25">
-        <v>16.75</v>
+        <v>21</v>
       </c>
       <c r="D25">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="E25">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25">
-        <v>15.35</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6809,22 +6809,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="C26">
         <v>8.5</v>
       </c>
       <c r="D26">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
       <c r="E26">
         <v>5.75</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6855,13 +6855,13 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C28">
         <v>7</v>
       </c>
       <c r="D28">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="E28">
         <v>6.75</v>
@@ -6870,7 +6870,7 @@
         <v>2</v>
       </c>
       <c r="G28">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6884,16 +6884,16 @@
         <v>6.5</v>
       </c>
       <c r="D29">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="E29">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6901,22 +6901,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D30">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="E30">
         <v>5.75</v>
       </c>
       <c r="F30">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6924,22 +6924,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>15.25</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>13.5</v>
+        <v>11.75</v>
       </c>
       <c r="D31">
-        <v>22.25</v>
+        <v>19.25</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>10.75</v>
+        <v>9.75</v>
       </c>
       <c r="G31">
-        <v>14.35</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6947,13 +6947,13 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>7.25</v>
       </c>
       <c r="D32">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>6.5</v>
@@ -6962,7 +6962,7 @@
         <v>2</v>
       </c>
       <c r="G32">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6970,22 +6970,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="C33">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="D33">
         <v>13.75</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="F33">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>10.6</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7016,22 +7016,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="D35">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="E35">
         <v>5.75</v>
       </c>
       <c r="F35">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7039,22 +7039,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="D36">
-        <v>12.25</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7071,13 +7071,13 @@
         <v>15.25</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>6.75</v>
       </c>
       <c r="G37">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7085,22 +7085,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="D38">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
       <c r="E38">
         <v>6.75</v>
       </c>
       <c r="F38">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -7114,16 +7114,16 @@
         <v>6.5</v>
       </c>
       <c r="D39">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="E39">
         <v>5.75</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7131,22 +7131,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C40">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="D40">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="E40">
         <v>5.75</v>
       </c>
       <c r="F40">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>7.05</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -7154,22 +7154,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>17.25</v>
+        <v>14.5</v>
       </c>
       <c r="C41">
-        <v>16.25</v>
+        <v>13.5</v>
       </c>
       <c r="D41">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E41">
         <v>10.5</v>
       </c>
       <c r="F41">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
       <c r="G41">
-        <v>14.95</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -7177,22 +7177,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C42">
         <v>8.5</v>
       </c>
       <c r="D42">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
       <c r="E42">
         <v>5.75</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>7.6</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7200,22 +7200,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="E43">
         <v>5.75</v>
       </c>
       <c r="F43">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>6.85</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7223,22 +7223,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="C44">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="D44">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="E44">
         <v>6.5</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44">
-        <v>6.55</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7255,13 +7255,13 @@
         <v>15.75</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G45">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -7269,22 +7269,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46">
-        <v>12.5</v>
+        <v>11.75</v>
       </c>
       <c r="E46">
         <v>5.75</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7292,22 +7292,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D47">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="E47">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>7.05</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7315,22 +7315,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="E48">
         <v>5.75</v>
       </c>
       <c r="F48">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>6.95</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7338,22 +7338,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="E49">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Rekap\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9E7B02-0BDE-46F2-A245-4B52DA037BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,10 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Panjang Jalur Real'!$A$1:$G$49</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -189,8 +198,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,13 +262,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,7 +314,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -331,6 +348,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -365,9 +383,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -540,11 +559,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,1108 +586,1108 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.0460137</v>
+        <v>4.6013699999999998E-2</v>
       </c>
       <c r="C2">
-        <v>0.037243725</v>
+        <v>3.7243724999999998E-2</v>
       </c>
       <c r="D2">
-        <v>0.03130615</v>
+        <v>3.1306149999999998E-2</v>
       </c>
       <c r="E2">
-        <v>0.06314729999999999</v>
+        <v>6.314729999999999E-2</v>
       </c>
       <c r="F2">
-        <v>0.095351275</v>
+        <v>9.5351274999999999E-2</v>
       </c>
       <c r="G2">
-        <v>0.05461243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>5.4612429999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006362725</v>
+        <v>6.3627249999999996E-3</v>
       </c>
       <c r="C3">
-        <v>0.006829100000000001</v>
+        <v>6.8291000000000011E-3</v>
       </c>
       <c r="D3">
-        <v>0.00565735</v>
+        <v>5.6573500000000002E-3</v>
       </c>
       <c r="E3">
-        <v>0.006724399999999999</v>
+        <v>6.7243999999999993E-3</v>
       </c>
       <c r="F3">
-        <v>0.005039425</v>
+        <v>5.0394250000000002E-3</v>
       </c>
       <c r="G3">
-        <v>0.006122600000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>6.1226000000000006E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.008479225</v>
+        <v>8.479225E-3</v>
       </c>
       <c r="C4">
-        <v>0.04526405</v>
+        <v>4.526405E-2</v>
       </c>
       <c r="D4">
-        <v>0.0189611</v>
+        <v>1.8961100000000002E-2</v>
       </c>
       <c r="E4">
-        <v>0.0069072</v>
+        <v>6.9071999999999996E-3</v>
       </c>
       <c r="F4">
-        <v>0.00603365</v>
+        <v>6.0336499999999998E-3</v>
       </c>
       <c r="G4">
-        <v>0.017129045</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1.7129044999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.02422885</v>
+        <v>2.422885E-2</v>
       </c>
       <c r="C5">
-        <v>0.032410825</v>
+        <v>3.2410824999999997E-2</v>
       </c>
       <c r="D5">
-        <v>0.02511424999999999</v>
+        <v>2.5114249999999991E-2</v>
       </c>
       <c r="E5">
-        <v>0.036170525</v>
+        <v>3.6170525000000002E-2</v>
       </c>
       <c r="F5">
-        <v>0.04625655</v>
+        <v>4.625655E-2</v>
       </c>
       <c r="G5">
-        <v>0.0328362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>3.2836200000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.004827349999999999</v>
+        <v>4.8273499999999993E-3</v>
       </c>
       <c r="C6">
-        <v>0.00425435</v>
+        <v>4.2543499999999996E-3</v>
       </c>
       <c r="D6">
-        <v>0.006761925</v>
+        <v>6.7619250000000002E-3</v>
       </c>
       <c r="E6">
-        <v>0.006501525</v>
+        <v>6.5015250000000002E-3</v>
       </c>
       <c r="F6">
-        <v>0.010427625</v>
+        <v>1.0427624999999999E-2</v>
       </c>
       <c r="G6">
-        <v>0.006554555000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>6.554555000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.047109075</v>
+        <v>4.7109075E-2</v>
       </c>
       <c r="C7">
-        <v>0.0377646</v>
+        <v>3.7764600000000002E-2</v>
       </c>
       <c r="D7">
-        <v>0.0318911</v>
+        <v>3.1891099999999999E-2</v>
       </c>
       <c r="E7">
-        <v>0.06217297500000001</v>
+        <v>6.2172975000000012E-2</v>
       </c>
       <c r="F7">
-        <v>0.09654549999999999</v>
+        <v>9.6545499999999992E-2</v>
       </c>
       <c r="G7">
-        <v>0.05509665</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>5.5096649999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.043956075</v>
+        <v>4.3956074999999997E-2</v>
       </c>
       <c r="C8">
-        <v>0.03524475</v>
+        <v>3.5244749999999998E-2</v>
       </c>
       <c r="D8">
-        <v>0.028158175</v>
+        <v>2.8158175000000001E-2</v>
       </c>
       <c r="E8">
-        <v>0.0586749</v>
+        <v>5.8674900000000002E-2</v>
       </c>
       <c r="F8">
-        <v>0.09563797499999999</v>
+        <v>9.5637974999999986E-2</v>
       </c>
       <c r="G8">
-        <v>0.052334375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>5.2334375000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.00403035</v>
+        <v>4.0303500000000003E-3</v>
       </c>
       <c r="C9">
-        <v>0.0159408</v>
+        <v>1.5940800000000001E-2</v>
       </c>
       <c r="D9">
-        <v>0.007063625</v>
+        <v>7.0636249999999996E-3</v>
       </c>
       <c r="E9">
-        <v>0.003768975</v>
+        <v>3.7689749999999999E-3</v>
       </c>
       <c r="F9">
-        <v>0.00290595</v>
+        <v>2.90595E-3</v>
       </c>
       <c r="G9">
-        <v>0.00674194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>6.7419400000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.007290474999999999</v>
+        <v>7.2904749999999994E-3</v>
       </c>
       <c r="C10">
-        <v>0.0081592</v>
+        <v>8.1592000000000001E-3</v>
       </c>
       <c r="D10">
-        <v>0.005459525000000001</v>
+        <v>5.4595250000000007E-3</v>
       </c>
       <c r="E10">
-        <v>0.008305525000000001</v>
+        <v>8.3055250000000011E-3</v>
       </c>
       <c r="F10">
-        <v>0.006956125000000001</v>
+        <v>6.9561250000000014E-3</v>
       </c>
       <c r="G10">
-        <v>0.007234170000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>7.2341700000000007E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.006693625</v>
+        <v>6.6936249999999999E-3</v>
       </c>
       <c r="C11">
-        <v>0.007111825</v>
+        <v>7.1118249999999996E-3</v>
       </c>
       <c r="D11">
-        <v>0.005992074999999999</v>
+        <v>5.9920749999999986E-3</v>
       </c>
       <c r="E11">
-        <v>0.006905175</v>
+        <v>6.9051750000000004E-3</v>
       </c>
       <c r="F11">
-        <v>0.005415375</v>
+        <v>5.415375E-3</v>
       </c>
       <c r="G11">
-        <v>0.006423614999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>6.4236149999999988E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.006958824999999999</v>
+        <v>6.9588249999999992E-3</v>
       </c>
       <c r="C12">
-        <v>0.007291674999999999</v>
+        <v>7.2916749999999992E-3</v>
       </c>
       <c r="D12">
-        <v>0.00604505</v>
+        <v>6.0450499999999997E-3</v>
       </c>
       <c r="E12">
-        <v>0.007211725</v>
+        <v>7.2117250000000004E-3</v>
       </c>
       <c r="F12">
-        <v>0.005276550000000001</v>
+        <v>5.2765500000000014E-3</v>
       </c>
       <c r="G12">
-        <v>0.006556765000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>6.5567650000000009E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.008603425000000001</v>
+        <v>8.6034250000000013E-3</v>
       </c>
       <c r="C13">
-        <v>0.045884525</v>
+        <v>4.5884525000000002E-2</v>
       </c>
       <c r="D13">
-        <v>0.01910955</v>
+        <v>1.9109549999999999E-2</v>
       </c>
       <c r="E13">
-        <v>0.006978</v>
+        <v>6.9779999999999998E-3</v>
       </c>
       <c r="F13">
-        <v>0.006425775000000001</v>
+        <v>6.4257750000000008E-3</v>
       </c>
       <c r="G13">
-        <v>0.017400255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1.7400255E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.0086344</v>
+        <v>8.6344000000000004E-3</v>
       </c>
       <c r="C14">
-        <v>0.04447937499999999</v>
+        <v>4.4479374999999988E-2</v>
       </c>
       <c r="D14">
-        <v>0.018521325</v>
+        <v>1.8521325000000002E-2</v>
       </c>
       <c r="E14">
-        <v>0.007215874999999999</v>
+        <v>7.2158749999999992E-3</v>
       </c>
       <c r="F14">
-        <v>0.006591975</v>
+        <v>6.5919749999999999E-3</v>
       </c>
       <c r="G14">
-        <v>0.01708859</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>1.7088590000000001E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.010101175</v>
+        <v>1.0101175E-2</v>
       </c>
       <c r="C15">
-        <v>0.04948885</v>
+        <v>4.9488850000000001E-2</v>
       </c>
       <c r="D15">
-        <v>0.0183353</v>
+        <v>1.8335299999999999E-2</v>
       </c>
       <c r="E15">
-        <v>0.008107675</v>
+        <v>8.107675E-3</v>
       </c>
       <c r="F15">
-        <v>0.009775600000000001</v>
+        <v>9.7756000000000006E-3</v>
       </c>
       <c r="G15">
-        <v>0.01916172</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>1.916172E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.024532875</v>
+        <v>2.4532874999999999E-2</v>
       </c>
       <c r="C16">
-        <v>0.0329486</v>
+        <v>3.2948600000000001E-2</v>
       </c>
       <c r="D16">
-        <v>0.0255309</v>
+        <v>2.5530899999999999E-2</v>
       </c>
       <c r="E16">
-        <v>0.035995875</v>
+        <v>3.5995874999999997E-2</v>
       </c>
       <c r="F16">
-        <v>0.046478675</v>
+        <v>4.6478674999999997E-2</v>
       </c>
       <c r="G16">
-        <v>0.033097385</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>3.3097385E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.025267675</v>
+        <v>2.5267675E-2</v>
       </c>
       <c r="C17">
-        <v>0.0314272</v>
+        <v>3.1427200000000002E-2</v>
       </c>
       <c r="D17">
-        <v>0.024368875</v>
+        <v>2.4368875000000002E-2</v>
       </c>
       <c r="E17">
-        <v>0.0331724</v>
+        <v>3.3172399999999998E-2</v>
       </c>
       <c r="F17">
-        <v>0.043006475</v>
+        <v>4.3006475000000002E-2</v>
       </c>
       <c r="G17">
-        <v>0.031448525</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>3.1448524999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.005567775000000001</v>
+        <v>5.5677750000000014E-3</v>
       </c>
       <c r="C18">
-        <v>0.003768625</v>
+        <v>3.7686249999999998E-3</v>
       </c>
       <c r="D18">
-        <v>0.005111275</v>
+        <v>5.1112750000000002E-3</v>
       </c>
       <c r="E18">
-        <v>0.003643475</v>
+        <v>3.6434750000000002E-3</v>
       </c>
       <c r="F18">
-        <v>0.007524825000000001</v>
+        <v>7.5248250000000006E-3</v>
       </c>
       <c r="G18">
-        <v>0.005123195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>5.1231949999999997E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.0031739</v>
+        <v>3.1738999999999999E-3</v>
       </c>
       <c r="C19">
-        <v>0.003989125</v>
+        <v>3.9891249999999996E-3</v>
       </c>
       <c r="D19">
-        <v>0.0022872</v>
+        <v>2.2872000000000001E-3</v>
       </c>
       <c r="E19">
-        <v>0.0021283</v>
+        <v>2.1283000000000001E-3</v>
       </c>
       <c r="F19">
-        <v>0.004496150000000001</v>
+        <v>4.4961500000000008E-3</v>
       </c>
       <c r="G19">
-        <v>0.003214935</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>3.2149349999999999E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004706325</v>
+        <v>4.7063249999999999E-3</v>
       </c>
       <c r="C20">
-        <v>0.00461575</v>
+        <v>4.6157500000000001E-3</v>
       </c>
       <c r="D20">
-        <v>0.004871725</v>
+        <v>4.8717250000000004E-3</v>
       </c>
       <c r="E20">
-        <v>0.004851225000000001</v>
+        <v>4.8512250000000007E-3</v>
       </c>
       <c r="F20">
-        <v>0.008211949999999999</v>
+        <v>8.2119499999999991E-3</v>
       </c>
       <c r="G20">
-        <v>0.005451395</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>5.4513950000000004E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.0049666</v>
+        <v>4.9665999999999998E-3</v>
       </c>
       <c r="C21">
-        <v>0.004285975</v>
+        <v>4.285975E-3</v>
       </c>
       <c r="D21">
-        <v>0.006827175</v>
+        <v>6.8271750000000004E-3</v>
       </c>
       <c r="E21">
-        <v>0.0066965</v>
+        <v>6.6965000000000002E-3</v>
       </c>
       <c r="F21">
-        <v>0.010546125</v>
+        <v>1.0546125E-2</v>
       </c>
       <c r="G21">
-        <v>0.006664475</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>6.6644749999999996E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.0442347</v>
+        <v>4.4234700000000002E-2</v>
       </c>
       <c r="C22">
-        <v>0.035764325</v>
+        <v>3.5764325E-2</v>
       </c>
       <c r="D22">
-        <v>0.028338375</v>
+        <v>2.8338374999999999E-2</v>
       </c>
       <c r="E22">
-        <v>0.05903795</v>
+        <v>5.9037949999999999E-2</v>
       </c>
       <c r="F22">
-        <v>0.097218875</v>
+        <v>9.7218874999999996E-2</v>
       </c>
       <c r="G22">
-        <v>0.05291884500000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>5.2918845000000013E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.004304400000000001</v>
+        <v>4.3044000000000008E-3</v>
       </c>
       <c r="C23">
-        <v>0.0158988</v>
+        <v>1.5898800000000001E-2</v>
       </c>
       <c r="D23">
-        <v>0.007082275</v>
+        <v>7.0822749999999999E-3</v>
       </c>
       <c r="E23">
-        <v>0.00404895</v>
+        <v>4.0489499999999999E-3</v>
       </c>
       <c r="F23">
-        <v>0.003194750000000001</v>
+        <v>3.194750000000001E-3</v>
       </c>
       <c r="G23">
-        <v>0.006905835000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>6.9058350000000008E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0042136</v>
+        <v>4.2135999999999996E-3</v>
       </c>
       <c r="C24">
-        <v>0.01605125</v>
+        <v>1.605125E-2</v>
       </c>
       <c r="D24">
-        <v>0.007044700000000001</v>
+        <v>7.044700000000001E-3</v>
       </c>
       <c r="E24">
-        <v>0.0041164</v>
+        <v>4.1164000000000001E-3</v>
       </c>
       <c r="F24">
-        <v>0.00314205</v>
+        <v>3.14205E-3</v>
       </c>
       <c r="G24">
-        <v>0.006913600000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>6.9136000000000006E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.006749049999999999</v>
+        <v>6.7490499999999986E-3</v>
       </c>
       <c r="C25">
-        <v>0.025034375</v>
+        <v>2.5034375000000001E-2</v>
       </c>
       <c r="D25">
-        <v>0.011096375</v>
+        <v>1.1096375E-2</v>
       </c>
       <c r="E25">
-        <v>0.005204375000000001</v>
+        <v>5.2043750000000007E-3</v>
       </c>
       <c r="F25">
-        <v>0.004723425</v>
+        <v>4.7234249999999998E-3</v>
       </c>
       <c r="G25">
-        <v>0.01056152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>1.056152E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.007572675000000001</v>
+        <v>7.5726750000000009E-3</v>
       </c>
       <c r="C26">
-        <v>0.008546149999999999</v>
+        <v>8.5461499999999989E-3</v>
       </c>
       <c r="D26">
-        <v>0.005658225</v>
+        <v>5.6582250000000002E-3</v>
       </c>
       <c r="E26">
-        <v>0.008509375000000001</v>
+        <v>8.5093750000000013E-3</v>
       </c>
       <c r="F26">
-        <v>0.00734525</v>
+        <v>7.3452500000000002E-3</v>
       </c>
       <c r="G26">
-        <v>0.007526334999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>7.5263349999999986E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.007833325</v>
+        <v>7.8333250000000004E-3</v>
       </c>
       <c r="C27">
-        <v>0.008700899999999999</v>
+        <v>8.7008999999999993E-3</v>
       </c>
       <c r="D27">
-        <v>0.005892125000000001</v>
+        <v>5.8921250000000007E-3</v>
       </c>
       <c r="E27">
-        <v>0.008405899999999999</v>
+        <v>8.4058999999999991E-3</v>
       </c>
       <c r="F27">
-        <v>0.007254825</v>
+        <v>7.2548250000000003E-3</v>
       </c>
       <c r="G27">
-        <v>0.007617415</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>7.6174149999999998E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.007200325</v>
+        <v>7.2003249999999996E-3</v>
       </c>
       <c r="C28">
-        <v>0.007617899999999999</v>
+        <v>7.6178999999999986E-3</v>
       </c>
       <c r="D28">
-        <v>0.006241175</v>
+        <v>6.2411749999999998E-3</v>
       </c>
       <c r="E28">
-        <v>0.007490025000000001</v>
+        <v>7.4900250000000008E-3</v>
       </c>
       <c r="F28">
-        <v>0.005766774999999999</v>
+        <v>5.7667749999999992E-3</v>
       </c>
       <c r="G28">
-        <v>0.00686324</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>6.8632399999999996E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.008827100000000001</v>
+        <v>8.8271000000000009E-3</v>
       </c>
       <c r="C29">
-        <v>0.045320525</v>
+        <v>4.5320525E-2</v>
       </c>
       <c r="D29">
-        <v>0.01910895</v>
+        <v>1.910895E-2</v>
       </c>
       <c r="E29">
-        <v>0.007552950000000001</v>
+        <v>7.552950000000001E-3</v>
       </c>
       <c r="F29">
-        <v>0.006935650000000001</v>
+        <v>6.9356500000000007E-3</v>
       </c>
       <c r="G29">
-        <v>0.017549035</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>1.7549035000000001E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.01038225</v>
+        <v>1.0382250000000001E-2</v>
       </c>
       <c r="C30">
-        <v>0.050268275</v>
+        <v>5.0268275000000001E-2</v>
       </c>
       <c r="D30">
-        <v>0.01862715</v>
+        <v>1.8627149999999999E-2</v>
       </c>
       <c r="E30">
-        <v>0.008213575000000001</v>
+        <v>8.2135750000000007E-3</v>
       </c>
       <c r="F30">
-        <v>0.010182475</v>
+        <v>1.0182475E-2</v>
       </c>
       <c r="G30">
-        <v>0.019534745</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>1.9534744999999999E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.0123384</v>
+        <v>1.2338399999999999E-2</v>
       </c>
       <c r="C31">
-        <v>0.043281225</v>
+        <v>4.3281225E-2</v>
       </c>
       <c r="D31">
-        <v>0.018552475</v>
+        <v>1.8552474999999999E-2</v>
       </c>
       <c r="E31">
-        <v>0.008341724999999999</v>
+        <v>8.3417249999999995E-3</v>
       </c>
       <c r="F31">
-        <v>0.01054165</v>
+        <v>1.054165E-2</v>
       </c>
       <c r="G31">
-        <v>0.018611095</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>1.8611095000000001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.025774</v>
+        <v>2.5773999999999998E-2</v>
       </c>
       <c r="C32">
-        <v>0.0320023</v>
+        <v>3.2002299999999997E-2</v>
       </c>
       <c r="D32">
-        <v>0.024446175</v>
+        <v>2.4446175000000001E-2</v>
       </c>
       <c r="E32">
-        <v>0.033374125</v>
+        <v>3.3374124999999998E-2</v>
       </c>
       <c r="F32">
-        <v>0.043136275</v>
+        <v>4.3136275000000002E-2</v>
       </c>
       <c r="G32">
-        <v>0.031746575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>3.1746574999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.005845725000000001</v>
+        <v>5.8457250000000013E-3</v>
       </c>
       <c r="C33">
-        <v>0.003891975</v>
+        <v>3.8919750000000002E-3</v>
       </c>
       <c r="D33">
-        <v>0.0030917</v>
+        <v>3.0917000000000002E-3</v>
       </c>
       <c r="E33">
-        <v>0.003483925</v>
+        <v>3.4839250000000001E-3</v>
       </c>
       <c r="F33">
-        <v>0.008622724999999999</v>
+        <v>8.6227249999999995E-3</v>
       </c>
       <c r="G33">
-        <v>0.004987210000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>4.9872100000000006E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.008765475</v>
+        <v>8.765475E-3</v>
       </c>
       <c r="C34">
-        <v>0.003922225000000001</v>
+        <v>3.9222250000000014E-3</v>
       </c>
       <c r="D34">
-        <v>0.0035071</v>
+        <v>3.5071E-3</v>
       </c>
       <c r="E34">
-        <v>0.003737375</v>
+        <v>3.7373749999999998E-3</v>
       </c>
       <c r="F34">
-        <v>0.009070375</v>
+        <v>9.0703750000000003E-3</v>
       </c>
       <c r="G34">
-        <v>0.00580051</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>5.80051E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.005755400000000001</v>
+        <v>5.7554000000000008E-3</v>
       </c>
       <c r="C35">
-        <v>0.003867675</v>
+        <v>3.8676750000000001E-3</v>
       </c>
       <c r="D35">
-        <v>0.0052889</v>
+        <v>5.2889E-3</v>
       </c>
       <c r="E35">
-        <v>0.003665575</v>
+        <v>3.6655749999999999E-3</v>
       </c>
       <c r="F35">
-        <v>0.007701725</v>
+        <v>7.7017250000000004E-3</v>
       </c>
       <c r="G35">
-        <v>0.005255855</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>5.2558550000000002E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.0031857</v>
+        <v>3.1857000000000001E-3</v>
       </c>
       <c r="C36">
-        <v>0.00400445</v>
+        <v>4.0044499999999997E-3</v>
       </c>
       <c r="D36">
-        <v>0.002279425000000001</v>
+        <v>2.2794250000000012E-3</v>
       </c>
       <c r="E36">
-        <v>0.002247025</v>
+        <v>2.2470250000000002E-3</v>
       </c>
       <c r="F36">
-        <v>0.0045243</v>
+        <v>4.5243000000000002E-3</v>
       </c>
       <c r="G36">
-        <v>0.003248180000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>3.2481800000000011E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.003650975</v>
+        <v>3.6509749999999999E-3</v>
       </c>
       <c r="C37">
-        <v>0.00385745</v>
+        <v>3.8574500000000001E-3</v>
       </c>
       <c r="D37">
-        <v>0.003507725</v>
+        <v>3.5077250000000002E-3</v>
       </c>
       <c r="E37">
-        <v>0.002606525</v>
+        <v>2.6065250000000002E-3</v>
       </c>
       <c r="F37">
-        <v>0.00468305</v>
+        <v>4.6830500000000002E-3</v>
       </c>
       <c r="G37">
-        <v>0.003661145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>3.6611450000000002E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.00485035</v>
+        <v>4.8503499999999998E-3</v>
       </c>
       <c r="C38">
-        <v>0.004667900000000001</v>
+        <v>4.6679000000000009E-3</v>
       </c>
       <c r="D38">
-        <v>0.004895725</v>
+        <v>4.8957250000000001E-3</v>
       </c>
       <c r="E38">
-        <v>0.00489805</v>
+        <v>4.8980500000000001E-3</v>
       </c>
       <c r="F38">
-        <v>0.008246425</v>
+        <v>8.2464249999999999E-3</v>
       </c>
       <c r="G38">
-        <v>0.00551169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>5.5116899999999996E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.004486325</v>
+        <v>4.4863250000000002E-3</v>
       </c>
       <c r="C39">
-        <v>0.0165773</v>
+        <v>1.65773E-2</v>
       </c>
       <c r="D39">
-        <v>0.007403925</v>
+        <v>7.4039249999999996E-3</v>
       </c>
       <c r="E39">
-        <v>0.004338325</v>
+        <v>4.3383249999999996E-3</v>
       </c>
       <c r="F39">
-        <v>0.0034511</v>
+        <v>3.4510999999999999E-3</v>
       </c>
       <c r="G39">
-        <v>0.007251394999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>7.251394999999999E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.007296175</v>
+        <v>7.2961750000000002E-3</v>
       </c>
       <c r="C40">
-        <v>0.02550535</v>
+        <v>2.550535E-2</v>
       </c>
       <c r="D40">
-        <v>0.0112842</v>
+        <v>1.1284199999999999E-2</v>
       </c>
       <c r="E40">
-        <v>0.00509355</v>
+        <v>5.0935499999999996E-3</v>
       </c>
       <c r="F40">
-        <v>0.0050067</v>
+        <v>5.0067000000000002E-3</v>
       </c>
       <c r="G40">
-        <v>0.010837195</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>1.0837195000000001E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.00823025</v>
+        <v>8.2302499999999997E-3</v>
       </c>
       <c r="C41">
-        <v>0.025785725</v>
+        <v>2.5785724999999999E-2</v>
       </c>
       <c r="D41">
-        <v>0.010390025</v>
+        <v>1.0390025000000001E-2</v>
       </c>
       <c r="E41">
-        <v>0.005171025000000001</v>
+        <v>5.171025000000001E-3</v>
       </c>
       <c r="F41">
-        <v>0.0043771</v>
+        <v>4.3771000000000001E-3</v>
       </c>
       <c r="G41">
-        <v>0.010790825</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>1.0790825E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.0080751</v>
+        <v>8.0751E-3</v>
       </c>
       <c r="C42">
-        <v>0.008979375</v>
+        <v>8.9793749999999995E-3</v>
       </c>
       <c r="D42">
-        <v>0.00585915</v>
+        <v>5.8591499999999996E-3</v>
       </c>
       <c r="E42">
-        <v>0.008786325000000001</v>
+        <v>8.7863250000000011E-3</v>
       </c>
       <c r="F42">
-        <v>0.007717975</v>
+        <v>7.7179750000000002E-3</v>
       </c>
       <c r="G42">
-        <v>0.007883585000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>7.883585000000002E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.012615575</v>
+        <v>1.2615575E-2</v>
       </c>
       <c r="C43">
-        <v>0.04353822500000001</v>
+        <v>4.3538225000000007E-2</v>
       </c>
       <c r="D43">
-        <v>0.01892695</v>
+        <v>1.8926950000000001E-2</v>
       </c>
       <c r="E43">
-        <v>0.008585074999999999</v>
+        <v>8.5850749999999993E-3</v>
       </c>
       <c r="F43">
-        <v>0.0108471</v>
+        <v>1.08471E-2</v>
       </c>
       <c r="G43">
-        <v>0.018902585</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1.8902585E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.005956025</v>
+        <v>5.9560250000000002E-3</v>
       </c>
       <c r="C44">
-        <v>0.003871775</v>
+        <v>3.871775E-3</v>
       </c>
       <c r="D44">
-        <v>0.003124024999999999</v>
+        <v>3.124024999999999E-3</v>
       </c>
       <c r="E44">
-        <v>0.0034552</v>
+        <v>3.4551999999999999E-3</v>
       </c>
       <c r="F44">
-        <v>0.008599975000000001</v>
+        <v>8.599975000000001E-3</v>
       </c>
       <c r="G44">
-        <v>0.0050014</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>5.0013999999999996E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0060807</v>
+        <v>6.0806999999999996E-3</v>
       </c>
       <c r="C45">
-        <v>0.004239224999999999</v>
+        <v>4.2392249999999992E-3</v>
       </c>
       <c r="D45">
-        <v>0.00390195</v>
+        <v>3.9019499999999999E-3</v>
       </c>
       <c r="E45">
-        <v>0.003792124999999999</v>
+        <v>3.7921249999999991E-3</v>
       </c>
       <c r="F45">
-        <v>0.00853225</v>
+        <v>8.5322499999999999E-3</v>
       </c>
       <c r="G45">
-        <v>0.00530925</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>5.3092499999999997E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.008637675000000001</v>
+        <v>8.6376750000000009E-3</v>
       </c>
       <c r="C46">
-        <v>0.003948574999999999</v>
+        <v>3.9485749999999993E-3</v>
       </c>
       <c r="D46">
-        <v>0.003574725</v>
+        <v>3.574725E-3</v>
       </c>
       <c r="E46">
-        <v>0.003812724999999999</v>
+        <v>3.812724999999999E-3</v>
       </c>
       <c r="F46">
-        <v>0.009032249999999999</v>
+        <v>9.0322499999999986E-3</v>
       </c>
       <c r="G46">
-        <v>0.005801189999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>5.8011899999999986E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.0037506</v>
+        <v>3.7506000000000002E-3</v>
       </c>
       <c r="C47">
-        <v>0.0038887</v>
+        <v>3.8887000000000001E-3</v>
       </c>
       <c r="D47">
-        <v>0.003555625</v>
+        <v>3.5556250000000002E-3</v>
       </c>
       <c r="E47">
-        <v>0.00273665</v>
+        <v>2.7366500000000002E-3</v>
       </c>
       <c r="F47">
-        <v>0.00476905</v>
+        <v>4.7690500000000004E-3</v>
       </c>
       <c r="G47">
-        <v>0.003740125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>3.740125E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.008376499999999999</v>
+        <v>8.3764999999999985E-3</v>
       </c>
       <c r="C48">
-        <v>0.02608495</v>
+        <v>2.6084949999999999E-2</v>
       </c>
       <c r="D48">
-        <v>0.01059355</v>
+        <v>1.059355E-2</v>
       </c>
       <c r="E48">
-        <v>0.005475900000000001</v>
+        <v>5.4759000000000014E-3</v>
       </c>
       <c r="F48">
-        <v>0.004670624999999999</v>
+        <v>4.6706249999999994E-3</v>
       </c>
       <c r="G48">
-        <v>0.011040305</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>1.1040305E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.0062583</v>
+        <v>6.2582999999999996E-3</v>
       </c>
       <c r="C49">
-        <v>0.004242775</v>
+        <v>4.2427749999999998E-3</v>
       </c>
       <c r="D49">
-        <v>0.0039376</v>
+        <v>3.9376000000000003E-3</v>
       </c>
       <c r="E49">
-        <v>0.003961475</v>
+        <v>3.9614749999999999E-3</v>
       </c>
       <c r="F49">
-        <v>0.008642225</v>
+        <v>8.6422249999999999E-3</v>
       </c>
       <c r="G49">
-        <v>0.005408474999999999</v>
+        <v>5.4084749999999994E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1677,11 +1696,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1704,7 +1723,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1727,7 +1746,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1769,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1773,7 +1792,7 @@
         <v>82.05</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1796,7 +1815,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1816,10 +1835,10 @@
         <v>11.5</v>
       </c>
       <c r="G6">
-        <v>18.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>18.149999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1842,7 +1861,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1865,7 +1884,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1888,7 +1907,7 @@
         <v>80.25</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1911,7 +1930,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1934,7 +1953,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1957,7 +1976,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1980,7 +1999,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2003,7 +2022,7 @@
         <v>82.05</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2023,10 +2042,10 @@
         <v>82.75</v>
       </c>
       <c r="G15">
-        <v>83.40000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2046,10 +2065,10 @@
         <v>4</v>
       </c>
       <c r="G16">
-        <v>8.449999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2072,7 +2091,7 @@
         <v>79.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2095,7 +2114,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2118,7 +2137,7 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2141,7 +2160,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2164,7 +2183,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2187,7 +2206,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2210,7 +2229,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2233,7 +2252,7 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -2256,7 +2275,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2279,7 +2298,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -2299,10 +2318,10 @@
         <v>78.75</v>
       </c>
       <c r="G27">
-        <v>82.90000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -2325,7 +2344,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -2348,7 +2367,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -2371,7 +2390,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -2391,10 +2410,10 @@
         <v>77.25</v>
       </c>
       <c r="G31">
-        <v>81.40000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>81.400000000000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -2417,7 +2436,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2437,10 +2456,10 @@
         <v>14.5</v>
       </c>
       <c r="G33">
-        <v>18.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>18.850000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -2460,10 +2479,10 @@
         <v>15</v>
       </c>
       <c r="G34">
-        <v>19.35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>19.350000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2483,10 +2502,10 @@
         <v>4</v>
       </c>
       <c r="G35">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2509,7 +2528,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2532,7 +2551,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2555,7 +2574,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -2578,7 +2597,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2598,10 +2617,10 @@
         <v>5.75</v>
       </c>
       <c r="G40">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -2624,7 +2643,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2647,7 +2666,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -2667,10 +2686,10 @@
         <v>5.75</v>
       </c>
       <c r="G43">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -2693,7 +2712,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2713,10 +2732,10 @@
         <v>15</v>
       </c>
       <c r="G45">
-        <v>19.35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>19.350000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -2739,7 +2758,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -2762,7 +2781,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -2782,10 +2801,10 @@
         <v>5.75</v>
       </c>
       <c r="G48">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2814,11 +2833,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2841,1121 +2864,1126 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>88.690246476118631</v>
+      </c>
+      <c r="C2">
+        <v>92.304315587087203</v>
+      </c>
+      <c r="D2">
+        <v>94.354007287940462</v>
+      </c>
+      <c r="E2">
+        <v>86.504359091194374</v>
+      </c>
+      <c r="F2">
+        <v>87.253379710785737</v>
+      </c>
+      <c r="G2">
+        <v>89.821261630625287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>88.690246476118631</v>
+      </c>
+      <c r="C3">
+        <v>93.249396698897044</v>
+      </c>
+      <c r="D3">
+        <v>94.354007287940462</v>
+      </c>
+      <c r="E3">
+        <v>86.504359091194374</v>
+      </c>
+      <c r="F3">
+        <v>87.253379710785737</v>
+      </c>
+      <c r="G3">
+        <v>90.010277852987244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>88.927416267078343</v>
+      </c>
+      <c r="C4">
+        <v>92.351551287584812</v>
+      </c>
+      <c r="D4">
+        <v>94.60476576617593</v>
+      </c>
+      <c r="E4">
+        <v>87.44194575170043</v>
+      </c>
+      <c r="F4">
+        <v>87.830841169309451</v>
+      </c>
+      <c r="G4">
+        <v>90.231304048369793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>89.282975996842495</v>
+      </c>
+      <c r="C5">
+        <v>92.356327127835982</v>
+      </c>
+      <c r="D5">
+        <v>94.338027336752958</v>
+      </c>
+      <c r="E5">
+        <v>88.886908187122629</v>
+      </c>
+      <c r="F5">
+        <v>87.253379710785737</v>
+      </c>
+      <c r="G5">
+        <v>90.423523671867954</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>89.25075883146134</v>
+      </c>
+      <c r="C6">
+        <v>92.92004125279729</v>
+      </c>
+      <c r="D6">
+        <v>94.600657995813393</v>
+      </c>
+      <c r="E6">
+        <v>88.121266456207152</v>
+      </c>
+      <c r="F6">
+        <v>87.336912389608585</v>
+      </c>
+      <c r="G6">
+        <v>90.445927385177555</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7">
+        <v>89.436324296550936</v>
+      </c>
+      <c r="C7">
+        <v>92.903077209189846</v>
+      </c>
+      <c r="D7">
+        <v>94.354528089753757</v>
+      </c>
+      <c r="E7">
+        <v>88.185460154514402</v>
+      </c>
+      <c r="F7">
+        <v>87.383939313344356</v>
+      </c>
+      <c r="G7">
+        <v>90.452665812670659</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>89.330993813373908</v>
+      </c>
+      <c r="C8">
+        <v>92.662021354573056</v>
+      </c>
+      <c r="D8">
+        <v>98.58481778704089</v>
+      </c>
+      <c r="E8">
+        <v>88.584207603918713</v>
+      </c>
+      <c r="F8">
+        <v>88.268651806618777</v>
+      </c>
+      <c r="G8">
+        <v>91.486138473105072</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9">
+        <v>89.444450950912938</v>
+      </c>
+      <c r="C9">
+        <v>92.706244893764378</v>
+      </c>
+      <c r="D9">
+        <v>98.58481778704089</v>
+      </c>
+      <c r="E9">
+        <v>88.864990047558067</v>
+      </c>
+      <c r="F9">
+        <v>87.912504271743074</v>
+      </c>
+      <c r="G9">
+        <v>91.502601590203881</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>92.769841259863327</v>
+      </c>
+      <c r="C10">
+        <v>93.848597222131218</v>
+      </c>
+      <c r="D10">
+        <v>95.193279940861686</v>
+      </c>
+      <c r="E10">
+        <v>88.868578945828489</v>
+      </c>
+      <c r="F10">
+        <v>87.253379710785737</v>
+      </c>
+      <c r="G10">
+        <v>91.586735415894083</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C11">
+        <v>94.462931798664059</v>
+      </c>
+      <c r="D11">
+        <v>98.473411732094462</v>
+      </c>
+      <c r="E11">
+        <v>88.691588430079037</v>
+      </c>
+      <c r="F11">
+        <v>87.909120792862268</v>
+      </c>
+      <c r="G11">
+        <v>91.726331283361546</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C12">
+        <v>94.624470416019449</v>
+      </c>
+      <c r="D12">
+        <v>98.897088517470934</v>
+      </c>
+      <c r="E12">
+        <v>88.782745467278573</v>
+      </c>
+      <c r="F12">
+        <v>87.83032228066719</v>
+      </c>
+      <c r="G12">
+        <v>91.845846068908813</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C13">
+        <v>96.708866007527405</v>
+      </c>
+      <c r="D13">
+        <v>97.569260179860109</v>
+      </c>
+      <c r="E13">
+        <v>88.864990047558067</v>
+      </c>
+      <c r="F13">
+        <v>87.912504271743074</v>
+      </c>
+      <c r="G13">
+        <v>92.030044833959323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C14">
+        <v>96.676461850882305</v>
+      </c>
+      <c r="D14">
+        <v>97.569260179860109</v>
+      </c>
+      <c r="E14">
+        <v>88.621334550596998</v>
+      </c>
+      <c r="F14">
+        <v>88.776455559174224</v>
+      </c>
+      <c r="G14">
+        <v>92.147623160724308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>88.870248082997946</v>
+      </c>
+      <c r="C15">
+        <v>97.007807585755671</v>
+      </c>
+      <c r="D15">
+        <v>97.582518510476007</v>
+      </c>
+      <c r="E15">
+        <v>88.864990047558067</v>
+      </c>
+      <c r="F15">
+        <v>88.534983635529727</v>
+      </c>
+      <c r="G15">
+        <v>92.172109572463484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16">
+        <v>89.086290188414253</v>
+      </c>
+      <c r="C16">
+        <v>97.051894930177568</v>
+      </c>
+      <c r="D16">
+        <v>97.703033013449073</v>
+      </c>
+      <c r="E16">
+        <v>88.864990047558067</v>
+      </c>
+      <c r="F16">
+        <v>88.534983635529727</v>
+      </c>
+      <c r="G16">
+        <v>92.248238363025749</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17">
+        <v>92.402805485099563</v>
+      </c>
+      <c r="C17">
+        <v>95.468557092323152</v>
+      </c>
+      <c r="D17">
+        <v>97.206444014677601</v>
+      </c>
+      <c r="E17">
+        <v>87.004666542935922</v>
+      </c>
+      <c r="F17">
+        <v>89.176766185985571</v>
+      </c>
+      <c r="G17">
+        <v>92.25184786420435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C18">
+        <v>94.453584643007119</v>
+      </c>
+      <c r="D18">
+        <v>99.27552891329529</v>
+      </c>
+      <c r="E18">
+        <v>88.854164674796209</v>
+      </c>
+      <c r="F18">
+        <v>89.66858848991086</v>
+      </c>
+      <c r="G18">
+        <v>92.269294076823485</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>89.094603663107904</v>
+      </c>
+      <c r="C19">
+        <v>94.581575562055832</v>
+      </c>
+      <c r="D19">
+        <v>99.629785149784141</v>
+      </c>
+      <c r="E19">
+        <v>88.584207603918713</v>
+      </c>
+      <c r="F19">
+        <v>89.66858848991086</v>
+      </c>
+      <c r="G19">
+        <v>92.311752093755473</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
+        <v>92.821010840228041</v>
+      </c>
+      <c r="C20">
+        <v>95.27757408669811</v>
+      </c>
+      <c r="D20">
+        <v>97.573162385108077</v>
+      </c>
+      <c r="E20">
+        <v>88.733811988493883</v>
+      </c>
+      <c r="F20">
+        <v>89.176766185985571</v>
+      </c>
+      <c r="G20">
+        <v>92.716465097302731</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21">
+        <v>92.751288244846165</v>
+      </c>
+      <c r="C21">
+        <v>98.643123041804301</v>
+      </c>
+      <c r="D21">
+        <v>96.045211358191381</v>
+      </c>
+      <c r="E21">
+        <v>87.213712376662002</v>
+      </c>
+      <c r="F21">
+        <v>89.881206652633054</v>
+      </c>
+      <c r="G21">
+        <v>92.906908334827378</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>92.769841259863327</v>
+      </c>
+      <c r="C22">
+        <v>98.424833694515542</v>
+      </c>
+      <c r="D22">
+        <v>99.2578970835078</v>
+      </c>
+      <c r="E22">
+        <v>88.653538202289468</v>
+      </c>
+      <c r="F22">
+        <v>88.76737542395162</v>
+      </c>
+      <c r="G22">
+        <v>93.574697132825548</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23">
+        <v>92.769841259863327</v>
+      </c>
+      <c r="C23">
+        <v>98.424833694515542</v>
+      </c>
+      <c r="D23">
+        <v>100.10982850083749</v>
+      </c>
+      <c r="E23">
+        <v>88.868578945828489</v>
+      </c>
+      <c r="F23">
+        <v>88.772135451947534</v>
+      </c>
+      <c r="G23">
+        <v>93.78904357059848</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24">
+        <v>92.402805485099563</v>
+      </c>
+      <c r="C24">
+        <v>99.267203641889878</v>
+      </c>
+      <c r="D24">
+        <v>100.6441618696342</v>
+      </c>
+      <c r="E24">
+        <v>89.885781931524775</v>
+      </c>
+      <c r="F24">
+        <v>88.531600156648906</v>
+      </c>
+      <c r="G24">
+        <v>94.146310616959468</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25">
+        <v>92.402805485099563</v>
+      </c>
+      <c r="C25">
+        <v>101.9623159042316</v>
+      </c>
+      <c r="D25">
+        <v>99.878016889931416</v>
+      </c>
+      <c r="E25">
+        <v>88.891848592279302</v>
+      </c>
+      <c r="F25">
+        <v>88.531600156648906</v>
+      </c>
+      <c r="G25">
+        <v>94.333317405638155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C2">
-        <v>97.44722215136416</v>
-      </c>
-      <c r="D2">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E2">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F2">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G2">
-        <v>94.58778131046631</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B26">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C26">
+        <v>97.447222151364159</v>
+      </c>
+      <c r="D26">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E26">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F26">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G26">
+        <v>94.587781310466312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C27">
+        <v>97.447222151364159</v>
+      </c>
+      <c r="D27">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E27">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F27">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G27">
+        <v>94.587781310466312</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C28">
+        <v>97.447222151364144</v>
+      </c>
+      <c r="D28">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E28">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F28">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G28">
+        <v>94.587781310466312</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C29">
+        <v>97.447222151364159</v>
+      </c>
+      <c r="D29">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E29">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F29">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G29">
+        <v>94.587781310466312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C30">
+        <v>97.447222151364144</v>
+      </c>
+      <c r="D30">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E30">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F30">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G30">
+        <v>94.587781310466312</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C31">
+        <v>97.593668760770868</v>
+      </c>
+      <c r="D31">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E31">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F31">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G31">
+        <v>94.617070632347648</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C32">
+        <v>98.325901807804513</v>
+      </c>
+      <c r="D32">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E32">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F32">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G32">
+        <v>94.763517241754386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>94.836309447890187</v>
+      </c>
+      <c r="C33">
+        <v>98.068542494923804</v>
+      </c>
+      <c r="D33">
+        <v>99.229707730091974</v>
+      </c>
+      <c r="E33">
+        <v>93.053823869162386</v>
+      </c>
+      <c r="F33">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G33">
+        <v>95.043416229076726</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
-        <v>94.83630944789019</v>
-      </c>
-      <c r="C3">
-        <v>98.27564927611034</v>
-      </c>
-      <c r="D3">
-        <v>99.4368145112785</v>
-      </c>
-      <c r="E3">
-        <v>93.05382386916239</v>
-      </c>
-      <c r="F3">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G3">
-        <v>95.12625894155136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="B34">
+        <v>94.836309447890187</v>
+      </c>
+      <c r="C34">
+        <v>98.275649276110343</v>
+      </c>
+      <c r="D34">
+        <v>99.436814511278499</v>
+      </c>
+      <c r="E34">
+        <v>93.053823869162386</v>
+      </c>
+      <c r="F34">
+        <v>90.028697603315294</v>
+      </c>
+      <c r="G34">
+        <v>95.126258941551356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C35">
+        <v>102.0477272147525</v>
+      </c>
+      <c r="D35">
+        <v>98.815494167718867</v>
+      </c>
+      <c r="E35">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F35">
+        <v>94.714989104330527</v>
+      </c>
+      <c r="G35">
+        <v>96.445140623347044</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>96.24011537017762</v>
+      </c>
+      <c r="C36">
+        <v>97.447222151364159</v>
+      </c>
+      <c r="D36">
+        <v>103.9368145112785</v>
+      </c>
+      <c r="E36">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F36">
+        <v>93.750523010263265</v>
+      </c>
+      <c r="G36">
+        <v>96.720014357499934</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
+        <v>96.861435713737251</v>
+      </c>
+      <c r="C37">
+        <v>98.068542494923804</v>
+      </c>
+      <c r="D37">
+        <v>103.9368145112785</v>
+      </c>
+      <c r="E37">
+        <v>92.63961030678928</v>
+      </c>
+      <c r="F37">
+        <v>92.57895013500945</v>
+      </c>
+      <c r="G37">
+        <v>96.817070632347651</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C38">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="D38">
+        <v>101.4870670429727</v>
+      </c>
+      <c r="E38">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F38">
+        <v>94.275649276110357</v>
+      </c>
+      <c r="G38">
+        <v>96.850165876516442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39">
+        <v>95.664736572636372</v>
+      </c>
+      <c r="C39">
+        <v>99.725396744416187</v>
+      </c>
+      <c r="D39">
+        <v>103.64392129246509</v>
+      </c>
+      <c r="E39">
+        <v>93.260930650348925</v>
+      </c>
+      <c r="F39">
+        <v>92.432503525602726</v>
+      </c>
+      <c r="G39">
+        <v>96.945497757093875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C40">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="D40">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="E40">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F40">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="G40">
+        <v>96.950165876516422</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C41">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="D41">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="E41">
+        <v>92.225396744416173</v>
+      </c>
+      <c r="F41">
+        <v>94.714989104330527</v>
+      </c>
+      <c r="G41">
+        <v>97.008744520279123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42">
+        <v>95.457629791449833</v>
+      </c>
+      <c r="C42">
+        <v>100.13961030678929</v>
+      </c>
+      <c r="D42">
+        <v>103.7045814642449</v>
+      </c>
+      <c r="E42">
+        <v>93.260930650348925</v>
+      </c>
+      <c r="F42">
+        <v>92.63961030678928</v>
+      </c>
+      <c r="G42">
+        <v>97.040472503924448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43">
+        <v>95.007882323143988</v>
+      </c>
+      <c r="C43">
+        <v>102.6690475583121</v>
+      </c>
+      <c r="D43">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="E43">
+        <v>93.053823869162386</v>
+      </c>
+      <c r="F43">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="G43">
+        <v>97.398694013940286</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44">
+        <v>95.04341622907674</v>
+      </c>
+      <c r="C44">
+        <v>102.4619407771256</v>
+      </c>
+      <c r="D44">
+        <v>102.19417382415919</v>
+      </c>
+      <c r="E44">
+        <v>92.993163697382556</v>
+      </c>
+      <c r="F44">
+        <v>94.750523010263294</v>
+      </c>
+      <c r="G44">
+        <v>97.488643507601481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="C45">
+        <v>103.4264068711929</v>
+      </c>
+      <c r="D45">
+        <v>101.4870670429727</v>
+      </c>
+      <c r="E45">
+        <v>94.275649276110357</v>
+      </c>
+      <c r="F45">
+        <v>94.275649276110357</v>
+      </c>
+      <c r="G45">
+        <v>97.57737367038068</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>94.83630944789019</v>
-      </c>
-      <c r="C4">
-        <v>99.72539674441619</v>
-      </c>
-      <c r="D4">
+      <c r="B46">
+        <v>94.836309447890187</v>
+      </c>
+      <c r="C46">
+        <v>99.725396744416187</v>
+      </c>
+      <c r="D46">
         <v>104.6083873865323</v>
       </c>
-      <c r="E4">
+      <c r="E46">
         <v>92.63961030678928</v>
       </c>
-      <c r="F4">
+      <c r="F46">
         <v>96.17945519839779</v>
       </c>
-      <c r="G4">
+      <c r="G46">
         <v>97.59783181680514</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C5">
-        <v>97.44722215136416</v>
-      </c>
-      <c r="D5">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E5">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F5">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G5">
-        <v>94.58778131046631</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C6">
-        <v>97.44722215136414</v>
-      </c>
-      <c r="D6">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E6">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F6">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G6">
-        <v>94.58778131046631</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>89.25075883146134</v>
-      </c>
-      <c r="C7">
-        <v>92.92004125279729</v>
-      </c>
-      <c r="D7">
-        <v>94.60065799581339</v>
-      </c>
-      <c r="E7">
-        <v>88.12126645620715</v>
-      </c>
-      <c r="F7">
-        <v>87.33691238960859</v>
-      </c>
-      <c r="G7">
-        <v>90.44592738517755</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C8">
-        <v>97.44722215136416</v>
-      </c>
-      <c r="D8">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E8">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F8">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G8">
-        <v>94.58778131046631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>95.45762979144983</v>
-      </c>
-      <c r="C9">
-        <v>100.1396103067893</v>
-      </c>
-      <c r="D9">
-        <v>103.7045814642449</v>
-      </c>
-      <c r="E9">
-        <v>93.26093065034893</v>
-      </c>
-      <c r="F9">
-        <v>92.63961030678928</v>
-      </c>
-      <c r="G9">
-        <v>97.04047250392445</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>95.00788232314399</v>
-      </c>
-      <c r="C10">
-        <v>102.6690475583121</v>
-      </c>
-      <c r="D10">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="E10">
-        <v>93.05382386916239</v>
-      </c>
-      <c r="F10">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="G10">
-        <v>97.39869401394029</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>88.92741626707834</v>
-      </c>
-      <c r="C11">
-        <v>92.35155128758481</v>
-      </c>
-      <c r="D11">
-        <v>94.60476576617593</v>
-      </c>
-      <c r="E11">
-        <v>87.44194575170043</v>
-      </c>
-      <c r="F11">
-        <v>87.83084116930945</v>
-      </c>
-      <c r="G11">
-        <v>90.23130404836979</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>94.83630944789019</v>
-      </c>
-      <c r="C12">
-        <v>98.0685424949238</v>
-      </c>
-      <c r="D12">
-        <v>99.22970773009197</v>
-      </c>
-      <c r="E12">
-        <v>93.05382386916239</v>
-      </c>
-      <c r="F12">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G12">
-        <v>95.04341622907673</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C13">
-        <v>94.58157556205583</v>
-      </c>
-      <c r="D13">
-        <v>99.62978514978414</v>
-      </c>
-      <c r="E13">
-        <v>88.58420760391871</v>
-      </c>
-      <c r="F13">
-        <v>89.66858848991086</v>
-      </c>
-      <c r="G13">
-        <v>92.31175209375547</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47">
+        <v>96.007882323143974</v>
+      </c>
+      <c r="C47">
+        <v>102.4619407771256</v>
+      </c>
+      <c r="D47">
+        <v>102.25483399593899</v>
+      </c>
+      <c r="E47">
+        <v>93.053823869162386</v>
+      </c>
+      <c r="F47">
+        <v>94.422095885517081</v>
+      </c>
+      <c r="G47">
+        <v>97.640115370177611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>19</v>
       </c>
-      <c r="B14">
-        <v>95.04341622907673</v>
-      </c>
-      <c r="C14">
-        <v>99.72539674441619</v>
-      </c>
-      <c r="D14">
-        <v>104.754833995939</v>
-      </c>
-      <c r="E14">
-        <v>93.05382386916239</v>
-      </c>
-      <c r="F14">
-        <v>96.03300858899107</v>
-      </c>
-      <c r="G14">
-        <v>97.72209588551706</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="B48">
+        <v>95.043416229076726</v>
+      </c>
+      <c r="C48">
+        <v>99.725396744416187</v>
+      </c>
+      <c r="D48">
+        <v>104.75483399593899</v>
+      </c>
+      <c r="E48">
+        <v>93.053823869162386</v>
+      </c>
+      <c r="F48">
+        <v>96.033008588991066</v>
+      </c>
+      <c r="G48">
+        <v>97.722095885517064</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>20</v>
       </c>
-      <c r="B15">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C15">
-        <v>102.254833995939</v>
-      </c>
-      <c r="D15">
-        <v>102.1941738241592</v>
-      </c>
-      <c r="E15">
-        <v>92.3718433538229</v>
-      </c>
-      <c r="F15">
-        <v>97.5936687607709</v>
-      </c>
-      <c r="G15">
-        <v>97.76732316404181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>88.69024647611863</v>
-      </c>
-      <c r="C16">
-        <v>92.3043155870872</v>
-      </c>
-      <c r="D16">
-        <v>94.35400728794046</v>
-      </c>
-      <c r="E16">
-        <v>86.50435909119437</v>
-      </c>
-      <c r="F16">
-        <v>87.25337971078574</v>
-      </c>
-      <c r="G16">
-        <v>89.82126163062529</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C17">
-        <v>98.32590180780451</v>
-      </c>
-      <c r="D17">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E17">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F17">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G17">
-        <v>94.76351724175439</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C18">
-        <v>97.44722215136414</v>
-      </c>
-      <c r="D18">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E18">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F18">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G18">
-        <v>94.58778131046631</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C19">
-        <v>103.4264068711929</v>
-      </c>
-      <c r="D19">
-        <v>101.4870670429727</v>
-      </c>
-      <c r="E19">
-        <v>94.27564927611036</v>
-      </c>
-      <c r="F19">
-        <v>94.27564927611036</v>
-      </c>
-      <c r="G19">
-        <v>97.57737367038068</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C20">
-        <v>97.59366876077087</v>
-      </c>
-      <c r="D20">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E20">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F20">
-        <v>90.02869760331529</v>
-      </c>
-      <c r="G20">
-        <v>94.61707063234765</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>92.82101084022804</v>
-      </c>
-      <c r="C21">
-        <v>95.27757408669811</v>
-      </c>
-      <c r="D21">
-        <v>97.57316238510808</v>
-      </c>
-      <c r="E21">
-        <v>88.73381198849388</v>
-      </c>
-      <c r="F21">
-        <v>89.17676618598557</v>
-      </c>
-      <c r="G21">
-        <v>92.71646509730273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22">
-        <v>89.43632429655094</v>
-      </c>
-      <c r="C22">
-        <v>92.90307720918985</v>
-      </c>
-      <c r="D22">
-        <v>94.35452808975376</v>
-      </c>
-      <c r="E22">
-        <v>88.1854601545144</v>
-      </c>
-      <c r="F22">
-        <v>87.38393931334436</v>
-      </c>
-      <c r="G22">
-        <v>90.45266581267066</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C23">
-        <v>94.62447041601945</v>
-      </c>
-      <c r="D23">
-        <v>98.89708851747093</v>
-      </c>
-      <c r="E23">
-        <v>88.78274546727857</v>
-      </c>
-      <c r="F23">
-        <v>87.83032228066719</v>
-      </c>
-      <c r="G23">
-        <v>91.84584606890881</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24">
-        <v>95.66473657263637</v>
-      </c>
-      <c r="C24">
-        <v>99.72539674441619</v>
-      </c>
-      <c r="D24">
-        <v>103.6439212924651</v>
-      </c>
-      <c r="E24">
-        <v>93.26093065034893</v>
-      </c>
-      <c r="F24">
-        <v>92.43250352560273</v>
-      </c>
-      <c r="G24">
-        <v>96.94549775709388</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25">
-        <v>95.04341622907674</v>
-      </c>
-      <c r="C25">
-        <v>102.4619407771256</v>
-      </c>
-      <c r="D25">
-        <v>102.1941738241592</v>
-      </c>
-      <c r="E25">
-        <v>92.99316369738256</v>
-      </c>
-      <c r="F25">
-        <v>94.75052301026329</v>
-      </c>
-      <c r="G25">
-        <v>97.48864350760148</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26">
-        <v>88.87024808299795</v>
-      </c>
-      <c r="C26">
-        <v>97.00780758575567</v>
-      </c>
-      <c r="D26">
-        <v>97.58251851047601</v>
-      </c>
-      <c r="E26">
-        <v>88.86499004755807</v>
-      </c>
-      <c r="F26">
-        <v>88.53498363552973</v>
-      </c>
-      <c r="G26">
-        <v>92.17210957246348</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27">
-        <v>96.00788232314397</v>
-      </c>
-      <c r="C27">
-        <v>102.4619407771256</v>
-      </c>
-      <c r="D27">
-        <v>102.254833995939</v>
-      </c>
-      <c r="E27">
-        <v>93.05382386916239</v>
-      </c>
-      <c r="F27">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="G27">
-        <v>97.64011537017761</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28">
-        <v>89.2829759968425</v>
-      </c>
-      <c r="C28">
-        <v>92.35632712783598</v>
-      </c>
-      <c r="D28">
-        <v>94.33802733675296</v>
-      </c>
-      <c r="E28">
-        <v>88.88690818712263</v>
-      </c>
-      <c r="F28">
-        <v>87.25337971078574</v>
-      </c>
-      <c r="G28">
-        <v>90.42352367186795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C29">
-        <v>94.45358464300712</v>
-      </c>
-      <c r="D29">
-        <v>99.27552891329529</v>
-      </c>
-      <c r="E29">
-        <v>88.85416467479621</v>
-      </c>
-      <c r="F29">
-        <v>89.66858848991086</v>
-      </c>
-      <c r="G29">
-        <v>92.26929407682348</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C30">
-        <v>96.6764618508823</v>
-      </c>
-      <c r="D30">
-        <v>97.56926017986011</v>
-      </c>
-      <c r="E30">
-        <v>88.621334550597</v>
-      </c>
-      <c r="F30">
-        <v>88.77645555917422</v>
-      </c>
-      <c r="G30">
-        <v>92.14762316072431</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31">
-        <v>96.24011537017762</v>
-      </c>
-      <c r="C31">
-        <v>97.44722215136416</v>
-      </c>
-      <c r="D31">
-        <v>103.9368145112785</v>
-      </c>
-      <c r="E31">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F31">
-        <v>93.75052301026327</v>
-      </c>
-      <c r="G31">
-        <v>96.72001435749993</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32">
-        <v>88.69024647611863</v>
-      </c>
-      <c r="C32">
-        <v>93.24939669889704</v>
-      </c>
-      <c r="D32">
-        <v>94.35400728794046</v>
-      </c>
-      <c r="E32">
-        <v>86.50435909119437</v>
-      </c>
-      <c r="F32">
-        <v>87.25337971078574</v>
-      </c>
-      <c r="G32">
-        <v>90.01027785298724</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C33">
-        <v>102.0477272147525</v>
-      </c>
-      <c r="D33">
-        <v>98.81549416771887</v>
-      </c>
-      <c r="E33">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F33">
-        <v>94.71498910433053</v>
-      </c>
-      <c r="G33">
-        <v>96.44514062334704</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C34">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="D34">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="E34">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F34">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="G34">
-        <v>96.95016587651642</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35">
-        <v>92.76984125986333</v>
-      </c>
-      <c r="C35">
-        <v>93.84859722213122</v>
-      </c>
-      <c r="D35">
-        <v>95.19327994086169</v>
-      </c>
-      <c r="E35">
-        <v>88.86857894582849</v>
-      </c>
-      <c r="F35">
-        <v>87.25337971078574</v>
-      </c>
-      <c r="G35">
-        <v>91.58673541589408</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36">
-        <v>92.40280548509956</v>
-      </c>
-      <c r="C36">
-        <v>101.9623159042316</v>
-      </c>
-      <c r="D36">
-        <v>99.87801688993142</v>
-      </c>
-      <c r="E36">
-        <v>88.8918485922793</v>
-      </c>
-      <c r="F36">
-        <v>88.53160015664891</v>
-      </c>
-      <c r="G36">
-        <v>94.33331740563816</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C37">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="D37">
-        <v>101.4870670429727</v>
-      </c>
-      <c r="E37">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F37">
-        <v>94.27564927611036</v>
-      </c>
-      <c r="G37">
-        <v>96.85016587651644</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38">
-        <v>92.40280548509956</v>
-      </c>
-      <c r="C38">
-        <v>95.46855709232315</v>
-      </c>
-      <c r="D38">
-        <v>97.2064440146776</v>
-      </c>
-      <c r="E38">
-        <v>87.00466654293592</v>
-      </c>
-      <c r="F38">
-        <v>89.17676618598557</v>
-      </c>
-      <c r="G38">
-        <v>92.25184786420435</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C39">
-        <v>94.46293179866406</v>
-      </c>
-      <c r="D39">
-        <v>98.47341173209446</v>
-      </c>
-      <c r="E39">
-        <v>88.69158843007904</v>
-      </c>
-      <c r="F39">
-        <v>87.90912079286227</v>
-      </c>
-      <c r="G39">
-        <v>91.72633128336155</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40">
-        <v>89.0946036631079</v>
-      </c>
-      <c r="C40">
-        <v>96.7088660075274</v>
-      </c>
-      <c r="D40">
-        <v>97.56926017986011</v>
-      </c>
-      <c r="E40">
-        <v>88.86499004755807</v>
-      </c>
-      <c r="F40">
-        <v>87.91250427174307</v>
-      </c>
-      <c r="G40">
-        <v>92.03004483395932</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41">
-        <v>96.86143571373725</v>
-      </c>
-      <c r="C41">
-        <v>98.0685424949238</v>
-      </c>
-      <c r="D41">
-        <v>103.9368145112785</v>
-      </c>
-      <c r="E41">
-        <v>92.63961030678928</v>
-      </c>
-      <c r="F41">
-        <v>92.57895013500945</v>
-      </c>
-      <c r="G41">
-        <v>96.81707063234765</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42">
-        <v>89.08629018841425</v>
-      </c>
-      <c r="C42">
-        <v>97.05189493017757</v>
-      </c>
-      <c r="D42">
-        <v>97.70303301344907</v>
-      </c>
-      <c r="E42">
-        <v>88.86499004755807</v>
-      </c>
-      <c r="F42">
-        <v>88.53498363552973</v>
-      </c>
-      <c r="G42">
-        <v>92.24823836302575</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43">
-        <v>89.33099381337391</v>
-      </c>
-      <c r="C43">
-        <v>92.66202135457306</v>
-      </c>
-      <c r="D43">
-        <v>98.58481778704089</v>
-      </c>
-      <c r="E43">
-        <v>88.58420760391871</v>
-      </c>
-      <c r="F43">
-        <v>88.26865180661878</v>
-      </c>
-      <c r="G43">
-        <v>91.48613847310507</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44">
-        <v>92.75128824484617</v>
-      </c>
-      <c r="C44">
-        <v>98.6431230418043</v>
-      </c>
-      <c r="D44">
-        <v>96.04521135819138</v>
-      </c>
-      <c r="E44">
-        <v>87.213712376662</v>
-      </c>
-      <c r="F44">
-        <v>89.88120665263305</v>
-      </c>
-      <c r="G44">
-        <v>92.90690833482738</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45">
-        <v>94.42209588551708</v>
-      </c>
-      <c r="C45">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="D45">
-        <v>101.8406204335659</v>
-      </c>
-      <c r="E45">
-        <v>92.22539674441617</v>
-      </c>
-      <c r="F45">
-        <v>94.71498910433053</v>
-      </c>
-      <c r="G45">
-        <v>97.00874452027912</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46">
-        <v>92.76984125986333</v>
-      </c>
-      <c r="C46">
-        <v>98.42483369451554</v>
-      </c>
-      <c r="D46">
-        <v>99.2578970835078</v>
-      </c>
-      <c r="E46">
-        <v>88.65353820228947</v>
-      </c>
-      <c r="F46">
-        <v>88.76737542395162</v>
-      </c>
-      <c r="G46">
-        <v>93.57469713282555</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47">
-        <v>92.40280548509956</v>
-      </c>
-      <c r="C47">
-        <v>99.26720364188988</v>
-      </c>
-      <c r="D47">
-        <v>100.6441618696342</v>
-      </c>
-      <c r="E47">
-        <v>89.88578193152478</v>
-      </c>
-      <c r="F47">
-        <v>88.53160015664891</v>
-      </c>
-      <c r="G47">
-        <v>94.14631061695947</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48">
-        <v>89.44445095091294</v>
-      </c>
-      <c r="C48">
-        <v>92.70624489376438</v>
-      </c>
-      <c r="D48">
-        <v>98.58481778704089</v>
-      </c>
-      <c r="E48">
-        <v>88.86499004755807</v>
-      </c>
-      <c r="F48">
-        <v>87.91250427174307</v>
-      </c>
-      <c r="G48">
-        <v>91.50260159020388</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
-        <v>54</v>
-      </c>
       <c r="B49">
-        <v>92.76984125986333</v>
+        <v>94.422095885517081</v>
       </c>
       <c r="C49">
-        <v>98.42483369451554</v>
+        <v>102.25483399593899</v>
       </c>
       <c r="D49">
-        <v>100.1098285008375</v>
+        <v>102.19417382415919</v>
       </c>
       <c r="E49">
-        <v>88.86857894582849</v>
+        <v>92.371843353822896</v>
       </c>
       <c r="F49">
-        <v>88.77213545194753</v>
+        <v>97.593668760770896</v>
       </c>
       <c r="G49">
-        <v>93.78904357059848</v>
+        <v>97.767323164041812</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G49" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G49">
+      <sortCondition ref="G1:G49"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3978,7 +4006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4001,7 +4029,7 @@
         <v>263.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4024,7 +4052,7 @@
         <v>326.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4047,7 +4075,7 @@
         <v>232.3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4070,7 +4098,7 @@
         <v>252.35</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4093,7 +4121,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4116,7 +4144,7 @@
         <v>263.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -4139,7 +4167,7 @@
         <v>225.55</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4159,10 +4187,10 @@
         <v>265</v>
       </c>
       <c r="G9">
-        <v>260.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>260.64999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -4185,7 +4213,7 @@
         <v>235.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4208,7 +4236,7 @@
         <v>326.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4231,7 +4259,7 @@
         <v>262.45</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4254,7 +4282,7 @@
         <v>232.3</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -4277,7 +4305,7 @@
         <v>235.55</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -4300,7 +4328,7 @@
         <v>217.95</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -4323,7 +4351,7 @@
         <v>252.35</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -4343,10 +4371,10 @@
         <v>406.25</v>
       </c>
       <c r="G17">
-        <v>270.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>270.85000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4369,7 +4397,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -4392,7 +4420,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -4415,7 +4443,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -4438,7 +4466,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -4461,7 +4489,7 @@
         <v>225.55</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -4481,10 +4509,10 @@
         <v>265</v>
       </c>
       <c r="G23">
-        <v>260.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>260.64999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4507,7 +4535,7 @@
         <v>243.95</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -4530,7 +4558,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -4553,7 +4581,7 @@
         <v>235.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -4576,7 +4604,7 @@
         <v>237.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -4599,7 +4627,7 @@
         <v>262.45</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -4622,7 +4650,7 @@
         <v>235.55</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -4645,7 +4673,7 @@
         <v>217.95</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -4668,7 +4696,7 @@
         <v>224.15</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -4688,10 +4716,10 @@
         <v>406.25</v>
       </c>
       <c r="G32">
-        <v>270.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>270.85000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -4714,7 +4742,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -4737,7 +4765,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -4760,7 +4788,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -4783,7 +4811,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4806,7 +4834,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -4829,7 +4857,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -4852,7 +4880,7 @@
         <v>243.95</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -4875,7 +4903,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -4898,7 +4926,7 @@
         <v>253.95</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -4921,7 +4949,7 @@
         <v>237.25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -4944,7 +4972,7 @@
         <v>224.15</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -4967,7 +4995,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -4990,7 +5018,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -5013,7 +5041,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -5036,7 +5064,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -5059,7 +5087,7 @@
         <v>253.95</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -5088,11 +5116,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5115,7 +5143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5138,7 +5166,7 @@
         <v>1440.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5161,7 +5189,7 @@
         <v>1056.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5184,7 +5212,7 @@
         <v>283.3</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -5207,7 +5235,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -5230,7 +5258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5253,7 +5281,7 @@
         <v>1440.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5276,7 +5304,7 @@
         <v>1475.9</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -5299,7 +5327,7 @@
         <v>291.45</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -5322,7 +5350,7 @@
         <v>850.55</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5345,7 +5373,7 @@
         <v>1056.7</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -5368,7 +5396,7 @@
         <v>1026.55</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -5391,7 +5419,7 @@
         <v>283.3</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -5414,7 +5442,7 @@
         <v>283.05</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -5434,10 +5462,10 @@
         <v>174</v>
       </c>
       <c r="G15">
-        <v>321.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>321.10000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -5460,7 +5488,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -5483,7 +5511,7 @@
         <v>909.3</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5506,7 +5534,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -5529,7 +5557,7 @@
         <v>22.55</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -5552,7 +5580,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -5575,7 +5603,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -5598,7 +5626,7 @@
         <v>1475.9</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -5621,7 +5649,7 @@
         <v>291.45</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -5641,10 +5669,10 @@
         <v>129.75</v>
       </c>
       <c r="G24">
-        <v>299.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>299.89999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -5667,7 +5695,7 @@
         <v>372.4</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -5690,7 +5718,7 @@
         <v>850.55</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -5713,7 +5741,7 @@
         <v>859.2</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -5736,7 +5764,7 @@
         <v>1026.55</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -5759,7 +5787,7 @@
         <v>283.05</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -5779,10 +5807,10 @@
         <v>174</v>
       </c>
       <c r="G30">
-        <v>321.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>321.10000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -5805,7 +5833,7 @@
         <v>316.3</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -5828,7 +5856,7 @@
         <v>909.3</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -5851,7 +5879,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -5874,7 +5902,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -5897,7 +5925,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -5920,7 +5948,7 @@
         <v>22.55</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -5943,7 +5971,7 @@
         <v>24.35</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -5966,7 +5994,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -5986,10 +6014,10 @@
         <v>129.75</v>
       </c>
       <c r="G39">
-        <v>299.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>299.89999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -6012,7 +6040,7 @@
         <v>372.4</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6035,7 +6063,7 @@
         <v>392.6</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -6058,7 +6086,7 @@
         <v>859.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -6081,7 +6109,7 @@
         <v>316.3</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -6104,7 +6132,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -6127,7 +6155,7 @@
         <v>31.15</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -6150,7 +6178,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -6173,7 +6201,7 @@
         <v>24.35</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -6196,7 +6224,7 @@
         <v>392.6</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -6225,11 +6253,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6252,7 +6280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -6275,7 +6303,7 @@
         <v>17.95</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6298,7 +6326,7 @@
         <v>12.65</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -6321,7 +6349,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -6344,7 +6372,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6367,7 +6395,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6390,7 +6418,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6413,7 +6441,7 @@
         <v>14.15</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -6436,7 +6464,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -6459,7 +6487,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6482,7 +6510,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -6505,7 +6533,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6528,7 +6556,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -6551,7 +6579,7 @@
         <v>13.95</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -6574,7 +6602,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -6597,7 +6625,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -6620,7 +6648,7 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -6643,7 +6671,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -6666,7 +6694,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -6689,7 +6717,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -6712,7 +6740,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -6735,7 +6763,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -6758,7 +6786,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -6781,7 +6809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -6801,10 +6829,10 @@
         <v>13</v>
       </c>
       <c r="G25">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -6827,7 +6855,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -6847,10 +6875,10 @@
         <v>11.5</v>
       </c>
       <c r="G27">
-        <v>16.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -6873,7 +6901,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -6896,7 +6924,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -6919,7 +6947,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -6942,7 +6970,7 @@
         <v>12.55</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -6965,7 +6993,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -6988,7 +7016,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -7011,7 +7039,7 @@
         <v>11.05</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -7034,7 +7062,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -7057,7 +7085,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -7077,10 +7105,10 @@
         <v>6.75</v>
       </c>
       <c r="G37">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -7103,7 +7131,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -7126,7 +7154,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -7149,7 +7177,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -7172,7 +7200,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -7195,7 +7223,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -7218,7 +7246,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -7241,7 +7269,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -7264,7 +7292,7 @@
         <v>11.05</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -7287,7 +7315,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -7310,7 +7338,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -7333,7 +7361,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>54</v>
       </c>

--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -572,22 +572,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.0441517</v>
+        <v>0.0452317</v>
       </c>
       <c r="C2">
-        <v>0.03607835</v>
+        <v>0.036541475</v>
       </c>
       <c r="D2">
-        <v>0.03017315</v>
+        <v>0.03091415</v>
       </c>
       <c r="E2">
-        <v>0.060272025</v>
+        <v>0.06115425</v>
       </c>
       <c r="F2">
-        <v>0.09276187500000001</v>
+        <v>0.09424257500000002</v>
       </c>
       <c r="G2">
-        <v>0.05268742</v>
+        <v>0.05361683</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006208375</v>
+        <v>0.006213449999999999</v>
       </c>
       <c r="C3">
-        <v>0.006603400000000001</v>
+        <v>0.0069333</v>
       </c>
       <c r="D3">
-        <v>0.005457549999999999</v>
+        <v>0.005457675</v>
       </c>
       <c r="E3">
-        <v>0.006598249999999999</v>
+        <v>0.006543125</v>
       </c>
       <c r="F3">
-        <v>0.005313099999999999</v>
+        <v>0.004896175000000001</v>
       </c>
       <c r="G3">
-        <v>0.006036135</v>
+        <v>0.006008745</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -618,22 +618,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.011850175</v>
+        <v>0.002451675</v>
       </c>
       <c r="C4">
-        <v>0.042843975</v>
+        <v>0.008575624999999998</v>
       </c>
       <c r="D4">
-        <v>0.018892825</v>
+        <v>0.00427445</v>
       </c>
       <c r="E4">
-        <v>0.010470825</v>
+        <v>0.00389225</v>
       </c>
       <c r="F4">
-        <v>0.026291975</v>
+        <v>0.002488175</v>
       </c>
       <c r="G4">
-        <v>0.022069955</v>
+        <v>0.004336435</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,22 +641,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.023534375</v>
+        <v>0.0237125</v>
       </c>
       <c r="C5">
-        <v>0.0310089</v>
+        <v>0.0318581</v>
       </c>
       <c r="D5">
-        <v>0.024431525</v>
+        <v>0.024729475</v>
       </c>
       <c r="E5">
-        <v>0.034040075</v>
+        <v>0.03515307500000001</v>
       </c>
       <c r="F5">
-        <v>0.04445299999999999</v>
+        <v>0.04533089999999999</v>
       </c>
       <c r="G5">
-        <v>0.031493575</v>
+        <v>0.03215681</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -664,22 +664,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.00472055</v>
+        <v>0.004762325</v>
       </c>
       <c r="C6">
-        <v>0.004249849999999999</v>
+        <v>0.004164775000000001</v>
       </c>
       <c r="D6">
-        <v>0.006563925</v>
+        <v>0.006717575</v>
       </c>
       <c r="E6">
-        <v>0.006368175</v>
+        <v>0.006517675</v>
       </c>
       <c r="F6">
-        <v>0.010119675</v>
+        <v>0.010284</v>
       </c>
       <c r="G6">
-        <v>0.006404435</v>
+        <v>0.00648927</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -687,22 +687,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.043874625</v>
+        <v>0.0449744</v>
       </c>
       <c r="C7">
-        <v>0.03584195</v>
+        <v>0.03718870000000001</v>
       </c>
       <c r="D7">
-        <v>0.030746975</v>
+        <v>0.0312947</v>
       </c>
       <c r="E7">
-        <v>0.05982767499999998</v>
+        <v>0.06227405</v>
       </c>
       <c r="F7">
-        <v>0.092931525</v>
+        <v>0.094641925</v>
       </c>
       <c r="G7">
-        <v>0.05264455</v>
+        <v>0.05407475500000001</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -710,22 +710,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.04145205</v>
+        <v>0.04234105000000001</v>
       </c>
       <c r="C8">
-        <v>0.034393775</v>
+        <v>0.035038625</v>
       </c>
       <c r="D8">
-        <v>0.0269828</v>
+        <v>0.02798665</v>
       </c>
       <c r="E8">
-        <v>0.056327475</v>
+        <v>0.058227925</v>
       </c>
       <c r="F8">
-        <v>0.09237465000000002</v>
+        <v>0.09482202499999999</v>
       </c>
       <c r="G8">
-        <v>0.05030615000000001</v>
+        <v>0.051683255</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -733,22 +733,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.006315675</v>
+        <v>0.0009395500000000002</v>
       </c>
       <c r="C9">
-        <v>0.024782325</v>
+        <v>0.0026948</v>
       </c>
       <c r="D9">
-        <v>0.0147507</v>
+        <v>0.0019456</v>
       </c>
       <c r="E9">
-        <v>0.0052658</v>
+        <v>0.001561875</v>
       </c>
       <c r="F9">
-        <v>0.00440495</v>
+        <v>0.000569225</v>
       </c>
       <c r="G9">
-        <v>0.01110389</v>
+        <v>0.00154221</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -756,22 +756,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.0072696</v>
+        <v>0.007290124999999999</v>
       </c>
       <c r="C10">
-        <v>0.008111449999999999</v>
+        <v>0.007981324999999999</v>
       </c>
       <c r="D10">
-        <v>0.005285900000000001</v>
+        <v>0.005205999999999999</v>
       </c>
       <c r="E10">
-        <v>0.008063674999999999</v>
+        <v>0.00816185</v>
       </c>
       <c r="F10">
-        <v>0.0067175</v>
+        <v>0.006714175000000001</v>
       </c>
       <c r="G10">
-        <v>0.007089625</v>
+        <v>0.007070695</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -779,22 +779,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.006638225</v>
+        <v>0.00654245</v>
       </c>
       <c r="C11">
-        <v>0.0069224</v>
+        <v>0.00699865</v>
       </c>
       <c r="D11">
-        <v>0.0056474</v>
+        <v>0.005720525000000001</v>
       </c>
       <c r="E11">
-        <v>0.006811225000000001</v>
+        <v>0.006909925000000001</v>
       </c>
       <c r="F11">
-        <v>0.00540315</v>
+        <v>0.005365475</v>
       </c>
       <c r="G11">
-        <v>0.00628448</v>
+        <v>0.006307405</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -802,22 +802,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.00671705</v>
+        <v>0.0069285</v>
       </c>
       <c r="C12">
-        <v>0.00711715</v>
+        <v>0.007235525</v>
       </c>
       <c r="D12">
-        <v>0.005716275</v>
+        <v>0.005759675</v>
       </c>
       <c r="E12">
-        <v>0.00709795</v>
+        <v>0.007071025</v>
       </c>
       <c r="F12">
-        <v>0.005271375</v>
+        <v>0.0051985</v>
       </c>
       <c r="G12">
-        <v>0.006383959999999999</v>
+        <v>0.006438645</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -825,22 +825,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.012163275</v>
+        <v>0.00277895</v>
       </c>
       <c r="C13">
-        <v>0.04300945</v>
+        <v>0.008770975</v>
       </c>
       <c r="D13">
-        <v>0.018972225</v>
+        <v>0.004296474999999999</v>
       </c>
       <c r="E13">
-        <v>0.010608775</v>
+        <v>0.004152275</v>
       </c>
       <c r="F13">
-        <v>0.026185</v>
+        <v>0.00278745</v>
       </c>
       <c r="G13">
-        <v>0.022187745</v>
+        <v>0.004557225</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -848,22 +848,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.012320375</v>
+        <v>0.0024737</v>
       </c>
       <c r="C14">
-        <v>0.0460285</v>
+        <v>0.009231524999999999</v>
       </c>
       <c r="D14">
-        <v>0.0187729</v>
+        <v>0.0039586</v>
       </c>
       <c r="E14">
-        <v>0.011030125</v>
+        <v>0.003883825</v>
       </c>
       <c r="F14">
-        <v>0.0265694</v>
+        <v>0.0025647</v>
       </c>
       <c r="G14">
-        <v>0.02294426</v>
+        <v>0.00442247</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -871,22 +871,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.013466975</v>
+        <v>0.00312735</v>
       </c>
       <c r="C15">
-        <v>0.0492595</v>
+        <v>0.015551325</v>
       </c>
       <c r="D15">
-        <v>0.02295755</v>
+        <v>0.01089085</v>
       </c>
       <c r="E15">
-        <v>0.011899275</v>
+        <v>0.004259750000000001</v>
       </c>
       <c r="F15">
-        <v>0.0330177</v>
+        <v>0.002602775</v>
       </c>
       <c r="G15">
-        <v>0.0261202</v>
+        <v>0.00728641</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -894,22 +894,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.023649675</v>
+        <v>0.02398195</v>
       </c>
       <c r="C16">
-        <v>0.031280275</v>
+        <v>0.031962125</v>
       </c>
       <c r="D16">
-        <v>0.0246079</v>
+        <v>0.025064025</v>
       </c>
       <c r="E16">
-        <v>0.03428002500000001</v>
+        <v>0.03554545</v>
       </c>
       <c r="F16">
-        <v>0.044652575</v>
+        <v>0.046054875</v>
       </c>
       <c r="G16">
-        <v>0.03169409</v>
+        <v>0.032521685</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -917,22 +917,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.024777</v>
+        <v>0.02494795</v>
       </c>
       <c r="C17">
-        <v>0.03016495</v>
+        <v>0.03118345</v>
       </c>
       <c r="D17">
-        <v>0.02352085</v>
+        <v>0.023824275</v>
       </c>
       <c r="E17">
-        <v>0.031682625</v>
+        <v>0.03257995</v>
       </c>
       <c r="F17">
-        <v>0.04076979999999999</v>
+        <v>0.04261645</v>
       </c>
       <c r="G17">
-        <v>0.030183045</v>
+        <v>0.031030415</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -940,22 +940,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.00545885</v>
+        <v>0.005579049999999999</v>
       </c>
       <c r="C18">
-        <v>0.0037426</v>
+        <v>0.003756375</v>
       </c>
       <c r="D18">
-        <v>0.005018999999999999</v>
+        <v>0.005035599999999999</v>
       </c>
       <c r="E18">
-        <v>0.003572375</v>
+        <v>0.003584725</v>
       </c>
       <c r="F18">
-        <v>0.00742085</v>
+        <v>0.007520725000000001</v>
       </c>
       <c r="G18">
-        <v>0.005042735</v>
+        <v>0.005095295</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -963,22 +963,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.0025457</v>
+        <v>0.002838025</v>
       </c>
       <c r="C19">
-        <v>0.00373465</v>
+        <v>0.002983449999999999</v>
       </c>
       <c r="D19">
-        <v>0.005708475000000001</v>
+        <v>0.002475825</v>
       </c>
       <c r="E19">
-        <v>0.00242125</v>
+        <v>0.00195465</v>
       </c>
       <c r="F19">
-        <v>0.0039884</v>
+        <v>0.0041357</v>
       </c>
       <c r="G19">
-        <v>0.003679695</v>
+        <v>0.002877530000000001</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -986,22 +986,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004657474999999999</v>
+        <v>0.004782</v>
       </c>
       <c r="C20">
-        <v>0.004547</v>
+        <v>0.004613674999999999</v>
       </c>
       <c r="D20">
-        <v>0.004681025</v>
+        <v>0.004806325</v>
       </c>
       <c r="E20">
-        <v>0.004764674999999999</v>
+        <v>0.004763125</v>
       </c>
       <c r="F20">
-        <v>0.007903799999999999</v>
+        <v>0.008031725</v>
       </c>
       <c r="G20">
-        <v>0.005310794999999999</v>
+        <v>0.00539937</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1009,22 +1009,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.004767725</v>
+        <v>0.004867349999999999</v>
       </c>
       <c r="C21">
-        <v>0.004267874999999999</v>
+        <v>0.0042467</v>
       </c>
       <c r="D21">
-        <v>0.0066336</v>
+        <v>0.006716049999999999</v>
       </c>
       <c r="E21">
-        <v>0.006533225</v>
+        <v>0.006551224999999999</v>
       </c>
       <c r="F21">
-        <v>0.0101767</v>
+        <v>0.010499225</v>
       </c>
       <c r="G21">
-        <v>0.006475824999999999</v>
+        <v>0.006576109999999999</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1032,22 +1032,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.042247975</v>
+        <v>0.04324717499999999</v>
       </c>
       <c r="C22">
-        <v>0.03443115</v>
+        <v>0.03570382499999999</v>
       </c>
       <c r="D22">
-        <v>0.027317425</v>
+        <v>0.0281297</v>
       </c>
       <c r="E22">
-        <v>0.056604025</v>
+        <v>0.05806404999999999</v>
       </c>
       <c r="F22">
-        <v>0.09254575</v>
+        <v>0.094231125</v>
       </c>
       <c r="G22">
-        <v>0.050629265</v>
+        <v>0.05187517499999998</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1055,22 +1055,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.006595375000000001</v>
+        <v>0.001228225</v>
       </c>
       <c r="C23">
-        <v>0.025096675</v>
+        <v>0.0030199</v>
       </c>
       <c r="D23">
-        <v>0.0149086</v>
+        <v>0.002174375</v>
       </c>
       <c r="E23">
-        <v>0.005456225</v>
+        <v>0.001762875</v>
       </c>
       <c r="F23">
-        <v>0.004655325</v>
+        <v>0.0008558999999999999</v>
       </c>
       <c r="G23">
-        <v>0.01134244</v>
+        <v>0.001808255</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1078,22 +1078,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0064797</v>
+        <v>0.00113705</v>
       </c>
       <c r="C24">
-        <v>0.024756475</v>
+        <v>0.003017425</v>
       </c>
       <c r="D24">
-        <v>0.0159886</v>
+        <v>0.00222085</v>
       </c>
       <c r="E24">
-        <v>0.0071872</v>
+        <v>0.00193915</v>
       </c>
       <c r="F24">
-        <v>0.004524925</v>
+        <v>0.0006869250000000001</v>
       </c>
       <c r="G24">
-        <v>0.01178738</v>
+        <v>0.00180028</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1101,22 +1101,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.0114216</v>
+        <v>0.001719625</v>
       </c>
       <c r="C25">
-        <v>0.03517535</v>
+        <v>0.005143375</v>
       </c>
       <c r="D25">
-        <v>0.018952625</v>
+        <v>0.003215625</v>
       </c>
       <c r="E25">
-        <v>0.006149025000000001</v>
+        <v>0.0020125</v>
       </c>
       <c r="F25">
-        <v>0.00846305</v>
+        <v>0.0009768749999999999</v>
       </c>
       <c r="G25">
-        <v>0.01603233</v>
+        <v>0.0026136</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1124,22 +1124,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.007398125</v>
+        <v>0.007620125</v>
       </c>
       <c r="C26">
-        <v>0.008683675</v>
+        <v>0.008429300000000001</v>
       </c>
       <c r="D26">
-        <v>0.005416575</v>
+        <v>0.005547825</v>
       </c>
       <c r="E26">
-        <v>0.008390524999999999</v>
+        <v>0.00830495</v>
       </c>
       <c r="F26">
-        <v>0.007035675000000001</v>
+        <v>0.007005974999999999</v>
       </c>
       <c r="G26">
-        <v>0.007384915000000001</v>
+        <v>0.007381634999999999</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1147,22 +1147,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.007685175</v>
+        <v>0.007696725</v>
       </c>
       <c r="C27">
-        <v>0.008732849999999999</v>
+        <v>0.008579450000000001</v>
       </c>
       <c r="D27">
-        <v>0.00545745</v>
+        <v>0.0055329</v>
       </c>
       <c r="E27">
-        <v>0.008272925</v>
+        <v>0.008242050000000001</v>
       </c>
       <c r="F27">
-        <v>0.007074575</v>
+        <v>0.007113400000000001</v>
       </c>
       <c r="G27">
-        <v>0.007444595</v>
+        <v>0.007432905000000001</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1170,22 +1170,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.007086325</v>
+        <v>0.007172224999999999</v>
       </c>
       <c r="C28">
-        <v>0.007420599999999999</v>
+        <v>0.007512549999999999</v>
       </c>
       <c r="D28">
-        <v>0.005938249999999999</v>
+        <v>0.005931375</v>
       </c>
       <c r="E28">
-        <v>0.0072954</v>
+        <v>0.007339075</v>
       </c>
       <c r="F28">
-        <v>0.005611700000000001</v>
+        <v>0.005680175</v>
       </c>
       <c r="G28">
-        <v>0.006670455</v>
+        <v>0.006727079999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1193,22 +1193,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.0126662</v>
+        <v>0.0028725</v>
       </c>
       <c r="C29">
-        <v>0.04638465000000001</v>
+        <v>0.009501275</v>
       </c>
       <c r="D29">
-        <v>0.0192775</v>
+        <v>0.004162374999999999</v>
       </c>
       <c r="E29">
-        <v>0.01115105</v>
+        <v>0.004142375</v>
       </c>
       <c r="F29">
-        <v>0.02653465</v>
+        <v>0.002841550000000001</v>
       </c>
       <c r="G29">
-        <v>0.02320281</v>
+        <v>0.004704015000000001</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1216,22 +1216,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.0140973</v>
+        <v>0.003363525</v>
       </c>
       <c r="C30">
-        <v>0.04958392500000001</v>
+        <v>0.015473075</v>
       </c>
       <c r="D30">
-        <v>0.02278235</v>
+        <v>0.010802075</v>
       </c>
       <c r="E30">
-        <v>0.0118015</v>
+        <v>0.004434975</v>
       </c>
       <c r="F30">
-        <v>0.03324869999999999</v>
+        <v>0.00287335</v>
       </c>
       <c r="G30">
-        <v>0.026302755</v>
+        <v>0.007389399999999999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1239,22 +1239,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.01294775</v>
+        <v>0.003466250000000001</v>
       </c>
       <c r="C31">
-        <v>0.05445545</v>
+        <v>0.014848125</v>
       </c>
       <c r="D31">
-        <v>0.0248607</v>
+        <v>0.01217725</v>
       </c>
       <c r="E31">
-        <v>0.014109625</v>
+        <v>0.005230249999999999</v>
       </c>
       <c r="F31">
-        <v>0.0255133</v>
+        <v>0.002642</v>
       </c>
       <c r="G31">
-        <v>0.026377365</v>
+        <v>0.007672775</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1262,22 +1262,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.0247692</v>
+        <v>0.02514425</v>
       </c>
       <c r="C32">
-        <v>0.03055275</v>
+        <v>0.03208905</v>
       </c>
       <c r="D32">
-        <v>0.023928475</v>
+        <v>0.0239537</v>
       </c>
       <c r="E32">
-        <v>0.031799675</v>
+        <v>0.032833225</v>
       </c>
       <c r="F32">
-        <v>0.04139857499999999</v>
+        <v>0.042393575</v>
       </c>
       <c r="G32">
-        <v>0.030489735</v>
+        <v>0.03128276</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1285,22 +1285,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.005177275</v>
+        <v>0.0051265</v>
       </c>
       <c r="C33">
-        <v>0.003034725</v>
+        <v>0.0029182</v>
       </c>
       <c r="D33">
-        <v>0.002605425</v>
+        <v>0.002500075</v>
       </c>
       <c r="E33">
-        <v>0.002927325</v>
+        <v>0.0027361</v>
       </c>
       <c r="F33">
-        <v>0.005988975000000001</v>
+        <v>0.005911650000000001</v>
       </c>
       <c r="G33">
-        <v>0.003946745</v>
+        <v>0.003838505</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1308,22 +1308,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.008312099999999999</v>
+        <v>0.0084963</v>
       </c>
       <c r="C34">
-        <v>0.003817275</v>
+        <v>0.0038308</v>
       </c>
       <c r="D34">
-        <v>0.0034136</v>
+        <v>0.003547750000000001</v>
       </c>
       <c r="E34">
-        <v>0.003771725</v>
+        <v>0.0037388</v>
       </c>
       <c r="F34">
-        <v>0.008824175</v>
+        <v>0.0090531</v>
       </c>
       <c r="G34">
-        <v>0.005627775</v>
+        <v>0.005733350000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1331,22 +1331,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.005508825</v>
+        <v>0.0055876</v>
       </c>
       <c r="C35">
-        <v>0.00380505</v>
+        <v>0.0038815</v>
       </c>
       <c r="D35">
-        <v>0.005021025</v>
+        <v>0.005151899999999999</v>
       </c>
       <c r="E35">
-        <v>0.003650525</v>
+        <v>0.00359165</v>
       </c>
       <c r="F35">
-        <v>0.007489925</v>
+        <v>0.007732525000000001</v>
       </c>
       <c r="G35">
-        <v>0.00509507</v>
+        <v>0.005189035</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1354,22 +1354,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.00258285</v>
+        <v>0.002909225</v>
       </c>
       <c r="C36">
-        <v>0.0038084</v>
+        <v>0.002985025</v>
       </c>
       <c r="D36">
-        <v>0.005747175</v>
+        <v>0.002501925</v>
       </c>
       <c r="E36">
-        <v>0.00248465</v>
+        <v>0.002061375</v>
       </c>
       <c r="F36">
-        <v>0.004041650000000001</v>
+        <v>0.004136475</v>
       </c>
       <c r="G36">
-        <v>0.003732945</v>
+        <v>0.002918805</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1377,22 +1377,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.003816974999999999</v>
+        <v>0.003401225</v>
       </c>
       <c r="C37">
-        <v>0.003997374999999999</v>
+        <v>0.002998475</v>
       </c>
       <c r="D37">
-        <v>0.005001299999999999</v>
+        <v>0.003041825</v>
       </c>
       <c r="E37">
-        <v>0.003384</v>
+        <v>0.00221115</v>
       </c>
       <c r="F37">
-        <v>0.005284975</v>
+        <v>0.004478025</v>
       </c>
       <c r="G37">
-        <v>0.004296924999999999</v>
+        <v>0.00322614</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1400,22 +1400,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004725999999999999</v>
+        <v>0.004843399999999999</v>
       </c>
       <c r="C38">
-        <v>0.00461</v>
+        <v>0.0046894</v>
       </c>
       <c r="D38">
-        <v>0.0047375</v>
+        <v>0.0048502</v>
       </c>
       <c r="E38">
-        <v>0.0047927</v>
+        <v>0.004854</v>
       </c>
       <c r="F38">
-        <v>0.0080255</v>
+        <v>0.00810955</v>
       </c>
       <c r="G38">
-        <v>0.00537834</v>
+        <v>0.00546931</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1423,22 +1423,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.0067075</v>
+        <v>0.00144745</v>
       </c>
       <c r="C39">
-        <v>0.02495575</v>
+        <v>0.003397325000000001</v>
       </c>
       <c r="D39">
-        <v>0.01615345</v>
+        <v>0.00242865</v>
       </c>
       <c r="E39">
-        <v>0.007426775000000001</v>
+        <v>0.00209715</v>
       </c>
       <c r="F39">
-        <v>0.004746274999999999</v>
+        <v>0.00099625</v>
       </c>
       <c r="G39">
-        <v>0.01199795</v>
+        <v>0.002073365</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1446,22 +1446,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.011648575</v>
+        <v>0.002029</v>
       </c>
       <c r="C40">
-        <v>0.0355093</v>
+        <v>0.005658875</v>
       </c>
       <c r="D40">
-        <v>0.0193791</v>
+        <v>0.003432625</v>
       </c>
       <c r="E40">
-        <v>0.006339575</v>
+        <v>0.002223475</v>
       </c>
       <c r="F40">
-        <v>0.008805200000000001</v>
+        <v>0.001226925</v>
       </c>
       <c r="G40">
-        <v>0.01633635</v>
+        <v>0.00291418</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1469,22 +1469,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.01261265</v>
+        <v>0.001856725</v>
       </c>
       <c r="C41">
-        <v>0.036982475</v>
+        <v>0.005913575</v>
       </c>
       <c r="D41">
-        <v>0.0206743</v>
+        <v>0.0038579</v>
       </c>
       <c r="E41">
-        <v>0.004981499999999999</v>
+        <v>0.002137125</v>
       </c>
       <c r="F41">
-        <v>0.0081137</v>
+        <v>0.001035425</v>
       </c>
       <c r="G41">
-        <v>0.016672925</v>
+        <v>0.00296015</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1492,22 +1492,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.007812224999999999</v>
+        <v>0.007849825</v>
       </c>
       <c r="C42">
-        <v>0.008918000000000001</v>
+        <v>0.008754025</v>
       </c>
       <c r="D42">
-        <v>0.005694125</v>
+        <v>0.0057701</v>
       </c>
       <c r="E42">
-        <v>0.008506675</v>
+        <v>0.008487</v>
       </c>
       <c r="F42">
-        <v>0.007432075000000001</v>
+        <v>0.007427700000000001</v>
       </c>
       <c r="G42">
-        <v>0.007672620000000001</v>
+        <v>0.00765773</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1515,22 +1515,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.0132328</v>
+        <v>0.003839375</v>
       </c>
       <c r="C43">
-        <v>0.05468035</v>
+        <v>0.0147082</v>
       </c>
       <c r="D43">
-        <v>0.02481015</v>
+        <v>0.01260295</v>
       </c>
       <c r="E43">
-        <v>0.014320975</v>
+        <v>0.005548125000000001</v>
       </c>
       <c r="F43">
-        <v>0.025819575</v>
+        <v>0.002906525000000001</v>
       </c>
       <c r="G43">
-        <v>0.02657277</v>
+        <v>0.007921035</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1538,22 +1538,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.005281075000000001</v>
+        <v>0.0052448</v>
       </c>
       <c r="C44">
-        <v>0.003165925</v>
+        <v>0.003054025</v>
       </c>
       <c r="D44">
-        <v>0.002780625</v>
+        <v>0.0026214</v>
       </c>
       <c r="E44">
-        <v>0.002939125</v>
+        <v>0.002794999999999999</v>
       </c>
       <c r="F44">
-        <v>0.006004600000000001</v>
+        <v>0.006072925</v>
       </c>
       <c r="G44">
-        <v>0.004034270000000001</v>
+        <v>0.003957629999999999</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1561,22 +1561,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0065813</v>
+        <v>0.006359800000000001</v>
       </c>
       <c r="C45">
-        <v>0.00321325</v>
+        <v>0.0031642</v>
       </c>
       <c r="D45">
-        <v>0.0035047</v>
+        <v>0.003377875</v>
       </c>
       <c r="E45">
-        <v>0.004075850000000001</v>
+        <v>0.0039372</v>
       </c>
       <c r="F45">
-        <v>0.005234725</v>
+        <v>0.005221325000000001</v>
       </c>
       <c r="G45">
-        <v>0.004521964999999999</v>
+        <v>0.004412080000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1584,22 +1584,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.008381300000000001</v>
+        <v>0.008485949999999999</v>
       </c>
       <c r="C46">
-        <v>0.003830925</v>
+        <v>0.003982275</v>
       </c>
       <c r="D46">
-        <v>0.003470675</v>
+        <v>0.003485475</v>
       </c>
       <c r="E46">
-        <v>0.00373185</v>
+        <v>0.003857775</v>
       </c>
       <c r="F46">
-        <v>0.008868475000000001</v>
+        <v>0.008893700000000001</v>
       </c>
       <c r="G46">
-        <v>0.005656645</v>
+        <v>0.005741035</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1607,22 +1607,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.00392735</v>
+        <v>0.00345695</v>
       </c>
       <c r="C47">
-        <v>0.003935200000000001</v>
+        <v>0.00309425</v>
       </c>
       <c r="D47">
-        <v>0.004970550000000001</v>
+        <v>0.00327605</v>
       </c>
       <c r="E47">
-        <v>0.003459925</v>
+        <v>0.002278075</v>
       </c>
       <c r="F47">
-        <v>0.00528795</v>
+        <v>0.004548775</v>
       </c>
       <c r="G47">
-        <v>0.004316195</v>
+        <v>0.00333082</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1630,22 +1630,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.012832725</v>
+        <v>0.00219415</v>
       </c>
       <c r="C48">
-        <v>0.03700879999999999</v>
+        <v>0.006386675000000001</v>
       </c>
       <c r="D48">
-        <v>0.020883</v>
+        <v>0.004078549999999999</v>
       </c>
       <c r="E48">
-        <v>0.00518805</v>
+        <v>0.002373725</v>
       </c>
       <c r="F48">
-        <v>0.008475450000000001</v>
+        <v>0.001295575</v>
       </c>
       <c r="G48">
-        <v>0.016877605</v>
+        <v>0.003265735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1653,22 +1653,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.00653345</v>
+        <v>0.006457075</v>
       </c>
       <c r="C49">
-        <v>0.0032393</v>
+        <v>0.003174275</v>
       </c>
       <c r="D49">
-        <v>0.003603775</v>
+        <v>0.0035188</v>
       </c>
       <c r="E49">
-        <v>0.004238375</v>
+        <v>0.0040665</v>
       </c>
       <c r="F49">
-        <v>0.005316125</v>
+        <v>0.005316149999999999</v>
       </c>
       <c r="G49">
-        <v>0.004586205</v>
+        <v>0.00450656</v>
       </c>
     </row>
   </sheetData>
@@ -1758,19 +1758,19 @@
         <v>78.75</v>
       </c>
       <c r="C4">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="D4">
-        <v>87</v>
+        <v>89.75</v>
       </c>
       <c r="E4">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="F4">
-        <v>75.25</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>79.90000000000001</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1827,19 +1827,19 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>11</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1870,22 +1870,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="C9">
-        <v>90.5</v>
+        <v>91</v>
       </c>
       <c r="D9">
-        <v>94.5</v>
+        <v>90.75</v>
       </c>
       <c r="E9">
-        <v>76</v>
+        <v>78.75</v>
       </c>
       <c r="F9">
-        <v>75.25</v>
+        <v>75</v>
       </c>
       <c r="G9">
-        <v>83.15000000000001</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1919,19 +1919,19 @@
         <v>6.75</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D11">
-        <v>12.75</v>
+        <v>14</v>
       </c>
       <c r="E11">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F11">
         <v>4</v>
       </c>
       <c r="G11">
-        <v>8.15</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1965,19 +1965,19 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>7.25</v>
       </c>
       <c r="D13">
-        <v>13.75</v>
+        <v>13.25</v>
       </c>
       <c r="E13">
-        <v>8.75</v>
+        <v>7.5</v>
       </c>
       <c r="F13">
         <v>7</v>
       </c>
       <c r="G13">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1991,16 +1991,16 @@
         <v>82.5</v>
       </c>
       <c r="D14">
-        <v>87</v>
+        <v>89.75</v>
       </c>
       <c r="E14">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F14">
         <v>75</v>
       </c>
       <c r="G14">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2014,16 +2014,16 @@
         <v>90</v>
       </c>
       <c r="D15">
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>75</v>
       </c>
       <c r="F15">
-        <v>79</v>
+        <v>77.25</v>
       </c>
       <c r="G15">
-        <v>82.25</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2034,19 +2034,19 @@
         <v>8.75</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="E16">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16">
-        <v>8.449999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2103,19 +2103,19 @@
         <v>16.5</v>
       </c>
       <c r="C19">
-        <v>18.75</v>
+        <v>19.5</v>
       </c>
       <c r="D19">
-        <v>22.75</v>
+        <v>23.5</v>
       </c>
       <c r="E19">
         <v>21</v>
       </c>
       <c r="F19">
-        <v>13.5</v>
+        <v>14.25</v>
       </c>
       <c r="G19">
-        <v>18.5</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2149,19 +2149,19 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="D21">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="E21">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>4</v>
       </c>
       <c r="G21">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2169,13 +2169,13 @@
         <v>27</v>
       </c>
       <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22">
         <v>7.25</v>
       </c>
-      <c r="C22">
-        <v>8</v>
-      </c>
       <c r="D22">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2184,7 +2184,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2192,22 +2192,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="E23">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="F23">
         <v>6</v>
       </c>
       <c r="G23">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2215,22 +2215,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="C24">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="D24">
-        <v>94.5</v>
+        <v>90.75</v>
       </c>
       <c r="E24">
-        <v>78</v>
+        <v>78.75</v>
       </c>
       <c r="F24">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="G24">
-        <v>83.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2238,7 +2238,7 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>79</v>
+        <v>78.75</v>
       </c>
       <c r="C25">
         <v>90</v>
@@ -2247,13 +2247,13 @@
         <v>89.75</v>
       </c>
       <c r="E25">
-        <v>75</v>
+        <v>75.75</v>
       </c>
       <c r="F25">
-        <v>77.75</v>
+        <v>76.5</v>
       </c>
       <c r="G25">
-        <v>82.3</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2264,19 +2264,19 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>14.75</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>9.6</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2310,19 +2310,19 @@
         <v>6.75</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28">
-        <v>8.35</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2333,19 +2333,19 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="E29">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F29">
         <v>7</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2356,19 +2356,19 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="E30">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="F30">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="G30">
-        <v>8.75</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2376,22 +2376,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>79.5</v>
+        <v>79.25</v>
       </c>
       <c r="C31">
+        <v>85.25</v>
+      </c>
+      <c r="D31">
         <v>90</v>
       </c>
-      <c r="D31">
-        <v>87.5</v>
-      </c>
       <c r="E31">
-        <v>76.5</v>
+        <v>75.25</v>
       </c>
       <c r="F31">
-        <v>75.75</v>
+        <v>76.25</v>
       </c>
       <c r="G31">
-        <v>81.84999999999999</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2402,19 +2402,19 @@
         <v>8.75</v>
       </c>
       <c r="C32">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="E32">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F32">
         <v>4</v>
       </c>
       <c r="G32">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2468,22 +2468,22 @@
         <v>40</v>
       </c>
       <c r="B35">
+        <v>7.75</v>
+      </c>
+      <c r="C35">
+        <v>9.25</v>
+      </c>
+      <c r="D35">
+        <v>14.5</v>
+      </c>
+      <c r="E35">
         <v>8</v>
-      </c>
-      <c r="C35">
-        <v>8.75</v>
-      </c>
-      <c r="D35">
-        <v>12.5</v>
-      </c>
-      <c r="E35">
-        <v>7.75</v>
       </c>
       <c r="F35">
         <v>4</v>
       </c>
       <c r="G35">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2494,19 +2494,19 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F36">
         <v>6</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2520,7 +2520,7 @@
         <v>19.75</v>
       </c>
       <c r="D37">
-        <v>22.5</v>
+        <v>23.25</v>
       </c>
       <c r="E37">
         <v>21</v>
@@ -2529,7 +2529,7 @@
         <v>14.5</v>
       </c>
       <c r="G37">
-        <v>18.85</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2540,10 +2540,10 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="D38">
-        <v>13.5</v>
+        <v>12.25</v>
       </c>
       <c r="E38">
         <v>8.75</v>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="G38">
-        <v>8.5</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2560,16 +2560,16 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="E39">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="F39">
         <v>6</v>
@@ -2583,22 +2583,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="C40">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="E40">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="G40">
-        <v>9.449999999999999</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2606,16 +2606,16 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>79.75</v>
+        <v>79.5</v>
       </c>
       <c r="C41">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D41">
-        <v>92.5</v>
+        <v>91.25</v>
       </c>
       <c r="E41">
-        <v>75.25</v>
+        <v>78.75</v>
       </c>
       <c r="F41">
         <v>75</v>
@@ -2629,22 +2629,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="C42">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="D42">
-        <v>14.75</v>
+        <v>16</v>
       </c>
       <c r="E42">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>9.65</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2652,22 +2652,22 @@
         <v>48</v>
       </c>
       <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>7.75</v>
+      </c>
+      <c r="D43">
+        <v>14.5</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43">
         <v>6.75</v>
       </c>
-      <c r="C43">
-        <v>10.5</v>
-      </c>
-      <c r="D43">
-        <v>13</v>
-      </c>
-      <c r="E43">
-        <v>8</v>
-      </c>
-      <c r="F43">
-        <v>5.5</v>
-      </c>
       <c r="G43">
-        <v>8.75</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2675,22 +2675,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F44">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="G44">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2721,22 +2721,22 @@
         <v>51</v>
       </c>
       <c r="B46">
+        <v>7.75</v>
+      </c>
+      <c r="C46">
+        <v>10.5</v>
+      </c>
+      <c r="D46">
+        <v>15</v>
+      </c>
+      <c r="E46">
         <v>8</v>
       </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>13.75</v>
-      </c>
-      <c r="E46">
-        <v>7.75</v>
-      </c>
       <c r="F46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46">
-        <v>8.9</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2747,19 +2747,19 @@
         <v>7</v>
       </c>
       <c r="C47">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="D47">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2770,19 +2770,19 @@
         <v>7</v>
       </c>
       <c r="C48">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="D48">
         <v>14.25</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="F48">
         <v>6</v>
       </c>
       <c r="G48">
-        <v>9.35</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2793,19 +2793,19 @@
         <v>7</v>
       </c>
       <c r="C49">
-        <v>9.75</v>
+        <v>10.25</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="E49">
         <v>7.25</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49">
-        <v>9</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -2892,22 +2892,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>96.70027047856911</v>
+        <v>96.07895013500946</v>
       </c>
       <c r="C4">
-        <v>100.6396103067893</v>
+        <v>98.48275605729691</v>
       </c>
       <c r="D4">
-        <v>100.2903679018718</v>
+        <v>101.6941738241592</v>
       </c>
       <c r="E4">
-        <v>95.41778489984132</v>
+        <v>94.50357133746822</v>
       </c>
       <c r="F4">
-        <v>94.02869760331529</v>
+        <v>93.88225099390857</v>
       </c>
       <c r="G4">
-        <v>97.41534623807736</v>
+        <v>96.92834046956845</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2961,22 +2961,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>89.25075883146134</v>
+        <v>89.26078573459853</v>
       </c>
       <c r="C7">
-        <v>92.92004125279729</v>
+        <v>92.9053469720055</v>
       </c>
       <c r="D7">
-        <v>94.60065799581339</v>
+        <v>94.52157307105429</v>
       </c>
       <c r="E7">
-        <v>88.12126645620715</v>
+        <v>88.15681650595542</v>
       </c>
       <c r="F7">
         <v>87.33691238960859</v>
       </c>
       <c r="G7">
-        <v>90.44592738517755</v>
+        <v>90.43628693464447</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3007,22 +3007,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>97.96803743153546</v>
+        <v>96.84671708797583</v>
       </c>
       <c r="C9">
-        <v>109.3822509939086</v>
+        <v>106.1543289325507</v>
       </c>
       <c r="D9">
-        <v>107.3761543394987</v>
+        <v>102.9012806053458</v>
       </c>
       <c r="E9">
-        <v>94.88225099390857</v>
+        <v>97.94291116568837</v>
       </c>
       <c r="F9">
-        <v>92.3718433538229</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="G9">
-        <v>100.3961074225349</v>
+        <v>99.21412690719538</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3053,22 +3053,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>88.92741626707834</v>
+        <v>88.84644040412962</v>
       </c>
       <c r="C11">
-        <v>92.35155128758481</v>
+        <v>92.27317775224984</v>
       </c>
       <c r="D11">
-        <v>94.60476576617593</v>
+        <v>94.48634630946313</v>
       </c>
       <c r="E11">
-        <v>87.44194575170043</v>
+        <v>87.54686429991816</v>
       </c>
       <c r="F11">
         <v>87.83084116930945</v>
       </c>
       <c r="G11">
-        <v>90.23130404836979</v>
+        <v>90.19673398701404</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3099,22 +3099,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>88.86831020593698</v>
+        <v>89.07991467279851</v>
       </c>
       <c r="C13">
-        <v>94.79342039202658</v>
+        <v>93.41253979641618</v>
       </c>
       <c r="D13">
-        <v>95.76366082234064</v>
+        <v>97.7446453717489</v>
       </c>
       <c r="E13">
-        <v>88.82006578861703</v>
+        <v>88.63203900887707</v>
       </c>
       <c r="F13">
-        <v>91.02793177992237</v>
+        <v>90.96241271314568</v>
       </c>
       <c r="G13">
-        <v>91.85467779776873</v>
+        <v>91.96631031259727</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3122,22 +3122,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>96.70027047856911</v>
+        <v>96.07895013500946</v>
       </c>
       <c r="C14">
-        <v>99.72539674441619</v>
+        <v>99.10407640085654</v>
       </c>
       <c r="D14">
-        <v>100.7045814642449</v>
+        <v>101.6941738241592</v>
       </c>
       <c r="E14">
-        <v>95.91778489984131</v>
+        <v>94.71067811865477</v>
       </c>
       <c r="F14">
-        <v>94.08935777509511</v>
+        <v>93.88225099390857</v>
       </c>
       <c r="G14">
-        <v>97.42747827243332</v>
+        <v>97.0940258945177</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3145,22 +3145,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>95.04341622907673</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C15">
-        <v>103.4974746830583</v>
+        <v>102.0477272147525</v>
       </c>
       <c r="D15">
-        <v>100.754833995939</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="E15">
         <v>92.22539674441617</v>
       </c>
       <c r="F15">
-        <v>94.98275605729691</v>
+        <v>94.37184335382291</v>
       </c>
       <c r="G15">
-        <v>97.30077554195742</v>
+        <v>96.98153672641492</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3168,22 +3168,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>88.69024647611863</v>
+        <v>88.66642008059104</v>
       </c>
       <c r="C16">
-        <v>92.3043155870872</v>
+        <v>92.29032168087473</v>
       </c>
       <c r="D16">
-        <v>94.35400728794046</v>
+        <v>94.04476045024403</v>
       </c>
       <c r="E16">
-        <v>86.50435909119437</v>
+        <v>86.73065860854024</v>
       </c>
       <c r="F16">
         <v>87.25337971078574</v>
       </c>
       <c r="G16">
-        <v>89.82126163062529</v>
+        <v>89.79710810620716</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3240,19 +3240,19 @@
         <v>94.42209588551708</v>
       </c>
       <c r="C19">
-        <v>97.44722215136414</v>
+        <v>101.5477272147525</v>
       </c>
       <c r="D19">
-        <v>98.81549416771887</v>
+        <v>101.4870670429727</v>
       </c>
       <c r="E19">
-        <v>92.22539674441617</v>
+        <v>94.27564927611036</v>
       </c>
       <c r="F19">
-        <v>92.22539674441617</v>
+        <v>94.27564927611036</v>
       </c>
       <c r="G19">
-        <v>95.0271211386865</v>
+        <v>97.2016377390926</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3283,22 +3283,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>92.82101084022804</v>
+        <v>92.74634703538689</v>
       </c>
       <c r="C21">
-        <v>95.27757408669811</v>
+        <v>93.84298918959182</v>
       </c>
       <c r="D21">
-        <v>97.57316238510808</v>
+        <v>95.69912185031986</v>
       </c>
       <c r="E21">
-        <v>88.73381198849388</v>
+        <v>88.04242989886052</v>
       </c>
       <c r="F21">
         <v>89.17676618598557</v>
       </c>
       <c r="G21">
-        <v>92.71646509730273</v>
+        <v>91.90153083202893</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3306,22 +3306,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>89.43632429655094</v>
+        <v>89.34383520836315</v>
       </c>
       <c r="C22">
-        <v>92.90307720918985</v>
+        <v>92.8786766708138</v>
       </c>
       <c r="D22">
-        <v>94.35452808975376</v>
+        <v>94.23488584070527</v>
       </c>
       <c r="E22">
-        <v>88.1854601545144</v>
+        <v>88.30011401827591</v>
       </c>
       <c r="F22">
         <v>87.38393931334436</v>
       </c>
       <c r="G22">
-        <v>90.45266581267066</v>
+        <v>90.4282902103005</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3329,22 +3329,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>89.30106030150095</v>
+        <v>89.43325734773254</v>
       </c>
       <c r="C23">
-        <v>101.492671232672</v>
+        <v>98.04657322754127</v>
       </c>
       <c r="D23">
-        <v>99.54178984635607</v>
+        <v>98.48408190155187</v>
       </c>
       <c r="E23">
-        <v>88.11095577784479</v>
+        <v>89.73787674880313</v>
       </c>
       <c r="F23">
-        <v>87.83032228066719</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G23">
-        <v>93.2553598878082</v>
+        <v>92.71085513489828</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3352,22 +3352,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>97.96803743153546</v>
+        <v>96.84671708797583</v>
       </c>
       <c r="C24">
-        <v>108.4680374315355</v>
+        <v>105.0330085889911</v>
       </c>
       <c r="D24">
-        <v>106.3406204335659</v>
+        <v>102.9012806053458</v>
       </c>
       <c r="E24">
-        <v>96.46803743153548</v>
+        <v>98.56423150924803</v>
       </c>
       <c r="F24">
-        <v>92.72539674441617</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="G24">
-        <v>100.3940258945177</v>
+        <v>99.11412690719538</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3375,22 +3375,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>96.01828996322965</v>
+        <v>95.25052301026328</v>
       </c>
       <c r="C25">
-        <v>103.0832611206852</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="D25">
-        <v>102.9368145112785</v>
+        <v>101.6941738241592</v>
       </c>
       <c r="E25">
-        <v>94.5035713374682</v>
+        <v>93.70027047856911</v>
       </c>
       <c r="F25">
-        <v>95.07895013500945</v>
+        <v>93.72539674441617</v>
       </c>
       <c r="G25">
-        <v>98.3241774135342</v>
+        <v>97.24219689819473</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3398,22 +3398,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>88.87024808299795</v>
+        <v>88.84628482064193</v>
       </c>
       <c r="C26">
-        <v>97.00780758575567</v>
+        <v>96.62714140628285</v>
       </c>
       <c r="D26">
-        <v>97.58251851047601</v>
+        <v>96.9765119838772</v>
       </c>
       <c r="E26">
-        <v>88.86499004755807</v>
+        <v>88.87912745854852</v>
       </c>
       <c r="F26">
-        <v>88.53498363552973</v>
+        <v>88.45732941103415</v>
       </c>
       <c r="G26">
-        <v>92.17210957246348</v>
+        <v>91.95727901607692</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3444,22 +3444,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>89.2829759968425</v>
+        <v>89.11698592365499</v>
       </c>
       <c r="C28">
-        <v>92.35632712783598</v>
+        <v>92.32834263634192</v>
       </c>
       <c r="D28">
-        <v>94.33802733675296</v>
+        <v>94.12651525479779</v>
       </c>
       <c r="E28">
-        <v>88.88690818712263</v>
+        <v>89.01591551793194</v>
       </c>
       <c r="F28">
         <v>87.25337971078574</v>
       </c>
       <c r="G28">
-        <v>90.42352367186795</v>
+        <v>90.36822780870247</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3467,22 +3467,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>88.86831020593698</v>
+        <v>89.07991467279851</v>
       </c>
       <c r="C29">
-        <v>94.32355566383158</v>
+        <v>93.852251325531</v>
       </c>
       <c r="D29">
-        <v>96.00083507883355</v>
+        <v>97.7446453717489</v>
       </c>
       <c r="E29">
-        <v>88.82006578861703</v>
+        <v>88.63203900887707</v>
       </c>
       <c r="F29">
-        <v>90.73685967425403</v>
+        <v>90.96241271314568</v>
       </c>
       <c r="G29">
-        <v>91.74992528229464</v>
+        <v>92.05425261842024</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3490,22 +3490,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>88.91529102457073</v>
+        <v>89.07991467279851</v>
       </c>
       <c r="C30">
-        <v>96.92802922016543</v>
+        <v>96.33430830807514</v>
       </c>
       <c r="D30">
-        <v>96.04640721778026</v>
+        <v>96.94409788918787</v>
       </c>
       <c r="E30">
-        <v>88.56678106895744</v>
+        <v>88.63084847786544</v>
       </c>
       <c r="F30">
-        <v>88.02215430017574</v>
+        <v>88.86215727725494</v>
       </c>
       <c r="G30">
-        <v>91.69573256632991</v>
+        <v>91.97026532503639</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3513,22 +3513,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>97.13961030678929</v>
+        <v>96.57895013500946</v>
       </c>
       <c r="C31">
-        <v>106.8111831820431</v>
+        <v>99.05813485483816</v>
       </c>
       <c r="D31">
-        <v>101.2045814642449</v>
+        <v>102.6690475583121</v>
       </c>
       <c r="E31">
-        <v>95.58935777509511</v>
+        <v>94.23580438450185</v>
       </c>
       <c r="F31">
-        <v>93.07895013500945</v>
+        <v>94.6144840409422</v>
       </c>
       <c r="G31">
-        <v>98.76473657263637</v>
+        <v>97.43128419472075</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3536,22 +3536,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>88.69024647611863</v>
+        <v>88.66642008059104</v>
       </c>
       <c r="C32">
-        <v>93.24939669889704</v>
+        <v>93.06322019813916</v>
       </c>
       <c r="D32">
-        <v>94.35400728794046</v>
+        <v>94.04476045024403</v>
       </c>
       <c r="E32">
-        <v>86.50435909119437</v>
+        <v>86.73065860854024</v>
       </c>
       <c r="F32">
         <v>87.25337971078574</v>
       </c>
       <c r="G32">
-        <v>90.01027785298724</v>
+        <v>89.95168780966004</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3605,22 +3605,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>92.76984125986333</v>
+        <v>92.76490005040405</v>
       </c>
       <c r="C35">
-        <v>93.84859722213122</v>
+        <v>93.90458593737934</v>
       </c>
       <c r="D35">
-        <v>95.19327994086169</v>
+        <v>96.19429259473162</v>
       </c>
       <c r="E35">
-        <v>88.86857894582849</v>
+        <v>89.09532048851781</v>
       </c>
       <c r="F35">
         <v>87.25337971078574</v>
       </c>
       <c r="G35">
-        <v>91.58673541589408</v>
+        <v>91.84249575636372</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3631,19 +3631,19 @@
         <v>92.40280548509956</v>
       </c>
       <c r="C36">
-        <v>95.27757408669811</v>
+        <v>98.92076471220372</v>
       </c>
       <c r="D36">
-        <v>98.05837543200732</v>
+        <v>100.4322807617903</v>
       </c>
       <c r="E36">
-        <v>89.88578193152478</v>
+        <v>89.23909495021958</v>
       </c>
       <c r="F36">
-        <v>89.5532129713166</v>
+        <v>89.4557226091525</v>
       </c>
       <c r="G36">
-        <v>93.03554998132928</v>
+        <v>94.09013370369314</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3657,7 +3657,7 @@
         <v>101.8406204335659</v>
       </c>
       <c r="D37">
-        <v>98.81549416771887</v>
+        <v>101.4870670429727</v>
       </c>
       <c r="E37">
         <v>92.22539674441617</v>
@@ -3666,7 +3666,7 @@
         <v>94.42209588551708</v>
       </c>
       <c r="G37">
-        <v>96.34514062334702</v>
+        <v>96.87945519839778</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3677,19 +3677,19 @@
         <v>92.40280548509956</v>
       </c>
       <c r="C38">
-        <v>95.46855709232315</v>
+        <v>94.00061836510076</v>
       </c>
       <c r="D38">
-        <v>97.2064440146776</v>
+        <v>96.01354346337776</v>
       </c>
       <c r="E38">
-        <v>87.00466654293592</v>
+        <v>87.14141390478646</v>
       </c>
       <c r="F38">
         <v>89.17676618598557</v>
       </c>
       <c r="G38">
-        <v>92.25184786420435</v>
+        <v>91.74702948087003</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3697,22 +3697,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>89.2852468596606</v>
+        <v>89.43325734773254</v>
       </c>
       <c r="C39">
-        <v>101.4740859670631</v>
+        <v>97.38211175267764</v>
       </c>
       <c r="D39">
-        <v>99.41462398748419</v>
+        <v>98.48408190155187</v>
       </c>
       <c r="E39">
-        <v>89.51099227649286</v>
+        <v>89.68046751382099</v>
       </c>
       <c r="F39">
-        <v>87.83032228066719</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G39">
-        <v>93.50305427427359</v>
+        <v>92.56648099292913</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3720,22 +3720,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>89.42318358997991</v>
+        <v>88.99990922486882</v>
       </c>
       <c r="C40">
-        <v>97.42603264267115</v>
+        <v>96.86761117637303</v>
       </c>
       <c r="D40">
-        <v>97.30031142856308</v>
+        <v>96.66843472492903</v>
       </c>
       <c r="E40">
-        <v>87.40421030813985</v>
+        <v>89.10436046563885</v>
       </c>
       <c r="F40">
-        <v>89.28944426655802</v>
+        <v>88.5188039919074</v>
       </c>
       <c r="G40">
-        <v>92.16863644718241</v>
+        <v>92.03182391674342</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3743,22 +3743,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>97.90737725975566</v>
+        <v>97.34671708797583</v>
       </c>
       <c r="C41">
-        <v>108.1898628384834</v>
+        <v>102.0477272147525</v>
       </c>
       <c r="D41">
-        <v>109.5182899632296</v>
+        <v>105.8865619795843</v>
       </c>
       <c r="E41">
-        <v>93.61448404094219</v>
+        <v>96.70027047856911</v>
       </c>
       <c r="F41">
-        <v>92.43250352560273</v>
+        <v>92.63961030678928</v>
       </c>
       <c r="G41">
-        <v>100.3325035256027</v>
+        <v>98.92417741353421</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3766,22 +3766,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>89.08629018841425</v>
+        <v>89.02567788830872</v>
       </c>
       <c r="C42">
-        <v>97.05189493017757</v>
+        <v>96.67122875070476</v>
       </c>
       <c r="D42">
-        <v>97.70303301344907</v>
+        <v>96.98700516383333</v>
       </c>
       <c r="E42">
-        <v>88.86499004755807</v>
+        <v>88.87912745854852</v>
       </c>
       <c r="F42">
-        <v>88.53498363552973</v>
+        <v>88.45732941103415</v>
       </c>
       <c r="G42">
-        <v>92.24823836302575</v>
+        <v>92.0040737344859</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3789,22 +3789,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>88.99792530500324</v>
+        <v>89.29618943656151</v>
       </c>
       <c r="C43">
-        <v>99.80548605735865</v>
+        <v>94.56498240418756</v>
       </c>
       <c r="D43">
-        <v>95.54039172992404</v>
+        <v>97.93643226568786</v>
       </c>
       <c r="E43">
-        <v>88.8374944426205</v>
+        <v>88.65873088301404</v>
       </c>
       <c r="F43">
-        <v>89.29497545687138</v>
+        <v>90.98307847109159</v>
       </c>
       <c r="G43">
-        <v>92.49525459835556</v>
+        <v>92.28788269210851</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3812,22 +3812,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>99.46988842192549</v>
+        <v>99.46494721246621</v>
       </c>
       <c r="C44">
-        <v>99.81773782181897</v>
+        <v>99.88490910316931</v>
       </c>
       <c r="D44">
-        <v>97.46005017649594</v>
+        <v>98.33267398735988</v>
       </c>
       <c r="E44">
-        <v>87.213712376662</v>
+        <v>87.42378466006728</v>
       </c>
       <c r="F44">
-        <v>92.62419327484824</v>
+        <v>93.53607631609822</v>
       </c>
       <c r="G44">
-        <v>95.31711641435012</v>
+        <v>95.72847825583219</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3858,22 +3858,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>92.76984125986333</v>
+        <v>92.76490005040405</v>
       </c>
       <c r="C46">
-        <v>98.42483369451554</v>
+        <v>98.49200497586588</v>
       </c>
       <c r="D46">
-        <v>99.2578970835078</v>
+        <v>100.239983757739</v>
       </c>
       <c r="E46">
-        <v>88.65353820228947</v>
+        <v>88.90636856186427</v>
       </c>
       <c r="F46">
-        <v>88.76737542395162</v>
+        <v>89.57502444824181</v>
       </c>
       <c r="G46">
-        <v>93.57469713282555</v>
+        <v>93.995656358823</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3884,19 +3884,19 @@
         <v>92.40280548509956</v>
       </c>
       <c r="C47">
-        <v>99.26720364188988</v>
+        <v>99.17134209323737</v>
       </c>
       <c r="D47">
-        <v>97.2064440146776</v>
+        <v>100.7030742644905</v>
       </c>
       <c r="E47">
-        <v>89.88578193152478</v>
+        <v>88.66139772254367</v>
       </c>
       <c r="F47">
-        <v>88.53498363552973</v>
+        <v>89.42841909744683</v>
       </c>
       <c r="G47">
-        <v>93.45944374174431</v>
+        <v>94.07340773256358</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3904,22 +3904,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>89.31639932960687</v>
+        <v>89.84350880950822</v>
       </c>
       <c r="C48">
-        <v>100.9499362888641</v>
+        <v>96.81916274705507</v>
       </c>
       <c r="D48">
-        <v>99.43174922146214</v>
+        <v>98.14758952142844</v>
       </c>
       <c r="E48">
-        <v>87.44982468494962</v>
+        <v>89.63861121414007</v>
       </c>
       <c r="F48">
-        <v>87.83032228066719</v>
+        <v>87.89295873608319</v>
       </c>
       <c r="G48">
-        <v>92.99564636110998</v>
+        <v>92.46836620564299</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3930,19 +3930,19 @@
         <v>92.40280548509956</v>
       </c>
       <c r="C49">
-        <v>97.98767362268885</v>
+        <v>98.05484490403919</v>
       </c>
       <c r="D49">
-        <v>98.30955600543238</v>
+        <v>99.3476313949117</v>
       </c>
       <c r="E49">
-        <v>88.91547743733915</v>
+        <v>89.21667250580074</v>
       </c>
       <c r="F49">
-        <v>93.04365432060089</v>
+        <v>93.937089782518</v>
       </c>
       <c r="G49">
-        <v>94.13183337423217</v>
+        <v>94.59180881447382</v>
       </c>
     </row>
   </sheetData>
@@ -4029,22 +4029,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>262.5</v>
+        <v>205.5</v>
       </c>
       <c r="C4">
-        <v>327.75</v>
+        <v>230</v>
       </c>
       <c r="D4">
-        <v>214.75</v>
+        <v>170.75</v>
       </c>
       <c r="E4">
-        <v>246</v>
+        <v>208.25</v>
       </c>
       <c r="F4">
-        <v>263</v>
+        <v>211.25</v>
       </c>
       <c r="G4">
-        <v>262.8</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4144,22 +4144,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>332.75</v>
+        <v>305.5</v>
       </c>
       <c r="C9">
-        <v>396.75</v>
+        <v>297</v>
       </c>
       <c r="D9">
-        <v>368.75</v>
+        <v>304</v>
       </c>
       <c r="E9">
-        <v>313.25</v>
+        <v>353.75</v>
       </c>
       <c r="F9">
-        <v>221.25</v>
+        <v>196.75</v>
       </c>
       <c r="G9">
-        <v>326.55</v>
+        <v>291.4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4236,22 +4236,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>262.5</v>
+        <v>205.5</v>
       </c>
       <c r="C13">
-        <v>327.75</v>
+        <v>230</v>
       </c>
       <c r="D13">
-        <v>214.75</v>
+        <v>170.75</v>
       </c>
       <c r="E13">
-        <v>246</v>
+        <v>208.25</v>
       </c>
       <c r="F13">
-        <v>263</v>
+        <v>211.25</v>
       </c>
       <c r="G13">
-        <v>262.8</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4259,22 +4259,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>263.25</v>
+        <v>203.25</v>
       </c>
       <c r="C14">
-        <v>333.25</v>
+        <v>233.25</v>
       </c>
       <c r="D14">
-        <v>216</v>
+        <v>166.25</v>
       </c>
       <c r="E14">
-        <v>241.5</v>
+        <v>208.5</v>
       </c>
       <c r="F14">
-        <v>265.5</v>
+        <v>211.5</v>
       </c>
       <c r="G14">
-        <v>263.9</v>
+        <v>204.55</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4282,22 +4282,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C15">
-        <v>189.25</v>
+        <v>185.25</v>
       </c>
       <c r="D15">
-        <v>180</v>
+        <v>177.75</v>
       </c>
       <c r="E15">
-        <v>225</v>
+        <v>204.25</v>
       </c>
       <c r="F15">
-        <v>295.25</v>
+        <v>208.75</v>
       </c>
       <c r="G15">
-        <v>223.9</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4374,22 +4374,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="C19">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="G19">
-        <v>10.9</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4466,22 +4466,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>332.75</v>
+        <v>305.5</v>
       </c>
       <c r="C23">
-        <v>396.75</v>
+        <v>297</v>
       </c>
       <c r="D23">
-        <v>368.75</v>
+        <v>304</v>
       </c>
       <c r="E23">
-        <v>313.25</v>
+        <v>353.75</v>
       </c>
       <c r="F23">
-        <v>221.25</v>
+        <v>196.75</v>
       </c>
       <c r="G23">
-        <v>326.55</v>
+        <v>291.4</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4489,22 +4489,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>346.25</v>
+        <v>304.5</v>
       </c>
       <c r="C24">
-        <v>403.75</v>
+        <v>329.5</v>
       </c>
       <c r="D24">
-        <v>384.75</v>
+        <v>312.5</v>
       </c>
       <c r="E24">
-        <v>368.5</v>
+        <v>356.5</v>
       </c>
       <c r="F24">
-        <v>219.75</v>
+        <v>196.75</v>
       </c>
       <c r="G24">
-        <v>344.6</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4512,22 +4512,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>324.75</v>
+        <v>343</v>
       </c>
       <c r="C25">
-        <v>213.25</v>
+        <v>190.25</v>
       </c>
       <c r="D25">
-        <v>180.5</v>
+        <v>200.5</v>
       </c>
       <c r="E25">
-        <v>322.5</v>
+        <v>363</v>
       </c>
       <c r="F25">
-        <v>285</v>
+        <v>237.5</v>
       </c>
       <c r="G25">
-        <v>265.2</v>
+        <v>266.85</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4604,22 +4604,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>263.25</v>
+        <v>203.25</v>
       </c>
       <c r="C29">
-        <v>333.25</v>
+        <v>233.25</v>
       </c>
       <c r="D29">
-        <v>216</v>
+        <v>166.25</v>
       </c>
       <c r="E29">
-        <v>241.5</v>
+        <v>208.5</v>
       </c>
       <c r="F29">
-        <v>265.5</v>
+        <v>211.5</v>
       </c>
       <c r="G29">
-        <v>263.9</v>
+        <v>204.55</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4627,22 +4627,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C30">
-        <v>189.25</v>
+        <v>185.25</v>
       </c>
       <c r="D30">
-        <v>180</v>
+        <v>177.75</v>
       </c>
       <c r="E30">
-        <v>225</v>
+        <v>204.25</v>
       </c>
       <c r="F30">
-        <v>295.25</v>
+        <v>208.75</v>
       </c>
       <c r="G30">
-        <v>223.9</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4650,22 +4650,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>225.25</v>
+        <v>216.75</v>
       </c>
       <c r="C31">
-        <v>226.75</v>
+        <v>196</v>
       </c>
       <c r="D31">
-        <v>193</v>
+        <v>183.5</v>
       </c>
       <c r="E31">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="F31">
-        <v>299.5</v>
+        <v>208</v>
       </c>
       <c r="G31">
-        <v>237.3</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4765,22 +4765,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="C36">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="E36">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F36">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="G36">
-        <v>10.9</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4788,22 +4788,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="C37">
-        <v>13.75</v>
+        <v>12.25</v>
       </c>
       <c r="D37">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="E37">
-        <v>17.25</v>
+        <v>14.25</v>
       </c>
       <c r="F37">
-        <v>9.75</v>
+        <v>8.75</v>
       </c>
       <c r="G37">
-        <v>13.3</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4834,22 +4834,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>346.25</v>
+        <v>304.5</v>
       </c>
       <c r="C39">
-        <v>403.75</v>
+        <v>329.5</v>
       </c>
       <c r="D39">
-        <v>384.75</v>
+        <v>312.5</v>
       </c>
       <c r="E39">
-        <v>368.5</v>
+        <v>356.5</v>
       </c>
       <c r="F39">
-        <v>219.75</v>
+        <v>196.75</v>
       </c>
       <c r="G39">
-        <v>344.6</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4857,22 +4857,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>324.75</v>
+        <v>343</v>
       </c>
       <c r="C40">
-        <v>213.25</v>
+        <v>190.25</v>
       </c>
       <c r="D40">
-        <v>180.5</v>
+        <v>200.5</v>
       </c>
       <c r="E40">
-        <v>322.5</v>
+        <v>363</v>
       </c>
       <c r="F40">
-        <v>285</v>
+        <v>237.5</v>
       </c>
       <c r="G40">
-        <v>265.2</v>
+        <v>266.85</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4880,22 +4880,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>382.5</v>
+        <v>329.5</v>
       </c>
       <c r="C41">
-        <v>282.5</v>
+        <v>204.75</v>
       </c>
       <c r="D41">
-        <v>203.5</v>
+        <v>232</v>
       </c>
       <c r="E41">
-        <v>266</v>
+        <v>300.5</v>
       </c>
       <c r="F41">
-        <v>278.5</v>
+        <v>218.25</v>
       </c>
       <c r="G41">
-        <v>282.6</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4926,22 +4926,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>225.25</v>
+        <v>216.75</v>
       </c>
       <c r="C43">
-        <v>226.75</v>
+        <v>196</v>
       </c>
       <c r="D43">
-        <v>193</v>
+        <v>183.5</v>
       </c>
       <c r="E43">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="F43">
-        <v>299.5</v>
+        <v>208</v>
       </c>
       <c r="G43">
-        <v>237.3</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5018,22 +5018,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="C47">
-        <v>13.75</v>
+        <v>12.25</v>
       </c>
       <c r="D47">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="E47">
-        <v>17.25</v>
+        <v>14.25</v>
       </c>
       <c r="F47">
-        <v>9.75</v>
+        <v>8.75</v>
       </c>
       <c r="G47">
-        <v>13.3</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5041,22 +5041,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>382.5</v>
+        <v>329.5</v>
       </c>
       <c r="C48">
-        <v>282.5</v>
+        <v>204.75</v>
       </c>
       <c r="D48">
-        <v>203.5</v>
+        <v>232</v>
       </c>
       <c r="E48">
-        <v>266</v>
+        <v>300.5</v>
       </c>
       <c r="F48">
-        <v>278.5</v>
+        <v>218.25</v>
       </c>
       <c r="G48">
-        <v>282.6</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5166,22 +5166,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>198.5</v>
+        <v>86.5</v>
       </c>
       <c r="C4">
-        <v>588</v>
+        <v>267.75</v>
       </c>
       <c r="D4">
-        <v>356.5</v>
+        <v>157.5</v>
       </c>
       <c r="E4">
-        <v>205.75</v>
+        <v>125.25</v>
       </c>
       <c r="F4">
-        <v>379.5</v>
+        <v>83</v>
       </c>
       <c r="G4">
-        <v>345.65</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5281,22 +5281,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>182.75</v>
+        <v>125.25</v>
       </c>
       <c r="C9">
-        <v>668.75</v>
+        <v>375.5</v>
       </c>
       <c r="D9">
-        <v>529.75</v>
+        <v>300.5</v>
       </c>
       <c r="E9">
-        <v>175.25</v>
+        <v>221.25</v>
       </c>
       <c r="F9">
-        <v>124.25</v>
+        <v>75</v>
       </c>
       <c r="G9">
-        <v>336.15</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5373,22 +5373,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>198.5</v>
+        <v>86.5</v>
       </c>
       <c r="C13">
-        <v>588</v>
+        <v>267.75</v>
       </c>
       <c r="D13">
-        <v>356.5</v>
+        <v>157.5</v>
       </c>
       <c r="E13">
-        <v>205.75</v>
+        <v>125.25</v>
       </c>
       <c r="F13">
-        <v>379.5</v>
+        <v>83</v>
       </c>
       <c r="G13">
-        <v>345.65</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5396,22 +5396,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>197</v>
+        <v>85.75</v>
       </c>
       <c r="C14">
-        <v>636.75</v>
+        <v>279.5</v>
       </c>
       <c r="D14">
-        <v>361.5</v>
+        <v>147.25</v>
       </c>
       <c r="E14">
-        <v>208</v>
+        <v>125.75</v>
       </c>
       <c r="F14">
-        <v>377</v>
+        <v>83.25</v>
       </c>
       <c r="G14">
-        <v>356.05</v>
+        <v>144.3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5419,22 +5419,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>204</v>
+        <v>109.25</v>
       </c>
       <c r="C15">
-        <v>748.75</v>
+        <v>509</v>
       </c>
       <c r="D15">
-        <v>419.75</v>
+        <v>352.25</v>
       </c>
       <c r="E15">
-        <v>193.5</v>
+        <v>125.75</v>
       </c>
       <c r="F15">
-        <v>486.25</v>
+        <v>88.25</v>
       </c>
       <c r="G15">
-        <v>410.45</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5511,22 +5511,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="C19">
-        <v>29.75</v>
+        <v>26.25</v>
       </c>
       <c r="D19">
-        <v>51.75</v>
+        <v>25.25</v>
       </c>
       <c r="E19">
-        <v>21.75</v>
+        <v>20.75</v>
       </c>
       <c r="F19">
-        <v>12.75</v>
+        <v>14.75</v>
       </c>
       <c r="G19">
-        <v>26.85</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5603,22 +5603,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>182.75</v>
+        <v>125.25</v>
       </c>
       <c r="C23">
-        <v>668.75</v>
+        <v>375.5</v>
       </c>
       <c r="D23">
-        <v>529.75</v>
+        <v>300.5</v>
       </c>
       <c r="E23">
-        <v>175.25</v>
+        <v>221.25</v>
       </c>
       <c r="F23">
-        <v>124.25</v>
+        <v>75</v>
       </c>
       <c r="G23">
-        <v>336.15</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5626,22 +5626,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>182.75</v>
+        <v>123.75</v>
       </c>
       <c r="C24">
-        <v>654</v>
+        <v>359.5</v>
       </c>
       <c r="D24">
-        <v>554.75</v>
+        <v>276.75</v>
       </c>
       <c r="E24">
-        <v>239.75</v>
+        <v>219.5</v>
       </c>
       <c r="F24">
-        <v>121.75</v>
+        <v>75</v>
       </c>
       <c r="G24">
-        <v>350.6</v>
+        <v>210.9</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5649,22 +5649,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>288.5</v>
+        <v>194</v>
       </c>
       <c r="C25">
-        <v>819.75</v>
+        <v>640.5</v>
       </c>
       <c r="D25">
-        <v>508</v>
+        <v>423.5</v>
       </c>
       <c r="E25">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="F25">
-        <v>229</v>
+        <v>109.5</v>
       </c>
       <c r="G25">
-        <v>406.45</v>
+        <v>320.3</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5741,22 +5741,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>197</v>
+        <v>85.75</v>
       </c>
       <c r="C29">
-        <v>636.75</v>
+        <v>279.5</v>
       </c>
       <c r="D29">
-        <v>361.5</v>
+        <v>147.25</v>
       </c>
       <c r="E29">
-        <v>208</v>
+        <v>125.75</v>
       </c>
       <c r="F29">
-        <v>377</v>
+        <v>83.25</v>
       </c>
       <c r="G29">
-        <v>356.05</v>
+        <v>144.3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5764,22 +5764,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>204</v>
+        <v>109.25</v>
       </c>
       <c r="C30">
-        <v>748.75</v>
+        <v>509</v>
       </c>
       <c r="D30">
-        <v>419.75</v>
+        <v>352.25</v>
       </c>
       <c r="E30">
-        <v>193.5</v>
+        <v>125.75</v>
       </c>
       <c r="F30">
-        <v>486.25</v>
+        <v>88.25</v>
       </c>
       <c r="G30">
-        <v>410.45</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5787,22 +5787,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>199.5</v>
+        <v>113</v>
       </c>
       <c r="C31">
-        <v>804.5</v>
+        <v>488.75</v>
       </c>
       <c r="D31">
-        <v>428.75</v>
+        <v>376.5</v>
       </c>
       <c r="E31">
-        <v>238.75</v>
+        <v>147.5</v>
       </c>
       <c r="F31">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="G31">
-        <v>412.1</v>
+        <v>241.75</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5902,22 +5902,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="C36">
-        <v>29.75</v>
+        <v>26.25</v>
       </c>
       <c r="D36">
-        <v>51.75</v>
+        <v>25.25</v>
       </c>
       <c r="E36">
-        <v>21.75</v>
+        <v>20.75</v>
       </c>
       <c r="F36">
-        <v>12.75</v>
+        <v>14.75</v>
       </c>
       <c r="G36">
-        <v>26.85</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5925,22 +5925,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>24.75</v>
+        <v>22.75</v>
       </c>
       <c r="C37">
-        <v>33.25</v>
+        <v>28.5</v>
       </c>
       <c r="D37">
-        <v>46.5</v>
+        <v>31.25</v>
       </c>
       <c r="E37">
-        <v>28.25</v>
+        <v>22.5</v>
       </c>
       <c r="F37">
-        <v>17</v>
+        <v>15.25</v>
       </c>
       <c r="G37">
-        <v>29.95</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5971,22 +5971,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>182.75</v>
+        <v>123.75</v>
       </c>
       <c r="C39">
-        <v>654</v>
+        <v>359.5</v>
       </c>
       <c r="D39">
-        <v>554.75</v>
+        <v>276.75</v>
       </c>
       <c r="E39">
-        <v>239.75</v>
+        <v>219.5</v>
       </c>
       <c r="F39">
-        <v>121.75</v>
+        <v>75</v>
       </c>
       <c r="G39">
-        <v>350.6</v>
+        <v>210.9</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5994,22 +5994,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>288.5</v>
+        <v>194</v>
       </c>
       <c r="C40">
-        <v>819.75</v>
+        <v>640.5</v>
       </c>
       <c r="D40">
-        <v>508</v>
+        <v>423.5</v>
       </c>
       <c r="E40">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="F40">
-        <v>229</v>
+        <v>109.5</v>
       </c>
       <c r="G40">
-        <v>406.45</v>
+        <v>320.3</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6017,22 +6017,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>320.75</v>
+        <v>183.5</v>
       </c>
       <c r="C41">
-        <v>848</v>
+        <v>642.25</v>
       </c>
       <c r="D41">
-        <v>516</v>
+        <v>427.75</v>
       </c>
       <c r="E41">
-        <v>127.25</v>
+        <v>207</v>
       </c>
       <c r="F41">
-        <v>217.25</v>
+        <v>98.5</v>
       </c>
       <c r="G41">
-        <v>405.85</v>
+        <v>311.8</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6063,22 +6063,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>199.5</v>
+        <v>113</v>
       </c>
       <c r="C43">
-        <v>804.5</v>
+        <v>488.75</v>
       </c>
       <c r="D43">
-        <v>428.75</v>
+        <v>376.5</v>
       </c>
       <c r="E43">
-        <v>238.75</v>
+        <v>147.5</v>
       </c>
       <c r="F43">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="G43">
-        <v>412.1</v>
+        <v>241.75</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6155,22 +6155,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>24.75</v>
+        <v>22.75</v>
       </c>
       <c r="C47">
-        <v>33.25</v>
+        <v>28.5</v>
       </c>
       <c r="D47">
-        <v>46.5</v>
+        <v>31.25</v>
       </c>
       <c r="E47">
-        <v>28.25</v>
+        <v>22.5</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>15.25</v>
       </c>
       <c r="G47">
-        <v>29.95</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6178,22 +6178,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>320.75</v>
+        <v>183.5</v>
       </c>
       <c r="C48">
-        <v>848</v>
+        <v>642.25</v>
       </c>
       <c r="D48">
-        <v>516</v>
+        <v>427.75</v>
       </c>
       <c r="E48">
-        <v>127.25</v>
+        <v>207</v>
       </c>
       <c r="F48">
-        <v>217.25</v>
+        <v>98.5</v>
       </c>
       <c r="G48">
-        <v>405.85</v>
+        <v>311.8</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6303,22 +6303,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>10.25</v>
       </c>
       <c r="C4">
+        <v>17.5</v>
+      </c>
+      <c r="D4">
         <v>16.25</v>
       </c>
-      <c r="D4">
-        <v>21.75</v>
-      </c>
       <c r="E4">
-        <v>18.75</v>
+        <v>14.5</v>
       </c>
       <c r="F4">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="G4">
-        <v>15.8</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -6375,19 +6375,19 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>9</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -6421,19 +6421,19 @@
         <v>10.5</v>
       </c>
       <c r="C9">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="D9">
+        <v>14.5</v>
+      </c>
+      <c r="E9">
         <v>18.5</v>
       </c>
-      <c r="E9">
-        <v>16</v>
-      </c>
       <c r="F9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>13.7</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6464,13 +6464,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D11">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -6479,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6510,22 +6510,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="D13">
-        <v>11.75</v>
+        <v>11.25</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6533,22 +6533,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="C14">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="D14">
-        <v>19.75</v>
+        <v>15.75</v>
       </c>
       <c r="E14">
-        <v>15.75</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="G14">
-        <v>14.25</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6556,22 +6556,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>10.5</v>
+        <v>18.25</v>
       </c>
       <c r="C15">
-        <v>21.75</v>
+        <v>18.25</v>
       </c>
       <c r="D15">
-        <v>26.75</v>
+        <v>18.75</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>20.75</v>
+        <v>23.75</v>
       </c>
       <c r="G15">
-        <v>19.15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6579,22 +6579,22 @@
         <v>21</v>
       </c>
       <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
         <v>6</v>
       </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
       <c r="D16">
-        <v>10</v>
+        <v>11.75</v>
       </c>
       <c r="E16">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6651,19 +6651,19 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="D19">
-        <v>13.75</v>
+        <v>15.25</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="G19">
-        <v>9.35</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6697,19 +6697,19 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="D21">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="E21">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6717,16 +6717,16 @@
         <v>27</v>
       </c>
       <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
         <v>5.25</v>
       </c>
-      <c r="C22">
+      <c r="D22">
+        <v>10.25</v>
+      </c>
+      <c r="E22">
         <v>6</v>
-      </c>
-      <c r="D22">
-        <v>9.5</v>
-      </c>
-      <c r="E22">
-        <v>5.75</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -6740,10 +6740,10 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>9.25</v>
@@ -6752,10 +6752,10 @@
         <v>6.75</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -6766,19 +6766,19 @@
         <v>10.5</v>
       </c>
       <c r="C24">
-        <v>16.5</v>
+        <v>13.25</v>
       </c>
       <c r="D24">
-        <v>14.75</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>13.05</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6786,22 +6786,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>10.75</v>
+        <v>15.5</v>
       </c>
       <c r="C25">
-        <v>14.5</v>
+        <v>11.75</v>
       </c>
       <c r="D25">
+        <v>18.75</v>
+      </c>
+      <c r="E25">
         <v>23.5</v>
       </c>
-      <c r="E25">
-        <v>13.25</v>
-      </c>
       <c r="F25">
-        <v>10.25</v>
+        <v>9.5</v>
       </c>
       <c r="G25">
-        <v>14.45</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6809,22 +6809,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C26">
         <v>8.5</v>
       </c>
       <c r="D26">
-        <v>12.75</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>5.75</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>7.25</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6855,16 +6855,16 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C28">
+        <v>6.5</v>
+      </c>
+      <c r="D28">
+        <v>11.5</v>
+      </c>
+      <c r="E28">
         <v>7</v>
-      </c>
-      <c r="D28">
-        <v>11</v>
-      </c>
-      <c r="E28">
-        <v>6.75</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -6878,22 +6878,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>6.55</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6901,22 +6901,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="D30">
-        <v>11.25</v>
+        <v>13</v>
       </c>
       <c r="E30">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="G30">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6924,22 +6924,22 @@
         <v>36</v>
       </c>
       <c r="B31">
+        <v>10.5</v>
+      </c>
+      <c r="C31">
+        <v>11.75</v>
+      </c>
+      <c r="D31">
+        <v>15.75</v>
+      </c>
+      <c r="E31">
         <v>10</v>
       </c>
-      <c r="C31">
-        <v>16.5</v>
-      </c>
-      <c r="D31">
-        <v>21.75</v>
-      </c>
-      <c r="E31">
-        <v>11.25</v>
-      </c>
       <c r="F31">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="G31">
-        <v>13.55</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6947,22 +6947,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C32">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>11.75</v>
       </c>
       <c r="E32">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>6.35</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7016,22 +7016,22 @@
         <v>40</v>
       </c>
       <c r="B35">
+        <v>5.75</v>
+      </c>
+      <c r="C35">
+        <v>7.25</v>
+      </c>
+      <c r="D35">
+        <v>12.5</v>
+      </c>
+      <c r="E35">
         <v>6</v>
-      </c>
-      <c r="C35">
-        <v>6.75</v>
-      </c>
-      <c r="D35">
-        <v>10.5</v>
-      </c>
-      <c r="E35">
-        <v>5.75</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7042,19 +7042,19 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="D36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="D37">
-        <v>13.75</v>
+        <v>15.25</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="G37">
-        <v>9.949999999999999</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7088,10 +7088,10 @@
         <v>5</v>
       </c>
       <c r="C38">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="D38">
-        <v>11.5</v>
+        <v>10.25</v>
       </c>
       <c r="E38">
         <v>6.75</v>
@@ -7100,7 +7100,7 @@
         <v>2</v>
       </c>
       <c r="G38">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -7108,22 +7108,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D39">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="E39">
         <v>6.75</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7131,22 +7131,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C40">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>11.75</v>
+        <v>12.5</v>
       </c>
       <c r="E40">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="F40">
         <v>4.75</v>
       </c>
       <c r="G40">
-        <v>7.35</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -7154,22 +7154,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="C41">
-        <v>15.75</v>
+        <v>11.75</v>
       </c>
       <c r="D41">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="G41">
-        <v>13.55</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -7177,22 +7177,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>8.5</v>
       </c>
       <c r="D42">
-        <v>12.75</v>
+        <v>14</v>
       </c>
       <c r="E42">
         <v>5.75</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>7.35</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7200,22 +7200,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C43">
-        <v>8.25</v>
+        <v>5.75</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="G43">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7223,22 +7223,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F44">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="G44">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7269,22 +7269,22 @@
         <v>51</v>
       </c>
       <c r="B46">
+        <v>5.75</v>
+      </c>
+      <c r="C46">
+        <v>8.5</v>
+      </c>
+      <c r="D46">
+        <v>13</v>
+      </c>
+      <c r="E46">
         <v>6</v>
       </c>
-      <c r="C46">
-        <v>8</v>
-      </c>
-      <c r="D46">
-        <v>11.75</v>
-      </c>
-      <c r="E46">
-        <v>5.75</v>
-      </c>
       <c r="F46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>6.9</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7298,16 +7298,16 @@
         <v>8.5</v>
       </c>
       <c r="D47">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7315,22 +7315,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C48">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="D48">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="E48">
         <v>6.75</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7341,19 +7341,19 @@
         <v>5</v>
       </c>
       <c r="C49">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G49">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Rekap/Keseluruhan_All.xlsx
+++ b/Excel/Rekap/Keseluruhan_All.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="71">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -102,6 +102,9 @@
     <t>JPS-PPO</t>
   </si>
   <si>
+    <t>JPS-TPF</t>
+  </si>
+  <si>
     <t>TPF-PPO</t>
   </si>
   <si>
@@ -144,13 +147,25 @@
     <t>JPS-BDS-PPO</t>
   </si>
   <si>
+    <t>JPS-BDS-TPF</t>
+  </si>
+  <si>
     <t>JPS-BRC-PPO</t>
+  </si>
+  <si>
+    <t>JPS-BRC-TPF</t>
   </si>
   <si>
     <t>JPS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-GL-PPO</t>
+  </si>
+  <si>
+    <t>JPS-GL-TPF</t>
+  </si>
+  <si>
+    <t>JPS-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-BRC-TPF-PPO</t>
@@ -171,19 +186,52 @@
     <t>JPS-BDS-BRC-PPO</t>
   </si>
   <si>
+    <t>JPS-BDS-BRC-TPF</t>
+  </si>
+  <si>
     <t>JPS-BDS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-BDS-GL-PPO</t>
   </si>
   <si>
+    <t>JPS-BDS-GL-TPF</t>
+  </si>
+  <si>
+    <t>JPS-BDS-TPF-PPO</t>
+  </si>
+  <si>
+    <t>JPS-BRC-TPF-PPO</t>
+  </si>
+  <si>
     <t>JPS-GL-BRC-PPO</t>
+  </si>
+  <si>
+    <t>JPS-GL-BRC-TPF</t>
+  </si>
+  <si>
+    <t>JPS-GL-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-GL-BRC-TPF-PPO</t>
   </si>
   <si>
+    <t>JPS-BDS-BRC-TPF-PPO</t>
+  </si>
+  <si>
     <t>JPS-BDS-GL-BRC-PPO</t>
+  </si>
+  <si>
+    <t>JPS-BDS-GL-BRC-TPF</t>
+  </si>
+  <si>
+    <t>JPS-BDS-GL-TPF-PPO</t>
+  </si>
+  <si>
+    <t>JPS-GL-BRC-TPF-PPO</t>
+  </si>
+  <si>
+    <t>JPS-BDS-GL-BRC-TPF-PPO</t>
   </si>
 </sst>
 </file>
@@ -541,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -572,22 +620,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.0452317</v>
+        <v>0.04764295</v>
       </c>
       <c r="C2">
-        <v>0.036541475</v>
+        <v>0.03907635000000001</v>
       </c>
       <c r="D2">
-        <v>0.03091415</v>
+        <v>0.032853575</v>
       </c>
       <c r="E2">
-        <v>0.06115425</v>
+        <v>0.064927525</v>
       </c>
       <c r="F2">
-        <v>0.09424257500000002</v>
+        <v>0.100059375</v>
       </c>
       <c r="G2">
-        <v>0.05361683</v>
+        <v>0.056911955</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +643,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006213449999999999</v>
+        <v>0.006648925</v>
       </c>
       <c r="C3">
-        <v>0.0069333</v>
+        <v>0.007088275</v>
       </c>
       <c r="D3">
-        <v>0.005457675</v>
+        <v>0.005857325</v>
       </c>
       <c r="E3">
-        <v>0.006543125</v>
+        <v>0.0070426</v>
       </c>
       <c r="F3">
-        <v>0.004896175000000001</v>
+        <v>0.005207275</v>
       </c>
       <c r="G3">
-        <v>0.006008745</v>
+        <v>0.00636888</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -618,22 +666,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.002451675</v>
+        <v>0.002588225</v>
       </c>
       <c r="C4">
-        <v>0.008575624999999998</v>
+        <v>0.00916025</v>
       </c>
       <c r="D4">
-        <v>0.00427445</v>
+        <v>0.004433325</v>
       </c>
       <c r="E4">
-        <v>0.00389225</v>
+        <v>0.004095125</v>
       </c>
       <c r="F4">
-        <v>0.002488175</v>
+        <v>0.002589575</v>
       </c>
       <c r="G4">
-        <v>0.004336435</v>
+        <v>0.004573300000000001</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,22 +689,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.0237125</v>
+        <v>0.025407225</v>
       </c>
       <c r="C5">
-        <v>0.0318581</v>
+        <v>0.03406155</v>
       </c>
       <c r="D5">
-        <v>0.024729475</v>
+        <v>0.026743175</v>
       </c>
       <c r="E5">
-        <v>0.03515307500000001</v>
+        <v>0.037765675</v>
       </c>
       <c r="F5">
-        <v>0.04533089999999999</v>
+        <v>0.04814410000000001</v>
       </c>
       <c r="G5">
-        <v>0.03215681</v>
+        <v>0.034424345</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -664,22 +712,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.004762325</v>
+        <v>0.005064474999999999</v>
       </c>
       <c r="C6">
-        <v>0.004164775000000001</v>
+        <v>0.004571675000000001</v>
       </c>
       <c r="D6">
-        <v>0.006717575</v>
+        <v>0.0071214</v>
       </c>
       <c r="E6">
-        <v>0.006517675</v>
+        <v>0.006872624999999999</v>
       </c>
       <c r="F6">
-        <v>0.010284</v>
+        <v>0.010961475</v>
       </c>
       <c r="G6">
-        <v>0.00648927</v>
+        <v>0.00691833</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -687,22 +735,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.0449744</v>
+        <v>0.0474748</v>
       </c>
       <c r="C7">
-        <v>0.03718870000000001</v>
+        <v>0.038919525</v>
       </c>
       <c r="D7">
-        <v>0.0312947</v>
+        <v>0.0329933</v>
       </c>
       <c r="E7">
-        <v>0.06227405</v>
+        <v>0.065116125</v>
       </c>
       <c r="F7">
-        <v>0.094641925</v>
+        <v>0.09991892499999999</v>
       </c>
       <c r="G7">
-        <v>0.05407475500000001</v>
+        <v>0.05688453499999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -710,22 +758,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.04234105000000001</v>
+        <v>0.04521294999999999</v>
       </c>
       <c r="C8">
-        <v>0.035038625</v>
+        <v>0.03770335</v>
       </c>
       <c r="D8">
-        <v>0.02798665</v>
+        <v>0.0296508</v>
       </c>
       <c r="E8">
-        <v>0.058227925</v>
+        <v>0.0617661</v>
       </c>
       <c r="F8">
-        <v>0.09482202499999999</v>
+        <v>0.1015836</v>
       </c>
       <c r="G8">
-        <v>0.051683255</v>
+        <v>0.05518335999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -733,22 +781,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.0009395500000000002</v>
+        <v>0.000970725</v>
       </c>
       <c r="C9">
-        <v>0.0026948</v>
+        <v>0.002852425</v>
       </c>
       <c r="D9">
-        <v>0.0019456</v>
+        <v>0.002062475</v>
       </c>
       <c r="E9">
-        <v>0.001561875</v>
+        <v>0.0016569</v>
       </c>
       <c r="F9">
-        <v>0.000569225</v>
+        <v>0.000586175</v>
       </c>
       <c r="G9">
-        <v>0.00154221</v>
+        <v>0.00162574</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -756,22 +804,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.007290124999999999</v>
+        <v>0.007698824999999999</v>
       </c>
       <c r="C10">
-        <v>0.007981324999999999</v>
+        <v>0.00850335</v>
       </c>
       <c r="D10">
-        <v>0.005205999999999999</v>
+        <v>0.005580825000000001</v>
       </c>
       <c r="E10">
-        <v>0.00816185</v>
+        <v>0.008663000000000001</v>
       </c>
       <c r="F10">
-        <v>0.006714175000000001</v>
+        <v>0.007167125000000001</v>
       </c>
       <c r="G10">
-        <v>0.007070695</v>
+        <v>0.007522625000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -779,22 +827,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.00654245</v>
+        <v>0.00665715</v>
       </c>
       <c r="C11">
-        <v>0.00699865</v>
+        <v>0.007073075</v>
       </c>
       <c r="D11">
-        <v>0.005720525000000001</v>
+        <v>0.00581245</v>
       </c>
       <c r="E11">
-        <v>0.006909925000000001</v>
+        <v>0.007052675</v>
       </c>
       <c r="F11">
-        <v>0.005365475</v>
+        <v>0.005158225000000001</v>
       </c>
       <c r="G11">
-        <v>0.006307405</v>
+        <v>0.006350715</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -802,22 +850,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.0069285</v>
+        <v>0.00705945</v>
       </c>
       <c r="C12">
-        <v>0.007235525</v>
+        <v>0.0074979</v>
       </c>
       <c r="D12">
-        <v>0.005759675</v>
+        <v>0.005938300000000001</v>
       </c>
       <c r="E12">
-        <v>0.007071025</v>
+        <v>0.007429575000000001</v>
       </c>
       <c r="F12">
-        <v>0.0051985</v>
+        <v>0.0054997</v>
       </c>
       <c r="G12">
-        <v>0.006438645</v>
+        <v>0.006684985</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -825,22 +873,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.00277895</v>
+        <v>0.002602025</v>
       </c>
       <c r="C13">
-        <v>0.008770975</v>
+        <v>0.009150450000000001</v>
       </c>
       <c r="D13">
-        <v>0.004296474999999999</v>
+        <v>0.0043745</v>
       </c>
       <c r="E13">
-        <v>0.004152275</v>
+        <v>0.00412535</v>
       </c>
       <c r="F13">
-        <v>0.00278745</v>
+        <v>0.0026058</v>
       </c>
       <c r="G13">
-        <v>0.004557225</v>
+        <v>0.004571625</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -848,22 +896,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.0024737</v>
+        <v>0.002617525</v>
       </c>
       <c r="C14">
-        <v>0.009231524999999999</v>
+        <v>0.009910274999999998</v>
       </c>
       <c r="D14">
-        <v>0.0039586</v>
+        <v>0.004175</v>
       </c>
       <c r="E14">
-        <v>0.003883825</v>
+        <v>0.004148975</v>
       </c>
       <c r="F14">
-        <v>0.0025647</v>
+        <v>0.0026973</v>
       </c>
       <c r="G14">
-        <v>0.00442247</v>
+        <v>0.004709814999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -871,22 +919,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.00312735</v>
+        <v>0.003251525</v>
       </c>
       <c r="C15">
-        <v>0.015551325</v>
+        <v>0.01651405</v>
       </c>
       <c r="D15">
-        <v>0.01089085</v>
+        <v>0.011281175</v>
       </c>
       <c r="E15">
-        <v>0.004259750000000001</v>
+        <v>0.00449935</v>
       </c>
       <c r="F15">
-        <v>0.002602775</v>
+        <v>0.002718025</v>
       </c>
       <c r="G15">
-        <v>0.00728641</v>
+        <v>0.007652824999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -894,22 +942,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.02398195</v>
+        <v>0.025315325</v>
       </c>
       <c r="C16">
-        <v>0.031962125</v>
+        <v>0.03400692500000001</v>
       </c>
       <c r="D16">
-        <v>0.025064025</v>
+        <v>0.026732975</v>
       </c>
       <c r="E16">
-        <v>0.03554545</v>
+        <v>0.03734214999999999</v>
       </c>
       <c r="F16">
-        <v>0.046054875</v>
+        <v>0.04814925</v>
       </c>
       <c r="G16">
-        <v>0.032521685</v>
+        <v>0.034309325</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -917,22 +965,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.02494795</v>
+        <v>0.02664795</v>
       </c>
       <c r="C17">
-        <v>0.03118345</v>
+        <v>0.03332055</v>
       </c>
       <c r="D17">
-        <v>0.023824275</v>
+        <v>0.025393925</v>
       </c>
       <c r="E17">
-        <v>0.03257995</v>
+        <v>0.034269675</v>
       </c>
       <c r="F17">
-        <v>0.04261645</v>
+        <v>0.0446882</v>
       </c>
       <c r="G17">
-        <v>0.031030415</v>
+        <v>0.03286405999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -940,22 +988,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.005579049999999999</v>
+        <v>0.0058038</v>
       </c>
       <c r="C18">
-        <v>0.003756375</v>
+        <v>0.0039341</v>
       </c>
       <c r="D18">
-        <v>0.005035599999999999</v>
+        <v>0.005339575</v>
       </c>
       <c r="E18">
-        <v>0.003584725</v>
+        <v>0.003742150000000001</v>
       </c>
       <c r="F18">
-        <v>0.007520725000000001</v>
+        <v>0.0081073</v>
       </c>
       <c r="G18">
-        <v>0.005095295</v>
+        <v>0.005385384999999999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -963,22 +1011,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.002838025</v>
+        <v>0.002952375</v>
       </c>
       <c r="C19">
-        <v>0.002983449999999999</v>
+        <v>0.003056875</v>
       </c>
       <c r="D19">
-        <v>0.002475825</v>
+        <v>0.00255635</v>
       </c>
       <c r="E19">
-        <v>0.00195465</v>
+        <v>0.0020707</v>
       </c>
       <c r="F19">
-        <v>0.0041357</v>
+        <v>0.00431775</v>
       </c>
       <c r="G19">
-        <v>0.002877530000000001</v>
+        <v>0.00299081</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -986,22 +1034,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.004782</v>
+        <v>0.00497655</v>
       </c>
       <c r="C20">
-        <v>0.004613674999999999</v>
+        <v>0.0048165</v>
       </c>
       <c r="D20">
-        <v>0.004806325</v>
+        <v>0.00503</v>
       </c>
       <c r="E20">
-        <v>0.004763125</v>
+        <v>0.005074025</v>
       </c>
       <c r="F20">
-        <v>0.008031725</v>
+        <v>0.008606974999999999</v>
       </c>
       <c r="G20">
-        <v>0.00539937</v>
+        <v>0.00570081</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1009,22 +1057,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.004867349999999999</v>
+        <v>0.00506885</v>
       </c>
       <c r="C21">
-        <v>0.0042467</v>
+        <v>0.004418875</v>
       </c>
       <c r="D21">
-        <v>0.006716049999999999</v>
+        <v>0.007092275</v>
       </c>
       <c r="E21">
-        <v>0.006551224999999999</v>
+        <v>0.00688325</v>
       </c>
       <c r="F21">
-        <v>0.010499225</v>
+        <v>0.010936275</v>
       </c>
       <c r="G21">
-        <v>0.006576109999999999</v>
+        <v>0.006879905</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1032,22 +1080,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.04324717499999999</v>
+        <v>0.0148665</v>
       </c>
       <c r="C22">
-        <v>0.03570382499999999</v>
+        <v>0.006751075</v>
       </c>
       <c r="D22">
-        <v>0.0281297</v>
+        <v>0.0078335</v>
       </c>
       <c r="E22">
-        <v>0.05806404999999999</v>
+        <v>0.014940275</v>
       </c>
       <c r="F22">
-        <v>0.094231125</v>
+        <v>0.013755725</v>
       </c>
       <c r="G22">
-        <v>0.05187517499999998</v>
+        <v>0.011629415</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1055,22 +1103,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.001228225</v>
+        <v>0.0455897</v>
       </c>
       <c r="C23">
-        <v>0.0030199</v>
+        <v>0.0374558</v>
       </c>
       <c r="D23">
-        <v>0.002174375</v>
+        <v>0.02972055000000001</v>
       </c>
       <c r="E23">
-        <v>0.001762875</v>
+        <v>0.0617829</v>
       </c>
       <c r="F23">
-        <v>0.0008558999999999999</v>
+        <v>0.102036475</v>
       </c>
       <c r="G23">
-        <v>0.001808255</v>
+        <v>0.055317085</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1078,22 +1126,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.00113705</v>
+        <v>0.00096265</v>
       </c>
       <c r="C24">
-        <v>0.003017425</v>
+        <v>0.002906475</v>
       </c>
       <c r="D24">
-        <v>0.00222085</v>
+        <v>0.002076575</v>
       </c>
       <c r="E24">
-        <v>0.00193915</v>
+        <v>0.00166415</v>
       </c>
       <c r="F24">
-        <v>0.0006869250000000001</v>
+        <v>0.0005872750000000001</v>
       </c>
       <c r="G24">
-        <v>0.00180028</v>
+        <v>0.001639425</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1101,22 +1149,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.001719625</v>
+        <v>0.001161475</v>
       </c>
       <c r="C25">
-        <v>0.005143375</v>
+        <v>0.003242225</v>
       </c>
       <c r="D25">
-        <v>0.003215625</v>
+        <v>0.00225865</v>
       </c>
       <c r="E25">
-        <v>0.0020125</v>
+        <v>0.00192805</v>
       </c>
       <c r="F25">
-        <v>0.0009768749999999999</v>
+        <v>0.0006991</v>
       </c>
       <c r="G25">
-        <v>0.0026136</v>
+        <v>0.0018579</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1124,22 +1172,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.007620125</v>
+        <v>0.00176135</v>
       </c>
       <c r="C26">
-        <v>0.008429300000000001</v>
+        <v>0.005455374999999999</v>
       </c>
       <c r="D26">
-        <v>0.005547825</v>
+        <v>0.00334375</v>
       </c>
       <c r="E26">
-        <v>0.00830495</v>
+        <v>0.002134325</v>
       </c>
       <c r="F26">
-        <v>0.007005974999999999</v>
+        <v>0.00100945</v>
       </c>
       <c r="G26">
-        <v>0.007381634999999999</v>
+        <v>0.00274085</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1147,22 +1195,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.007696725</v>
+        <v>0.0077148</v>
       </c>
       <c r="C27">
-        <v>0.008579450000000001</v>
+        <v>0.008472250000000001</v>
       </c>
       <c r="D27">
-        <v>0.0055329</v>
+        <v>0.005567375</v>
       </c>
       <c r="E27">
-        <v>0.008242050000000001</v>
+        <v>0.008672175000000001</v>
       </c>
       <c r="F27">
-        <v>0.007113400000000001</v>
+        <v>0.007168425000000001</v>
       </c>
       <c r="G27">
-        <v>0.007432905000000001</v>
+        <v>0.007519005</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1170,22 +1218,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.007172224999999999</v>
+        <v>0.007969775</v>
       </c>
       <c r="C28">
-        <v>0.007512549999999999</v>
+        <v>0.008887275</v>
       </c>
       <c r="D28">
-        <v>0.005931375</v>
+        <v>0.005725299999999999</v>
       </c>
       <c r="E28">
-        <v>0.007339075</v>
+        <v>0.008598900000000001</v>
       </c>
       <c r="F28">
-        <v>0.005680175</v>
+        <v>0.007474900000000001</v>
       </c>
       <c r="G28">
-        <v>0.006727079999999999</v>
+        <v>0.00773123</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1193,22 +1241,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.0028725</v>
+        <v>0.007030025000000001</v>
       </c>
       <c r="C29">
-        <v>0.009501275</v>
+        <v>0.0075126</v>
       </c>
       <c r="D29">
-        <v>0.004162374999999999</v>
+        <v>0.005954200000000001</v>
       </c>
       <c r="E29">
-        <v>0.004142375</v>
+        <v>0.007359650000000001</v>
       </c>
       <c r="F29">
-        <v>0.002841550000000001</v>
+        <v>0.0054783</v>
       </c>
       <c r="G29">
-        <v>0.004704015000000001</v>
+        <v>0.006666955</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1216,22 +1264,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.003363525</v>
+        <v>0.002613975</v>
       </c>
       <c r="C30">
-        <v>0.015473075</v>
+        <v>0.00995505</v>
       </c>
       <c r="D30">
-        <v>0.010802075</v>
+        <v>0.004153125</v>
       </c>
       <c r="E30">
-        <v>0.004434975</v>
+        <v>0.00418445</v>
       </c>
       <c r="F30">
-        <v>0.00287335</v>
+        <v>0.0027193</v>
       </c>
       <c r="G30">
-        <v>0.007389399999999999</v>
+        <v>0.004725180000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1239,22 +1287,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.003466250000000001</v>
+        <v>0.00325965</v>
       </c>
       <c r="C31">
-        <v>0.014848125</v>
+        <v>0.016506525</v>
       </c>
       <c r="D31">
-        <v>0.01217725</v>
+        <v>0.0113073</v>
       </c>
       <c r="E31">
-        <v>0.005230249999999999</v>
+        <v>0.004469550000000001</v>
       </c>
       <c r="F31">
-        <v>0.002642</v>
+        <v>0.00271435</v>
       </c>
       <c r="G31">
-        <v>0.007672775</v>
+        <v>0.007651475</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1262,22 +1310,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.02514425</v>
+        <v>0.00368675</v>
       </c>
       <c r="C32">
-        <v>0.03208905</v>
+        <v>0.0153672</v>
       </c>
       <c r="D32">
-        <v>0.0239537</v>
+        <v>0.01285465</v>
       </c>
       <c r="E32">
-        <v>0.032833225</v>
+        <v>0.00551215</v>
       </c>
       <c r="F32">
-        <v>0.042393575</v>
+        <v>0.00270755</v>
       </c>
       <c r="G32">
-        <v>0.03128276</v>
+        <v>0.00802566</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1285,22 +1333,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.0051265</v>
+        <v>0.02664265</v>
       </c>
       <c r="C33">
-        <v>0.0029182</v>
+        <v>0.03332524999999999</v>
       </c>
       <c r="D33">
-        <v>0.002500075</v>
+        <v>0.0253889</v>
       </c>
       <c r="E33">
-        <v>0.0027361</v>
+        <v>0.03422942499999999</v>
       </c>
       <c r="F33">
-        <v>0.005911650000000001</v>
+        <v>0.04470304999999999</v>
       </c>
       <c r="G33">
-        <v>0.003838505</v>
+        <v>0.03285785499999999</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1308,22 +1356,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.0084963</v>
+        <v>0.005387975</v>
       </c>
       <c r="C34">
-        <v>0.0038308</v>
+        <v>0.00310015</v>
       </c>
       <c r="D34">
-        <v>0.003547750000000001</v>
+        <v>0.00266785</v>
       </c>
       <c r="E34">
-        <v>0.0037388</v>
+        <v>0.0029206</v>
       </c>
       <c r="F34">
-        <v>0.0090531</v>
+        <v>0.006312575000000001</v>
       </c>
       <c r="G34">
-        <v>0.005733350000000001</v>
+        <v>0.00407783</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1331,22 +1379,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.0055876</v>
+        <v>0.008894300000000001</v>
       </c>
       <c r="C35">
-        <v>0.0038815</v>
+        <v>0.00416915</v>
       </c>
       <c r="D35">
-        <v>0.005151899999999999</v>
+        <v>0.003651950000000001</v>
       </c>
       <c r="E35">
-        <v>0.00359165</v>
+        <v>0.003958925</v>
       </c>
       <c r="F35">
-        <v>0.007732525000000001</v>
+        <v>0.009440749999999999</v>
       </c>
       <c r="G35">
-        <v>0.005189035</v>
+        <v>0.006023015</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1354,22 +1402,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.002909225</v>
+        <v>0.005776525</v>
       </c>
       <c r="C36">
-        <v>0.002985025</v>
+        <v>0.0039381</v>
       </c>
       <c r="D36">
-        <v>0.002501925</v>
+        <v>0.005328075</v>
       </c>
       <c r="E36">
-        <v>0.002061375</v>
+        <v>0.00377575</v>
       </c>
       <c r="F36">
-        <v>0.004136475</v>
+        <v>0.007946099999999999</v>
       </c>
       <c r="G36">
-        <v>0.002918805</v>
+        <v>0.00535291</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1377,22 +1425,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.003401225</v>
+        <v>0.008011175000000001</v>
       </c>
       <c r="C37">
-        <v>0.002998475</v>
+        <v>0.0065894</v>
       </c>
       <c r="D37">
-        <v>0.003041825</v>
+        <v>0.0045927</v>
       </c>
       <c r="E37">
-        <v>0.00221115</v>
+        <v>0.0067014</v>
       </c>
       <c r="F37">
-        <v>0.004478025</v>
+        <v>0.006958925000000001</v>
       </c>
       <c r="G37">
-        <v>0.00322614</v>
+        <v>0.00657072</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1400,22 +1448,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004843399999999999</v>
+        <v>0.002946175</v>
       </c>
       <c r="C38">
-        <v>0.0046894</v>
+        <v>0.003057175</v>
       </c>
       <c r="D38">
-        <v>0.0048502</v>
+        <v>0.002547999999999999</v>
       </c>
       <c r="E38">
-        <v>0.004854</v>
+        <v>0.002130575</v>
       </c>
       <c r="F38">
-        <v>0.00810955</v>
+        <v>0.0043175</v>
       </c>
       <c r="G38">
-        <v>0.00546931</v>
+        <v>0.002999885</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1423,22 +1471,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.00144745</v>
+        <v>0.0039312</v>
       </c>
       <c r="C39">
-        <v>0.003397325000000001</v>
+        <v>0.0040897</v>
       </c>
       <c r="D39">
-        <v>0.00242865</v>
+        <v>0.004911125000000001</v>
       </c>
       <c r="E39">
-        <v>0.00209715</v>
+        <v>0.004627175000000001</v>
       </c>
       <c r="F39">
-        <v>0.00099625</v>
+        <v>0.007101925</v>
       </c>
       <c r="G39">
-        <v>0.002073365</v>
+        <v>0.004932225000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1446,22 +1494,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.002029</v>
+        <v>0.003569025</v>
       </c>
       <c r="C40">
-        <v>0.005658875</v>
+        <v>0.0031267</v>
       </c>
       <c r="D40">
-        <v>0.003432625</v>
+        <v>0.003190175</v>
       </c>
       <c r="E40">
-        <v>0.002223475</v>
+        <v>0.002331975</v>
       </c>
       <c r="F40">
-        <v>0.001226925</v>
+        <v>0.0047347</v>
       </c>
       <c r="G40">
-        <v>0.00291418</v>
+        <v>0.003390514999999999</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1469,22 +1517,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.001856725</v>
+        <v>0.005005575</v>
       </c>
       <c r="C41">
-        <v>0.005913575</v>
+        <v>0.004797575</v>
       </c>
       <c r="D41">
-        <v>0.0038579</v>
+        <v>0.005016675</v>
       </c>
       <c r="E41">
-        <v>0.002137125</v>
+        <v>0.005084475</v>
       </c>
       <c r="F41">
-        <v>0.001035425</v>
+        <v>0.008547475000000001</v>
       </c>
       <c r="G41">
-        <v>0.00296015</v>
+        <v>0.005690354999999999</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1492,22 +1540,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.007849825</v>
+        <v>0.006884325</v>
       </c>
       <c r="C42">
-        <v>0.008754025</v>
+        <v>0.005431375</v>
       </c>
       <c r="D42">
-        <v>0.0057701</v>
+        <v>0.006402025</v>
       </c>
       <c r="E42">
-        <v>0.008487</v>
+        <v>0.008810124999999999</v>
       </c>
       <c r="F42">
-        <v>0.007427700000000001</v>
+        <v>0.013662625</v>
       </c>
       <c r="G42">
-        <v>0.00765773</v>
+        <v>0.008238094999999999</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1515,22 +1563,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.003839375</v>
+        <v>0.01489105</v>
       </c>
       <c r="C43">
-        <v>0.0147082</v>
+        <v>0.00674725</v>
       </c>
       <c r="D43">
-        <v>0.01260295</v>
+        <v>0.007827525</v>
       </c>
       <c r="E43">
-        <v>0.005548125000000001</v>
+        <v>0.01505705</v>
       </c>
       <c r="F43">
-        <v>0.002906525000000001</v>
+        <v>0.01378315</v>
       </c>
       <c r="G43">
-        <v>0.007921035</v>
+        <v>0.011661205</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1538,22 +1586,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.0052448</v>
+        <v>0.001147625</v>
       </c>
       <c r="C44">
-        <v>0.003054025</v>
+        <v>0.003240425</v>
       </c>
       <c r="D44">
-        <v>0.0026214</v>
+        <v>0.002242275</v>
       </c>
       <c r="E44">
-        <v>0.002794999999999999</v>
+        <v>0.001932075</v>
       </c>
       <c r="F44">
-        <v>0.006072925</v>
+        <v>0.000709025</v>
       </c>
       <c r="G44">
-        <v>0.003957629999999999</v>
+        <v>0.001854285</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1561,22 +1609,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.006359800000000001</v>
+        <v>0.001775475</v>
       </c>
       <c r="C45">
-        <v>0.0031642</v>
+        <v>0.005465975000000001</v>
       </c>
       <c r="D45">
-        <v>0.003377875</v>
+        <v>0.003347675</v>
       </c>
       <c r="E45">
-        <v>0.0039372</v>
+        <v>0.002119975</v>
       </c>
       <c r="F45">
-        <v>0.005221325000000001</v>
+        <v>0.0009894750000000001</v>
       </c>
       <c r="G45">
-        <v>0.004412080000000001</v>
+        <v>0.002739715</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1584,22 +1632,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.008485949999999999</v>
+        <v>0.001891</v>
       </c>
       <c r="C46">
-        <v>0.003982275</v>
+        <v>0.006138124999999999</v>
       </c>
       <c r="D46">
-        <v>0.003485475</v>
+        <v>0.004229800000000001</v>
       </c>
       <c r="E46">
-        <v>0.003857775</v>
+        <v>0.00206055</v>
       </c>
       <c r="F46">
-        <v>0.008893700000000001</v>
+        <v>0.0010075</v>
       </c>
       <c r="G46">
-        <v>0.005741035</v>
+        <v>0.003065394999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1607,22 +1655,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.00345695</v>
+        <v>0.0079518</v>
       </c>
       <c r="C47">
-        <v>0.00309425</v>
+        <v>0.008919449999999999</v>
       </c>
       <c r="D47">
-        <v>0.00327605</v>
+        <v>0.005753524999999999</v>
       </c>
       <c r="E47">
-        <v>0.002278075</v>
+        <v>0.008608125000000001</v>
       </c>
       <c r="F47">
-        <v>0.004548775</v>
+        <v>0.0074947</v>
       </c>
       <c r="G47">
-        <v>0.00333082</v>
+        <v>0.007745520000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1630,22 +1678,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.00219415</v>
+        <v>0.0037248</v>
       </c>
       <c r="C48">
-        <v>0.006386675000000001</v>
+        <v>0.015336</v>
       </c>
       <c r="D48">
-        <v>0.004078549999999999</v>
+        <v>0.012926525</v>
       </c>
       <c r="E48">
-        <v>0.002373725</v>
+        <v>0.005517274999999999</v>
       </c>
       <c r="F48">
-        <v>0.001295575</v>
+        <v>0.002710275</v>
       </c>
       <c r="G48">
-        <v>0.003265735</v>
+        <v>0.008042974999999999</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1653,22 +1701,390 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.006457075</v>
+        <v>0.00538015</v>
       </c>
       <c r="C49">
-        <v>0.003174275</v>
+        <v>0.003110925</v>
       </c>
       <c r="D49">
-        <v>0.0035188</v>
+        <v>0.002657675</v>
       </c>
       <c r="E49">
-        <v>0.0040665</v>
+        <v>0.00291705</v>
       </c>
       <c r="F49">
-        <v>0.005316149999999999</v>
+        <v>0.006295375000000001</v>
       </c>
       <c r="G49">
-        <v>0.00450656</v>
+        <v>0.004072235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>0.005427674999999999</v>
+      </c>
+      <c r="C50">
+        <v>0.00435055</v>
+      </c>
+      <c r="D50">
+        <v>0.0040619</v>
+      </c>
+      <c r="E50">
+        <v>0.00545445</v>
+      </c>
+      <c r="F50">
+        <v>0.006943224999999999</v>
+      </c>
+      <c r="G50">
+        <v>0.00524756</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>0.006704675</v>
+      </c>
+      <c r="C51">
+        <v>0.0032546</v>
+      </c>
+      <c r="D51">
+        <v>0.0037517</v>
+      </c>
+      <c r="E51">
+        <v>0.004217275</v>
+      </c>
+      <c r="F51">
+        <v>0.005527850000000001</v>
+      </c>
+      <c r="G51">
+        <v>0.00469122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>0.008865399999999999</v>
+      </c>
+      <c r="C52">
+        <v>0.004041575</v>
+      </c>
+      <c r="D52">
+        <v>0.003652475</v>
+      </c>
+      <c r="E52">
+        <v>0.003971825</v>
+      </c>
+      <c r="F52">
+        <v>0.009466425000000001</v>
+      </c>
+      <c r="G52">
+        <v>0.00599954</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>0.008233499999999999</v>
+      </c>
+      <c r="C53">
+        <v>0.006451324999999999</v>
+      </c>
+      <c r="D53">
+        <v>0.00551735</v>
+      </c>
+      <c r="E53">
+        <v>0.00462885</v>
+      </c>
+      <c r="F53">
+        <v>0.006973825000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.006360970000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>0.008002</v>
+      </c>
+      <c r="C54">
+        <v>0.006575425</v>
+      </c>
+      <c r="D54">
+        <v>0.004588075</v>
+      </c>
+      <c r="E54">
+        <v>0.006677499999999999</v>
+      </c>
+      <c r="F54">
+        <v>0.007012</v>
+      </c>
+      <c r="G54">
+        <v>0.006571</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
+        <v>0.003941525</v>
+      </c>
+      <c r="C55">
+        <v>0.0039752</v>
+      </c>
+      <c r="D55">
+        <v>0.004903275</v>
+      </c>
+      <c r="E55">
+        <v>0.004643325</v>
+      </c>
+      <c r="F55">
+        <v>0.0069938</v>
+      </c>
+      <c r="G55">
+        <v>0.004891425</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>0.003564925</v>
+      </c>
+      <c r="C56">
+        <v>0.00313525</v>
+      </c>
+      <c r="D56">
+        <v>0.003187275</v>
+      </c>
+      <c r="E56">
+        <v>0.0023457</v>
+      </c>
+      <c r="F56">
+        <v>0.004740375</v>
+      </c>
+      <c r="G56">
+        <v>0.003394704999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>0.003925125</v>
+      </c>
+      <c r="C57">
+        <v>0.004368775</v>
+      </c>
+      <c r="D57">
+        <v>0.005284275</v>
+      </c>
+      <c r="E57">
+        <v>0.004411</v>
+      </c>
+      <c r="F57">
+        <v>0.009653800000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.005528595</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>0.006850950000000001</v>
+      </c>
+      <c r="C58">
+        <v>0.005437000000000001</v>
+      </c>
+      <c r="D58">
+        <v>0.006411875</v>
+      </c>
+      <c r="E58">
+        <v>0.008843800000000001</v>
+      </c>
+      <c r="F58">
+        <v>0.0136091</v>
+      </c>
+      <c r="G58">
+        <v>0.008230545000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>0.001903</v>
+      </c>
+      <c r="C59">
+        <v>0.006132275</v>
+      </c>
+      <c r="D59">
+        <v>0.00400065</v>
+      </c>
+      <c r="E59">
+        <v>0.00207035</v>
+      </c>
+      <c r="F59">
+        <v>0.001008075</v>
+      </c>
+      <c r="G59">
+        <v>0.00302287</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>0.00538335</v>
+      </c>
+      <c r="C60">
+        <v>0.0043306</v>
+      </c>
+      <c r="D60">
+        <v>0.004066874999999999</v>
+      </c>
+      <c r="E60">
+        <v>0.005480625</v>
+      </c>
+      <c r="F60">
+        <v>0.00693495</v>
+      </c>
+      <c r="G60">
+        <v>0.00523928</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>0.00671725</v>
+      </c>
+      <c r="C61">
+        <v>0.003307</v>
+      </c>
+      <c r="D61">
+        <v>0.003606075</v>
+      </c>
+      <c r="E61">
+        <v>0.004192675</v>
+      </c>
+      <c r="F61">
+        <v>0.005517650000000001</v>
+      </c>
+      <c r="G61">
+        <v>0.00466813</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>0.00548525</v>
+      </c>
+      <c r="C62">
+        <v>0.004792825</v>
+      </c>
+      <c r="D62">
+        <v>0.004934875</v>
+      </c>
+      <c r="E62">
+        <v>0.005394599999999999</v>
+      </c>
+      <c r="F62">
+        <v>0.009040825000000001</v>
+      </c>
+      <c r="G62">
+        <v>0.005929675</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>0.008160300000000001</v>
+      </c>
+      <c r="C63">
+        <v>0.006436875</v>
+      </c>
+      <c r="D63">
+        <v>0.005520625000000001</v>
+      </c>
+      <c r="E63">
+        <v>0.004796874999999999</v>
+      </c>
+      <c r="F63">
+        <v>0.006965899999999999</v>
+      </c>
+      <c r="G63">
+        <v>0.006376115</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>0.003937075000000001</v>
+      </c>
+      <c r="C64">
+        <v>0.0044931</v>
+      </c>
+      <c r="D64">
+        <v>0.00527615</v>
+      </c>
+      <c r="E64">
+        <v>0.00441095</v>
+      </c>
+      <c r="F64">
+        <v>0.009621174999999999</v>
+      </c>
+      <c r="G64">
+        <v>0.00554769</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>0.005478149999999999</v>
+      </c>
+      <c r="C65">
+        <v>0.004782225</v>
+      </c>
+      <c r="D65">
+        <v>0.00494835</v>
+      </c>
+      <c r="E65">
+        <v>0.005460374999999999</v>
+      </c>
+      <c r="F65">
+        <v>0.009065725</v>
+      </c>
+      <c r="G65">
+        <v>0.005946965</v>
       </c>
     </row>
   </sheetData>
@@ -1678,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1951,10 +2367,10 @@
         <v>75</v>
       </c>
       <c r="F12">
-        <v>71.25</v>
+        <v>71.5</v>
       </c>
       <c r="G12">
-        <v>78.75</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2169,22 +2585,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>16.25</v>
       </c>
       <c r="C22">
-        <v>7.25</v>
+        <v>18.5</v>
       </c>
       <c r="D22">
-        <v>12.25</v>
+        <v>21.75</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>22.5</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="G22">
-        <v>7.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2192,22 +2608,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="D23">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
       <c r="E23">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>8.949999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2215,22 +2631,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>79</v>
+        <v>7.75</v>
       </c>
       <c r="C24">
-        <v>90.5</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>90.75</v>
+        <v>11.5</v>
       </c>
       <c r="E24">
-        <v>78.75</v>
+        <v>9.5</v>
       </c>
       <c r="F24">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>82.8</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2238,22 +2654,22 @@
         <v>30</v>
       </c>
       <c r="B25">
+        <v>79</v>
+      </c>
+      <c r="C25">
+        <v>90.5</v>
+      </c>
+      <c r="D25">
+        <v>90.75</v>
+      </c>
+      <c r="E25">
         <v>78.75</v>
       </c>
-      <c r="C25">
-        <v>90</v>
-      </c>
-      <c r="D25">
-        <v>89.75</v>
-      </c>
-      <c r="E25">
-        <v>75.75</v>
-      </c>
       <c r="F25">
-        <v>76.5</v>
+        <v>75</v>
       </c>
       <c r="G25">
-        <v>82.15000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2261,22 +2677,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>78.75</v>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>89.75</v>
       </c>
       <c r="E26">
-        <v>8.75</v>
+        <v>75.75</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>76.5</v>
       </c>
       <c r="G26">
-        <v>10.15</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2284,22 +2700,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>80.75</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E27">
-        <v>75</v>
+        <v>8.75</v>
       </c>
       <c r="F27">
-        <v>78.75</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>82.90000000000001</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2307,22 +2723,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>6.75</v>
+        <v>80.25</v>
       </c>
       <c r="C28">
-        <v>8.5</v>
+        <v>90</v>
       </c>
       <c r="D28">
-        <v>13.5</v>
+        <v>90</v>
       </c>
       <c r="E28">
-        <v>9.25</v>
+        <v>75</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>78.75</v>
       </c>
       <c r="G28">
-        <v>8.4</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2330,22 +2746,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="C29">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="D29">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="E29">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>8.4</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2356,19 +2772,19 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>13.25</v>
       </c>
       <c r="E30">
+        <v>7.5</v>
+      </c>
+      <c r="F30">
         <v>6.75</v>
       </c>
-      <c r="F30">
-        <v>6.5</v>
-      </c>
       <c r="G30">
-        <v>9.050000000000001</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2376,22 +2792,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>79.25</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>85.25</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E31">
-        <v>75.25</v>
+        <v>6.75</v>
       </c>
       <c r="F31">
-        <v>76.25</v>
+        <v>6.5</v>
       </c>
       <c r="G31">
-        <v>81.2</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2399,22 +2815,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>8.75</v>
+        <v>79.25</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>85.25</v>
       </c>
       <c r="D32">
-        <v>13.75</v>
+        <v>90</v>
       </c>
       <c r="E32">
-        <v>9.5</v>
+        <v>75.75</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2422,22 +2838,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>16.5</v>
+        <v>8.75</v>
       </c>
       <c r="C33">
-        <v>19.25</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>19.25</v>
+        <v>13.75</v>
       </c>
       <c r="E33">
-        <v>21.75</v>
+        <v>9.5</v>
       </c>
       <c r="F33">
-        <v>14.25</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>18.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2445,22 +2861,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="C34">
         <v>19.25</v>
       </c>
       <c r="D34">
-        <v>22.5</v>
+        <v>19.25</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="G34">
-        <v>19.35</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2468,22 +2884,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>7.75</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>9.25</v>
+        <v>19.25</v>
       </c>
       <c r="D35">
-        <v>14.5</v>
+        <v>22.5</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>8.699999999999999</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2491,22 +2907,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E36">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>9.15</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2514,22 +2930,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>16.5</v>
+        <v>19.75</v>
       </c>
       <c r="C37">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="D37">
-        <v>23.25</v>
+        <v>18.75</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>23.75</v>
       </c>
       <c r="F37">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
       <c r="G37">
-        <v>19</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2540,19 +2956,19 @@
         <v>7</v>
       </c>
       <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>15</v>
+      </c>
+      <c r="E38">
         <v>7.75</v>
       </c>
-      <c r="D38">
-        <v>12.25</v>
-      </c>
-      <c r="E38">
-        <v>8.75</v>
-      </c>
       <c r="F38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38">
-        <v>7.95</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2560,22 +2976,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>7.75</v>
+        <v>16.5</v>
       </c>
       <c r="C39">
-        <v>9.5</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>11.5</v>
+        <v>21.75</v>
       </c>
       <c r="E39">
-        <v>9.5</v>
+        <v>21.75</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G39">
-        <v>8.85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2583,22 +2999,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>6.75</v>
+        <v>16.5</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>19.75</v>
       </c>
       <c r="D40">
-        <v>14.75</v>
+        <v>23.25</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F40">
-        <v>6.75</v>
+        <v>14.5</v>
       </c>
       <c r="G40">
-        <v>9.050000000000001</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2606,22 +3022,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>79.5</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>90</v>
+        <v>7.75</v>
       </c>
       <c r="D41">
-        <v>91.25</v>
+        <v>12.25</v>
       </c>
       <c r="E41">
-        <v>78.75</v>
+        <v>8.75</v>
       </c>
       <c r="F41">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>82.90000000000001</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2629,22 +3045,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>9.25</v>
+        <v>16.5</v>
       </c>
       <c r="C42">
-        <v>10.75</v>
+        <v>19</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E42">
-        <v>8.75</v>
+        <v>23</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="G42">
-        <v>10.15</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2652,22 +3068,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C43">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="D43">
-        <v>14.5</v>
+        <v>11.25</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43">
-        <v>6.75</v>
+        <v>4</v>
       </c>
       <c r="G43">
-        <v>8.6</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2675,22 +3091,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="C44">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="E44">
         <v>9.5</v>
       </c>
       <c r="F44">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>9.199999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2698,22 +3114,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>16.75</v>
+        <v>6.75</v>
       </c>
       <c r="C45">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <v>22</v>
+        <v>14.75</v>
       </c>
       <c r="E45">
-        <v>23.5</v>
+        <v>8</v>
       </c>
       <c r="F45">
-        <v>14.5</v>
+        <v>6.75</v>
       </c>
       <c r="G45">
-        <v>19.15</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2721,22 +3137,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>7.75</v>
+        <v>79.5</v>
       </c>
       <c r="C46">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>91.25</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>78.75</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G46">
-        <v>9.449999999999999</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2744,22 +3160,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C47">
         <v>10.75</v>
       </c>
       <c r="D47">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="F47">
         <v>6</v>
       </c>
       <c r="G47">
-        <v>9.25</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2770,19 +3186,19 @@
         <v>7</v>
       </c>
       <c r="C48">
-        <v>10.25</v>
+        <v>7.75</v>
       </c>
       <c r="D48">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="E48">
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>9.25</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2790,22 +3206,390 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>6.75</v>
+      </c>
+      <c r="C49">
+        <v>10.5</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>9.5</v>
+      </c>
+      <c r="F49">
+        <v>8.25</v>
+      </c>
+      <c r="G49">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>16.5</v>
+      </c>
+      <c r="C50">
+        <v>18.75</v>
+      </c>
+      <c r="D50">
+        <v>18.25</v>
+      </c>
+      <c r="E50">
+        <v>22.5</v>
+      </c>
+      <c r="F50">
+        <v>15</v>
+      </c>
+      <c r="G50">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>16.75</v>
+      </c>
+      <c r="C51">
+        <v>19</v>
+      </c>
+      <c r="D51">
+        <v>22</v>
+      </c>
+      <c r="E51">
+        <v>23.5</v>
+      </c>
+      <c r="F51">
+        <v>14.5</v>
+      </c>
+      <c r="G51">
+        <v>19.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>7.75</v>
+      </c>
+      <c r="C52">
+        <v>10.5</v>
+      </c>
+      <c r="D52">
+        <v>15</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>19.5</v>
+      </c>
+      <c r="C53">
+        <v>20.25</v>
+      </c>
+      <c r="D53">
+        <v>22.25</v>
+      </c>
+      <c r="E53">
+        <v>23</v>
+      </c>
+      <c r="F53">
+        <v>14</v>
+      </c>
+      <c r="G53">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>9.75</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54">
+        <v>10.25</v>
+      </c>
+      <c r="F54">
+        <v>4.75</v>
+      </c>
+      <c r="G54">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
         <v>7</v>
       </c>
-      <c r="C49">
+      <c r="C55">
+        <v>8.25</v>
+      </c>
+      <c r="D55">
+        <v>11.25</v>
+      </c>
+      <c r="E55">
+        <v>7.75</v>
+      </c>
+      <c r="F55">
+        <v>4.5</v>
+      </c>
+      <c r="G55">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56">
+        <v>10.75</v>
+      </c>
+      <c r="D56">
+        <v>15.5</v>
+      </c>
+      <c r="E56">
+        <v>7</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>16.5</v>
+      </c>
+      <c r="C57">
+        <v>19</v>
+      </c>
+      <c r="D57">
+        <v>22.25</v>
+      </c>
+      <c r="E57">
+        <v>21.75</v>
+      </c>
+      <c r="F57">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>8.5</v>
+      </c>
+      <c r="D58">
+        <v>11.75</v>
+      </c>
+      <c r="E58">
+        <v>9.25</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>6.75</v>
+      </c>
+      <c r="C59">
         <v>10.25</v>
       </c>
-      <c r="D49">
+      <c r="D59">
+        <v>14.25</v>
+      </c>
+      <c r="E59">
+        <v>8.75</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>9.75</v>
+      </c>
+      <c r="D60">
+        <v>9</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60">
+        <v>4.5</v>
+      </c>
+      <c r="G60">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>7</v>
+      </c>
+      <c r="C61">
+        <v>10.25</v>
+      </c>
+      <c r="D61">
         <v>14.5</v>
       </c>
-      <c r="E49">
+      <c r="E61">
         <v>7.25</v>
       </c>
-      <c r="F49">
+      <c r="F61">
         <v>9</v>
       </c>
-      <c r="G49">
+      <c r="G61">
         <v>9.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>16.75</v>
+      </c>
+      <c r="C62">
+        <v>19.5</v>
+      </c>
+      <c r="D62">
+        <v>21.5</v>
+      </c>
+      <c r="E62">
+        <v>21.75</v>
+      </c>
+      <c r="F62">
+        <v>13.25</v>
+      </c>
+      <c r="G62">
+        <v>18.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>8.75</v>
+      </c>
+      <c r="C63">
+        <v>10.25</v>
+      </c>
+      <c r="D63">
+        <v>14</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>4.5</v>
+      </c>
+      <c r="G63">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>8.5</v>
+      </c>
+      <c r="D64">
+        <v>13.25</v>
+      </c>
+      <c r="E64">
+        <v>7.75</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>10.25</v>
+      </c>
+      <c r="D65">
+        <v>13.5</v>
+      </c>
+      <c r="E65">
+        <v>8.75</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -2815,7 +3599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3088,10 +3872,10 @@
         <v>93.05382386916239</v>
       </c>
       <c r="F12">
-        <v>90.02869760331529</v>
+        <v>90.17514421272202</v>
       </c>
       <c r="G12">
-        <v>95.04341622907673</v>
+        <v>95.07270555095809</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3122,7 +3906,7 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>96.07895013500946</v>
+        <v>95.87184335382291</v>
       </c>
       <c r="C14">
         <v>99.10407640085654</v>
@@ -3131,13 +3915,13 @@
         <v>101.6941738241592</v>
       </c>
       <c r="E14">
-        <v>94.71067811865477</v>
+        <v>94.50357133746823</v>
       </c>
       <c r="F14">
-        <v>93.88225099390857</v>
+        <v>93.67514421272202</v>
       </c>
       <c r="G14">
-        <v>97.0940258945177</v>
+        <v>96.96976182580576</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3306,22 +4090,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>89.34383520836315</v>
+        <v>98.14392129246505</v>
       </c>
       <c r="C22">
-        <v>92.8786766708138</v>
+        <v>99.41168824543142</v>
       </c>
       <c r="D22">
-        <v>94.23488584070527</v>
+        <v>98.81549416771887</v>
       </c>
       <c r="E22">
-        <v>88.30011401827591</v>
+        <v>93.81118318204307</v>
       </c>
       <c r="F22">
-        <v>87.38393931334436</v>
+        <v>90.02869760331529</v>
       </c>
       <c r="G22">
-        <v>90.4282902103005</v>
+        <v>96.04219689819475</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3329,22 +4113,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>89.43325734773254</v>
+        <v>89.34383520836315</v>
       </c>
       <c r="C23">
-        <v>98.04657322754127</v>
+        <v>92.8786766708138</v>
       </c>
       <c r="D23">
-        <v>98.48408190155187</v>
+        <v>94.23488584070527</v>
       </c>
       <c r="E23">
-        <v>89.73787674880313</v>
+        <v>88.30011401827591</v>
       </c>
       <c r="F23">
-        <v>87.85248644886262</v>
+        <v>87.38393931334436</v>
       </c>
       <c r="G23">
-        <v>92.71085513489828</v>
+        <v>90.4282902103005</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3352,22 +4136,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>96.84671708797583</v>
+        <v>89.43325734773254</v>
       </c>
       <c r="C24">
-        <v>105.0330085889911</v>
+        <v>98.04657322754127</v>
       </c>
       <c r="D24">
-        <v>102.9012806053458</v>
+        <v>98.48408190155187</v>
       </c>
       <c r="E24">
-        <v>98.56423150924803</v>
+        <v>89.73787674880313</v>
       </c>
       <c r="F24">
-        <v>92.22539674441617</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G24">
-        <v>99.11412690719538</v>
+        <v>92.71085513489828</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3375,22 +4159,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>95.25052301026328</v>
+        <v>96.84671708797583</v>
       </c>
       <c r="C25">
-        <v>101.8406204335659</v>
+        <v>105.0330085889911</v>
       </c>
       <c r="D25">
-        <v>101.6941738241592</v>
+        <v>102.9012806053458</v>
       </c>
       <c r="E25">
-        <v>93.70027047856911</v>
+        <v>98.56423150924803</v>
       </c>
       <c r="F25">
-        <v>93.72539674441617</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="G25">
-        <v>97.24219689819473</v>
+        <v>99.11412690719538</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3398,22 +4182,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>88.84628482064193</v>
+        <v>95.25052301026328</v>
       </c>
       <c r="C26">
-        <v>96.62714140628285</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="D26">
-        <v>96.9765119838772</v>
+        <v>101.6941738241592</v>
       </c>
       <c r="E26">
-        <v>88.87912745854852</v>
+        <v>93.70027047856911</v>
       </c>
       <c r="F26">
-        <v>88.45732941103415</v>
+        <v>93.72539674441617</v>
       </c>
       <c r="G26">
-        <v>91.95727901607692</v>
+        <v>97.24219689819473</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3421,22 +4205,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>96.00788232314397</v>
+        <v>88.84628482064193</v>
       </c>
       <c r="C27">
-        <v>102.4619407771256</v>
+        <v>96.62714140628285</v>
       </c>
       <c r="D27">
-        <v>102.254833995939</v>
+        <v>96.9765119838772</v>
       </c>
       <c r="E27">
-        <v>93.05382386916239</v>
+        <v>88.87912745854852</v>
       </c>
       <c r="F27">
-        <v>94.42209588551708</v>
+        <v>88.45732941103415</v>
       </c>
       <c r="G27">
-        <v>97.64011537017761</v>
+        <v>91.95727901607692</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3444,22 +4228,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>89.11698592365499</v>
+        <v>95.50788232314399</v>
       </c>
       <c r="C28">
-        <v>92.32834263634192</v>
+        <v>102.4619407771256</v>
       </c>
       <c r="D28">
-        <v>94.12651525479779</v>
+        <v>102.254833995939</v>
       </c>
       <c r="E28">
-        <v>89.01591551793194</v>
+        <v>93.05382386916239</v>
       </c>
       <c r="F28">
-        <v>87.25337971078574</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="G28">
-        <v>90.36822780870247</v>
+        <v>97.54011537017762</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3467,22 +4251,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>89.07991467279851</v>
+        <v>89.11698592365499</v>
       </c>
       <c r="C29">
-        <v>93.852251325531</v>
+        <v>92.34018006226728</v>
       </c>
       <c r="D29">
-        <v>97.7446453717489</v>
+        <v>94.12651525479779</v>
       </c>
       <c r="E29">
-        <v>88.63203900887707</v>
+        <v>88.41713916575145</v>
       </c>
       <c r="F29">
-        <v>90.96241271314568</v>
+        <v>87.25337971078574</v>
       </c>
       <c r="G29">
-        <v>92.05425261842024</v>
+        <v>90.25084002345145</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3493,19 +4277,19 @@
         <v>89.07991467279851</v>
       </c>
       <c r="C30">
-        <v>96.33430830807514</v>
+        <v>93.852251325531</v>
       </c>
       <c r="D30">
-        <v>96.94409788918787</v>
+        <v>97.7446453717489</v>
       </c>
       <c r="E30">
-        <v>88.63084847786544</v>
+        <v>88.63203900887707</v>
       </c>
       <c r="F30">
-        <v>88.86215727725494</v>
+        <v>90.79984232817746</v>
       </c>
       <c r="G30">
-        <v>91.97026532503639</v>
+        <v>92.0217385414266</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3513,22 +4297,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>96.57895013500946</v>
+        <v>89.07991467279851</v>
       </c>
       <c r="C31">
-        <v>99.05813485483816</v>
+        <v>96.33430830807514</v>
       </c>
       <c r="D31">
-        <v>102.6690475583121</v>
+        <v>96.94409788918787</v>
       </c>
       <c r="E31">
-        <v>94.23580438450185</v>
+        <v>88.63084847786544</v>
       </c>
       <c r="F31">
-        <v>94.6144840409422</v>
+        <v>88.86215727725494</v>
       </c>
       <c r="G31">
-        <v>97.43128419472075</v>
+        <v>91.97026532503639</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3536,22 +4320,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>88.66642008059104</v>
+        <v>96.57895013500946</v>
       </c>
       <c r="C32">
-        <v>93.06322019813916</v>
+        <v>99.05813485483816</v>
       </c>
       <c r="D32">
-        <v>94.04476045024403</v>
+        <v>102.6690475583121</v>
       </c>
       <c r="E32">
-        <v>86.73065860854024</v>
+        <v>94.73580438450183</v>
       </c>
       <c r="F32">
-        <v>87.25337971078574</v>
+        <v>94.46803743153546</v>
       </c>
       <c r="G32">
-        <v>89.95168780966004</v>
+        <v>97.50199487283939</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3559,22 +4343,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>103.2444263558534</v>
+        <v>88.66642008059104</v>
       </c>
       <c r="C33">
-        <v>114.865746699413</v>
+        <v>93.06322019813916</v>
       </c>
       <c r="D33">
-        <v>100.8657466994131</v>
+        <v>94.04476045024403</v>
       </c>
       <c r="E33">
-        <v>92.22539674441617</v>
+        <v>86.73065860854024</v>
       </c>
       <c r="F33">
-        <v>98.3761543394987</v>
+        <v>87.25337971078574</v>
       </c>
       <c r="G33">
-        <v>101.9154941677189</v>
+        <v>89.95168780966004</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3582,22 +4366,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>94.42209588551708</v>
+        <v>103.2444263558534</v>
       </c>
       <c r="C34">
-        <v>101.8406204335659</v>
+        <v>114.865746699413</v>
       </c>
       <c r="D34">
-        <v>101.8406204335659</v>
+        <v>100.8657466994131</v>
       </c>
       <c r="E34">
         <v>92.22539674441617</v>
       </c>
       <c r="F34">
-        <v>94.42209588551708</v>
+        <v>98.3761543394987</v>
       </c>
       <c r="G34">
-        <v>96.95016587651642</v>
+        <v>101.9154941677189</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3605,22 +4389,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>92.76490005040405</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C35">
-        <v>93.90458593737934</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="D35">
-        <v>96.19429259473162</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="E35">
-        <v>89.09532048851781</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="F35">
-        <v>87.25337971078574</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="G35">
-        <v>91.84249575636372</v>
+        <v>96.95016587651642</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3628,22 +4412,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>92.40280548509956</v>
+        <v>92.76490005040405</v>
       </c>
       <c r="C36">
-        <v>98.92076471220372</v>
+        <v>93.90458593737934</v>
       </c>
       <c r="D36">
-        <v>100.4322807617903</v>
+        <v>96.19429259473162</v>
       </c>
       <c r="E36">
-        <v>89.23909495021958</v>
+        <v>89.09532048851781</v>
       </c>
       <c r="F36">
-        <v>89.4557226091525</v>
+        <v>87.25337971078574</v>
       </c>
       <c r="G36">
-        <v>94.09013370369314</v>
+        <v>91.84249575636372</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3651,22 +4435,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>94.42209588551708</v>
+        <v>102.3510280736516</v>
       </c>
       <c r="C37">
-        <v>101.8406204335659</v>
+        <v>104.5121933088197</v>
       </c>
       <c r="D37">
-        <v>101.4870670429727</v>
+        <v>102.9159992311072</v>
       </c>
       <c r="E37">
-        <v>92.22539674441617</v>
+        <v>106.4576297914498</v>
       </c>
       <c r="F37">
-        <v>94.42209588551708</v>
+        <v>90.61448404094219</v>
       </c>
       <c r="G37">
-        <v>96.87945519839778</v>
+        <v>101.3702668891941</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3677,19 +4461,19 @@
         <v>92.40280548509956</v>
       </c>
       <c r="C38">
-        <v>94.00061836510076</v>
+        <v>98.92076471220372</v>
       </c>
       <c r="D38">
-        <v>96.01354346337776</v>
+        <v>100.4322807617903</v>
       </c>
       <c r="E38">
-        <v>87.14141390478646</v>
+        <v>89.23909495021958</v>
       </c>
       <c r="F38">
-        <v>89.17676618598557</v>
+        <v>89.4557226091525</v>
       </c>
       <c r="G38">
-        <v>91.74702948087003</v>
+        <v>94.09013370369314</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3697,22 +4481,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>89.43325734773254</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C39">
-        <v>97.38211175267764</v>
+        <v>99.70458146424488</v>
       </c>
       <c r="D39">
-        <v>98.48408190155187</v>
+        <v>98.81549416771887</v>
       </c>
       <c r="E39">
-        <v>89.68046751382099</v>
+        <v>92.43250352560273</v>
       </c>
       <c r="F39">
-        <v>87.85248644886262</v>
+        <v>90.17514421272202</v>
       </c>
       <c r="G39">
-        <v>92.56648099292913</v>
+        <v>95.10996385116111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3720,22 +4504,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>88.99990922486882</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C40">
-        <v>96.86761117637303</v>
+        <v>101.8406204335659</v>
       </c>
       <c r="D40">
-        <v>96.66843472492903</v>
+        <v>101.4870670429727</v>
       </c>
       <c r="E40">
-        <v>89.10436046563885</v>
+        <v>92.22539674441617</v>
       </c>
       <c r="F40">
-        <v>88.5188039919074</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="G40">
-        <v>92.03182391674342</v>
+        <v>96.87945519839778</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3743,22 +4527,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>97.34671708797583</v>
+        <v>92.40280548509956</v>
       </c>
       <c r="C41">
-        <v>102.0477272147525</v>
+        <v>94.00061836510076</v>
       </c>
       <c r="D41">
-        <v>105.8865619795843</v>
+        <v>96.01354346337776</v>
       </c>
       <c r="E41">
-        <v>96.70027047856911</v>
+        <v>87.14141390478646</v>
       </c>
       <c r="F41">
-        <v>92.63961030678928</v>
+        <v>89.17676618598557</v>
       </c>
       <c r="G41">
-        <v>98.92417741353421</v>
+        <v>91.74702948087003</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3766,22 +4550,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>89.02567788830872</v>
+        <v>94.42209588551708</v>
       </c>
       <c r="C42">
-        <v>96.67122875070476</v>
+        <v>97.74011537017759</v>
       </c>
       <c r="D42">
-        <v>96.98700516383333</v>
+        <v>98.81549416771887</v>
       </c>
       <c r="E42">
-        <v>88.87912745854852</v>
+        <v>92.63961030678928</v>
       </c>
       <c r="F42">
-        <v>88.45732941103415</v>
+        <v>90.02869760331529</v>
       </c>
       <c r="G42">
-        <v>92.0040737344859</v>
+        <v>94.72920266670363</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3789,22 +4573,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>89.29618943656151</v>
+        <v>97.28918944244936</v>
       </c>
       <c r="C43">
-        <v>94.56498240418756</v>
+        <v>96.40373009322457</v>
       </c>
       <c r="D43">
-        <v>97.93643226568786</v>
+        <v>95.30096112388452</v>
       </c>
       <c r="E43">
-        <v>88.65873088301404</v>
+        <v>90.26940794981491</v>
       </c>
       <c r="F43">
-        <v>90.98307847109159</v>
+        <v>89.17676618598557</v>
       </c>
       <c r="G43">
-        <v>92.28788269210851</v>
+        <v>93.68801095907179</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3812,22 +4596,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>99.46494721246621</v>
+        <v>89.43325734773254</v>
       </c>
       <c r="C44">
-        <v>99.88490910316931</v>
+        <v>97.38211175267764</v>
       </c>
       <c r="D44">
-        <v>98.33267398735988</v>
+        <v>98.48408190155187</v>
       </c>
       <c r="E44">
-        <v>87.42378466006728</v>
+        <v>89.68046751382099</v>
       </c>
       <c r="F44">
-        <v>93.53607631609822</v>
+        <v>87.85248644886262</v>
       </c>
       <c r="G44">
-        <v>95.72847825583219</v>
+        <v>92.56648099292913</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3835,22 +4619,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>94.42209588551708</v>
+        <v>88.99990922486882</v>
       </c>
       <c r="C45">
-        <v>101.8406204335659</v>
+        <v>96.86761117637303</v>
       </c>
       <c r="D45">
-        <v>101.4870670429727</v>
+        <v>96.66843472492903</v>
       </c>
       <c r="E45">
-        <v>97.87184335382292</v>
+        <v>89.10436046563885</v>
       </c>
       <c r="F45">
-        <v>98.81549416771887</v>
+        <v>88.5188039919074</v>
       </c>
       <c r="G45">
-        <v>98.88742417671949</v>
+        <v>92.03182391674342</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3858,22 +4642,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>92.76490005040405</v>
+        <v>97.34671708797583</v>
       </c>
       <c r="C46">
-        <v>98.49200497586588</v>
+        <v>102.0477272147525</v>
       </c>
       <c r="D46">
-        <v>100.239983757739</v>
+        <v>105.8865619795843</v>
       </c>
       <c r="E46">
-        <v>88.90636856186427</v>
+        <v>96.70027047856911</v>
       </c>
       <c r="F46">
-        <v>89.57502444824181</v>
+        <v>92.43250352560273</v>
       </c>
       <c r="G46">
-        <v>93.995656358823</v>
+        <v>98.8827560572969</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3881,22 +4665,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>92.40280548509956</v>
+        <v>88.92938668652509</v>
       </c>
       <c r="C47">
-        <v>99.17134209323737</v>
+        <v>96.67122875070476</v>
       </c>
       <c r="D47">
-        <v>100.7030742644905</v>
+        <v>97.06403490025755</v>
       </c>
       <c r="E47">
-        <v>88.66139772254367</v>
+        <v>88.87912745854852</v>
       </c>
       <c r="F47">
-        <v>89.42841909744683</v>
+        <v>88.45732941103415</v>
       </c>
       <c r="G47">
-        <v>94.07340773256358</v>
+        <v>92.00022144141401</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3904,22 +4688,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>89.84350880950822</v>
+        <v>89.29618943656151</v>
       </c>
       <c r="C48">
-        <v>96.81916274705507</v>
+        <v>94.56498240418756</v>
       </c>
       <c r="D48">
-        <v>98.14758952142844</v>
+        <v>98.12525075159105</v>
       </c>
       <c r="E48">
-        <v>89.63861121414007</v>
+        <v>88.66139772254367</v>
       </c>
       <c r="F48">
-        <v>87.89295873608319</v>
+        <v>90.9309218192103</v>
       </c>
       <c r="G48">
-        <v>92.46836620564299</v>
+        <v>92.31574842681883</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3927,22 +4711,390 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>99.46494721246621</v>
+      </c>
+      <c r="C49">
+        <v>99.88490910316931</v>
+      </c>
+      <c r="D49">
+        <v>98.33267398735988</v>
+      </c>
+      <c r="E49">
+        <v>87.42378466006728</v>
+      </c>
+      <c r="F49">
+        <v>93.53607631609822</v>
+      </c>
+      <c r="G49">
+        <v>95.72847825583219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>94.42209588551708</v>
+      </c>
+      <c r="C50">
+        <v>99.70458146424487</v>
+      </c>
+      <c r="D50">
+        <v>112.2340187157677</v>
+      </c>
+      <c r="E50">
+        <v>101.1439212924651</v>
+      </c>
+      <c r="F50">
+        <v>90.17514421272202</v>
+      </c>
+      <c r="G50">
+        <v>99.53595231414336</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>94.42209588551708</v>
+      </c>
+      <c r="C51">
+        <v>101.8406204335659</v>
+      </c>
+      <c r="D51">
+        <v>101.4870670429727</v>
+      </c>
+      <c r="E51">
+        <v>97.87184335382292</v>
+      </c>
+      <c r="F51">
+        <v>98.81549416771887</v>
+      </c>
+      <c r="G51">
+        <v>98.88742417671949</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>92.76490005040405</v>
+      </c>
+      <c r="C52">
+        <v>98.49200497586588</v>
+      </c>
+      <c r="D52">
+        <v>100.239983757739</v>
+      </c>
+      <c r="E52">
+        <v>88.90636856186427</v>
+      </c>
+      <c r="F52">
+        <v>89.57502444824181</v>
+      </c>
+      <c r="G52">
+        <v>93.995656358823</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>105.3761543394987</v>
+      </c>
+      <c r="C53">
+        <v>110.0330085889911</v>
+      </c>
+      <c r="D53">
+        <v>99.66904755831214</v>
+      </c>
+      <c r="E53">
+        <v>94.8111831820431</v>
+      </c>
+      <c r="F53">
+        <v>90.61448404094219</v>
+      </c>
+      <c r="G53">
+        <v>100.1007755419575</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>100.3198533943509</v>
+      </c>
+      <c r="C54">
+        <v>101.6387303439018</v>
+      </c>
+      <c r="D54">
+        <v>100.2115090137377</v>
+      </c>
+      <c r="E54">
+        <v>99.75871027327172</v>
+      </c>
+      <c r="F54">
+        <v>87.87118321562048</v>
+      </c>
+      <c r="G54">
+        <v>97.95999724817652</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
+        <v>92.70408500909821</v>
+      </c>
+      <c r="C55">
+        <v>96.87834402230158</v>
+      </c>
+      <c r="D55">
+        <v>95.30096112388452</v>
+      </c>
+      <c r="E55">
+        <v>89.11220383817889</v>
+      </c>
+      <c r="F55">
+        <v>89.15730662177263</v>
+      </c>
+      <c r="G55">
+        <v>92.63058012304717</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
         <v>92.40280548509956</v>
       </c>
-      <c r="C49">
+      <c r="C56">
+        <v>99.17134209323737</v>
+      </c>
+      <c r="D56">
+        <v>100.7030742644905</v>
+      </c>
+      <c r="E56">
+        <v>88.66139772254367</v>
+      </c>
+      <c r="F56">
+        <v>89.42841909744683</v>
+      </c>
+      <c r="G56">
+        <v>94.07340773256358</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>94.42209588551708</v>
+      </c>
+      <c r="C57">
+        <v>98.03300858899105</v>
+      </c>
+      <c r="D57">
+        <v>103.3302127934803</v>
+      </c>
+      <c r="E57">
+        <v>92.43250352560273</v>
+      </c>
+      <c r="F57">
+        <v>90.90737725975565</v>
+      </c>
+      <c r="G57">
+        <v>95.82503961066936</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>92.70408500909821</v>
+      </c>
+      <c r="C58">
+        <v>94.09356657062547</v>
+      </c>
+      <c r="D58">
+        <v>95.39003391632119</v>
+      </c>
+      <c r="E58">
+        <v>89.12052142006024</v>
+      </c>
+      <c r="F58">
+        <v>89.17676618598557</v>
+      </c>
+      <c r="G58">
+        <v>92.09699462041814</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>89.74881700566679</v>
+      </c>
+      <c r="C59">
+        <v>96.81916274705507</v>
+      </c>
+      <c r="D59">
+        <v>98.14758952142844</v>
+      </c>
+      <c r="E59">
+        <v>89.63861121414007</v>
+      </c>
+      <c r="F59">
+        <v>87.89295873608319</v>
+      </c>
+      <c r="G59">
+        <v>92.44942784487471</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>92.44506751138823</v>
+      </c>
+      <c r="C60">
+        <v>96.4749603564162</v>
+      </c>
+      <c r="D60">
+        <v>102.7772775321916</v>
+      </c>
+      <c r="E60">
+        <v>98.1773284646096</v>
+      </c>
+      <c r="F60">
+        <v>87.27978661941248</v>
+      </c>
+      <c r="G60">
+        <v>95.43088409680362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>92.40280548509956</v>
+      </c>
+      <c r="C61">
         <v>98.05484490403919</v>
       </c>
-      <c r="D49">
+      <c r="D61">
         <v>99.3476313949117</v>
       </c>
-      <c r="E49">
+      <c r="E61">
         <v>89.21667250580074</v>
       </c>
-      <c r="F49">
+      <c r="F61">
         <v>93.937089782518</v>
       </c>
-      <c r="G49">
+      <c r="G61">
         <v>94.59180881447382</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>94.42209588551708</v>
+      </c>
+      <c r="C62">
+        <v>107.3510280736516</v>
+      </c>
+      <c r="D62">
+        <v>110.3908729652601</v>
+      </c>
+      <c r="E62">
+        <v>98.55813485483816</v>
+      </c>
+      <c r="F62">
+        <v>90.76093065034891</v>
+      </c>
+      <c r="G62">
+        <v>100.2966124859232</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>101.2917139546376</v>
+      </c>
+      <c r="C63">
+        <v>96.94832103562194</v>
+      </c>
+      <c r="D63">
+        <v>96.9645229173662</v>
+      </c>
+      <c r="E63">
+        <v>91.10046826980667</v>
+      </c>
+      <c r="F63">
+        <v>87.67602255442925</v>
+      </c>
+      <c r="G63">
+        <v>94.79620974637234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>92.64322576422821</v>
+      </c>
+      <c r="C64">
+        <v>94.44903128073967</v>
+      </c>
+      <c r="D64">
+        <v>101.8136111294782</v>
+      </c>
+      <c r="E64">
+        <v>89.11220383817889</v>
+      </c>
+      <c r="F64">
+        <v>89.15903514334775</v>
+      </c>
+      <c r="G64">
+        <v>93.43542143119456</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>92.40280548509956</v>
+      </c>
+      <c r="C65">
+        <v>96.67782284686413</v>
+      </c>
+      <c r="D65">
+        <v>100.9515915734736</v>
+      </c>
+      <c r="E65">
+        <v>94.56109262150554</v>
+      </c>
+      <c r="F65">
+        <v>87.70242946305598</v>
+      </c>
+      <c r="G65">
+        <v>94.45914839799975</v>
       </c>
     </row>
   </sheetData>
@@ -3952,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4121,22 +5273,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>157.5</v>
+        <v>165.25</v>
       </c>
       <c r="C8">
-        <v>134.25</v>
+        <v>139.25</v>
       </c>
       <c r="D8">
-        <v>100.25</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>278.75</v>
+        <v>293</v>
       </c>
       <c r="F8">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="G8">
-        <v>225.55</v>
+        <v>235.1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4213,22 +5365,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>298.25</v>
+        <v>310.75</v>
       </c>
       <c r="C12">
-        <v>264.5</v>
+        <v>269.25</v>
       </c>
       <c r="D12">
-        <v>127.75</v>
+        <v>129</v>
       </c>
       <c r="E12">
-        <v>278.75</v>
+        <v>294</v>
       </c>
       <c r="F12">
-        <v>343</v>
+        <v>354.25</v>
       </c>
       <c r="G12">
-        <v>262.45</v>
+        <v>271.45</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4259,22 +5411,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>203.25</v>
+        <v>202.75</v>
       </c>
       <c r="C14">
-        <v>233.25</v>
+        <v>239.25</v>
       </c>
       <c r="D14">
-        <v>166.25</v>
+        <v>166.5</v>
       </c>
       <c r="E14">
-        <v>208.5</v>
+        <v>209.25</v>
       </c>
       <c r="F14">
         <v>211.5</v>
       </c>
       <c r="G14">
-        <v>204.55</v>
+        <v>205.85</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4328,22 +5480,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>331.5</v>
+        <v>346.75</v>
       </c>
       <c r="C17">
-        <v>252.5</v>
+        <v>264.25</v>
       </c>
       <c r="D17">
-        <v>121.5</v>
+        <v>122.75</v>
       </c>
       <c r="E17">
-        <v>242.5</v>
+        <v>247</v>
       </c>
       <c r="F17">
-        <v>406.25</v>
+        <v>423</v>
       </c>
       <c r="G17">
-        <v>270.85</v>
+        <v>280.75</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4443,22 +5595,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>157.5</v>
+        <v>13.75</v>
       </c>
       <c r="C22">
-        <v>134.25</v>
+        <v>10.5</v>
       </c>
       <c r="D22">
-        <v>100.25</v>
+        <v>6.5</v>
       </c>
       <c r="E22">
-        <v>278.75</v>
+        <v>20.25</v>
       </c>
       <c r="F22">
-        <v>457</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>225.55</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4466,22 +5618,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>305.5</v>
+        <v>165.25</v>
       </c>
       <c r="C23">
-        <v>297</v>
+        <v>139.25</v>
       </c>
       <c r="D23">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="E23">
-        <v>353.75</v>
+        <v>293</v>
       </c>
       <c r="F23">
-        <v>196.75</v>
+        <v>476</v>
       </c>
       <c r="G23">
-        <v>291.4</v>
+        <v>235.1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4489,22 +5641,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>304.5</v>
+        <v>305.5</v>
       </c>
       <c r="C24">
-        <v>329.5</v>
+        <v>297</v>
       </c>
       <c r="D24">
-        <v>312.5</v>
+        <v>304</v>
       </c>
       <c r="E24">
-        <v>356.5</v>
+        <v>353.75</v>
       </c>
       <c r="F24">
         <v>196.75</v>
       </c>
       <c r="G24">
-        <v>299.95</v>
+        <v>291.4</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4512,22 +5664,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>343</v>
+        <v>305.5</v>
       </c>
       <c r="C25">
-        <v>190.25</v>
+        <v>335.25</v>
       </c>
       <c r="D25">
-        <v>200.5</v>
+        <v>314.75</v>
       </c>
       <c r="E25">
-        <v>363</v>
+        <v>357.25</v>
       </c>
       <c r="F25">
-        <v>237.5</v>
+        <v>196.75</v>
       </c>
       <c r="G25">
-        <v>266.85</v>
+        <v>301.9</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4535,22 +5687,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>304.75</v>
+        <v>343</v>
       </c>
       <c r="C26">
-        <v>171.25</v>
+        <v>190.25</v>
       </c>
       <c r="D26">
-        <v>178.25</v>
+        <v>200.5</v>
       </c>
       <c r="E26">
-        <v>206.75</v>
+        <v>363</v>
       </c>
       <c r="F26">
-        <v>315.25</v>
+        <v>237.5</v>
       </c>
       <c r="G26">
-        <v>235.25</v>
+        <v>266.85</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4558,22 +5710,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>329.5</v>
+        <v>304.75</v>
       </c>
       <c r="C27">
-        <v>157.5</v>
+        <v>171.25</v>
       </c>
       <c r="D27">
-        <v>180.75</v>
+        <v>178.25</v>
       </c>
       <c r="E27">
-        <v>234</v>
+        <v>206.75</v>
       </c>
       <c r="F27">
-        <v>284.5</v>
+        <v>315.25</v>
       </c>
       <c r="G27">
-        <v>237.25</v>
+        <v>235.25</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4581,22 +5733,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>298.25</v>
+        <v>336</v>
       </c>
       <c r="C28">
-        <v>264.5</v>
+        <v>161.25</v>
       </c>
       <c r="D28">
-        <v>127.75</v>
+        <v>189</v>
       </c>
       <c r="E28">
-        <v>278.75</v>
+        <v>236.75</v>
       </c>
       <c r="F28">
-        <v>343</v>
+        <v>301.25</v>
       </c>
       <c r="G28">
-        <v>262.45</v>
+        <v>244.85</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -4604,22 +5756,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>203.25</v>
+        <v>310.75</v>
       </c>
       <c r="C29">
-        <v>233.25</v>
+        <v>269.25</v>
       </c>
       <c r="D29">
-        <v>166.25</v>
+        <v>129</v>
       </c>
       <c r="E29">
-        <v>208.5</v>
+        <v>294</v>
       </c>
       <c r="F29">
-        <v>211.5</v>
+        <v>354.25</v>
       </c>
       <c r="G29">
-        <v>204.55</v>
+        <v>271.45</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4627,22 +5779,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>205</v>
+        <v>202.75</v>
       </c>
       <c r="C30">
-        <v>185.25</v>
+        <v>239.25</v>
       </c>
       <c r="D30">
-        <v>177.75</v>
+        <v>166.5</v>
       </c>
       <c r="E30">
-        <v>204.25</v>
+        <v>209.25</v>
       </c>
       <c r="F30">
-        <v>208.75</v>
+        <v>211.5</v>
       </c>
       <c r="G30">
-        <v>196.2</v>
+        <v>205.85</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4650,22 +5802,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>216.75</v>
+        <v>205</v>
       </c>
       <c r="C31">
-        <v>196</v>
+        <v>185.25</v>
       </c>
       <c r="D31">
-        <v>183.5</v>
+        <v>177.75</v>
       </c>
       <c r="E31">
-        <v>219</v>
+        <v>204.25</v>
       </c>
       <c r="F31">
-        <v>208</v>
+        <v>208.75</v>
       </c>
       <c r="G31">
-        <v>204.65</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4673,22 +5825,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>331.5</v>
+        <v>217.75</v>
       </c>
       <c r="C32">
-        <v>252.5</v>
+        <v>198.25</v>
       </c>
       <c r="D32">
-        <v>121.5</v>
+        <v>183.25</v>
       </c>
       <c r="E32">
-        <v>242.5</v>
+        <v>219</v>
       </c>
       <c r="F32">
-        <v>406.25</v>
+        <v>208</v>
       </c>
       <c r="G32">
-        <v>270.85</v>
+        <v>205.25</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4696,22 +5848,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>18.75</v>
+        <v>346.75</v>
       </c>
       <c r="C33">
-        <v>16.75</v>
+        <v>264.25</v>
       </c>
       <c r="D33">
-        <v>15.25</v>
+        <v>122.75</v>
       </c>
       <c r="E33">
-        <v>20.5</v>
+        <v>247</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>423</v>
       </c>
       <c r="G33">
-        <v>16.05</v>
+        <v>280.75</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4719,22 +5871,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>24</v>
+        <v>18.75</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="D34">
-        <v>17.5</v>
+        <v>15.25</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="F34">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>19.7</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4742,22 +5894,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>17.25</v>
+        <v>24</v>
       </c>
       <c r="C35">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="E35">
+        <v>22</v>
+      </c>
+      <c r="F35">
         <v>18</v>
       </c>
-      <c r="F35">
-        <v>17.5</v>
-      </c>
       <c r="G35">
-        <v>16.75</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4765,22 +5917,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>11.75</v>
+        <v>17.25</v>
       </c>
       <c r="C36">
-        <v>11.75</v>
+        <v>16.5</v>
       </c>
       <c r="D36">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F36">
-        <v>7.25</v>
+        <v>17.5</v>
       </c>
       <c r="G36">
-        <v>11.05</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4788,22 +5940,22 @@
         <v>42</v>
       </c>
       <c r="B37">
+        <v>21.25</v>
+      </c>
+      <c r="C37">
+        <v>17.75</v>
+      </c>
+      <c r="D37">
+        <v>14</v>
+      </c>
+      <c r="E37">
+        <v>28</v>
+      </c>
+      <c r="F37">
         <v>13.25</v>
       </c>
-      <c r="C37">
-        <v>12.25</v>
-      </c>
-      <c r="D37">
-        <v>13.25</v>
-      </c>
-      <c r="E37">
-        <v>14.25</v>
-      </c>
-      <c r="F37">
-        <v>8.75</v>
-      </c>
       <c r="G37">
-        <v>12.35</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4811,22 +5963,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>15.75</v>
+        <v>11.75</v>
       </c>
       <c r="C38">
-        <v>15.25</v>
+        <v>11.75</v>
       </c>
       <c r="D38">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
       <c r="E38">
-        <v>21.75</v>
+        <v>13</v>
       </c>
       <c r="F38">
-        <v>13</v>
+        <v>7.25</v>
       </c>
       <c r="G38">
-        <v>15.6</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4834,22 +5986,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>304.5</v>
+        <v>11.75</v>
       </c>
       <c r="C39">
-        <v>329.5</v>
+        <v>11.5</v>
       </c>
       <c r="D39">
-        <v>312.5</v>
+        <v>13.5</v>
       </c>
       <c r="E39">
-        <v>356.5</v>
+        <v>14</v>
       </c>
       <c r="F39">
-        <v>196.75</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>299.95</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4857,22 +6009,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>343</v>
+        <v>13.25</v>
       </c>
       <c r="C40">
-        <v>190.25</v>
+        <v>12.25</v>
       </c>
       <c r="D40">
-        <v>200.5</v>
+        <v>13.25</v>
       </c>
       <c r="E40">
-        <v>363</v>
+        <v>14.25</v>
       </c>
       <c r="F40">
-        <v>237.5</v>
+        <v>8.75</v>
       </c>
       <c r="G40">
-        <v>266.85</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4880,22 +6032,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>329.5</v>
+        <v>15.75</v>
       </c>
       <c r="C41">
-        <v>204.75</v>
+        <v>15.25</v>
       </c>
       <c r="D41">
-        <v>232</v>
+        <v>12.25</v>
       </c>
       <c r="E41">
-        <v>300.5</v>
+        <v>21.75</v>
       </c>
       <c r="F41">
-        <v>218.25</v>
+        <v>13</v>
       </c>
       <c r="G41">
-        <v>257</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4903,22 +6055,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>329.5</v>
+        <v>15.25</v>
       </c>
       <c r="C42">
-        <v>157.5</v>
+        <v>14.25</v>
       </c>
       <c r="D42">
-        <v>180.75</v>
+        <v>9.75</v>
       </c>
       <c r="E42">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="F42">
-        <v>284.5</v>
+        <v>6.75</v>
       </c>
       <c r="G42">
-        <v>237.25</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4926,22 +6078,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>216.75</v>
+        <v>13.75</v>
       </c>
       <c r="C43">
-        <v>196</v>
+        <v>10.5</v>
       </c>
       <c r="D43">
-        <v>183.5</v>
+        <v>6.5</v>
       </c>
       <c r="E43">
-        <v>219</v>
+        <v>20.25</v>
       </c>
       <c r="F43">
-        <v>208</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>204.65</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4949,22 +6101,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>18.75</v>
+        <v>305.5</v>
       </c>
       <c r="C44">
-        <v>16.75</v>
+        <v>335.25</v>
       </c>
       <c r="D44">
-        <v>15.25</v>
+        <v>314.75</v>
       </c>
       <c r="E44">
-        <v>20.5</v>
+        <v>357.25</v>
       </c>
       <c r="F44">
-        <v>9</v>
+        <v>196.75</v>
       </c>
       <c r="G44">
-        <v>16.05</v>
+        <v>301.9</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4972,22 +6124,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>27.5</v>
+        <v>343</v>
       </c>
       <c r="C45">
-        <v>17</v>
+        <v>190.25</v>
       </c>
       <c r="D45">
-        <v>16</v>
+        <v>200.5</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="F45">
-        <v>11.5</v>
+        <v>237.5</v>
       </c>
       <c r="G45">
-        <v>19</v>
+        <v>266.85</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4995,22 +6147,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>24</v>
+        <v>330.25</v>
       </c>
       <c r="C46">
-        <v>17</v>
+        <v>205.75</v>
       </c>
       <c r="D46">
-        <v>17.5</v>
+        <v>233.75</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>287.25</v>
       </c>
       <c r="F46">
-        <v>18</v>
+        <v>212.75</v>
       </c>
       <c r="G46">
-        <v>19.7</v>
+        <v>253.95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5018,22 +6170,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>13.25</v>
+        <v>336</v>
       </c>
       <c r="C47">
-        <v>12.25</v>
+        <v>161.25</v>
       </c>
       <c r="D47">
-        <v>13.25</v>
+        <v>189</v>
       </c>
       <c r="E47">
-        <v>14.25</v>
+        <v>236.75</v>
       </c>
       <c r="F47">
-        <v>8.75</v>
+        <v>301.25</v>
       </c>
       <c r="G47">
-        <v>12.35</v>
+        <v>244.85</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5041,22 +6193,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>329.5</v>
+        <v>217.75</v>
       </c>
       <c r="C48">
-        <v>204.75</v>
+        <v>198.25</v>
       </c>
       <c r="D48">
-        <v>232</v>
+        <v>183.25</v>
       </c>
       <c r="E48">
-        <v>300.5</v>
+        <v>219</v>
       </c>
       <c r="F48">
-        <v>218.25</v>
+        <v>208</v>
       </c>
       <c r="G48">
-        <v>257</v>
+        <v>205.25</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5064,22 +6216,390 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>18.75</v>
+      </c>
+      <c r="C49">
+        <v>16.75</v>
+      </c>
+      <c r="D49">
+        <v>15.25</v>
+      </c>
+      <c r="E49">
+        <v>20.5</v>
+      </c>
+      <c r="F49">
+        <v>9</v>
+      </c>
+      <c r="G49">
+        <v>16.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>20.5</v>
+      </c>
+      <c r="C50">
+        <v>17.25</v>
+      </c>
+      <c r="D50">
+        <v>13.75</v>
+      </c>
+      <c r="E50">
+        <v>25.5</v>
+      </c>
+      <c r="F50">
+        <v>13.5</v>
+      </c>
+      <c r="G50">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
         <v>27.5</v>
       </c>
-      <c r="C49">
+      <c r="C51">
         <v>17</v>
       </c>
-      <c r="D49">
+      <c r="D51">
         <v>16</v>
       </c>
-      <c r="E49">
+      <c r="E51">
         <v>23</v>
       </c>
-      <c r="F49">
+      <c r="F51">
         <v>11.5</v>
       </c>
-      <c r="G49">
+      <c r="G51">
         <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>24</v>
+      </c>
+      <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>17.5</v>
+      </c>
+      <c r="E52">
+        <v>22</v>
+      </c>
+      <c r="F52">
+        <v>18</v>
+      </c>
+      <c r="G52">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>22.5</v>
+      </c>
+      <c r="C53">
+        <v>18.25</v>
+      </c>
+      <c r="D53">
+        <v>17.25</v>
+      </c>
+      <c r="E53">
+        <v>20.5</v>
+      </c>
+      <c r="F53">
+        <v>14.75</v>
+      </c>
+      <c r="G53">
+        <v>18.65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>21.25</v>
+      </c>
+      <c r="C54">
+        <v>17.75</v>
+      </c>
+      <c r="D54">
+        <v>14</v>
+      </c>
+      <c r="E54">
+        <v>28</v>
+      </c>
+      <c r="F54">
+        <v>13.25</v>
+      </c>
+      <c r="G54">
+        <v>18.85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
+        <v>11.75</v>
+      </c>
+      <c r="C55">
+        <v>11.5</v>
+      </c>
+      <c r="D55">
+        <v>13.5</v>
+      </c>
+      <c r="E55">
+        <v>14</v>
+      </c>
+      <c r="F55">
+        <v>7</v>
+      </c>
+      <c r="G55">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>13.25</v>
+      </c>
+      <c r="C56">
+        <v>12.25</v>
+      </c>
+      <c r="D56">
+        <v>13.25</v>
+      </c>
+      <c r="E56">
+        <v>14.25</v>
+      </c>
+      <c r="F56">
+        <v>8.75</v>
+      </c>
+      <c r="G56">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>13.75</v>
+      </c>
+      <c r="D57">
+        <v>13.25</v>
+      </c>
+      <c r="E57">
+        <v>15.25</v>
+      </c>
+      <c r="F57">
+        <v>8.5</v>
+      </c>
+      <c r="G57">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>15.25</v>
+      </c>
+      <c r="C58">
+        <v>14.25</v>
+      </c>
+      <c r="D58">
+        <v>9.75</v>
+      </c>
+      <c r="E58">
+        <v>21</v>
+      </c>
+      <c r="F58">
+        <v>6.75</v>
+      </c>
+      <c r="G58">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>330.25</v>
+      </c>
+      <c r="C59">
+        <v>205.75</v>
+      </c>
+      <c r="D59">
+        <v>233.75</v>
+      </c>
+      <c r="E59">
+        <v>287.25</v>
+      </c>
+      <c r="F59">
+        <v>212.75</v>
+      </c>
+      <c r="G59">
+        <v>253.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>20.5</v>
+      </c>
+      <c r="C60">
+        <v>17.25</v>
+      </c>
+      <c r="D60">
+        <v>13.75</v>
+      </c>
+      <c r="E60">
+        <v>25.5</v>
+      </c>
+      <c r="F60">
+        <v>13.5</v>
+      </c>
+      <c r="G60">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>27.5</v>
+      </c>
+      <c r="C61">
+        <v>17</v>
+      </c>
+      <c r="D61">
+        <v>16</v>
+      </c>
+      <c r="E61">
+        <v>23</v>
+      </c>
+      <c r="F61">
+        <v>11.5</v>
+      </c>
+      <c r="G61">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>22.75</v>
+      </c>
+      <c r="C62">
+        <v>19</v>
+      </c>
+      <c r="D62">
+        <v>16</v>
+      </c>
+      <c r="E62">
+        <v>28</v>
+      </c>
+      <c r="F62">
+        <v>16.25</v>
+      </c>
+      <c r="G62">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>22.5</v>
+      </c>
+      <c r="C63">
+        <v>18.25</v>
+      </c>
+      <c r="D63">
+        <v>17.25</v>
+      </c>
+      <c r="E63">
+        <v>20.5</v>
+      </c>
+      <c r="F63">
+        <v>14.75</v>
+      </c>
+      <c r="G63">
+        <v>18.65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>12</v>
+      </c>
+      <c r="C64">
+        <v>13.75</v>
+      </c>
+      <c r="D64">
+        <v>13.25</v>
+      </c>
+      <c r="E64">
+        <v>15.25</v>
+      </c>
+      <c r="F64">
+        <v>8.5</v>
+      </c>
+      <c r="G64">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>22.75</v>
+      </c>
+      <c r="C65">
+        <v>19</v>
+      </c>
+      <c r="D65">
+        <v>16</v>
+      </c>
+      <c r="E65">
+        <v>28</v>
+      </c>
+      <c r="F65">
+        <v>16.25</v>
+      </c>
+      <c r="G65">
+        <v>20.4</v>
       </c>
     </row>
   </sheetData>
@@ -5089,7 +6609,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5258,7 +6778,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>1337</v>
+        <v>1336.75</v>
       </c>
       <c r="C8">
         <v>1398.5</v>
@@ -5267,13 +6787,13 @@
         <v>1314.25</v>
       </c>
       <c r="E8">
-        <v>1630.75</v>
+        <v>1630</v>
       </c>
       <c r="F8">
         <v>1699</v>
       </c>
       <c r="G8">
-        <v>1475.9</v>
+        <v>1475.7</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5350,22 +6870,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>1071.75</v>
+        <v>1074</v>
       </c>
       <c r="C12">
-        <v>1162.25</v>
+        <v>1164.75</v>
       </c>
       <c r="D12">
-        <v>943</v>
+        <v>943.25</v>
       </c>
       <c r="E12">
-        <v>1138.5</v>
+        <v>1133.25</v>
       </c>
       <c r="F12">
-        <v>817.25</v>
+        <v>821.5</v>
       </c>
       <c r="G12">
-        <v>1026.55</v>
+        <v>1027.35</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5396,7 +6916,7 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>85.75</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>279.5</v>
@@ -5405,13 +6925,13 @@
         <v>147.25</v>
       </c>
       <c r="E14">
-        <v>125.75</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>83.25</v>
+        <v>83.5</v>
       </c>
       <c r="G14">
-        <v>144.3</v>
+        <v>144.45</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5465,7 +6985,7 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>685.5</v>
+        <v>685</v>
       </c>
       <c r="C17">
         <v>1030</v>
@@ -5474,13 +6994,13 @@
         <v>932</v>
       </c>
       <c r="E17">
-        <v>962.75</v>
+        <v>962.25</v>
       </c>
       <c r="F17">
         <v>936.25</v>
       </c>
       <c r="G17">
-        <v>909.3</v>
+        <v>909.1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5580,22 +7100,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>1337</v>
+        <v>60.5</v>
       </c>
       <c r="C22">
-        <v>1398.5</v>
+        <v>48.75</v>
       </c>
       <c r="D22">
-        <v>1314.25</v>
+        <v>64.25</v>
       </c>
       <c r="E22">
-        <v>1630.75</v>
+        <v>98.25</v>
       </c>
       <c r="F22">
-        <v>1699</v>
+        <v>39.25</v>
       </c>
       <c r="G22">
-        <v>1475.9</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5603,22 +7123,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>125.25</v>
+        <v>1336.75</v>
       </c>
       <c r="C23">
-        <v>375.5</v>
+        <v>1398.5</v>
       </c>
       <c r="D23">
-        <v>300.5</v>
+        <v>1314.25</v>
       </c>
       <c r="E23">
-        <v>221.25</v>
+        <v>1630</v>
       </c>
       <c r="F23">
-        <v>75</v>
+        <v>1699</v>
       </c>
       <c r="G23">
-        <v>219.5</v>
+        <v>1475.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5626,22 +7146,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>123.75</v>
+        <v>125.25</v>
       </c>
       <c r="C24">
-        <v>359.5</v>
+        <v>375.5</v>
       </c>
       <c r="D24">
-        <v>276.75</v>
+        <v>300.5</v>
       </c>
       <c r="E24">
-        <v>219.5</v>
+        <v>221.25</v>
       </c>
       <c r="F24">
         <v>75</v>
       </c>
       <c r="G24">
-        <v>210.9</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5649,22 +7169,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>194</v>
+        <v>124.25</v>
       </c>
       <c r="C25">
-        <v>640.5</v>
+        <v>360</v>
       </c>
       <c r="D25">
-        <v>423.5</v>
+        <v>277.25</v>
       </c>
       <c r="E25">
-        <v>234</v>
+        <v>218.5</v>
       </c>
       <c r="F25">
-        <v>109.5</v>
+        <v>75</v>
       </c>
       <c r="G25">
-        <v>320.3</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5672,22 +7192,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>867</v>
+        <v>194</v>
       </c>
       <c r="C26">
-        <v>979.75</v>
+        <v>640.5</v>
       </c>
       <c r="D26">
-        <v>652</v>
+        <v>423.5</v>
       </c>
       <c r="E26">
-        <v>971.25</v>
+        <v>234</v>
       </c>
       <c r="F26">
-        <v>782.75</v>
+        <v>109.5</v>
       </c>
       <c r="G26">
-        <v>850.55</v>
+        <v>320.3</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5695,22 +7215,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>868.25</v>
+        <v>867</v>
       </c>
       <c r="C27">
-        <v>1003.75</v>
+        <v>979.75</v>
       </c>
       <c r="D27">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E27">
-        <v>973.5</v>
+        <v>971.25</v>
       </c>
       <c r="F27">
-        <v>799.5</v>
+        <v>782.75</v>
       </c>
       <c r="G27">
-        <v>859.2</v>
+        <v>850.55</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -5718,22 +7238,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>1071.75</v>
+        <v>869.75</v>
       </c>
       <c r="C28">
-        <v>1162.25</v>
+        <v>1006</v>
       </c>
       <c r="D28">
-        <v>943</v>
+        <v>653.5</v>
       </c>
       <c r="E28">
-        <v>1138.5</v>
+        <v>974.5</v>
       </c>
       <c r="F28">
-        <v>817.25</v>
+        <v>804.5</v>
       </c>
       <c r="G28">
-        <v>1026.55</v>
+        <v>861.65</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5741,22 +7261,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>85.75</v>
+        <v>1074</v>
       </c>
       <c r="C29">
-        <v>279.5</v>
+        <v>1164.75</v>
       </c>
       <c r="D29">
-        <v>147.25</v>
+        <v>943.25</v>
       </c>
       <c r="E29">
-        <v>125.75</v>
+        <v>1133.25</v>
       </c>
       <c r="F29">
-        <v>83.25</v>
+        <v>821.5</v>
       </c>
       <c r="G29">
-        <v>144.3</v>
+        <v>1027.35</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5764,22 +7284,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>109.25</v>
+        <v>86</v>
       </c>
       <c r="C30">
-        <v>509</v>
+        <v>279.5</v>
       </c>
       <c r="D30">
-        <v>352.25</v>
+        <v>147.25</v>
       </c>
       <c r="E30">
-        <v>125.75</v>
+        <v>126</v>
       </c>
       <c r="F30">
-        <v>88.25</v>
+        <v>83.5</v>
       </c>
       <c r="G30">
-        <v>236.9</v>
+        <v>144.45</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5787,22 +7307,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>113</v>
+        <v>109.25</v>
       </c>
       <c r="C31">
-        <v>488.75</v>
+        <v>509</v>
       </c>
       <c r="D31">
-        <v>376.5</v>
+        <v>352.25</v>
       </c>
       <c r="E31">
-        <v>147.5</v>
+        <v>125.75</v>
       </c>
       <c r="F31">
-        <v>83</v>
+        <v>88.25</v>
       </c>
       <c r="G31">
-        <v>241.75</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5810,22 +7330,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>685.5</v>
+        <v>113</v>
       </c>
       <c r="C32">
-        <v>1030</v>
+        <v>488.75</v>
       </c>
       <c r="D32">
-        <v>932</v>
+        <v>377.5</v>
       </c>
       <c r="E32">
-        <v>962.75</v>
+        <v>147</v>
       </c>
       <c r="F32">
-        <v>936.25</v>
+        <v>82.25</v>
       </c>
       <c r="G32">
-        <v>909.3</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5833,22 +7353,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>28.75</v>
+        <v>685</v>
       </c>
       <c r="C33">
-        <v>25.75</v>
+        <v>1030</v>
       </c>
       <c r="D33">
-        <v>25.25</v>
+        <v>932</v>
       </c>
       <c r="E33">
-        <v>27</v>
+        <v>962.25</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>936.25</v>
       </c>
       <c r="G33">
-        <v>24.75</v>
+        <v>909.1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5856,22 +7376,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>45</v>
+        <v>28.75</v>
       </c>
       <c r="C34">
-        <v>35</v>
+        <v>25.75</v>
       </c>
       <c r="D34">
-        <v>32.75</v>
+        <v>25.25</v>
       </c>
       <c r="E34">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F34">
+        <v>17</v>
+      </c>
+      <c r="G34">
         <v>24.75</v>
-      </c>
-      <c r="G34">
-        <v>35.9</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5879,22 +7399,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>31.5</v>
+        <v>45</v>
       </c>
       <c r="C35">
-        <v>33.75</v>
+        <v>35</v>
       </c>
       <c r="D35">
-        <v>38</v>
+        <v>32.75</v>
       </c>
       <c r="E35">
-        <v>39.5</v>
+        <v>42</v>
       </c>
       <c r="F35">
-        <v>21.75</v>
+        <v>24.75</v>
       </c>
       <c r="G35">
-        <v>32.9</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5902,22 +7422,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>19.25</v>
+        <v>31.5</v>
       </c>
       <c r="C36">
-        <v>26.25</v>
+        <v>33.75</v>
       </c>
       <c r="D36">
-        <v>25.25</v>
+        <v>38</v>
       </c>
       <c r="E36">
-        <v>20.75</v>
+        <v>39.5</v>
       </c>
       <c r="F36">
-        <v>14.75</v>
+        <v>21.75</v>
       </c>
       <c r="G36">
-        <v>21.25</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5925,22 +7445,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>22.75</v>
+        <v>41.75</v>
       </c>
       <c r="C37">
-        <v>28.5</v>
+        <v>50</v>
       </c>
       <c r="D37">
-        <v>31.25</v>
+        <v>35.75</v>
       </c>
       <c r="E37">
-        <v>22.5</v>
+        <v>49</v>
       </c>
       <c r="F37">
-        <v>15.25</v>
+        <v>17.25</v>
       </c>
       <c r="G37">
-        <v>24.05</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5948,22 +7468,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>31.25</v>
+        <v>19.25</v>
       </c>
       <c r="C38">
-        <v>41</v>
+        <v>26.25</v>
       </c>
       <c r="D38">
-        <v>48.75</v>
+        <v>25.25</v>
       </c>
       <c r="E38">
-        <v>44.5</v>
+        <v>20.75</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>14.75</v>
       </c>
       <c r="G38">
-        <v>38.1</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5971,22 +7491,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>123.75</v>
+        <v>21.25</v>
       </c>
       <c r="C39">
-        <v>359.5</v>
+        <v>27.25</v>
       </c>
       <c r="D39">
-        <v>276.75</v>
+        <v>38</v>
       </c>
       <c r="E39">
-        <v>219.5</v>
+        <v>30.75</v>
       </c>
       <c r="F39">
-        <v>75</v>
+        <v>15.25</v>
       </c>
       <c r="G39">
-        <v>210.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5994,22 +7514,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>194</v>
+        <v>22.75</v>
       </c>
       <c r="C40">
-        <v>640.5</v>
+        <v>28.5</v>
       </c>
       <c r="D40">
-        <v>423.5</v>
+        <v>31.25</v>
       </c>
       <c r="E40">
-        <v>234</v>
+        <v>22.5</v>
       </c>
       <c r="F40">
-        <v>109.5</v>
+        <v>15.25</v>
       </c>
       <c r="G40">
-        <v>320.3</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6017,22 +7537,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>183.5</v>
+        <v>31.25</v>
       </c>
       <c r="C41">
-        <v>642.25</v>
+        <v>41</v>
       </c>
       <c r="D41">
-        <v>427.75</v>
+        <v>48.75</v>
       </c>
       <c r="E41">
-        <v>207</v>
+        <v>44.5</v>
       </c>
       <c r="F41">
-        <v>98.5</v>
+        <v>25</v>
       </c>
       <c r="G41">
-        <v>311.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6040,22 +7560,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>868.25</v>
+        <v>34.75</v>
       </c>
       <c r="C42">
-        <v>1003.75</v>
+        <v>43.5</v>
       </c>
       <c r="D42">
-        <v>651</v>
+        <v>54.25</v>
       </c>
       <c r="E42">
-        <v>973.5</v>
+        <v>63</v>
       </c>
       <c r="F42">
-        <v>799.5</v>
+        <v>34</v>
       </c>
       <c r="G42">
-        <v>859.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6063,22 +7583,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>113</v>
+        <v>60.5</v>
       </c>
       <c r="C43">
-        <v>488.75</v>
+        <v>48.75</v>
       </c>
       <c r="D43">
-        <v>376.5</v>
+        <v>64.25</v>
       </c>
       <c r="E43">
-        <v>147.5</v>
+        <v>98.25</v>
       </c>
       <c r="F43">
-        <v>83</v>
+        <v>39.25</v>
       </c>
       <c r="G43">
-        <v>241.75</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6086,22 +7606,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>28.75</v>
+        <v>124.25</v>
       </c>
       <c r="C44">
-        <v>25.75</v>
+        <v>360</v>
       </c>
       <c r="D44">
-        <v>25.25</v>
+        <v>277.25</v>
       </c>
       <c r="E44">
-        <v>27</v>
+        <v>218.5</v>
       </c>
       <c r="F44">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G44">
-        <v>24.75</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6109,22 +7629,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>36.5</v>
+        <v>194</v>
       </c>
       <c r="C45">
-        <v>25.5</v>
+        <v>640.5</v>
       </c>
       <c r="D45">
-        <v>28.5</v>
+        <v>423.5</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F45">
-        <v>16.25</v>
+        <v>109.5</v>
       </c>
       <c r="G45">
-        <v>27.15</v>
+        <v>320.3</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6132,22 +7652,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>45</v>
+        <v>182.25</v>
       </c>
       <c r="C46">
-        <v>35</v>
+        <v>642.5</v>
       </c>
       <c r="D46">
-        <v>32.75</v>
+        <v>428</v>
       </c>
       <c r="E46">
-        <v>42</v>
+        <v>202.5</v>
       </c>
       <c r="F46">
-        <v>24.75</v>
+        <v>96</v>
       </c>
       <c r="G46">
-        <v>35.9</v>
+        <v>310.25</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6155,22 +7675,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>22.75</v>
+        <v>869.75</v>
       </c>
       <c r="C47">
-        <v>28.5</v>
+        <v>1006</v>
       </c>
       <c r="D47">
-        <v>31.25</v>
+        <v>653.5</v>
       </c>
       <c r="E47">
-        <v>22.5</v>
+        <v>974.5</v>
       </c>
       <c r="F47">
-        <v>15.25</v>
+        <v>804.5</v>
       </c>
       <c r="G47">
-        <v>24.05</v>
+        <v>861.65</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6178,22 +7698,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>183.5</v>
+        <v>113</v>
       </c>
       <c r="C48">
-        <v>642.25</v>
+        <v>488.75</v>
       </c>
       <c r="D48">
-        <v>427.75</v>
+        <v>377.5</v>
       </c>
       <c r="E48">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="F48">
-        <v>98.5</v>
+        <v>82.25</v>
       </c>
       <c r="G48">
-        <v>311.8</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6201,22 +7721,390 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>28.75</v>
+      </c>
+      <c r="C49">
+        <v>25.75</v>
+      </c>
+      <c r="D49">
+        <v>25.25</v>
+      </c>
+      <c r="E49">
+        <v>27</v>
+      </c>
+      <c r="F49">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>27</v>
+      </c>
+      <c r="C50">
+        <v>29</v>
+      </c>
+      <c r="D50">
+        <v>29.5</v>
+      </c>
+      <c r="E50">
+        <v>40.25</v>
+      </c>
+      <c r="F50">
+        <v>16.5</v>
+      </c>
+      <c r="G50">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
         <v>36.5</v>
       </c>
-      <c r="C49">
+      <c r="C51">
         <v>25.5</v>
       </c>
-      <c r="D49">
+      <c r="D51">
         <v>28.5</v>
       </c>
-      <c r="E49">
+      <c r="E51">
         <v>29</v>
       </c>
-      <c r="F49">
+      <c r="F51">
         <v>16.25</v>
       </c>
-      <c r="G49">
+      <c r="G51">
         <v>27.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>45</v>
+      </c>
+      <c r="C52">
+        <v>35</v>
+      </c>
+      <c r="D52">
+        <v>32.75</v>
+      </c>
+      <c r="E52">
+        <v>42</v>
+      </c>
+      <c r="F52">
+        <v>24.75</v>
+      </c>
+      <c r="G52">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>39</v>
+      </c>
+      <c r="C53">
+        <v>45.75</v>
+      </c>
+      <c r="D53">
+        <v>37.25</v>
+      </c>
+      <c r="E53">
+        <v>37.25</v>
+      </c>
+      <c r="F53">
+        <v>19</v>
+      </c>
+      <c r="G53">
+        <v>35.65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>41.75</v>
+      </c>
+      <c r="C54">
+        <v>50</v>
+      </c>
+      <c r="D54">
+        <v>35.75</v>
+      </c>
+      <c r="E54">
+        <v>49</v>
+      </c>
+      <c r="F54">
+        <v>17.25</v>
+      </c>
+      <c r="G54">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
+        <v>21.25</v>
+      </c>
+      <c r="C55">
+        <v>27.25</v>
+      </c>
+      <c r="D55">
+        <v>38</v>
+      </c>
+      <c r="E55">
+        <v>30.75</v>
+      </c>
+      <c r="F55">
+        <v>15.25</v>
+      </c>
+      <c r="G55">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>22.75</v>
+      </c>
+      <c r="C56">
+        <v>28.5</v>
+      </c>
+      <c r="D56">
+        <v>31.25</v>
+      </c>
+      <c r="E56">
+        <v>22.5</v>
+      </c>
+      <c r="F56">
+        <v>15.25</v>
+      </c>
+      <c r="G56">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>22</v>
+      </c>
+      <c r="C57">
+        <v>33</v>
+      </c>
+      <c r="D57">
+        <v>39.25</v>
+      </c>
+      <c r="E57">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>18</v>
+      </c>
+      <c r="G57">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>34.75</v>
+      </c>
+      <c r="C58">
+        <v>43.5</v>
+      </c>
+      <c r="D58">
+        <v>54.25</v>
+      </c>
+      <c r="E58">
+        <v>63</v>
+      </c>
+      <c r="F58">
+        <v>34</v>
+      </c>
+      <c r="G58">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>182.25</v>
+      </c>
+      <c r="C59">
+        <v>642.5</v>
+      </c>
+      <c r="D59">
+        <v>428</v>
+      </c>
+      <c r="E59">
+        <v>202.5</v>
+      </c>
+      <c r="F59">
+        <v>96</v>
+      </c>
+      <c r="G59">
+        <v>310.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>27</v>
+      </c>
+      <c r="C60">
+        <v>29</v>
+      </c>
+      <c r="D60">
+        <v>29.5</v>
+      </c>
+      <c r="E60">
+        <v>40.25</v>
+      </c>
+      <c r="F60">
+        <v>16.5</v>
+      </c>
+      <c r="G60">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>36.5</v>
+      </c>
+      <c r="C61">
+        <v>25.5</v>
+      </c>
+      <c r="D61">
+        <v>28.5</v>
+      </c>
+      <c r="E61">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>16.25</v>
+      </c>
+      <c r="G61">
+        <v>27.15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>29</v>
+      </c>
+      <c r="C62">
+        <v>31.75</v>
+      </c>
+      <c r="D62">
+        <v>35.25</v>
+      </c>
+      <c r="E62">
+        <v>39</v>
+      </c>
+      <c r="F62">
+        <v>20.5</v>
+      </c>
+      <c r="G62">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>39</v>
+      </c>
+      <c r="C63">
+        <v>45.75</v>
+      </c>
+      <c r="D63">
+        <v>37.25</v>
+      </c>
+      <c r="E63">
+        <v>37.25</v>
+      </c>
+      <c r="F63">
+        <v>19</v>
+      </c>
+      <c r="G63">
+        <v>35.65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>22</v>
+      </c>
+      <c r="C64">
+        <v>33</v>
+      </c>
+      <c r="D64">
+        <v>39.25</v>
+      </c>
+      <c r="E64">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>18</v>
+      </c>
+      <c r="G64">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>29</v>
+      </c>
+      <c r="C65">
+        <v>31.75</v>
+      </c>
+      <c r="D65">
+        <v>35.25</v>
+      </c>
+      <c r="E65">
+        <v>39</v>
+      </c>
+      <c r="F65">
+        <v>20.5</v>
+      </c>
+      <c r="G65">
+        <v>31.1</v>
       </c>
     </row>
   </sheetData>
@@ -6226,7 +8114,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6490,19 +8378,19 @@
         <v>11.5</v>
       </c>
       <c r="C12">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="D12">
         <v>16.25</v>
       </c>
       <c r="E12">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="F12">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="G12">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6533,7 +8421,7 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="C14">
         <v>11.5</v>
@@ -6545,10 +8433,10 @@
         <v>13</v>
       </c>
       <c r="F14">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="G14">
-        <v>11.35</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6717,22 +8605,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>5.25</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>10.25</v>
+        <v>12.75</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="G22">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6740,22 +8628,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="D23">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="E23">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>6.75</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -6763,22 +8651,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>10.5</v>
+        <v>5.75</v>
       </c>
       <c r="C24">
-        <v>13.25</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>9.25</v>
       </c>
       <c r="E24">
-        <v>18.5</v>
+        <v>6.75</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>12.45</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6786,22 +8674,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="C25">
-        <v>11.75</v>
+        <v>13.25</v>
       </c>
       <c r="D25">
-        <v>18.75</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="F25">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>15.8</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6809,22 +8697,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>6.75</v>
+        <v>15.5</v>
       </c>
       <c r="C26">
-        <v>8.5</v>
+        <v>11.75</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>18.75</v>
       </c>
       <c r="E26">
-        <v>5.75</v>
+        <v>23.5</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="G26">
-        <v>7.8</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6832,22 +8720,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>17.25</v>
+        <v>6.75</v>
       </c>
       <c r="C27">
-        <v>17.75</v>
+        <v>8.5</v>
       </c>
       <c r="D27">
-        <v>20.75</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>14.5</v>
+        <v>5.75</v>
       </c>
       <c r="F27">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>16.35</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6855,22 +8743,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>6.5</v>
+        <v>17.75</v>
       </c>
       <c r="D28">
+        <v>20.75</v>
+      </c>
+      <c r="E28">
+        <v>14.5</v>
+      </c>
+      <c r="F28">
         <v>11.5</v>
       </c>
-      <c r="E28">
-        <v>7</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
       <c r="G28">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6878,22 +8766,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C29">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="D29">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>6.3</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6904,19 +8792,19 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>7.75</v>
+        <v>5.25</v>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>11.25</v>
       </c>
       <c r="E30">
+        <v>5</v>
+      </c>
+      <c r="F30">
         <v>4.75</v>
       </c>
-      <c r="F30">
-        <v>4.5</v>
-      </c>
       <c r="G30">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6924,22 +8812,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>11.75</v>
+        <v>7.75</v>
       </c>
       <c r="D31">
-        <v>15.75</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="F31">
-        <v>9.25</v>
+        <v>4.5</v>
       </c>
       <c r="G31">
-        <v>11.45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6947,22 +8835,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="C32">
-        <v>6.75</v>
+        <v>11.75</v>
       </c>
       <c r="D32">
-        <v>11.75</v>
+        <v>16.25</v>
       </c>
       <c r="E32">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>8.75</v>
       </c>
       <c r="G32">
-        <v>6.9</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6970,22 +8858,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="C33">
-        <v>12.5</v>
+        <v>6.75</v>
       </c>
       <c r="D33">
-        <v>9.75</v>
+        <v>11.75</v>
       </c>
       <c r="E33">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="F33">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>10.25</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6993,22 +8881,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
       <c r="D34">
-        <v>15.75</v>
+        <v>9.75</v>
       </c>
       <c r="E34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="F34">
         <v>7.5</v>
       </c>
       <c r="G34">
-        <v>11.05</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7016,22 +8904,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>5.75</v>
+        <v>7.75</v>
       </c>
       <c r="C35">
-        <v>7.25</v>
+        <v>13.75</v>
       </c>
       <c r="D35">
-        <v>12.5</v>
+        <v>15.75</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="G35">
-        <v>6.7</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7039,22 +8927,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="C36">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="E36">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7062,22 +8950,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>10.25</v>
       </c>
       <c r="C37">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="D37">
-        <v>15.25</v>
+        <v>9.25</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>12.25</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="G37">
-        <v>10.25</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7088,19 +8976,19 @@
         <v>5</v>
       </c>
       <c r="C38">
+        <v>7.75</v>
+      </c>
+      <c r="D38">
+        <v>13</v>
+      </c>
+      <c r="E38">
         <v>5.75</v>
       </c>
-      <c r="D38">
-        <v>10.25</v>
-      </c>
-      <c r="E38">
-        <v>6.75</v>
-      </c>
       <c r="F38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38">
-        <v>5.95</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -7108,22 +8996,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="D39">
-        <v>9.25</v>
+        <v>12.75</v>
       </c>
       <c r="E39">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G39">
-        <v>6.65</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7131,22 +9019,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="C40">
+        <v>13</v>
+      </c>
+      <c r="D40">
+        <v>15.25</v>
+      </c>
+      <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40">
         <v>7</v>
       </c>
-      <c r="D40">
-        <v>12.5</v>
-      </c>
-      <c r="E40">
-        <v>5.75</v>
-      </c>
-      <c r="F40">
-        <v>4.75</v>
-      </c>
       <c r="G40">
-        <v>6.9</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -7154,22 +9042,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>11.75</v>
+        <v>5.75</v>
       </c>
       <c r="D41">
-        <v>17</v>
+        <v>10.25</v>
       </c>
       <c r="E41">
-        <v>12.5</v>
+        <v>6.75</v>
       </c>
       <c r="F41">
-        <v>6.25</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>11.8</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -7180,19 +9068,19 @@
         <v>7</v>
       </c>
       <c r="C42">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="E42">
-        <v>5.75</v>
+        <v>13</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="G42">
-        <v>7.85</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7200,22 +9088,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C43">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="D43">
-        <v>12.5</v>
+        <v>9.25</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F43">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>6.6</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7223,22 +9111,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="C44">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="E44">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="F44">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>7.2</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7246,22 +9134,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="C45">
-        <v>11.75</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>15.25</v>
+        <v>12.5</v>
       </c>
       <c r="E45">
-        <v>12.25</v>
+        <v>5.75</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="G45">
-        <v>11</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -7269,22 +9157,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>5.75</v>
+        <v>11.5</v>
       </c>
       <c r="C46">
-        <v>8.5</v>
+        <v>11.75</v>
       </c>
       <c r="D46">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="G46">
-        <v>7.45</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7292,22 +9180,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="C47">
         <v>8.5</v>
       </c>
       <c r="D47">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="F47">
         <v>4</v>
       </c>
       <c r="G47">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7315,22 +9203,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="E48">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G48">
-        <v>7.1</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7338,22 +9226,390 @@
         <v>54</v>
       </c>
       <c r="B49">
+        <v>4.75</v>
+      </c>
+      <c r="C49">
+        <v>8.5</v>
+      </c>
+      <c r="D49">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>7.5</v>
+      </c>
+      <c r="F49">
+        <v>6.25</v>
+      </c>
+      <c r="G49">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
+        <v>7.75</v>
+      </c>
+      <c r="C50">
+        <v>12.25</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>13.75</v>
+      </c>
+      <c r="F50">
+        <v>4.5</v>
+      </c>
+      <c r="G50">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>7.75</v>
+      </c>
+      <c r="C51">
+        <v>11.75</v>
+      </c>
+      <c r="D51">
+        <v>15.25</v>
+      </c>
+      <c r="E51">
+        <v>12.25</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>5.75</v>
+      </c>
+      <c r="C52">
+        <v>8.5</v>
+      </c>
+      <c r="D52">
+        <v>13</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
+        <v>10.5</v>
+      </c>
+      <c r="C53">
+        <v>14.25</v>
+      </c>
+      <c r="D53">
+        <v>14.25</v>
+      </c>
+      <c r="E53">
+        <v>11.75</v>
+      </c>
+      <c r="F53">
+        <v>4.25</v>
+      </c>
+      <c r="G53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
+        <v>7.75</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>8.25</v>
+      </c>
+      <c r="F54">
+        <v>2.75</v>
+      </c>
+      <c r="G54">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
         <v>5</v>
       </c>
-      <c r="C49">
+      <c r="C55">
+        <v>6.25</v>
+      </c>
+      <c r="D55">
+        <v>9.25</v>
+      </c>
+      <c r="E55">
+        <v>5.75</v>
+      </c>
+      <c r="F55">
+        <v>2.5</v>
+      </c>
+      <c r="G55">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>8.5</v>
+      </c>
+      <c r="D56">
+        <v>13.5</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>11.5</v>
+      </c>
+      <c r="D57">
+        <v>13.75</v>
+      </c>
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58">
+        <v>6.5</v>
+      </c>
+      <c r="D58">
+        <v>9.75</v>
+      </c>
+      <c r="E58">
+        <v>7.25</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <v>4.5</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59">
+        <v>12</v>
+      </c>
+      <c r="E59">
+        <v>6.75</v>
+      </c>
+      <c r="F59">
+        <v>4</v>
+      </c>
+      <c r="G59">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+      <c r="C60">
+        <v>7.75</v>
+      </c>
+      <c r="D60">
+        <v>7</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <v>2.5</v>
+      </c>
+      <c r="G60">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61">
         <v>8.25</v>
       </c>
-      <c r="D49">
+      <c r="D61">
         <v>12.5</v>
       </c>
-      <c r="E49">
+      <c r="E61">
         <v>5.25</v>
       </c>
-      <c r="F49">
+      <c r="F61">
         <v>7</v>
       </c>
-      <c r="G49">
+      <c r="G61">
         <v>7.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
+        <v>7.75</v>
+      </c>
+      <c r="C62">
+        <v>12.5</v>
+      </c>
+      <c r="D62">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>12.25</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
+        <v>6.75</v>
+      </c>
+      <c r="C63">
+        <v>8.25</v>
+      </c>
+      <c r="D63">
+        <v>12</v>
+      </c>
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63">
+        <v>2.5</v>
+      </c>
+      <c r="G63">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>6.25</v>
+      </c>
+      <c r="D64">
+        <v>11.25</v>
+      </c>
+      <c r="E64">
+        <v>5.75</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65">
+        <v>8.25</v>
+      </c>
+      <c r="D65">
+        <v>11.5</v>
+      </c>
+      <c r="E65">
+        <v>6.75</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
